--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -581,27 +581,27 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>candidate_rank</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
@@ -744,18 +744,18 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>105219</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr">
+        <v>315657</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>https://www.dravitalwertheimer.com/</t>
         </is>
       </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
         <v>1</v>
       </c>
@@ -893,18 +893,18 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>https://drnamazov.co.il/about/</t>
         </is>
       </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
         <v>1</v>
       </c>
@@ -1042,18 +1042,18 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>https://www.dr-bruchim.co.il/</t>
         </is>
       </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
       <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
         <v>1</v>
       </c>
@@ -1191,18 +1191,18 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>https://drsamandarov.gnssweb.co.il/</t>
         </is>
       </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
         <v>1</v>
       </c>
@@ -1340,18 +1340,18 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
       </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
         <v>1</v>
       </c>
@@ -1489,18 +1489,18 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>https://dr-annapetruseva.co.il/</t>
         </is>
       </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
         <v>1</v>
       </c>
@@ -1641,18 +1641,18 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
       </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
       <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
         <v>1</v>
       </c>
@@ -1791,18 +1791,18 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>https://www.drbenshitrit.co.il/</t>
         </is>
       </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
       <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
         <v>1</v>
       </c>
@@ -1940,18 +1940,18 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>104976</v>
-      </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr">
+        <v>314928</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>https://www.dr-avnet.co.il/</t>
         </is>
       </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
       <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
         <v>1</v>
       </c>
@@ -2089,18 +2089,18 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>104976</v>
-      </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr">
+        <v>314928</v>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
       </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
         <v>1</v>
       </c>
@@ -2238,18 +2238,18 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>104976</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr">
+        <v>314928</v>
+      </c>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
       </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
         <v>1</v>
       </c>
@@ -2387,18 +2387,18 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>98496</v>
-      </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr">
+        <v>295488</v>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>https://www.droshribarel.com/</t>
         </is>
       </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
       <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
         <v>1</v>
       </c>
@@ -2536,18 +2536,18 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>104976</v>
-      </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr">
+        <v>314928</v>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
       </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
         <v>1</v>
       </c>
@@ -2685,20 +2685,20 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>104976</v>
-      </c>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr">
+        <v>314928</v>
+      </c>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
       </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
       <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="n">
-        <v>2</v>
-      </c>
+      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ15" t="b">
         <v>0</v>
@@ -2834,18 +2834,18 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>105246</v>
-      </c>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr">
+        <v>315738</v>
+      </c>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>https://elidretzen.co.il/</t>
         </is>
       </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
         <v>1</v>
       </c>
@@ -2983,18 +2983,18 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>85374</v>
-      </c>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr">
+        <v>256122</v>
+      </c>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>https://www.dr-hartoov.co.il/</t>
         </is>
       </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
         <v>1</v>
       </c>
@@ -3132,18 +3132,18 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>105255</v>
-      </c>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr">
+        <v>315765</v>
+      </c>
+      <c r="AE18" t="inlineStr">
         <is>
           <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
       </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
         <v>1</v>
       </c>
@@ -3281,18 +3281,18 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>85374</v>
-      </c>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr">
+        <v>256122</v>
+      </c>
+      <c r="AE19" t="inlineStr">
         <is>
           <t>https://drweissbach.co.il/</t>
         </is>
       </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
       <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
         <v>1</v>
       </c>
@@ -3430,18 +3430,18 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>104976</v>
-      </c>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr">
+        <v>314928</v>
+      </c>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
       <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
         <v>1</v>
       </c>
@@ -3579,18 +3579,18 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
       <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
         <v>1</v>
       </c>
@@ -3728,18 +3728,18 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
       <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
         <v>1</v>
       </c>
@@ -3877,20 +3877,20 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE23" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
+      <c r="AF23" t="n">
+        <v>1</v>
+      </c>
       <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="n">
-        <v>2</v>
-      </c>
+      <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ23" t="b">
         <v>0</v>
@@ -4026,18 +4026,18 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>85374</v>
-      </c>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr">
+        <v>256122</v>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>https://www.dr-stockheim.com/</t>
         </is>
       </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
       <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
         <v>1</v>
       </c>
@@ -4175,18 +4175,18 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE25" t="inlineStr">
         <is>
           <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
       <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
         <v>1</v>
       </c>
@@ -4324,18 +4324,18 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE26" t="inlineStr">
         <is>
           <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
       <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
         <v>1</v>
       </c>
@@ -4463,18 +4463,18 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE27" t="inlineStr">
         <is>
           <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
         </is>
       </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
       <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
         <v>1</v>
       </c>
@@ -4612,18 +4612,18 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE28" t="inlineStr">
         <is>
           <t>https://profkamilhighrisk.wixsite.com/home</t>
         </is>
       </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
       <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
@@ -4761,18 +4761,18 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE29" t="inlineStr">
         <is>
           <t>https://www.profmeirow.com/</t>
         </is>
       </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
       <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
         <v>1</v>
       </c>
@@ -4910,18 +4910,18 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE30" t="inlineStr">
         <is>
           <t>https://dr-hila.com/</t>
         </is>
       </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
       <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
         <v>1</v>
       </c>
@@ -5049,18 +5049,18 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE31" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
       </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
       <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
         <v>1</v>
       </c>
@@ -5198,18 +5198,18 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE32" t="inlineStr">
         <is>
           <t>https://dr-web.club/%D7%90%D7%AA%D7%A8%D7%99%D7%9D/%D7%A4%D7%A8%D7%95%D7%A4%D7%A1%D7%95%D7%A8-%D7%99%D7%95%D7%90%D7%91-%D7%A4%D7%9C%D7%93/</t>
         </is>
       </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
       <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
         <v>1</v>
       </c>
@@ -5347,18 +5347,18 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>80946</v>
-      </c>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr">
+        <v>242838</v>
+      </c>
+      <c r="AE33" t="inlineStr">
         <is>
           <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
       <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
         <v>1</v>
       </c>
@@ -5494,18 +5494,18 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>98415</v>
-      </c>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr">
+        <v>295245</v>
+      </c>
+      <c r="AE34" t="inlineStr">
         <is>
           <t>https://www.babygaga.co.il/</t>
         </is>
       </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
       <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
         <v>1</v>
       </c>
@@ -5633,18 +5633,18 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE35" t="inlineStr">
         <is>
           <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
       </c>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
       <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
         <v>1</v>
       </c>
@@ -5782,18 +5782,18 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE36" t="inlineStr">
         <is>
           <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
+      <c r="AF36" t="n">
+        <v>1</v>
+      </c>
       <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
         <v>1</v>
       </c>
@@ -5929,18 +5929,18 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>98415</v>
-      </c>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr">
+        <v>295245</v>
+      </c>
+      <c r="AE37" t="inlineStr">
         <is>
           <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
       </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
       <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
         <v>1</v>
       </c>
@@ -6078,18 +6078,18 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE38" t="inlineStr">
         <is>
           <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
       </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
       <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
         <v>1</v>
       </c>
@@ -6227,18 +6227,18 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE39" t="inlineStr">
         <is>
           <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
       <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
         <v>1</v>
       </c>
@@ -6381,18 +6381,18 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE40" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
       </c>
+      <c r="AF40" t="n">
+        <v>1</v>
+      </c>
       <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
         <v>1</v>
       </c>
@@ -6530,20 +6530,20 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE41" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
       </c>
+      <c r="AF41" t="n">
+        <v>1</v>
+      </c>
       <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="n">
-        <v>2</v>
-      </c>
+      <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ41" t="b">
         <v>0</v>
@@ -6684,18 +6684,18 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE42" t="inlineStr">
         <is>
           <t>https://www.pregnancy.co.il/</t>
         </is>
       </c>
+      <c r="AF42" t="n">
+        <v>1</v>
+      </c>
       <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
         <v>1</v>
       </c>
@@ -6833,18 +6833,18 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>105219</v>
-      </c>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr">
+        <v>315657</v>
+      </c>
+      <c r="AE43" t="inlineStr">
         <is>
           <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
+      <c r="AF43" t="n">
+        <v>1</v>
+      </c>
       <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
         <v>1</v>
       </c>
@@ -6982,18 +6982,18 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE44" t="inlineStr">
         <is>
           <t>https://www.drmillo.co.il/</t>
         </is>
       </c>
+      <c r="AF44" t="n">
+        <v>1</v>
+      </c>
       <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
         <v>1</v>
       </c>
@@ -7131,18 +7131,18 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE45" t="inlineStr">
         <is>
           <t>https://roeebirnbaum.com/</t>
         </is>
       </c>
+      <c r="AF45" t="n">
+        <v>1</v>
+      </c>
       <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
         <v>1</v>
       </c>
@@ -7270,18 +7270,18 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE46" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
       <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
         <v>1</v>
       </c>
@@ -7419,18 +7419,18 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE47" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
       <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
         <v>1</v>
       </c>
@@ -7568,18 +7568,18 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE48" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
+      <c r="AF48" t="n">
+        <v>1</v>
+      </c>
       <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
         <v>1</v>
       </c>
@@ -7717,18 +7717,18 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE49" t="inlineStr">
         <is>
           <t>https://www.baby-ivf.com/</t>
         </is>
       </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
       <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
         <v>1</v>
       </c>
@@ -7866,18 +7866,18 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE50" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
+      <c r="AF50" t="n">
+        <v>1</v>
+      </c>
       <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
         <v>1</v>
       </c>
@@ -8015,18 +8015,18 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE51" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
+      <c r="AF51" t="n">
+        <v>1</v>
+      </c>
       <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
         <v>1</v>
       </c>
@@ -8164,18 +8164,18 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>98508</v>
-      </c>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr">
+        <v>295524</v>
+      </c>
+      <c r="AE52" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
+      <c r="AF52" t="n">
+        <v>1</v>
+      </c>
       <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
         <v>1</v>
       </c>
@@ -8313,18 +8313,18 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>104976</v>
-      </c>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr">
+        <v>314928</v>
+      </c>
+      <c r="AE53" t="inlineStr">
         <is>
           <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
+      <c r="AF53" t="n">
+        <v>1</v>
+      </c>
       <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
         <v>1</v>
       </c>
@@ -8462,18 +8462,18 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE54" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
       <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
         <v>1</v>
       </c>
@@ -8611,18 +8611,18 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>118350</v>
-      </c>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr">
+        <v>355050</v>
+      </c>
+      <c r="AE55" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
+      <c r="AF55" t="n">
+        <v>1</v>
+      </c>
       <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
         <v>1</v>
       </c>
@@ -8760,18 +8760,18 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>80946</v>
-      </c>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr">
+        <v>242838</v>
+      </c>
+      <c r="AE56" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
       <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
         <v>1</v>
       </c>
@@ -8909,18 +8909,18 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>80946</v>
-      </c>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr">
+        <v>242838</v>
+      </c>
+      <c r="AE57" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
+      <c r="AF57" t="n">
+        <v>1</v>
+      </c>
       <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
         <v>1</v>
       </c>
@@ -9061,18 +9061,18 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>80946</v>
-      </c>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr">
+        <v>242838</v>
+      </c>
+      <c r="AE58" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
       </c>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
       <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
         <v>1</v>
       </c>
@@ -9210,18 +9210,18 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>80946</v>
-      </c>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr">
+        <v>242838</v>
+      </c>
+      <c r="AE59" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
+      <c r="AF59" t="n">
+        <v>1</v>
+      </c>
       <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
         <v>1</v>
       </c>
@@ -9359,18 +9359,18 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>78984</v>
-      </c>
-      <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr">
+        <v>236952</v>
+      </c>
+      <c r="AE60" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
+      <c r="AF60" t="n">
+        <v>1</v>
+      </c>
       <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
         <v>1</v>
       </c>
@@ -9508,18 +9508,18 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>78984</v>
-      </c>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr">
+        <v>236952</v>
+      </c>
+      <c r="AE61" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
+      <c r="AF61" t="n">
+        <v>1</v>
+      </c>
       <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
         <v>1</v>
       </c>
@@ -9657,18 +9657,18 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE62" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/kuperminc-michael/</t>
         </is>
       </c>
+      <c r="AF62" t="n">
+        <v>1</v>
+      </c>
       <c r="AG62" t="inlineStr"/>
-      <c r="AH62" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
         <v>1</v>
       </c>
@@ -9806,18 +9806,18 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE63" t="inlineStr">
         <is>
           <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
+      <c r="AF63" t="n">
+        <v>1</v>
+      </c>
       <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
         <v>1</v>
       </c>
@@ -9955,18 +9955,18 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE64" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
       <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
         <v>1</v>
       </c>
@@ -10104,18 +10104,18 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>78813</v>
-      </c>
-      <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr">
+        <v>236439</v>
+      </c>
+      <c r="AE65" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
       <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
         <v>1</v>
       </c>
@@ -10253,18 +10253,18 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>78813</v>
-      </c>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr">
+        <v>236439</v>
+      </c>
+      <c r="AE66" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/maslovitz-sharon/</t>
         </is>
       </c>
+      <c r="AF66" t="n">
+        <v>1</v>
+      </c>
       <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
         <v>1</v>
       </c>
@@ -10402,18 +10402,18 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>78816</v>
-      </c>
-      <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr">
+        <v>236448</v>
+      </c>
+      <c r="AE67" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
       <c r="AG67" t="inlineStr"/>
-      <c r="AH67" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
         <v>1</v>
       </c>
@@ -10541,18 +10541,18 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE68" t="inlineStr"/>
-      <c r="AF68" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE68" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
+      <c r="AF68" t="n">
+        <v>1</v>
+      </c>
       <c r="AG68" t="inlineStr"/>
-      <c r="AH68" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
         <v>1</v>
       </c>
@@ -10680,18 +10680,18 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
       <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
         <v>1</v>
       </c>
@@ -10829,18 +10829,18 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>85302</v>
-      </c>
-      <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr">
+        <v>255906</v>
+      </c>
+      <c r="AE70" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
       <c r="AG70" t="inlineStr"/>
-      <c r="AH70" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
         <v>1</v>
       </c>
@@ -10978,18 +10978,18 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>85302</v>
-      </c>
-      <c r="AE71" t="inlineStr"/>
-      <c r="AF71" t="inlineStr">
+        <v>255906</v>
+      </c>
+      <c r="AE71" t="inlineStr">
         <is>
           <t>https://pain.coi.co.il/</t>
         </is>
       </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
       <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
         <v>1</v>
       </c>
@@ -11127,18 +11127,18 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE72" t="inlineStr">
         <is>
           <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
       <c r="AG72" t="inlineStr"/>
-      <c r="AH72" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
         <v>1</v>
       </c>
@@ -11276,18 +11276,18 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>85293</v>
-      </c>
-      <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="inlineStr">
+        <v>255879</v>
+      </c>
+      <c r="AE73" t="inlineStr">
         <is>
           <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
       <c r="AG73" t="inlineStr"/>
-      <c r="AH73" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
         <v>1</v>
       </c>
@@ -11425,18 +11425,18 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>85302</v>
-      </c>
-      <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr">
+        <v>255906</v>
+      </c>
+      <c r="AE74" t="inlineStr">
         <is>
           <t>https://dinaeisen.com/about/</t>
         </is>
       </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
       <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
         <v>1</v>
       </c>
@@ -11564,18 +11564,18 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE75" t="inlineStr"/>
-      <c r="AF75" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE75" t="inlineStr">
         <is>
           <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
       <c r="AG75" t="inlineStr"/>
-      <c r="AH75" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
         <v>1</v>
       </c>
@@ -11713,18 +11713,18 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE76" t="inlineStr">
         <is>
           <t>https://www.tau.ac.il/profile/shalevv</t>
         </is>
       </c>
+      <c r="AF76" t="n">
+        <v>1</v>
+      </c>
       <c r="AG76" t="inlineStr"/>
-      <c r="AH76" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
         <v>1</v>
       </c>
@@ -11862,18 +11862,18 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>99144</v>
-      </c>
-      <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr">
+        <v>297432</v>
+      </c>
+      <c r="AE77" t="inlineStr">
         <is>
           <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
+      <c r="AF77" t="n">
+        <v>1</v>
+      </c>
       <c r="AG77" t="inlineStr"/>
-      <c r="AH77" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
         <v>1</v>
       </c>
@@ -12014,18 +12014,18 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>78984</v>
-      </c>
-      <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr">
+        <v>236952</v>
+      </c>
+      <c r="AE78" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/3175</t>
         </is>
       </c>
+      <c r="AF78" t="n">
+        <v>1</v>
+      </c>
       <c r="AG78" t="inlineStr"/>
-      <c r="AH78" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
         <v>1</v>
       </c>
@@ -12165,18 +12165,18 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE79" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
+      <c r="AF79" t="n">
+        <v>1</v>
+      </c>
       <c r="AG79" t="inlineStr"/>
-      <c r="AH79" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
         <v>1</v>
       </c>
@@ -12318,18 +12318,18 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE80" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
       </c>
+      <c r="AF80" t="n">
+        <v>1</v>
+      </c>
       <c r="AG80" t="inlineStr"/>
-      <c r="AH80" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
         <v>1</v>
       </c>
@@ -12470,18 +12470,18 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>78816</v>
-      </c>
-      <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr">
+        <v>236448</v>
+      </c>
+      <c r="AE81" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/8119</t>
         </is>
       </c>
+      <c r="AF81" t="n">
+        <v>1</v>
+      </c>
       <c r="AG81" t="inlineStr"/>
-      <c r="AH81" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
         <v>1</v>
       </c>
@@ -12622,18 +12622,18 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>78813</v>
-      </c>
-      <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr">
+        <v>236439</v>
+      </c>
+      <c r="AE82" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
       </c>
+      <c r="AF82" t="n">
+        <v>1</v>
+      </c>
       <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
         <v>1</v>
       </c>
@@ -12775,18 +12775,18 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>78759</v>
-      </c>
-      <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr">
+        <v>236277</v>
+      </c>
+      <c r="AE83" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6696</t>
         </is>
       </c>
+      <c r="AF83" t="n">
+        <v>1</v>
+      </c>
       <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
         <v>1</v>
       </c>
@@ -12927,18 +12927,18 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>78759</v>
-      </c>
-      <c r="AE84" t="inlineStr"/>
-      <c r="AF84" t="inlineStr">
+        <v>236277</v>
+      </c>
+      <c r="AE84" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
       </c>
+      <c r="AF84" t="n">
+        <v>1</v>
+      </c>
       <c r="AG84" t="inlineStr"/>
-      <c r="AH84" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
         <v>1</v>
       </c>
@@ -13076,18 +13076,18 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>78759</v>
-      </c>
-      <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr">
+        <v>236277</v>
+      </c>
+      <c r="AE85" t="inlineStr">
         <is>
           <t>https://www.doctorlouria.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A9%D7%95%D7%9C%D7%9E%D7%99%D7%AA-%D7%9C%D7%95%D7%A8%D7%99%D7%90</t>
         </is>
       </c>
+      <c r="AF85" t="n">
+        <v>1</v>
+      </c>
       <c r="AG85" t="inlineStr"/>
-      <c r="AH85" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
         <v>1</v>
       </c>
@@ -13225,18 +13225,18 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>98415</v>
-      </c>
-      <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr">
+        <v>295245</v>
+      </c>
+      <c r="AE86" t="inlineStr">
         <is>
           <t>https://www.michalgilad.com/</t>
         </is>
       </c>
+      <c r="AF86" t="n">
+        <v>1</v>
+      </c>
       <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
         <v>1</v>
       </c>
@@ -13374,18 +13374,18 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>78759</v>
-      </c>
-      <c r="AE87" t="inlineStr"/>
-      <c r="AF87" t="inlineStr">
+        <v>236277</v>
+      </c>
+      <c r="AE87" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
+      <c r="AF87" t="n">
+        <v>1</v>
+      </c>
       <c r="AG87" t="inlineStr"/>
-      <c r="AH87" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
         <v>1</v>
       </c>
@@ -13523,18 +13523,18 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>78759</v>
-      </c>
-      <c r="AE88" t="inlineStr"/>
-      <c r="AF88" t="inlineStr">
+        <v>236277</v>
+      </c>
+      <c r="AE88" t="inlineStr">
         <is>
           <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
+      <c r="AF88" t="n">
+        <v>1</v>
+      </c>
       <c r="AG88" t="inlineStr"/>
-      <c r="AH88" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
         <v>1</v>
       </c>
@@ -13662,18 +13662,18 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE89" t="inlineStr">
         <is>
           <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
+      <c r="AF89" t="n">
+        <v>1</v>
+      </c>
       <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
         <v>1</v>
       </c>
@@ -13801,18 +13801,18 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE90" t="inlineStr">
         <is>
           <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
+      <c r="AF90" t="n">
+        <v>1</v>
+      </c>
       <c r="AG90" t="inlineStr"/>
-      <c r="AH90" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
         <v>1</v>
       </c>
@@ -13952,20 +13952,20 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE91" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
+      <c r="AF91" t="n">
+        <v>1</v>
+      </c>
       <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="n">
-        <v>2</v>
-      </c>
+      <c r="AH91" t="inlineStr"/>
       <c r="AI91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ91" t="b">
         <v>0</v>
@@ -14105,20 +14105,20 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>78813</v>
-      </c>
-      <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr">
+        <v>236439</v>
+      </c>
+      <c r="AE92" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
       </c>
+      <c r="AF92" t="n">
+        <v>1</v>
+      </c>
       <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="n">
-        <v>2</v>
-      </c>
+      <c r="AH92" t="inlineStr"/>
       <c r="AI92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ92" t="b">
         <v>0</v>
@@ -14258,20 +14258,20 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>78759</v>
-      </c>
-      <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr">
+        <v>236277</v>
+      </c>
+      <c r="AE93" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
       </c>
+      <c r="AF93" t="n">
+        <v>1</v>
+      </c>
       <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="n">
-        <v>2</v>
-      </c>
+      <c r="AH93" t="inlineStr"/>
       <c r="AI93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ93" t="b">
         <v>0</v>
@@ -14397,18 +14397,18 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE94" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
+      <c r="AF94" t="n">
+        <v>1</v>
+      </c>
       <c r="AG94" t="inlineStr"/>
-      <c r="AH94" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH94" t="inlineStr"/>
       <c r="AI94" t="n">
         <v>1</v>
       </c>
@@ -14536,18 +14536,18 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
+      <c r="AF95" t="n">
+        <v>1</v>
+      </c>
       <c r="AG95" t="inlineStr"/>
-      <c r="AH95" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH95" t="inlineStr"/>
       <c r="AI95" t="n">
         <v>1</v>
       </c>
@@ -14675,18 +14675,18 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
+      <c r="AF96" t="n">
+        <v>1</v>
+      </c>
       <c r="AG96" t="inlineStr"/>
-      <c r="AH96" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH96" t="inlineStr"/>
       <c r="AI96" t="n">
         <v>1</v>
       </c>
@@ -14814,18 +14814,18 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE97" t="inlineStr"/>
-      <c r="AF97" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
+      <c r="AF97" t="n">
+        <v>1</v>
+      </c>
       <c r="AG97" t="inlineStr"/>
-      <c r="AH97" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH97" t="inlineStr"/>
       <c r="AI97" t="n">
         <v>1</v>
       </c>
@@ -14953,18 +14953,18 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
+      <c r="AF98" t="n">
+        <v>1</v>
+      </c>
       <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH98" t="inlineStr"/>
       <c r="AI98" t="n">
         <v>1</v>
       </c>
@@ -15092,18 +15092,18 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
+      <c r="AF99" t="n">
+        <v>1</v>
+      </c>
       <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH99" t="inlineStr"/>
       <c r="AI99" t="n">
         <v>1</v>
       </c>
@@ -15231,18 +15231,18 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
+      <c r="AF100" t="n">
+        <v>1</v>
+      </c>
       <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH100" t="inlineStr"/>
       <c r="AI100" t="n">
         <v>1</v>
       </c>
@@ -15370,18 +15370,18 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
+      <c r="AF101" t="n">
+        <v>1</v>
+      </c>
       <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH101" t="inlineStr"/>
       <c r="AI101" t="n">
         <v>1</v>
       </c>
@@ -15509,18 +15509,18 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
+      <c r="AF102" t="n">
+        <v>1</v>
+      </c>
       <c r="AG102" t="inlineStr"/>
-      <c r="AH102" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH102" t="inlineStr"/>
       <c r="AI102" t="n">
         <v>1</v>
       </c>
@@ -15648,18 +15648,18 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE103" t="inlineStr"/>
-      <c r="AF103" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
+      <c r="AF103" t="n">
+        <v>1</v>
+      </c>
       <c r="AG103" t="inlineStr"/>
-      <c r="AH103" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH103" t="inlineStr"/>
       <c r="AI103" t="n">
         <v>1</v>
       </c>
@@ -15787,18 +15787,18 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE104" t="inlineStr"/>
-      <c r="AF104" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
+      <c r="AF104" t="n">
+        <v>1</v>
+      </c>
       <c r="AG104" t="inlineStr"/>
-      <c r="AH104" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH104" t="inlineStr"/>
       <c r="AI104" t="n">
         <v>1</v>
       </c>
@@ -15926,18 +15926,18 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>78732</v>
-      </c>
-      <c r="AE105" t="inlineStr"/>
-      <c r="AF105" t="inlineStr">
+        <v>236196</v>
+      </c>
+      <c r="AE105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
         </is>
       </c>
+      <c r="AF105" t="n">
+        <v>1</v>
+      </c>
       <c r="AG105" t="inlineStr"/>
-      <c r="AH105" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH105" t="inlineStr"/>
       <c r="AI105" t="n">
         <v>1</v>
       </c>
@@ -16078,18 +16078,18 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>85302</v>
-      </c>
-      <c r="AE106" t="inlineStr"/>
-      <c r="AF106" t="inlineStr">
+        <v>255906</v>
+      </c>
+      <c r="AE106" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2435</t>
         </is>
       </c>
+      <c r="AF106" t="n">
+        <v>1</v>
+      </c>
       <c r="AG106" t="inlineStr"/>
-      <c r="AH106" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH106" t="inlineStr"/>
       <c r="AI106" t="n">
         <v>1</v>
       </c>
@@ -16230,18 +16230,18 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>78975</v>
-      </c>
-      <c r="AE107" t="inlineStr"/>
-      <c r="AF107" t="inlineStr">
+        <v>236925</v>
+      </c>
+      <c r="AE107" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5230</t>
         </is>
       </c>
+      <c r="AF107" t="n">
+        <v>1</v>
+      </c>
       <c r="AG107" t="inlineStr"/>
-      <c r="AH107" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH107" t="inlineStr"/>
       <c r="AI107" t="n">
         <v>1</v>
       </c>
@@ -16383,18 +16383,18 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>85320</v>
-      </c>
-      <c r="AE108" t="inlineStr"/>
-      <c r="AF108" t="inlineStr">
+        <v>255960</v>
+      </c>
+      <c r="AE108" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5287</t>
         </is>
       </c>
+      <c r="AF108" t="n">
+        <v>1</v>
+      </c>
       <c r="AG108" t="inlineStr"/>
-      <c r="AH108" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH108" t="inlineStr"/>
       <c r="AI108" t="n">
         <v>1</v>
       </c>
@@ -16535,18 +16535,18 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>80928</v>
-      </c>
-      <c r="AE109" t="inlineStr"/>
-      <c r="AF109" t="inlineStr">
+        <v>242784</v>
+      </c>
+      <c r="AE109" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7026</t>
         </is>
       </c>
+      <c r="AF109" t="n">
+        <v>1</v>
+      </c>
       <c r="AG109" t="inlineStr"/>
-      <c r="AH109" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH109" t="inlineStr"/>
       <c r="AI109" t="n">
         <v>1</v>
       </c>
@@ -16682,18 +16682,18 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>98415</v>
-      </c>
-      <c r="AE110" t="inlineStr"/>
-      <c r="AF110" t="inlineStr">
+        <v>295245</v>
+      </c>
+      <c r="AE110" t="inlineStr">
         <is>
           <t>https://www.goodnights.co.il/</t>
         </is>
       </c>
+      <c r="AF110" t="n">
+        <v>1</v>
+      </c>
       <c r="AG110" t="inlineStr"/>
-      <c r="AH110" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH110" t="inlineStr"/>
       <c r="AI110" t="n">
         <v>1</v>
       </c>
@@ -16834,18 +16834,18 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>78813</v>
-      </c>
-      <c r="AE111" t="inlineStr"/>
-      <c r="AF111" t="inlineStr">
+        <v>236439</v>
+      </c>
+      <c r="AE111" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2414</t>
         </is>
       </c>
+      <c r="AF111" t="n">
+        <v>1</v>
+      </c>
       <c r="AG111" t="inlineStr"/>
-      <c r="AH111" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH111" t="inlineStr"/>
       <c r="AI111" t="n">
         <v>1</v>
       </c>
@@ -16987,18 +16987,18 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>78816</v>
-      </c>
-      <c r="AE112" t="inlineStr"/>
-      <c r="AF112" t="inlineStr">
+        <v>236448</v>
+      </c>
+      <c r="AE112" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2624</t>
         </is>
       </c>
+      <c r="AF112" t="n">
+        <v>1</v>
+      </c>
       <c r="AG112" t="inlineStr"/>
-      <c r="AH112" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH112" t="inlineStr"/>
       <c r="AI112" t="n">
         <v>1</v>
       </c>
@@ -17140,18 +17140,18 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>78813</v>
-      </c>
-      <c r="AE113" t="inlineStr"/>
-      <c r="AF113" t="inlineStr">
+        <v>236439</v>
+      </c>
+      <c r="AE113" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5282</t>
         </is>
       </c>
+      <c r="AF113" t="n">
+        <v>1</v>
+      </c>
       <c r="AG113" t="inlineStr"/>
-      <c r="AH113" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH113" t="inlineStr"/>
       <c r="AI113" t="n">
         <v>1</v>
       </c>
@@ -17292,18 +17292,18 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>78813</v>
-      </c>
-      <c r="AE114" t="inlineStr"/>
-      <c r="AF114" t="inlineStr">
+        <v>236439</v>
+      </c>
+      <c r="AE114" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2596</t>
         </is>
       </c>
+      <c r="AF114" t="n">
+        <v>1</v>
+      </c>
       <c r="AG114" t="inlineStr"/>
-      <c r="AH114" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH114" t="inlineStr"/>
       <c r="AI114" t="n">
         <v>1</v>
       </c>
@@ -17444,18 +17444,18 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>78759</v>
-      </c>
-      <c r="AE115" t="inlineStr"/>
-      <c r="AF115" t="inlineStr">
+        <v>236277</v>
+      </c>
+      <c r="AE115" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/525</t>
         </is>
       </c>
+      <c r="AF115" t="n">
+        <v>1</v>
+      </c>
       <c r="AG115" t="inlineStr"/>
-      <c r="AH115" t="n">
-        <v>1</v>
-      </c>
+      <c r="AH115" t="inlineStr"/>
       <c r="AI115" t="n">
         <v>1</v>
       </c>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -744,15 +744,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>315657</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>946971</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.dravitalwertheimer.com/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -893,15 +893,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://drnamazov.co.il/about/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1042,15 +1042,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.dr-bruchim.co.il/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1191,15 +1191,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://drsamandarov.gnssweb.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1340,15 +1340,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1489,15 +1489,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://dr-annapetruseva.co.il/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1641,15 +1641,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1791,15 +1791,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.drbenshitrit.co.il/</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1940,15 +1940,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.dr-avnet.co.il/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>1</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2089,15 +2089,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2238,15 +2238,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2387,15 +2387,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://www.droshribarel.com/</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2536,15 +2536,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2685,15 +2685,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2834,15 +2834,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>315738</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>947214</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://elidretzen.co.il/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2983,15 +2983,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>256122</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>768366</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://www.dr-hartoov.co.il/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3132,15 +3132,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>315765</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>947295</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3281,15 +3281,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>256122</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>768366</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://drweissbach.co.il/</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3430,15 +3430,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://www.drmoranpaz.com/</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3579,15 +3579,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3728,15 +3728,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>1</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3877,15 +3877,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -4026,15 +4026,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>256122</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>768366</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>https://www.dr-stockheim.com/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4175,15 +4175,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4324,15 +4324,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://www.davidgordon.co.il/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4463,15 +4463,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4612,15 +4612,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://profkamilhighrisk.wixsite.com/home</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4761,15 +4761,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://www.profmeirow.com/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4910,15 +4910,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://dr-hila.com/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>1</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -5049,15 +5049,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5198,15 +5198,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://dr-web.club/%D7%90%D7%AA%D7%A8%D7%99%D7%9D/%D7%A4%D7%A8%D7%95%D7%A4%D7%A1%D7%95%D7%A8-%D7%99%D7%95%D7%90%D7%91-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5347,15 +5347,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://www.zipori-obgyn.com/</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5494,15 +5494,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://www.babygaga.co.il/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>1</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5633,15 +5633,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>1</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5782,15 +5782,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5929,15 +5929,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>1</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -6078,15 +6078,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6227,15 +6227,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6381,15 +6381,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>1</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6530,15 +6530,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>1</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6684,15 +6684,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://www.pregnancy.co.il/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>1</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6833,15 +6833,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>315657</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>946971</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://www.dr-mishan.co.il/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>1</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6982,15 +6982,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://www.drmillo.co.il/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>1</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -7131,15 +7131,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://roeebirnbaum.com/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7270,15 +7270,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>1</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7419,15 +7419,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>1</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7568,15 +7568,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>1</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7717,15 +7717,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://www.baby-ivf.com/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>1</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7866,15 +7866,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>1</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -8015,15 +8015,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>1</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -8164,15 +8164,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>295524</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>886572</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -8313,15 +8313,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>314928</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>944784</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://www.arad-medical.co.il/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>1</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8462,15 +8462,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8611,15 +8611,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>355050</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>1065150</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8760,15 +8760,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>1</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8909,15 +8909,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>1</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -9061,15 +9061,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>1</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -9210,15 +9210,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>1</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -9359,15 +9359,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>236952</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>710856</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>1</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9508,15 +9508,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>236952</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>710856</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>1</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9657,15 +9657,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/kuperminc-michael/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>1</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9806,15 +9806,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://www.drlinder.co.il/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>1</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9955,15 +9955,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>1</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -10104,15 +10104,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>1</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -10253,15 +10253,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/maslovitz-sharon/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>1</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -10402,15 +10402,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>1</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10541,15 +10541,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>1</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10680,15 +10680,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>1</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10829,15 +10829,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>1</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10978,15 +10978,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>https://pain.coi.co.il/</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>1</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -11127,15 +11127,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://www.drzivony.co.il/</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>1</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -11276,15 +11276,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://www.dr-batya-kornboim.com/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>1</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -11425,15 +11425,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://dinaeisen.com/about/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>1</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11564,15 +11564,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://www.dafyrahavhass.com/</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>1</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11713,15 +11713,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://www.tau.ac.il/profile/shalevv</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>1</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11862,15 +11862,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>297432</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>892296</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>1</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -12014,15 +12014,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>236952</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>710856</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/3175</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>1</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -12165,15 +12165,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>1</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -12318,15 +12318,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>1</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -12470,15 +12470,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/8119</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>1</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12622,15 +12622,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>1</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12775,15 +12775,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6696</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>1</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12927,15 +12927,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>1</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -13076,15 +13076,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://www.doctorlouria.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A9%D7%95%D7%9C%D7%9E%D7%99%D7%AA-%D7%9C%D7%95%D7%A8%D7%99%D7%90</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>1</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -13225,15 +13225,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://www.michalgilad.com/</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>1</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -13374,15 +13374,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>1</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -13523,15 +13523,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>1</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13662,15 +13662,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>1</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13801,15 +13801,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>1</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13952,15 +13952,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>1</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -14105,15 +14105,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>1</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -14258,15 +14258,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>1</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -14397,15 +14397,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>1</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -14536,15 +14536,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>1</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -14675,15 +14675,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>1</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14814,15 +14814,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>1</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14953,15 +14953,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>1</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -15092,15 +15092,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>1</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -15231,15 +15231,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>1</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -15370,15 +15370,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>1</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -15509,15 +15509,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>1</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -15648,15 +15648,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>1</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15787,15 +15787,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>1</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15926,15 +15926,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>1</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -16078,15 +16078,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>255906</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>767718</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2435</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>1</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -16230,15 +16230,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5230</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>1</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -16383,15 +16383,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>255960</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>767880</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5287</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>1</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -16535,15 +16535,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>242784</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>728352</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7026</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>1</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -16682,15 +16682,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://www.goodnights.co.il/</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>1</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16834,15 +16834,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2414</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>1</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16987,15 +16987,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>236448</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>709344</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2624</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>1</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -17140,15 +17140,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5282</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>1</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -17292,15 +17292,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>236439</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>709317</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2596</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>1</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -17444,15 +17444,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>236277</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>708831</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/525</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>1</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>946971</v>
+        <v>2840913</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>947214</v>
+        <v>2841642</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>768366</v>
+        <v>2305098</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>947295</v>
+        <v>2841885</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>768366</v>
+        <v>2305098</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>768366</v>
+        <v>2305098</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>946971</v>
+        <v>2840913</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>886572</v>
+        <v>2659716</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>944784</v>
+        <v>2834352</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1065150</v>
+        <v>3195450</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>710856</v>
+        <v>2132568</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>710856</v>
+        <v>2132568</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>892296</v>
+        <v>2676888</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>710856</v>
+        <v>2132568</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12622,7 +12622,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13662,7 +13662,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13801,7 +13801,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14258,7 +14258,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14536,7 +14536,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -14814,7 +14814,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15231,7 +15231,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>767718</v>
+        <v>2303154</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>767880</v>
+        <v>2303640</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>728352</v>
+        <v>2185056</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -16834,7 +16834,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>709344</v>
+        <v>2128032</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>709317</v>
+        <v>2127951</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17444,7 +17444,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>708831</v>
+        <v>2126493</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2840913</v>
+        <v>8522739</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2841642</v>
+        <v>8524926</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2305098</v>
+        <v>6915294</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2841885</v>
+        <v>8525655</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2305098</v>
+        <v>6915294</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2305098</v>
+        <v>6915294</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2840913</v>
+        <v>8522739</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2659716</v>
+        <v>7979148</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2834352</v>
+        <v>8503056</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>3195450</v>
+        <v>9586350</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2132568</v>
+        <v>6397704</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2132568</v>
+        <v>6397704</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10680,7 +10680,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2676888</v>
+        <v>8030664</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>2132568</v>
+        <v>6397704</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12622,7 +12622,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12927,7 +12927,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13662,7 +13662,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13801,7 +13801,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14258,7 +14258,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14536,7 +14536,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -14814,7 +14814,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15231,7 +15231,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -15787,7 +15787,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16078,7 +16078,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2303154</v>
+        <v>6909462</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2303640</v>
+        <v>6910920</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2185056</v>
+        <v>6555168</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -16834,7 +16834,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2128032</v>
+        <v>6384096</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>2127951</v>
+        <v>6383853</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17444,7 +17444,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>2126493</v>
+        <v>6379479</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -744,15 +744,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>25568217</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>76704651</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.dravitalwertheimer.com/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -893,15 +893,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://drnamazov.co.il/about/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1042,15 +1042,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.dr-bruchim.co.il/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1191,15 +1191,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://drsamandarov.gnssweb.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1340,15 +1340,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1489,15 +1489,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://dr-annapetruseva.co.il/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1641,15 +1641,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1791,15 +1791,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.drbenshitrit.co.il/</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1940,15 +1940,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.dr-avnet.co.il/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>1</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2089,15 +2089,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2238,15 +2238,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2387,15 +2387,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://www.droshribarel.com/</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2536,15 +2536,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2685,15 +2685,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2834,15 +2834,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>25574778</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>76724334</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://elidretzen.co.il/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2983,15 +2983,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>20745882</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>62237646</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://www.dr-hartoov.co.il/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3132,15 +3132,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>25576965</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>76730895</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3281,15 +3281,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>20745882</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>62237646</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://drweissbach.co.il/</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3430,15 +3430,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://www.drmoranpaz.com/</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3579,15 +3579,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3728,15 +3728,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>1</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3877,15 +3877,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -4026,15 +4026,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>20745882</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>62237646</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>https://www.dr-stockheim.com/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4175,15 +4175,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4324,15 +4324,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://www.davidgordon.co.il/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4463,15 +4463,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4612,15 +4612,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://profkamilhighrisk.wixsite.com/home</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4761,15 +4761,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://www.profmeirow.com/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4910,15 +4910,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://dr-hila.com/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>1</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -5049,15 +5049,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5198,15 +5198,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://dr-web.club/%D7%90%D7%AA%D7%A8%D7%99%D7%9D/%D7%A4%D7%A8%D7%95%D7%A4%D7%A1%D7%95%D7%A8-%D7%99%D7%95%D7%90%D7%91-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5347,15 +5347,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://www.zipori-obgyn.com/</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5494,15 +5494,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://www.babygaga.co.il/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>1</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5633,15 +5633,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>1</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5782,15 +5782,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5929,15 +5929,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>1</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -6078,15 +6078,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>19193358</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>57580074</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://indocs.co.il/drtunitski-s/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6227,15 +6227,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6376,15 +6376,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>1</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6530,15 +6530,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>1</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6679,15 +6679,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>1</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6833,15 +6833,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://www.pregnancy.co.il/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>1</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6982,15 +6982,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>25568217</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>76704651</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://www.dr-mishan.co.il/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>1</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -7131,15 +7131,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://www.drmillo.co.il/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7280,15 +7280,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://roeebirnbaum.com/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>1</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7419,15 +7419,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>1</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7568,15 +7568,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>1</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7717,15 +7717,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>1</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7866,15 +7866,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://www.baby-ivf.com/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>1</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -8015,15 +8015,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>1</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -8164,15 +8164,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -8313,15 +8313,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>23937444</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>71812332</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>1</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8462,15 +8462,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>25509168</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>76527504</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://www.arad-medical.co.il/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8611,15 +8611,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8760,15 +8760,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>28759050</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>86277150</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>1</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8909,15 +8909,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>1</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -9058,15 +9058,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>1</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -9210,15 +9210,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>1</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -9359,15 +9359,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>1</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9508,15 +9508,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>19193112</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>57579336</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>1</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9657,15 +9657,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>19193112</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>57579336</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>1</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9806,15 +9806,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/kuperminc-michael/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>1</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9955,15 +9955,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://www.drlinder.co.il/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>1</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -10104,15 +10104,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>1</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -10253,15 +10253,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>1</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -10402,15 +10402,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/maslovitz-sharon/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>1</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10551,15 +10551,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>1</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10690,15 +10690,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>1</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10829,15 +10829,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>1</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10978,15 +10978,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>1</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -11127,15 +11127,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://pain.coi.co.il/</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>1</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -11276,15 +11276,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://www.drzivony.co.il/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>1</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -11425,15 +11425,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://www.dr-batya-kornboim.com/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>1</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11574,15 +11574,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://dinaeisen.com/about/</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>1</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11713,15 +11713,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://www.dafyrahavhass.com/</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>1</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11862,15 +11862,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://www.tau.ac.il/profile/shalevv</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>1</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -12011,15 +12011,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>24091992</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>72275976</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>1</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -12163,15 +12163,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>19193112</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>57579336</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/3175</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>1</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -12314,15 +12314,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>1</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -12467,15 +12467,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>1</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12619,15 +12619,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/8119</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>1</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12771,15 +12771,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>1</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12924,15 +12924,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6696</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>1</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -13076,15 +13076,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>1</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -13225,15 +13225,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://www.doctorlouria.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A9%D7%95%D7%9C%D7%9E%D7%99%D7%AA-%D7%9C%D7%95%D7%A8%D7%99%D7%90</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>1</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -13374,15 +13374,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://www.michalgilad.com/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>1</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -13523,15 +13523,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>1</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13672,15 +13672,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>1</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13811,15 +13811,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>1</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13950,15 +13950,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>1</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -14101,15 +14101,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>1</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -14254,15 +14254,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>1</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -14407,15 +14407,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>1</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -14546,15 +14546,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>1</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -14685,15 +14685,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>1</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14824,15 +14824,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>1</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14963,15 +14963,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>1</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -15102,15 +15102,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>1</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -15241,15 +15241,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>1</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -15380,15 +15380,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>1</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -15519,15 +15519,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>1</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -15658,15 +15658,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>1</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15797,15 +15797,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>1</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15936,15 +15936,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>1</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -16075,15 +16075,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>1</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -16227,15 +16227,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>20728386</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>62185158</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2435</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>1</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -16379,15 +16379,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5230</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>1</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -16532,15 +16532,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>20732760</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>62198280</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5287</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>1</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -16684,15 +16684,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>19665504</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>58996512</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7026</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>1</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16836,15 +16836,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2414</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>1</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16989,15 +16989,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>19152288</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>57456864</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2624</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>1</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -17142,15 +17142,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5282</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>1</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -17294,15 +17294,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>19151559</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>57454677</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2596</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>1</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -17446,15 +17446,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>19138437</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>57415311</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/525</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>1</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>76704651</v>
+        <v>230113953</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>76724334</v>
+        <v>230173002</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>62237646</v>
+        <v>186712938</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>76730895</v>
+        <v>230192685</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>62237646</v>
+        <v>186712938</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>62237646</v>
+        <v>186712938</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>57580074</v>
+        <v>172740222</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6679,7 +6679,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>76704651</v>
+        <v>230113953</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>71812332</v>
+        <v>215436996</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>76527504</v>
+        <v>229582512</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>86277150</v>
+        <v>258831450</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>57579336</v>
+        <v>172738008</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>57579336</v>
+        <v>172738008</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>72275976</v>
+        <v>216827928</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>57579336</v>
+        <v>172738008</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13672,7 +13672,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -13950,7 +13950,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14101,7 +14101,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -14824,7 +14824,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15102,7 +15102,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -15936,7 +15936,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16227,7 +16227,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>62185158</v>
+        <v>186555474</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>62198280</v>
+        <v>186594840</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16684,7 +16684,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>58996512</v>
+        <v>176989536</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -16836,7 +16836,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>57456864</v>
+        <v>172370592</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17142,7 +17142,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17294,7 +17294,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>57454677</v>
+        <v>172364031</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>57415311</v>
+        <v>172245933</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>230113953</v>
+        <v>690341859</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>230173002</v>
+        <v>690519006</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>186712938</v>
+        <v>560138814</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>230192685</v>
+        <v>690578055</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>186712938</v>
+        <v>560138814</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>186712938</v>
+        <v>560138814</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>172740222</v>
+        <v>518220666</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6679,7 +6679,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>230113953</v>
+        <v>690341859</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>215436996</v>
+        <v>646310988</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>229582512</v>
+        <v>688747536</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>258831450</v>
+        <v>776494350</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>172738008</v>
+        <v>518214024</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>172738008</v>
+        <v>518214024</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>216827928</v>
+        <v>650483784</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>172738008</v>
+        <v>518214024</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13672,7 +13672,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -13950,7 +13950,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14101,7 +14101,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -14824,7 +14824,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15102,7 +15102,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -15936,7 +15936,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16227,7 +16227,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>186555474</v>
+        <v>559666422</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>186594840</v>
+        <v>559784520</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16684,7 +16684,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>176989536</v>
+        <v>530968608</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -16836,7 +16836,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>172370592</v>
+        <v>517111776</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17142,7 +17142,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17294,7 +17294,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>172364031</v>
+        <v>517092093</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>172245933</v>
+        <v>516737799</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>690341859</v>
+        <v>2071025577</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>690519006</v>
+        <v>2071557018</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>560138814</v>
+        <v>1680416442</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>690578055</v>
+        <v>2071734165</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>560138814</v>
+        <v>1680416442</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>560138814</v>
+        <v>1680416442</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>518220666</v>
+        <v>1554661998</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6679,7 +6679,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>690341859</v>
+        <v>2071025577</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>646310988</v>
+        <v>1938932964</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>688747536</v>
+        <v>2066242608</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>776494350</v>
+        <v>2329483050</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>518214024</v>
+        <v>1554642072</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>518214024</v>
+        <v>1554642072</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10551,7 +10551,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>650483784</v>
+        <v>1951451352</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>518214024</v>
+        <v>1554642072</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -12771,7 +12771,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -13672,7 +13672,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -13950,7 +13950,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14101,7 +14101,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -14824,7 +14824,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15102,7 +15102,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -15936,7 +15936,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16227,7 +16227,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>559666422</v>
+        <v>1678999266</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>559784520</v>
+        <v>1679353560</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -16684,7 +16684,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>530968608</v>
+        <v>1592905824</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -16836,7 +16836,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>517111776</v>
+        <v>1551335328</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17142,7 +17142,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17294,7 +17294,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>517092093</v>
+        <v>1551276279</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -17446,7 +17446,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>516737799</v>
+        <v>1550213397</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>shared_target_count</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>identity_url</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -744,15 +744,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2071025577</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr">
+        <v>6213076731</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>https://www.dravitalwertheimer.com/</t>
         </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -893,15 +893,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>https://drnamazov.co.il/about/</t>
         </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1042,15 +1042,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>https://www.dr-bruchim.co.il/</t>
         </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1191,15 +1191,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>https://drsamandarov.gnssweb.co.il/</t>
         </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1340,15 +1340,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1489,15 +1489,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>https://dr-annapetruseva.co.il/</t>
         </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1641,15 +1641,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1791,15 +1791,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>https://www.drbenshitrit.co.il/</t>
         </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1940,15 +1940,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2066242608</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr">
+        <v>6198727824</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>https://www.dr-avnet.co.il/</t>
         </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2089,15 +2089,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2066242608</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr">
+        <v>6198727824</v>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2238,15 +2238,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2066242608</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr">
+        <v>6198727824</v>
+      </c>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2387,15 +2387,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1938696768</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr">
+        <v>5816090304</v>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>https://www.droshribarel.com/</t>
         </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2536,15 +2536,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2066242608</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="inlineStr">
+        <v>6198727824</v>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2685,15 +2685,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2066242608</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr">
+        <v>6198727824</v>
+      </c>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2834,15 +2834,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2071557018</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr">
+        <v>6214671054</v>
+      </c>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>https://elidretzen.co.il/</t>
         </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2983,15 +2983,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1680416442</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="inlineStr">
+        <v>5041249326</v>
+      </c>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>https://www.dr-hartoov.co.il/</t>
         </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3132,15 +3132,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2071734165</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr">
+        <v>6215202495</v>
+      </c>
+      <c r="AE18" t="inlineStr">
         <is>
           <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3281,15 +3281,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1680416442</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr">
+        <v>5041249326</v>
+      </c>
+      <c r="AE19" t="inlineStr">
         <is>
           <t>https://drweissbach.co.il/</t>
         </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3430,15 +3430,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2066242608</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr">
+        <v>6198727824</v>
+      </c>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>https://www.drmoranpaz.com/</t>
         </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3579,15 +3579,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3728,15 +3728,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3877,15 +3877,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE23" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -4026,15 +4026,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1680416442</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr">
+        <v>5041249326</v>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>https://www.dr-stockheim.com/</t>
         </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4175,15 +4175,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE25" t="inlineStr">
         <is>
           <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4324,15 +4324,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE26" t="inlineStr">
         <is>
           <t>https://www.davidgordon.co.il/</t>
         </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4463,15 +4463,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE27" t="inlineStr">
         <is>
           <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
         </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4612,15 +4612,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE28" t="inlineStr">
         <is>
           <t>https://profkamilhighrisk.wixsite.com/home</t>
         </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4761,15 +4761,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE29" t="inlineStr">
         <is>
           <t>https://www.profmeirow.com/</t>
         </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4910,15 +4910,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE30" t="inlineStr">
         <is>
           <t>https://dr-hila.com/</t>
         </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -5049,15 +5049,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE31" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5198,15 +5198,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE32" t="inlineStr">
         <is>
           <t>https://dr-web.club/%D7%90%D7%AA%D7%A8%D7%99%D7%9D/%D7%A4%D7%A8%D7%95%D7%A4%D7%A1%D7%95%D7%A8-%D7%99%D7%95%D7%90%D7%91-%D7%A4%D7%9C%D7%93/</t>
         </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5347,15 +5347,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1593260118</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="inlineStr">
+        <v>4779780354</v>
+      </c>
+      <c r="AE33" t="inlineStr">
         <is>
           <t>https://www.zipori-obgyn.com/</t>
         </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5494,15 +5494,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1937102445</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr">
+        <v>5811307335</v>
+      </c>
+      <c r="AE34" t="inlineStr">
         <is>
           <t>https://www.babygaga.co.il/</t>
         </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5633,15 +5633,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE35" t="inlineStr">
         <is>
           <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>1</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5782,15 +5782,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE36" t="inlineStr">
         <is>
           <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5929,15 +5929,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1937102445</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="inlineStr">
+        <v>5811307335</v>
+      </c>
+      <c r="AE37" t="inlineStr">
         <is>
           <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -6078,15 +6078,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1554661998</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr">
+        <v>4663985994</v>
+      </c>
+      <c r="AE38" t="inlineStr">
         <is>
           <t>https://indocs.co.il/drtunitski-s/</t>
         </is>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6227,15 +6227,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE39" t="inlineStr">
         <is>
           <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6376,15 +6376,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE40" t="inlineStr">
         <is>
           <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>1</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6530,15 +6530,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE41" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>1</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6679,15 +6679,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE42" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
+      </c>
+      <c r="AF42" t="n">
+        <v>1</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6833,15 +6833,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE43" t="inlineStr">
         <is>
           <t>https://www.pregnancy.co.il/</t>
         </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>1</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6982,15 +6982,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2071025577</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="inlineStr">
+        <v>6213076731</v>
+      </c>
+      <c r="AE44" t="inlineStr">
         <is>
           <t>https://www.dr-mishan.co.il/</t>
         </is>
+      </c>
+      <c r="AF44" t="n">
+        <v>1</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -7131,15 +7131,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE45" t="inlineStr">
         <is>
           <t>https://www.drmillo.co.il/</t>
         </is>
+      </c>
+      <c r="AF45" t="n">
+        <v>1</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7280,15 +7280,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE46" t="inlineStr">
         <is>
           <t>https://roeebirnbaum.com/</t>
         </is>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7419,15 +7419,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE47" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7568,15 +7568,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE48" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
+      </c>
+      <c r="AF48" t="n">
+        <v>1</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7717,15 +7717,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE49" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7866,15 +7866,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF50" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE50" t="inlineStr">
         <is>
           <t>https://www.baby-ivf.com/</t>
         </is>
+      </c>
+      <c r="AF50" t="n">
+        <v>1</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -8015,15 +8015,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE51" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
+      </c>
+      <c r="AF51" t="n">
+        <v>1</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -8164,15 +8164,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE52" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
+      </c>
+      <c r="AF52" t="n">
+        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -8313,15 +8313,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1938932964</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF53" t="inlineStr">
+        <v>5816798892</v>
+      </c>
+      <c r="AE53" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
+      </c>
+      <c r="AF53" t="n">
+        <v>1</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8462,15 +8462,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2066242608</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF54" t="inlineStr">
+        <v>6198727824</v>
+      </c>
+      <c r="AE54" t="inlineStr">
         <is>
           <t>https://www.arad-medical.co.il/</t>
         </is>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8611,15 +8611,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE55" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
+      </c>
+      <c r="AF55" t="n">
+        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8760,15 +8760,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2329483050</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="inlineStr">
+        <v>6988449150</v>
+      </c>
+      <c r="AE56" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
+      </c>
+      <c r="AF56" t="n">
+        <v>1</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8909,15 +8909,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1593260118</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF57" t="inlineStr">
+        <v>4779780354</v>
+      </c>
+      <c r="AE57" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
+      </c>
+      <c r="AF57" t="n">
+        <v>1</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -9058,15 +9058,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1593260118</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF58" t="inlineStr">
+        <v>4779780354</v>
+      </c>
+      <c r="AE58" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
+      </c>
+      <c r="AF58" t="n">
+        <v>1</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -9210,15 +9210,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1593260118</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF59" t="inlineStr">
+        <v>4779780354</v>
+      </c>
+      <c r="AE59" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
+      </c>
+      <c r="AF59" t="n">
+        <v>1</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -9359,15 +9359,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1593260118</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF60" t="inlineStr">
+        <v>4779780354</v>
+      </c>
+      <c r="AE60" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
+      </c>
+      <c r="AF60" t="n">
+        <v>1</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9508,15 +9508,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1554642072</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF61" t="inlineStr">
+        <v>4663926216</v>
+      </c>
+      <c r="AE61" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
+      </c>
+      <c r="AF61" t="n">
+        <v>1</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9657,15 +9657,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1554642072</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF62" t="inlineStr">
+        <v>4663926216</v>
+      </c>
+      <c r="AE62" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
+      </c>
+      <c r="AF62" t="n">
+        <v>1</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9806,15 +9806,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF63" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE63" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/kuperminc-michael/</t>
         </is>
+      </c>
+      <c r="AF63" t="n">
+        <v>1</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9955,15 +9955,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF64" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE64" t="inlineStr">
         <is>
           <t>https://www.drlinder.co.il/</t>
         </is>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -10104,15 +10104,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF65" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE65" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -10253,15 +10253,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1551276279</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF66" t="inlineStr">
+        <v>4653828837</v>
+      </c>
+      <c r="AE66" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
+      </c>
+      <c r="AF66" t="n">
+        <v>1</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -10402,15 +10402,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1551276279</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF67" t="inlineStr">
+        <v>4653828837</v>
+      </c>
+      <c r="AE67" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/maslovitz-sharon/</t>
         </is>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10551,15 +10551,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1551335328</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF68" t="inlineStr">
+        <v>4654005984</v>
+      </c>
+      <c r="AE68" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
+      </c>
+      <c r="AF68" t="n">
+        <v>1</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10690,15 +10690,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF69" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10829,15 +10829,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF70" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE70" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10978,15 +10978,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1678999266</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF71" t="inlineStr">
+        <v>5036997798</v>
+      </c>
+      <c r="AE71" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -11127,15 +11127,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1678999266</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF72" t="inlineStr">
+        <v>5036997798</v>
+      </c>
+      <c r="AE72" t="inlineStr">
         <is>
           <t>https://pain.coi.co.il/</t>
         </is>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -11276,15 +11276,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF73" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE73" t="inlineStr">
         <is>
           <t>https://www.drzivony.co.il/</t>
         </is>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -11425,15 +11425,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1678822119</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF74" t="inlineStr">
+        <v>5036466357</v>
+      </c>
+      <c r="AE74" t="inlineStr">
         <is>
           <t>https://www.dr-batya-kornboim.com/</t>
         </is>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11574,15 +11574,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1678999266</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF75" t="inlineStr">
+        <v>5036997798</v>
+      </c>
+      <c r="AE75" t="inlineStr">
         <is>
           <t>https://dinaeisen.com/about/</t>
         </is>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11713,15 +11713,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF76" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE76" t="inlineStr">
         <is>
           <t>https://www.dafyrahavhass.com/</t>
         </is>
+      </c>
+      <c r="AF76" t="n">
+        <v>1</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11862,15 +11862,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF77" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE77" t="inlineStr">
         <is>
           <t>https://www.tau.ac.il/profile/shalevv</t>
         </is>
+      </c>
+      <c r="AF77" t="n">
+        <v>1</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -12011,15 +12011,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1951451352</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF78" t="inlineStr">
+        <v>5854354056</v>
+      </c>
+      <c r="AE78" t="inlineStr">
         <is>
           <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
+      </c>
+      <c r="AF78" t="n">
+        <v>1</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -12163,15 +12163,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1554642072</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF79" t="inlineStr">
+        <v>4663926216</v>
+      </c>
+      <c r="AE79" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/3175</t>
         </is>
+      </c>
+      <c r="AF79" t="n">
+        <v>1</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -12314,15 +12314,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF80" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE80" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
+      </c>
+      <c r="AF80" t="n">
+        <v>1</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -12467,15 +12467,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF81" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE81" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
+      </c>
+      <c r="AF81" t="n">
+        <v>1</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12619,15 +12619,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1551335328</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF82" t="inlineStr">
+        <v>4654005984</v>
+      </c>
+      <c r="AE82" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/8119</t>
         </is>
+      </c>
+      <c r="AF82" t="n">
+        <v>1</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12771,15 +12771,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1551276279</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF83" t="inlineStr">
+        <v>4653828837</v>
+      </c>
+      <c r="AE83" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
+      </c>
+      <c r="AF83" t="n">
+        <v>1</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12924,15 +12924,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1550213397</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF84" t="inlineStr">
+        <v>4650640191</v>
+      </c>
+      <c r="AE84" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6696</t>
         </is>
+      </c>
+      <c r="AF84" t="n">
+        <v>1</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -13076,15 +13076,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1550213397</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF85" t="inlineStr">
+        <v>4650640191</v>
+      </c>
+      <c r="AE85" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
+      </c>
+      <c r="AF85" t="n">
+        <v>1</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -13225,15 +13225,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1550213397</v>
-      </c>
-      <c r="AE86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF86" t="inlineStr">
+        <v>4650640191</v>
+      </c>
+      <c r="AE86" t="inlineStr">
         <is>
           <t>https://www.doctorlouria.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A9%D7%95%D7%9C%D7%9E%D7%99%D7%AA-%D7%9C%D7%95%D7%A8%D7%99%D7%90</t>
         </is>
+      </c>
+      <c r="AF86" t="n">
+        <v>1</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -13374,15 +13374,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1937102445</v>
-      </c>
-      <c r="AE87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF87" t="inlineStr">
+        <v>5811307335</v>
+      </c>
+      <c r="AE87" t="inlineStr">
         <is>
           <t>https://www.michalgilad.com/</t>
         </is>
+      </c>
+      <c r="AF87" t="n">
+        <v>1</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -13523,15 +13523,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1550213397</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF88" t="inlineStr">
+        <v>4650640191</v>
+      </c>
+      <c r="AE88" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
+      </c>
+      <c r="AF88" t="n">
+        <v>1</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13672,15 +13672,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1550213397</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF89" t="inlineStr">
+        <v>4650640191</v>
+      </c>
+      <c r="AE89" t="inlineStr">
         <is>
           <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
+      </c>
+      <c r="AF89" t="n">
+        <v>1</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13811,15 +13811,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF90" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE90" t="inlineStr">
         <is>
           <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
+      </c>
+      <c r="AF90" t="n">
+        <v>1</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13950,15 +13950,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF91" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE91" t="inlineStr">
         <is>
           <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
+      </c>
+      <c r="AF91" t="n">
+        <v>1</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -14101,15 +14101,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE92" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF92" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE92" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
+      </c>
+      <c r="AF92" t="n">
+        <v>1</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -14254,15 +14254,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1551276279</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF93" t="inlineStr">
+        <v>4653828837</v>
+      </c>
+      <c r="AE93" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
+      </c>
+      <c r="AF93" t="n">
+        <v>1</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -14407,15 +14407,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1550213397</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF94" t="inlineStr">
+        <v>4650640191</v>
+      </c>
+      <c r="AE94" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
+      </c>
+      <c r="AF94" t="n">
+        <v>1</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -14546,15 +14546,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF95" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
+      </c>
+      <c r="AF95" t="n">
+        <v>1</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -14685,15 +14685,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF96" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
+      </c>
+      <c r="AF96" t="n">
+        <v>1</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14824,15 +14824,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF97" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
+      </c>
+      <c r="AF97" t="n">
+        <v>1</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14963,15 +14963,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF98" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
+      </c>
+      <c r="AF98" t="n">
+        <v>1</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -15102,15 +15102,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF99" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
+      </c>
+      <c r="AF99" t="n">
+        <v>1</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -15241,15 +15241,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF100" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
+      </c>
+      <c r="AF100" t="n">
+        <v>1</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -15380,15 +15380,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF101" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
+      </c>
+      <c r="AF101" t="n">
+        <v>1</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -15519,15 +15519,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF102" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
+      </c>
+      <c r="AF102" t="n">
+        <v>1</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -15658,15 +15658,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF103" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
+      </c>
+      <c r="AF103" t="n">
+        <v>1</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15797,15 +15797,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF104" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
+      </c>
+      <c r="AF104" t="n">
+        <v>1</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15936,15 +15936,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF105" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
+      </c>
+      <c r="AF105" t="n">
+        <v>1</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -16075,15 +16075,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1549681956</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF106" t="inlineStr">
+        <v>4649045868</v>
+      </c>
+      <c r="AE106" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
         </is>
+      </c>
+      <c r="AF106" t="n">
+        <v>1</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -16227,15 +16227,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1678999266</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF107" t="inlineStr">
+        <v>5036997798</v>
+      </c>
+      <c r="AE107" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2435</t>
         </is>
+      </c>
+      <c r="AF107" t="n">
+        <v>1</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -16379,15 +16379,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1554464925</v>
-      </c>
-      <c r="AE108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF108" t="inlineStr">
+        <v>4663394775</v>
+      </c>
+      <c r="AE108" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5230</t>
         </is>
+      </c>
+      <c r="AF108" t="n">
+        <v>1</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -16532,15 +16532,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1679353560</v>
-      </c>
-      <c r="AE109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF109" t="inlineStr">
+        <v>5038060680</v>
+      </c>
+      <c r="AE109" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5287</t>
         </is>
+      </c>
+      <c r="AF109" t="n">
+        <v>1</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -16684,15 +16684,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1592905824</v>
-      </c>
-      <c r="AE110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF110" t="inlineStr">
+        <v>4778717472</v>
+      </c>
+      <c r="AE110" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7026</t>
         </is>
+      </c>
+      <c r="AF110" t="n">
+        <v>1</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16836,15 +16836,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1551276279</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF111" t="inlineStr">
+        <v>4653828837</v>
+      </c>
+      <c r="AE111" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2414</t>
         </is>
+      </c>
+      <c r="AF111" t="n">
+        <v>1</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16989,15 +16989,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1551335328</v>
-      </c>
-      <c r="AE112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF112" t="inlineStr">
+        <v>4654005984</v>
+      </c>
+      <c r="AE112" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2624</t>
         </is>
+      </c>
+      <c r="AF112" t="n">
+        <v>1</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -17142,15 +17142,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1551276279</v>
-      </c>
-      <c r="AE113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF113" t="inlineStr">
+        <v>4653828837</v>
+      </c>
+      <c r="AE113" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5282</t>
         </is>
+      </c>
+      <c r="AF113" t="n">
+        <v>1</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -17294,15 +17294,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1551276279</v>
-      </c>
-      <c r="AE114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF114" t="inlineStr">
+        <v>4653828837</v>
+      </c>
+      <c r="AE114" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2596</t>
         </is>
+      </c>
+      <c r="AF114" t="n">
+        <v>1</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -17446,15 +17446,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1550213397</v>
-      </c>
-      <c r="AE115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF115" t="inlineStr">
+        <v>4650640191</v>
+      </c>
+      <c r="AE115" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/525</t>
         </is>
+      </c>
+      <c r="AF115" t="n">
+        <v>1</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -744,15 +744,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>6213076731</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>18639230193</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.dravitalwertheimer.com/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -893,15 +893,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://drnamazov.co.il/about/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1042,15 +1042,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.dr-bruchim.co.il/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1191,15 +1191,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://drsamandarov.gnssweb.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1340,15 +1340,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1489,15 +1489,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://dr-annapetruseva.co.il/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1641,15 +1641,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1791,15 +1791,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.drbenshitrit.co.il/</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1940,15 +1940,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>6198727824</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>18596183472</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.dr-avnet.co.il/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>1</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2089,15 +2089,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>6198727824</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>18596183472</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2238,15 +2238,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>6198727824</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>18596183472</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2387,15 +2387,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>5816090304</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>17448270912</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://www.droshribarel.com/</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2536,15 +2536,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>6198727824</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>18596183472</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2685,15 +2685,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>6198727824</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>18596183472</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2834,15 +2834,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>6214671054</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>18644013162</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://elidretzen.co.il/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2983,15 +2983,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>5041249326</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>15123747978</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://www.dr-hartoov.co.il/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3132,15 +3132,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>6215202495</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>18645607485</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3281,15 +3281,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>5041249326</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>15123747978</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://drweissbach.co.il/</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3430,15 +3430,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>6198727824</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>18596183472</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://www.drmoranpaz.com/</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3579,15 +3579,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3728,15 +3728,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>1</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3877,15 +3877,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -4026,15 +4026,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>5041249326</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>15123747978</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>https://www.dr-stockheim.com/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4175,15 +4175,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>1</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4324,15 +4324,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://www.davidgordon.co.il/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4463,15 +4463,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4612,15 +4612,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://profkamilhighrisk.wixsite.com/home</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4761,15 +4761,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://www.profmeirow.com/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>1</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4910,15 +4910,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://dr-hila.com/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>1</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -5049,15 +5049,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5198,15 +5198,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://dr-web.club/%D7%90%D7%AA%D7%A8%D7%99%D7%9D/%D7%A4%D7%A8%D7%95%D7%A4%D7%A1%D7%95%D7%A8-%D7%99%D7%95%D7%90%D7%91-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5347,15 +5347,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4779780354</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>14339341062</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://www.zipori-obgyn.com/</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5494,15 +5494,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://www.babygaga.co.il/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>1</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5633,15 +5633,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>1</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5782,15 +5782,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5929,15 +5929,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>1</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -6078,15 +6078,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4663985994</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>13991957982</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://indocs.co.il/drtunitski-s/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6227,15 +6227,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6376,15 +6376,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>1</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6530,15 +6530,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>1</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6679,15 +6679,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>1</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6833,15 +6833,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://www.pregnancy.co.il/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>1</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6982,15 +6982,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>6213076731</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>18639230193</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://www.dr-mishan.co.il/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>1</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -7131,15 +7131,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://www.drmillo.co.il/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7280,15 +7280,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://roeebirnbaum.com/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>1</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7419,15 +7419,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>1</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7568,15 +7568,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>1</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7717,15 +7717,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>1</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7866,15 +7866,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://www.baby-ivf.com/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>1</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -8015,15 +8015,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>1</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -8164,15 +8164,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -8313,15 +8313,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>5816798892</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>17450396676</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>1</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8462,15 +8462,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>6198727824</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>18596183472</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://www.arad-medical.co.il/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>1</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8611,15 +8611,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8760,15 +8760,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>6988449150</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>20965347450</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>1</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8909,15 +8909,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4779780354</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>14339341062</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>1</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -9058,15 +9058,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4779780354</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>14339341062</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>1</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -9210,15 +9210,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4779780354</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>14339341062</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>1</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -9359,15 +9359,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4779780354</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>14339341062</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>1</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9508,15 +9508,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4663926216</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>13991778648</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>1</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9657,15 +9657,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>4663926216</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>13991778648</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>1</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9806,15 +9806,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/kuperminc-michael/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>1</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9955,15 +9955,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://www.drlinder.co.il/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>1</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -10104,15 +10104,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>1</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -10253,15 +10253,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>4653828837</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>13961486511</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>1</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -10402,15 +10402,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>4653828837</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>13961486511</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/maslovitz-sharon/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>1</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10551,15 +10551,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>4654005984</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>13962017952</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>1</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10690,15 +10690,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>1</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10829,15 +10829,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>1</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10978,15 +10978,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>5036997798</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>15110993394</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>1</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -11127,15 +11127,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>5036997798</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>15110993394</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://pain.coi.co.il/</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>1</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -11276,15 +11276,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://www.drzivony.co.il/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>1</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -11425,15 +11425,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://www.dr-batya-kornboim.com/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>1</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11574,15 +11574,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>5036997798</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>15110993394</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://dinaeisen.com/about/</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>1</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11713,15 +11713,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://www.dafyrahavhass.com/</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>1</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11862,15 +11862,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://www.tau.ac.il/profile/shalevv</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>1</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -12011,15 +12011,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>5854354056</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>17563062168</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>1</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -12163,15 +12163,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4663926216</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>13991778648</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/3175</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>1</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -12314,15 +12314,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>1</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -12467,15 +12467,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>1</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12619,15 +12619,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>4654005984</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>13962017952</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/8119</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>1</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12771,15 +12771,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>4653828837</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>13961486511</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>1</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12924,15 +12924,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>4650640191</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>13951920573</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6696</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>1</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -13076,15 +13076,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>4650640191</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>13951920573</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>1</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -13225,15 +13225,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>4650640191</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>13951920573</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://www.doctorlouria.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A9%D7%95%D7%9C%D7%9E%D7%99%D7%AA-%D7%9C%D7%95%D7%A8%D7%99%D7%90</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>1</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -13374,15 +13374,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://www.michalgilad.com/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>1</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -13523,15 +13523,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>4650640191</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>13951920573</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>1</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13672,15 +13672,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>4650640191</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>13951920573</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>1</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13811,15 +13811,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>1</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13950,15 +13950,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>1</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -14101,15 +14101,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>1</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -14254,15 +14254,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>4653828837</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>13961486511</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>1</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -14407,15 +14407,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>4650640191</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>13951920573</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>1</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -14546,15 +14546,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>1</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -14685,15 +14685,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>1</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14824,15 +14824,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>1</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14963,15 +14963,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>1</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -15102,15 +15102,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>1</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -15241,15 +15241,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>1</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -15380,15 +15380,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>1</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -15519,15 +15519,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>1</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -15658,15 +15658,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>1</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15797,15 +15797,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>1</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15936,15 +15936,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>1</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -16075,15 +16075,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>1</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -16227,15 +16227,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>5036997798</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>15110993394</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2435</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>1</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -16379,15 +16379,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5230</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>1</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -16532,15 +16532,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>5038060680</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>15114182040</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5287</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>1</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -16684,15 +16684,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>4778717472</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>14336152416</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7026</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>1</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16836,15 +16836,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>4653828837</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>13961486511</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2414</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>1</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16989,15 +16989,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>4654005984</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>13962017952</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2624</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>1</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -17142,15 +17142,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>4653828837</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>13961486511</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5282</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>1</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -17294,15 +17294,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>4653828837</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>13961486511</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2596</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>1</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -17446,15 +17446,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>4650640191</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>13951920573</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/525</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>1</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,201 +413,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM115"/>
+  <dimension ref="A1:AQ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>algo_version</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>physician_search_version</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>shared_target_count</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>unchanged_search_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>verification_review_required</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>resolution_reason</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>search_fingerprint</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
         <is>
           <t>candidate_rank</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>shared_contact</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>send_eligible</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>personalization_safe</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -630,7 +638,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -744,31 +752,39 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>18639230193</v>
+        <v>37278460386</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.dravitalwertheimer.com/</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -779,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -893,31 +909,39 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>https://drnamazov.co.il/about/</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -928,7 +952,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1042,31 +1066,39 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>https://www.dr-bruchim.co.il/</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1077,7 +1109,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1191,31 +1223,39 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>https://drsamandarov.gnssweb.co.il/</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1226,7 +1266,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1340,31 +1380,39 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>https://www.kedemalon.co.il/</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1375,7 +1423,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1489,31 +1537,39 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>https://dr-annapetruseva.co.il/</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1524,7 +1580,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1641,31 +1697,39 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1676,7 +1740,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1791,31 +1855,39 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>https://www.drbenshitrit.co.il/</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1826,7 +1898,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1940,31 +2012,39 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>18596183472</v>
+        <v>37192366944</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>https://www.dr-avnet.co.il/</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1975,7 +2055,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2089,31 +2169,39 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>18596183472</v>
+        <v>37192366944</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AI11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2124,7 +2212,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2238,31 +2326,39 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>18596183472</v>
+        <v>37192366944</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AI12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2273,7 +2369,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2387,31 +2483,39 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>17448270912</v>
+        <v>34896541824</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>https://www.droshribarel.com/</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AI13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2422,7 +2526,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2536,31 +2640,39 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>18596183472</v>
+        <v>37192366944</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AI14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2571,7 +2683,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2685,31 +2797,39 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>18596183472</v>
+        <v>37192366944</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>https://www.urogynecologist.co.il/</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="n">
+      <c r="AI15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="n">
         <v>2</v>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AN15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2720,7 +2840,7 @@
         <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2834,31 +2954,39 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>18644013162</v>
+        <v>37288026324</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
         <is>
           <t>https://elidretzen.co.il/</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM16" t="inlineStr">
+      <c r="AI16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2869,7 +2997,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2983,31 +3111,39 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>15123747978</v>
+        <v>30247495956</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
         <is>
           <t>https://www.dr-hartoov.co.il/</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AI17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3018,7 +3154,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3132,31 +3268,39 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>18645607485</v>
+        <v>37291214970</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
         <is>
           <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AI18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3167,7 +3311,7 @@
         <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3281,31 +3425,39 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>15123747978</v>
+        <v>30247495956</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
         <is>
           <t>https://drweissbach.co.il/</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AI19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3316,7 +3468,7 @@
         <v>12</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3430,31 +3582,39 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>18596183472</v>
+        <v>37192366944</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AI20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3465,7 +3625,7 @@
         <v>12</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3579,31 +3739,39 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AI21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3614,7 +3782,7 @@
         <v>12</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3728,31 +3896,39 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AI22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3763,7 +3939,7 @@
         <v>12</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3877,31 +4053,39 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="inlineStr">
         <is>
           <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="n">
+      <c r="AI23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="n">
         <v>2</v>
       </c>
-      <c r="AJ23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AN23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3912,7 +4096,7 @@
         <v>12</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4026,31 +4210,39 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>15123747978</v>
+        <v>30247495956</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="inlineStr">
         <is>
           <t>https://www.dr-stockheim.com/</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AI24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4061,7 +4253,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4175,31 +4367,39 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
       </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="inlineStr">
         <is>
           <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AI25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4210,7 +4410,7 @@
         <v>12</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4324,31 +4524,39 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AI26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4463,31 +4671,37 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="inlineStr">
         <is>
           <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4498,7 +4712,7 @@
         <v>12</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4612,31 +4826,39 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
       </c>
-      <c r="AF28" t="inlineStr">
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="inlineStr">
         <is>
           <t>https://profkamilhighrisk.wixsite.com/home</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AI28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4647,7 +4869,7 @@
         <v>12</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4761,31 +4983,39 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>https://www.profmeirow.com/</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AI29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4796,7 +5026,7 @@
         <v>12</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4910,31 +5140,39 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>https://dr-hila.com/</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AI30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5049,31 +5287,37 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5084,7 +5328,7 @@
         <v>12</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5198,31 +5442,39 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
       </c>
-      <c r="AF32" t="inlineStr">
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="inlineStr">
         <is>
           <t>https://dr-web.club/%D7%90%D7%AA%D7%A8%D7%99%D7%9D/%D7%A4%D7%A8%D7%95%D7%A4%D7%A1%D7%95%D7%A8-%D7%99%D7%95%D7%90%D7%91-%D7%A4%D7%9C%D7%93/</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AI32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5233,7 +5485,7 @@
         <v>12</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5347,31 +5599,39 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>14339341062</v>
+        <v>28678682124</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
-      <c r="AF33" t="inlineStr">
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="inlineStr">
         <is>
           <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AI33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5494,31 +5754,37 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>17433922005</v>
+        <v>34867844010</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
       </c>
-      <c r="AF34" t="inlineStr">
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="inlineStr">
         <is>
           <t>https://www.babygaga.co.il/</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5633,31 +5899,37 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
       </c>
-      <c r="AF35" t="inlineStr">
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="inlineStr">
         <is>
           <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
       </c>
-      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5668,7 +5940,7 @@
         <v>12</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5782,31 +6054,39 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
       </c>
-      <c r="AF36" t="inlineStr">
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="inlineStr">
         <is>
           <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
-      <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM36" t="inlineStr">
+      <c r="AI36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5929,31 +6209,37 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>17433922005</v>
+        <v>34867844010</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
       </c>
-      <c r="AF37" t="inlineStr">
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="inlineStr">
         <is>
           <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5964,7 +6250,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -6078,31 +6364,39 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>13991957982</v>
+        <v>27983915964</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
       </c>
-      <c r="AF38" t="inlineStr">
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="inlineStr">
         <is>
           <t>https://indocs.co.il/drtunitski-s/</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AI38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6113,7 +6407,7 @@
         <v>12</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6227,31 +6521,39 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
       </c>
-      <c r="AF39" t="inlineStr">
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="inlineStr">
         <is>
           <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AI39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6262,7 +6564,7 @@
         <v>12</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6376,31 +6678,39 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
       </c>
-      <c r="AF40" t="inlineStr">
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="inlineStr">
         <is>
           <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
-      <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AI40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ40" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6411,7 +6721,7 @@
         <v>12</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6530,31 +6840,39 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
       </c>
-      <c r="AF41" t="inlineStr">
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
       </c>
-      <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AI41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ41" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6565,7 +6883,7 @@
         <v>12</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6679,31 +6997,39 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
       </c>
-      <c r="AF42" t="inlineStr">
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="inlineStr">
         <is>
           <t>https://www.profeitan.com/</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="n">
+      <c r="AI42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="n">
         <v>2</v>
       </c>
-      <c r="AJ42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM42" t="inlineStr">
+      <c r="AN42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ42" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6714,7 +7040,7 @@
         <v>12</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6833,31 +7159,39 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
       </c>
-      <c r="AF43" t="inlineStr">
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="inlineStr">
         <is>
           <t>https://www.pregnancy.co.il/</t>
         </is>
       </c>
-      <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM43" t="inlineStr">
+      <c r="AI43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ43" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6868,7 +7202,7 @@
         <v>12</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6982,31 +7316,39 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>18639230193</v>
+        <v>37278460386</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AF44" t="inlineStr">
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
-      <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM44" t="inlineStr">
+      <c r="AI44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ44" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7017,7 +7359,7 @@
         <v>12</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -7131,31 +7473,39 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
       </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="inlineStr">
         <is>
           <t>https://www.drmillo.co.il/</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AI45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ45" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7166,7 +7516,7 @@
         <v>12</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7280,31 +7630,39 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
       </c>
-      <c r="AF46" t="inlineStr">
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="inlineStr">
         <is>
           <t>https://roeebirnbaum.com/</t>
         </is>
       </c>
-      <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AI46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ46" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7419,31 +7777,37 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
       </c>
-      <c r="AF47" t="inlineStr">
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="inlineStr">
         <is>
           <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
-      <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM47" t="inlineStr">
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ47" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7454,7 +7818,7 @@
         <v>12</v>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7568,31 +7932,39 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
       </c>
-      <c r="AF48" t="inlineStr">
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
-      <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM48" t="inlineStr">
+      <c r="AI48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ48" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7603,7 +7975,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7717,31 +8089,39 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
       </c>
-      <c r="AF49" t="inlineStr">
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
-      <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM49" t="inlineStr">
+      <c r="AI49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ49" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7752,7 +8132,7 @@
         <v>12</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7866,31 +8246,39 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
       </c>
-      <c r="AF50" t="inlineStr">
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="inlineStr">
         <is>
           <t>https://www.baby-ivf.com/</t>
         </is>
       </c>
-      <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM50" t="inlineStr">
+      <c r="AI50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ50" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7901,7 +8289,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -8015,31 +8403,39 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
       </c>
-      <c r="AF51" t="inlineStr">
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
-      <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AI51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ51" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8050,7 +8446,7 @@
         <v>12</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -8164,31 +8560,39 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
       </c>
-      <c r="AF52" t="inlineStr">
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
-      <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AI52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ52" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8199,7 +8603,7 @@
         <v>12</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -8313,31 +8717,39 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>17450396676</v>
+        <v>34900793352</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
       </c>
-      <c r="AF53" t="inlineStr">
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
-      <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AI53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ53" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8348,7 +8760,7 @@
         <v>12</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8462,31 +8874,39 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>18596183472</v>
+        <v>37192366944</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
       </c>
-      <c r="AF54" t="inlineStr">
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="inlineStr">
         <is>
           <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
-      <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AI54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ54" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8497,7 +8917,7 @@
         <v>12</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8611,31 +9031,39 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
       </c>
-      <c r="AF55" t="inlineStr">
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
-      <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AI55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ55" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8646,7 +9074,7 @@
         <v>12</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8760,31 +9188,39 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>20965347450</v>
+        <v>41930694900</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
       </c>
-      <c r="AF56" t="inlineStr">
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
-      <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AI56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ56" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8795,7 +9231,7 @@
         <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8909,31 +9345,39 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>14339341062</v>
+        <v>28678682124</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
       </c>
-      <c r="AF57" t="inlineStr">
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
-      <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AI57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ57" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8944,7 +9388,7 @@
         <v>12</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -9058,31 +9502,39 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>14339341062</v>
+        <v>28678682124</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
       </c>
-      <c r="AF58" t="inlineStr">
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
-      <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AI58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ58" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9093,7 +9545,7 @@
         <v>12</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -9210,31 +9662,39 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>14339341062</v>
+        <v>28678682124</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
       </c>
-      <c r="AF59" t="inlineStr">
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="inlineStr">
         <is>
           <t>https://urogyn.org.il/</t>
         </is>
       </c>
-      <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AI59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ59" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9245,7 +9705,7 @@
         <v>12</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -9359,31 +9819,39 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>14339341062</v>
+        <v>28678682124</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
       </c>
-      <c r="AF60" t="inlineStr">
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
-      <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AI60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ60" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9394,7 +9862,7 @@
         <v>12</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9508,31 +9976,39 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>13991778648</v>
+        <v>27983557296</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
       </c>
-      <c r="AF61" t="inlineStr">
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AI61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ61" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9543,7 +10019,7 @@
         <v>12</v>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9657,31 +10133,39 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>13991778648</v>
+        <v>27983557296</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
       </c>
-      <c r="AF62" t="inlineStr">
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AI62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ62" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9692,7 +10176,7 @@
         <v>12</v>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9806,31 +10290,39 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
       </c>
-      <c r="AF63" t="inlineStr">
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/kuperminc-michael/</t>
         </is>
       </c>
-      <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AI63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ63" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9841,7 +10333,7 @@
         <v>12</v>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9955,31 +10447,39 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
       </c>
-      <c r="AF64" t="inlineStr">
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="inlineStr">
         <is>
           <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
-      <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AI64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ64" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9990,7 +10490,7 @@
         <v>12</v>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -10104,31 +10604,39 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
       </c>
-      <c r="AF65" t="inlineStr">
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="inlineStr">
         <is>
           <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
-      <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM65" t="inlineStr">
+      <c r="AI65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ65" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10139,7 +10647,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -10253,31 +10761,39 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>13961486511</v>
+        <v>27922973022</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
       </c>
-      <c r="AF66" t="inlineStr">
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
-      <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AI66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ66" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10288,7 +10804,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -10402,31 +10918,39 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>13961486511</v>
+        <v>27922973022</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
       </c>
-      <c r="AF67" t="inlineStr">
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/doctorssearch/dr/maslovitz-sharon/</t>
         </is>
       </c>
-      <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AI67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ67" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10437,7 +10961,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -10551,31 +11075,39 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>13962017952</v>
+        <v>27924035904</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
       </c>
-      <c r="AF68" t="inlineStr">
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="inlineStr">
         <is>
           <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
-      <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AI68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ68" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10690,31 +11222,37 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
       </c>
-      <c r="AF69" t="inlineStr">
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
-      <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ69" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10829,31 +11367,37 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
       </c>
-      <c r="AF70" t="inlineStr">
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
-      <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ70" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10864,7 +11408,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10978,31 +11522,39 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>15110993394</v>
+        <v>30221986788</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
       </c>
-      <c r="AF71" t="inlineStr">
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="inlineStr">
         <is>
           <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
-      <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AI71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ71" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11013,7 +11565,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -11127,31 +11679,39 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>15110993394</v>
+        <v>30221986788</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
       </c>
-      <c r="AF72" t="inlineStr">
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="inlineStr">
         <is>
           <t>https://pain.coi.co.il/</t>
         </is>
       </c>
-      <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AI72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ72" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11162,7 +11722,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -11276,31 +11836,39 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
       </c>
-      <c r="AF73" t="inlineStr">
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="inlineStr">
         <is>
           <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
-      <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AI73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ73" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11311,7 +11879,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -11425,31 +11993,39 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>15109399071</v>
+        <v>30218798142</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
       </c>
-      <c r="AF74" t="inlineStr">
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="inlineStr">
         <is>
           <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
-      <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AI74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ74" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11460,7 +12036,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -11574,31 +12150,39 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>15110993394</v>
+        <v>30221986788</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
       </c>
-      <c r="AF75" t="inlineStr">
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="inlineStr">
         <is>
           <t>https://dinaeisen.com/about/</t>
         </is>
       </c>
-      <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AI75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ75" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11713,31 +12297,37 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
       </c>
-      <c r="AF76" t="inlineStr">
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="inlineStr">
         <is>
           <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
-      <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM76" t="inlineStr">
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ76" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11748,7 +12338,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11862,31 +12452,39 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
       </c>
-      <c r="AF77" t="inlineStr">
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="inlineStr">
         <is>
           <t>https://www.tau.ac.il/profile/shalevv</t>
         </is>
       </c>
-      <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM77" t="inlineStr">
+      <c r="AI77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ77" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12011,31 +12609,37 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>17563062168</v>
+        <v>35126124336</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
       </c>
-      <c r="AF78" t="inlineStr">
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="inlineStr">
         <is>
           <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
-      <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ78" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12046,7 +12650,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -12163,31 +12767,39 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>13991778648</v>
+        <v>27983557296</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
       </c>
-      <c r="AF79" t="inlineStr">
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/3175</t>
         </is>
       </c>
-      <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM79" t="inlineStr">
+      <c r="AI79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ79" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12198,7 +12810,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -12314,31 +12926,39 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
       </c>
-      <c r="AF80" t="inlineStr">
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
-      <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM80" t="inlineStr">
+      <c r="AI80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ80" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12349,7 +12969,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -12467,31 +13087,39 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
       </c>
-      <c r="AF81" t="inlineStr">
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
       </c>
-      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM81" t="inlineStr">
+      <c r="AI81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ81" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12502,7 +13130,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -12619,31 +13247,39 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>13962017952</v>
+        <v>27924035904</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
       </c>
-      <c r="AF82" t="inlineStr">
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/8119</t>
         </is>
       </c>
-      <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM82" t="inlineStr">
+      <c r="AI82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ82" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12654,7 +13290,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12771,31 +13407,39 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>13961486511</v>
+        <v>27922973022</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
       </c>
-      <c r="AF83" t="inlineStr">
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
       </c>
-      <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM83" t="inlineStr">
+      <c r="AI83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ83" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12806,7 +13450,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12924,31 +13568,39 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>13951920573</v>
+        <v>27903841146</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
       </c>
-      <c r="AF84" t="inlineStr">
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/6696</t>
         </is>
       </c>
-      <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM84" t="inlineStr">
+      <c r="AI84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ84" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12959,7 +13611,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -13076,31 +13728,39 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>13951920573</v>
+        <v>27903841146</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
       </c>
-      <c r="AF85" t="inlineStr">
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
       </c>
-      <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM85" t="inlineStr">
+      <c r="AI85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ85" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13111,7 +13771,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -13225,31 +13885,39 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>13951920573</v>
+        <v>27903841146</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
       </c>
-      <c r="AF86" t="inlineStr">
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="inlineStr">
         <is>
           <t>https://www.doctorlouria.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%A9%D7%95%D7%9C%D7%9E%D7%99%D7%AA-%D7%9C%D7%95%D7%A8%D7%99%D7%90</t>
         </is>
       </c>
-      <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM86" t="inlineStr">
+      <c r="AI86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ86" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13374,31 +14042,37 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>17433922005</v>
+        <v>34867844010</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
       </c>
-      <c r="AF87" t="inlineStr">
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="inlineStr">
         <is>
           <t>https://www.michalgilad.com/</t>
         </is>
       </c>
-      <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM87" t="inlineStr">
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ87" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13409,7 +14083,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -13523,31 +14197,39 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>13951920573</v>
+        <v>27903841146</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
       </c>
-      <c r="AF88" t="inlineStr">
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
-      <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AI88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ88" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13558,7 +14240,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -13672,31 +14354,39 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>13951920573</v>
+        <v>27903841146</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
       </c>
-      <c r="AF89" t="inlineStr">
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="inlineStr">
         <is>
           <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
-      <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM89" t="inlineStr">
+      <c r="AI89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ89" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13811,31 +14501,37 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
       </c>
-      <c r="AF90" t="inlineStr">
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="inlineStr">
         <is>
           <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
-      <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ90" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13950,31 +14646,37 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
       </c>
-      <c r="AF91" t="inlineStr">
+      <c r="AF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="inlineStr">
         <is>
           <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
-      <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ91" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13985,7 +14687,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -14101,31 +14803,39 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
       </c>
-      <c r="AF92" t="inlineStr">
+      <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
-      <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="n">
+      <c r="AI92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="n">
         <v>2</v>
       </c>
-      <c r="AJ92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM92" t="inlineStr">
+      <c r="AN92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ92" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14136,7 +14846,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -14254,31 +14964,39 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>13961486511</v>
+        <v>27922973022</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
       </c>
-      <c r="AF93" t="inlineStr">
+      <c r="AF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/964</t>
         </is>
       </c>
-      <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="n">
+      <c r="AI93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="n">
         <v>2</v>
       </c>
-      <c r="AJ93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM93" t="inlineStr">
+      <c r="AN93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO93" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP93" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ93" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14289,7 +15007,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -14407,31 +15125,39 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>13951920573</v>
+        <v>27903841146</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
       </c>
-      <c r="AF94" t="inlineStr">
+      <c r="AF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2622</t>
         </is>
       </c>
-      <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="n">
+      <c r="AI94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="n">
         <v>2</v>
       </c>
-      <c r="AJ94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM94" t="inlineStr">
+      <c r="AN94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO94" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP94" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ94" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14546,31 +15272,37 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
       </c>
-      <c r="AF95" t="inlineStr">
+      <c r="AF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
-      <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK95" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL95" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM95" t="inlineStr">
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ95" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14685,31 +15417,37 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
       </c>
-      <c r="AF96" t="inlineStr">
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
-      <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM96" t="inlineStr">
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ96" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14824,31 +15562,37 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
       </c>
-      <c r="AF97" t="inlineStr">
+      <c r="AF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
-      <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM97" t="inlineStr">
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ97" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14963,31 +15707,37 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
       </c>
-      <c r="AF98" t="inlineStr">
+      <c r="AF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
-      <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ98" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15102,31 +15852,37 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
       </c>
-      <c r="AF99" t="inlineStr">
+      <c r="AF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
-      <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO99" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP99" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ99" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15241,31 +15997,37 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
       </c>
-      <c r="AF100" t="inlineStr">
+      <c r="AF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
-      <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ100" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15380,31 +16142,37 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
       </c>
-      <c r="AF101" t="inlineStr">
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
-      <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP101" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ101" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15519,31 +16287,37 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
       </c>
-      <c r="AF102" t="inlineStr">
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
-      <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM102" t="inlineStr">
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO102" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP102" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ102" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15658,31 +16432,37 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
       </c>
-      <c r="AF103" t="inlineStr">
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
-      <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM103" t="inlineStr">
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO103" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP103" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ103" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15797,31 +16577,37 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
       </c>
-      <c r="AF104" t="inlineStr">
+      <c r="AF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
-      <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK104" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL104" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM104" t="inlineStr">
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO104" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP104" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ104" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15936,31 +16722,37 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
       </c>
-      <c r="AF105" t="inlineStr">
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
-      <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM105" t="inlineStr">
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ105" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16075,31 +16867,37 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>13947137604</v>
+        <v>27894275208</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
       </c>
-      <c r="AF106" t="inlineStr">
+      <c r="AF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
         </is>
       </c>
-      <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK106" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL106" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM106" t="inlineStr">
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO106" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP106" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ106" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16110,7 +16908,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -16227,31 +17025,39 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>15110993394</v>
+        <v>30221986788</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
       </c>
-      <c r="AF107" t="inlineStr">
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2435</t>
         </is>
       </c>
-      <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK107" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL107" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM107" t="inlineStr">
+      <c r="AI107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ107" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16262,7 +17068,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -16379,31 +17185,39 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>13990184325</v>
+        <v>27980368650</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
       </c>
-      <c r="AF108" t="inlineStr">
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5230</t>
         </is>
       </c>
-      <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK108" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL108" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM108" t="inlineStr">
+      <c r="AI108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ108" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16414,7 +17228,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -16532,31 +17346,39 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>15114182040</v>
+        <v>30228364080</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
       </c>
-      <c r="AF109" t="inlineStr">
+      <c r="AF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5287</t>
         </is>
       </c>
-      <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK109" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL109" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM109" t="inlineStr">
+      <c r="AI109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO109" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP109" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ109" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16567,7 +17389,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -16684,31 +17506,39 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>14336152416</v>
+        <v>28672304832</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
       </c>
-      <c r="AF110" t="inlineStr">
+      <c r="AF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/7026</t>
         </is>
       </c>
-      <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM110" t="inlineStr">
+      <c r="AI110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ110" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16719,7 +17549,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -16836,31 +17666,39 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>13961486511</v>
+        <v>27922973022</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
       </c>
-      <c r="AF111" t="inlineStr">
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2414</t>
         </is>
       </c>
-      <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK111" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL111" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM111" t="inlineStr">
+      <c r="AI111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr"/>
+      <c r="AK111" t="inlineStr"/>
+      <c r="AL111" t="inlineStr"/>
+      <c r="AM111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO111" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP111" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ111" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16871,7 +17709,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -16989,31 +17827,39 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>13962017952</v>
+        <v>27924035904</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
       </c>
-      <c r="AF112" t="inlineStr">
+      <c r="AF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2624</t>
         </is>
       </c>
-      <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM112" t="inlineStr">
+      <c r="AI112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ112" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17024,7 +17870,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -17142,31 +17988,39 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>13961486511</v>
+        <v>27922973022</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
       </c>
-      <c r="AF113" t="inlineStr">
+      <c r="AF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/5282</t>
         </is>
       </c>
-      <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK113" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL113" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM113" t="inlineStr">
+      <c r="AI113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO113" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP113" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ113" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17177,7 +18031,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -17294,31 +18148,39 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>13961486511</v>
+        <v>27922973022</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
       </c>
-      <c r="AF114" t="inlineStr">
+      <c r="AF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/2596</t>
         </is>
       </c>
-      <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK114" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL114" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM114" t="inlineStr">
+      <c r="AI114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ114" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17329,7 +18191,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -17446,31 +18308,39 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>13951920573</v>
+        <v>27903841146</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
       </c>
-      <c r="AF115" t="inlineStr">
+      <c r="AF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="inlineStr">
         <is>
           <t>https://medicine.biu.ac.il/node/525</t>
         </is>
       </c>
-      <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK115" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL115" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM115" t="inlineStr">
+      <c r="AI115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO115" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP115" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ115" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,217 +429,217 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>algo_version</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>physician_search_version</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>shared_target_count</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>unchanged_search_count</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_reason</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>search_fingerprint</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>resolution_reason</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>search_fingerprint</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>candidate_rank</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>shared_contact</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>send_eligible</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>personalization_safe</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -752,7 +764,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>37278460386</v>
+        <v>111835381158</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -766,11 +778,11 @@
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
         <v>1</v>
@@ -909,7 +921,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -923,11 +935,11 @@
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
         <v>1</v>
@@ -1066,7 +1078,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1080,11 +1092,11 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AK4" t="b">
+        <v>0</v>
+      </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
         <v>1</v>
@@ -1223,7 +1235,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1237,11 +1249,11 @@
         </is>
       </c>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AK5" t="b">
+        <v>0</v>
+      </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
         <v>1</v>
@@ -1380,7 +1392,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1394,11 +1406,11 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
         <v>1</v>
@@ -1537,7 +1549,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1551,11 +1563,11 @@
         </is>
       </c>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
         <v>1</v>
@@ -1697,7 +1709,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1711,11 +1723,11 @@
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
         <v>1</v>
@@ -1855,7 +1867,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1869,11 +1881,11 @@
         </is>
       </c>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+      <c r="AK9" t="b">
+        <v>0</v>
+      </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
         <v>1</v>
@@ -2012,7 +2024,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2026,11 +2038,11 @@
         </is>
       </c>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+      <c r="AK10" t="b">
+        <v>0</v>
+      </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
         <v>1</v>
@@ -2169,7 +2181,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2183,11 +2195,11 @@
         </is>
       </c>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+      <c r="AK11" t="b">
+        <v>0</v>
+      </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
         <v>1</v>
@@ -2326,7 +2338,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2340,11 +2352,11 @@
         </is>
       </c>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+      <c r="AK12" t="b">
+        <v>0</v>
+      </c>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="n">
         <v>1</v>
@@ -2483,7 +2495,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2497,11 +2509,11 @@
         </is>
       </c>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+      <c r="AK13" t="b">
+        <v>0</v>
+      </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="n">
         <v>1</v>
@@ -2640,7 +2652,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2654,11 +2666,11 @@
         </is>
       </c>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
+      <c r="AK14" t="b">
+        <v>0</v>
+      </c>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="n">
         <v>1</v>
@@ -2797,7 +2809,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2811,11 +2823,11 @@
         </is>
       </c>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AK15" t="b">
+        <v>0</v>
+      </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="n">
         <v>2</v>
@@ -2954,7 +2966,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>37288026324</v>
+        <v>111864078972</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2968,11 +2980,11 @@
         </is>
       </c>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AK16" t="b">
+        <v>0</v>
+      </c>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
         <v>1</v>
@@ -3111,7 +3123,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>30247495956</v>
+        <v>90742487868</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3125,11 +3137,11 @@
         </is>
       </c>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AK17" t="b">
+        <v>0</v>
+      </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
         <v>1</v>
@@ -3268,7 +3280,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>37291214970</v>
+        <v>111873644910</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3282,11 +3294,11 @@
         </is>
       </c>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+      <c r="AK18" t="b">
+        <v>0</v>
+      </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
         <v>1</v>
@@ -3425,7 +3437,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>30247495956</v>
+        <v>90742487868</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3439,11 +3451,11 @@
         </is>
       </c>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+      <c r="AK19" t="b">
+        <v>0</v>
+      </c>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="n">
         <v>1</v>
@@ -3582,7 +3594,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3596,11 +3608,11 @@
         </is>
       </c>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
+      <c r="AK20" t="b">
+        <v>0</v>
+      </c>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
         <v>1</v>
@@ -3739,7 +3751,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3753,11 +3765,11 @@
         </is>
       </c>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+      <c r="AK21" t="b">
+        <v>0</v>
+      </c>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="n">
         <v>1</v>
@@ -3896,7 +3908,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3910,11 +3922,11 @@
         </is>
       </c>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
+      <c r="AK22" t="b">
+        <v>0</v>
+      </c>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="n">
         <v>1</v>
@@ -4053,7 +4065,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4067,11 +4079,11 @@
         </is>
       </c>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
+      <c r="AK23" t="b">
+        <v>0</v>
+      </c>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="n">
         <v>2</v>
@@ -4210,7 +4222,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>30247495956</v>
+        <v>90742487868</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4224,11 +4236,11 @@
         </is>
       </c>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
+      <c r="AK24" t="b">
+        <v>0</v>
+      </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="n">
         <v>1</v>
@@ -4367,7 +4379,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4381,11 +4393,11 @@
         </is>
       </c>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
+      <c r="AK25" t="b">
+        <v>0</v>
+      </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="n">
         <v>1</v>
@@ -4524,7 +4536,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4538,11 +4550,11 @@
         </is>
       </c>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
+      <c r="AK26" t="b">
+        <v>0</v>
+      </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="n">
         <v>1</v>
@@ -4671,7 +4683,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4826,7 +4838,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4840,11 +4852,11 @@
         </is>
       </c>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
+      <c r="AK28" t="b">
+        <v>0</v>
+      </c>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="n">
         <v>1</v>
@@ -4983,7 +4995,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4997,11 +5009,11 @@
         </is>
       </c>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
+      <c r="AK29" t="b">
+        <v>0</v>
+      </c>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="n">
         <v>1</v>
@@ -5140,7 +5152,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5154,11 +5166,11 @@
         </is>
       </c>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
+      <c r="AK30" t="b">
+        <v>0</v>
+      </c>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="n">
         <v>1</v>
@@ -5287,7 +5299,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5442,7 +5454,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5456,11 +5468,11 @@
         </is>
       </c>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
+      <c r="AK32" t="b">
+        <v>0</v>
+      </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
         <v>1</v>
@@ -5599,7 +5611,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5613,11 +5625,11 @@
         </is>
       </c>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
+      <c r="AK33" t="b">
+        <v>0</v>
+      </c>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="n">
         <v>1</v>
@@ -5754,7 +5766,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5899,7 +5911,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6054,7 +6066,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6068,11 +6080,11 @@
         </is>
       </c>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
+      <c r="AK36" t="b">
+        <v>0</v>
+      </c>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="n">
         <v>1</v>
@@ -6209,7 +6221,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6364,7 +6376,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>27983915964</v>
+        <v>83951747892</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6378,11 +6390,11 @@
         </is>
       </c>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
+      <c r="AK38" t="b">
+        <v>0</v>
+      </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="n">
         <v>1</v>
@@ -6521,7 +6533,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6535,11 +6547,11 @@
         </is>
       </c>
       <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
+      <c r="AK39" t="b">
+        <v>0</v>
+      </c>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="n">
         <v>1</v>
@@ -6678,7 +6690,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6692,11 +6704,11 @@
         </is>
       </c>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
+      <c r="AK40" t="b">
+        <v>0</v>
+      </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="n">
         <v>1</v>
@@ -6840,7 +6852,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6854,11 +6866,11 @@
         </is>
       </c>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
+      <c r="AK41" t="b">
+        <v>0</v>
+      </c>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="n">
         <v>1</v>
@@ -6997,7 +7009,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7011,11 +7023,11 @@
         </is>
       </c>
       <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
+      <c r="AK42" t="b">
+        <v>0</v>
+      </c>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="n">
         <v>2</v>
@@ -7159,7 +7171,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7173,11 +7185,11 @@
         </is>
       </c>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
+      <c r="AK43" t="b">
+        <v>0</v>
+      </c>
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="n">
         <v>1</v>
@@ -7316,7 +7328,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>37278460386</v>
+        <v>111835381158</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7330,11 +7342,11 @@
         </is>
       </c>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
+      <c r="AK44" t="b">
+        <v>0</v>
+      </c>
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="n">
         <v>1</v>
@@ -7473,7 +7485,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7487,11 +7499,11 @@
         </is>
       </c>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
+      <c r="AK45" t="b">
+        <v>0</v>
+      </c>
       <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="n">
         <v>1</v>
@@ -7630,7 +7642,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7644,11 +7656,11 @@
         </is>
       </c>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
+      <c r="AK46" t="b">
+        <v>0</v>
+      </c>
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="n">
         <v>1</v>
@@ -7777,7 +7789,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7932,7 +7944,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7946,11 +7958,11 @@
         </is>
       </c>
       <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
+      <c r="AK48" t="b">
+        <v>0</v>
+      </c>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="n">
         <v>1</v>
@@ -8089,7 +8101,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8103,11 +8115,11 @@
         </is>
       </c>
       <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
+      <c r="AK49" t="b">
+        <v>0</v>
+      </c>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="n">
         <v>1</v>
@@ -8246,7 +8258,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8260,11 +8272,11 @@
         </is>
       </c>
       <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
+      <c r="AK50" t="b">
+        <v>0</v>
+      </c>
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="n">
         <v>1</v>
@@ -8403,7 +8415,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8417,11 +8429,11 @@
         </is>
       </c>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
+      <c r="AK51" t="b">
+        <v>0</v>
+      </c>
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="n">
         <v>1</v>
@@ -8560,7 +8572,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8574,11 +8586,11 @@
         </is>
       </c>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
+      <c r="AK52" t="b">
+        <v>0</v>
+      </c>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="n">
         <v>1</v>
@@ -8717,7 +8729,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>34900793352</v>
+        <v>104702380056</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8731,11 +8743,11 @@
         </is>
       </c>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
+      <c r="AK53" t="b">
+        <v>0</v>
+      </c>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="n">
         <v>1</v>
@@ -8874,7 +8886,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>37192366944</v>
+        <v>111577100832</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8888,11 +8900,11 @@
         </is>
       </c>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
+      <c r="AK54" t="b">
+        <v>0</v>
+      </c>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="n">
         <v>1</v>
@@ -9031,7 +9043,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9045,11 +9057,11 @@
         </is>
       </c>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
+      <c r="AK55" t="b">
+        <v>0</v>
+      </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="n">
         <v>1</v>
@@ -9188,7 +9200,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>41930694900</v>
+        <v>125792084700</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9202,11 +9214,11 @@
         </is>
       </c>
       <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
+      <c r="AK56" t="b">
+        <v>0</v>
+      </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="n">
         <v>1</v>
@@ -9345,7 +9357,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9359,11 +9371,11 @@
         </is>
       </c>
       <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
+      <c r="AK57" t="b">
+        <v>0</v>
+      </c>
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="n">
         <v>1</v>
@@ -9502,7 +9514,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9516,11 +9528,11 @@
         </is>
       </c>
       <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
+      <c r="AK58" t="b">
+        <v>0</v>
+      </c>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="n">
         <v>1</v>
@@ -9662,7 +9674,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9676,11 +9688,11 @@
         </is>
       </c>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
+      <c r="AK59" t="b">
+        <v>0</v>
+      </c>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="n">
         <v>1</v>
@@ -9819,7 +9831,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9833,11 +9845,11 @@
         </is>
       </c>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
+      <c r="AK60" t="b">
+        <v>0</v>
+      </c>
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="n">
         <v>1</v>
@@ -9976,7 +9988,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>27983557296</v>
+        <v>83950671888</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9990,11 +10002,11 @@
         </is>
       </c>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AK61" t="b">
+        <v>0</v>
+      </c>
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="n">
         <v>1</v>
@@ -10133,7 +10145,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>27983557296</v>
+        <v>83950671888</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10147,11 +10159,11 @@
         </is>
       </c>
       <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
+      <c r="AK62" t="b">
+        <v>0</v>
+      </c>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="n">
         <v>1</v>
@@ -10290,7 +10302,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10304,11 +10316,11 @@
         </is>
       </c>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
+      <c r="AK63" t="b">
+        <v>0</v>
+      </c>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="n">
         <v>1</v>
@@ -10447,7 +10459,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10461,11 +10473,11 @@
         </is>
       </c>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
+      <c r="AK64" t="b">
+        <v>0</v>
+      </c>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="n">
         <v>1</v>
@@ -10604,7 +10616,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10618,11 +10630,11 @@
         </is>
       </c>
       <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
+      <c r="AK65" t="b">
+        <v>0</v>
+      </c>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="n">
         <v>1</v>
@@ -10761,7 +10773,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10775,11 +10787,11 @@
         </is>
       </c>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
+      <c r="AK66" t="b">
+        <v>0</v>
+      </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="n">
         <v>1</v>
@@ -10918,7 +10930,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10932,11 +10944,11 @@
         </is>
       </c>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
+      <c r="AK67" t="b">
+        <v>0</v>
+      </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="n">
         <v>1</v>
@@ -11075,7 +11087,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11089,11 +11101,11 @@
         </is>
       </c>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI68" t="inlineStr"/>
       <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
+      <c r="AK68" t="b">
+        <v>0</v>
+      </c>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="n">
         <v>1</v>
@@ -11222,7 +11234,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11367,7 +11379,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11522,7 +11534,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11536,11 +11548,11 @@
         </is>
       </c>
       <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI71" t="inlineStr"/>
       <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
+      <c r="AK71" t="b">
+        <v>0</v>
+      </c>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="n">
         <v>1</v>
@@ -11679,7 +11691,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11693,11 +11705,11 @@
         </is>
       </c>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI72" t="inlineStr"/>
       <c r="AJ72" t="inlineStr"/>
-      <c r="AK72" t="inlineStr"/>
+      <c r="AK72" t="b">
+        <v>0</v>
+      </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="n">
         <v>1</v>
@@ -11836,7 +11848,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11850,11 +11862,11 @@
         </is>
       </c>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI73" t="inlineStr"/>
       <c r="AJ73" t="inlineStr"/>
-      <c r="AK73" t="inlineStr"/>
+      <c r="AK73" t="b">
+        <v>0</v>
+      </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="n">
         <v>1</v>
@@ -11993,7 +12005,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12007,11 +12019,11 @@
         </is>
       </c>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr"/>
-      <c r="AK74" t="inlineStr"/>
+      <c r="AK74" t="b">
+        <v>0</v>
+      </c>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="n">
         <v>1</v>
@@ -12150,7 +12162,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12164,11 +12176,11 @@
         </is>
       </c>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI75" t="inlineStr"/>
       <c r="AJ75" t="inlineStr"/>
-      <c r="AK75" t="inlineStr"/>
+      <c r="AK75" t="b">
+        <v>0</v>
+      </c>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="n">
         <v>1</v>
@@ -12297,7 +12309,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12452,7 +12464,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12466,11 +12478,11 @@
         </is>
       </c>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
+      <c r="AK77" t="b">
+        <v>0</v>
+      </c>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="n">
         <v>1</v>
@@ -12609,7 +12621,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>35126124336</v>
+        <v>105378373008</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12767,7 +12779,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>27983557296</v>
+        <v>83950671888</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12781,11 +12793,11 @@
         </is>
       </c>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr"/>
-      <c r="AK79" t="inlineStr"/>
+      <c r="AK79" t="b">
+        <v>0</v>
+      </c>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="n">
         <v>1</v>
@@ -12926,7 +12938,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12940,11 +12952,11 @@
         </is>
       </c>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
+      <c r="AK80" t="b">
+        <v>0</v>
+      </c>
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="n">
         <v>1</v>
@@ -13087,7 +13099,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13101,11 +13113,11 @@
         </is>
       </c>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
-      <c r="AK81" t="inlineStr"/>
+      <c r="AK81" t="b">
+        <v>0</v>
+      </c>
       <c r="AL81" t="inlineStr"/>
       <c r="AM81" t="n">
         <v>1</v>
@@ -13247,7 +13259,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13261,11 +13273,11 @@
         </is>
       </c>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
+      <c r="AK82" t="b">
+        <v>0</v>
+      </c>
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="n">
         <v>1</v>
@@ -13407,7 +13419,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13421,11 +13433,11 @@
         </is>
       </c>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
+      <c r="AK83" t="b">
+        <v>0</v>
+      </c>
       <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="n">
         <v>1</v>
@@ -13568,7 +13580,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13582,11 +13594,11 @@
         </is>
       </c>
       <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI84" t="inlineStr"/>
       <c r="AJ84" t="inlineStr"/>
-      <c r="AK84" t="inlineStr"/>
+      <c r="AK84" t="b">
+        <v>0</v>
+      </c>
       <c r="AL84" t="inlineStr"/>
       <c r="AM84" t="n">
         <v>1</v>
@@ -13728,7 +13740,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13742,11 +13754,11 @@
         </is>
       </c>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr"/>
-      <c r="AK85" t="inlineStr"/>
+      <c r="AK85" t="b">
+        <v>0</v>
+      </c>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="n">
         <v>1</v>
@@ -13885,7 +13897,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13899,11 +13911,11 @@
         </is>
       </c>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI86" t="inlineStr"/>
       <c r="AJ86" t="inlineStr"/>
-      <c r="AK86" t="inlineStr"/>
+      <c r="AK86" t="b">
+        <v>0</v>
+      </c>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="n">
         <v>1</v>
@@ -14042,7 +14054,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14197,7 +14209,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14211,11 +14223,11 @@
         </is>
       </c>
       <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI88" t="inlineStr"/>
       <c r="AJ88" t="inlineStr"/>
-      <c r="AK88" t="inlineStr"/>
+      <c r="AK88" t="b">
+        <v>0</v>
+      </c>
       <c r="AL88" t="inlineStr"/>
       <c r="AM88" t="n">
         <v>1</v>
@@ -14354,7 +14366,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14368,11 +14380,11 @@
         </is>
       </c>
       <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI89" t="inlineStr"/>
       <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
+      <c r="AK89" t="b">
+        <v>0</v>
+      </c>
       <c r="AL89" t="inlineStr"/>
       <c r="AM89" t="n">
         <v>1</v>
@@ -14501,7 +14513,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14646,7 +14658,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14803,7 +14815,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14817,11 +14829,11 @@
         </is>
       </c>
       <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI92" t="inlineStr"/>
       <c r="AJ92" t="inlineStr"/>
-      <c r="AK92" t="inlineStr"/>
+      <c r="AK92" t="b">
+        <v>0</v>
+      </c>
       <c r="AL92" t="inlineStr"/>
       <c r="AM92" t="n">
         <v>2</v>
@@ -14964,7 +14976,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14978,11 +14990,11 @@
         </is>
       </c>
       <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI93" t="inlineStr"/>
       <c r="AJ93" t="inlineStr"/>
-      <c r="AK93" t="inlineStr"/>
+      <c r="AK93" t="b">
+        <v>0</v>
+      </c>
       <c r="AL93" t="inlineStr"/>
       <c r="AM93" t="n">
         <v>2</v>
@@ -15125,7 +15137,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15139,11 +15151,11 @@
         </is>
       </c>
       <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI94" t="inlineStr"/>
       <c r="AJ94" t="inlineStr"/>
-      <c r="AK94" t="inlineStr"/>
+      <c r="AK94" t="b">
+        <v>0</v>
+      </c>
       <c r="AL94" t="inlineStr"/>
       <c r="AM94" t="n">
         <v>2</v>
@@ -15272,7 +15284,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15417,7 +15429,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15562,7 +15574,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15707,7 +15719,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15852,7 +15864,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15997,7 +16009,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16142,7 +16154,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16287,7 +16299,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16432,7 +16444,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16577,7 +16589,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16722,7 +16734,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16867,7 +16879,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -17025,7 +17037,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>30221986788</v>
+        <v>90665960364</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17039,11 +17051,11 @@
         </is>
       </c>
       <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI107" t="inlineStr"/>
       <c r="AJ107" t="inlineStr"/>
-      <c r="AK107" t="inlineStr"/>
+      <c r="AK107" t="b">
+        <v>0</v>
+      </c>
       <c r="AL107" t="inlineStr"/>
       <c r="AM107" t="n">
         <v>1</v>
@@ -17185,7 +17197,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17199,11 +17211,11 @@
         </is>
       </c>
       <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI108" t="inlineStr"/>
       <c r="AJ108" t="inlineStr"/>
-      <c r="AK108" t="inlineStr"/>
+      <c r="AK108" t="b">
+        <v>0</v>
+      </c>
       <c r="AL108" t="inlineStr"/>
       <c r="AM108" t="n">
         <v>1</v>
@@ -17346,7 +17358,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>30228364080</v>
+        <v>90685092240</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17360,11 +17372,11 @@
         </is>
       </c>
       <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI109" t="inlineStr"/>
       <c r="AJ109" t="inlineStr"/>
-      <c r="AK109" t="inlineStr"/>
+      <c r="AK109" t="b">
+        <v>0</v>
+      </c>
       <c r="AL109" t="inlineStr"/>
       <c r="AM109" t="n">
         <v>1</v>
@@ -17506,7 +17518,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>28672304832</v>
+        <v>86016914496</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17520,11 +17532,11 @@
         </is>
       </c>
       <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI110" t="inlineStr"/>
       <c r="AJ110" t="inlineStr"/>
-      <c r="AK110" t="inlineStr"/>
+      <c r="AK110" t="b">
+        <v>0</v>
+      </c>
       <c r="AL110" t="inlineStr"/>
       <c r="AM110" t="n">
         <v>1</v>
@@ -17666,7 +17678,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17680,11 +17692,11 @@
         </is>
       </c>
       <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI111" t="inlineStr"/>
       <c r="AJ111" t="inlineStr"/>
-      <c r="AK111" t="inlineStr"/>
+      <c r="AK111" t="b">
+        <v>0</v>
+      </c>
       <c r="AL111" t="inlineStr"/>
       <c r="AM111" t="n">
         <v>1</v>
@@ -17827,7 +17839,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>27924035904</v>
+        <v>83772107712</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17841,11 +17853,11 @@
         </is>
       </c>
       <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI112" t="inlineStr"/>
       <c r="AJ112" t="inlineStr"/>
-      <c r="AK112" t="inlineStr"/>
+      <c r="AK112" t="b">
+        <v>0</v>
+      </c>
       <c r="AL112" t="inlineStr"/>
       <c r="AM112" t="n">
         <v>1</v>
@@ -17988,7 +18000,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18002,11 +18014,11 @@
         </is>
       </c>
       <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI113" t="inlineStr"/>
       <c r="AJ113" t="inlineStr"/>
-      <c r="AK113" t="inlineStr"/>
+      <c r="AK113" t="b">
+        <v>0</v>
+      </c>
       <c r="AL113" t="inlineStr"/>
       <c r="AM113" t="n">
         <v>1</v>
@@ -18148,7 +18160,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>27922973022</v>
+        <v>83768919066</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18162,11 +18174,11 @@
         </is>
       </c>
       <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI114" t="inlineStr"/>
       <c r="AJ114" t="inlineStr"/>
-      <c r="AK114" t="inlineStr"/>
+      <c r="AK114" t="b">
+        <v>0</v>
+      </c>
       <c r="AL114" t="inlineStr"/>
       <c r="AM114" t="n">
         <v>1</v>
@@ -18308,7 +18320,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>27903841146</v>
+        <v>83711523438</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18322,11 +18334,11 @@
         </is>
       </c>
       <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI115" t="inlineStr"/>
       <c r="AJ115" t="inlineStr"/>
-      <c r="AK115" t="inlineStr"/>
+      <c r="AK115" t="b">
+        <v>0</v>
+      </c>
       <c r="AL115" t="inlineStr"/>
       <c r="AM115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>111835381158</v>
+        <v>335506143474</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>111864078972</v>
+        <v>335592236916</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>90742487868</v>
+        <v>272227463604</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>111873644910</v>
+        <v>335620934730</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>90742487868</v>
+        <v>272227463604</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>90742487868</v>
+        <v>272227463604</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>83951747892</v>
+        <v>251855243676</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>111835381158</v>
+        <v>335506143474</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>104702380056</v>
+        <v>314107140168</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>111577100832</v>
+        <v>334731302496</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>125792084700</v>
+        <v>377376254100</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>83950671888</v>
+        <v>251852015664</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>83950671888</v>
+        <v>251852015664</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10616,7 +10616,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11379,7 +11379,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11534,7 +11534,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12162,7 +12162,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>105378373008</v>
+        <v>316135119024</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12779,7 +12779,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>83950671888</v>
+        <v>251852015664</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13580,7 +13580,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13740,7 +13740,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14815,7 +14815,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14976,7 +14976,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15284,7 +15284,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16154,7 +16154,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16299,7 +16299,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16879,7 +16879,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -17037,7 +17037,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>90665960364</v>
+        <v>271997881092</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17358,7 +17358,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>90685092240</v>
+        <v>272055276720</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17518,7 +17518,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>86016914496</v>
+        <v>258050743488</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17839,7 +17839,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>83772107712</v>
+        <v>251316323136</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18000,7 +18000,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18160,7 +18160,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>83768919066</v>
+        <v>251306757198</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>83711523438</v>
+        <v>251134570314</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>335506143474</v>
+        <v>1006518430422</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>335592236916</v>
+        <v>1006776710748</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>272227463604</v>
+        <v>816682390812</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>335620934730</v>
+        <v>1006862804190</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>272227463604</v>
+        <v>816682390812</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>272227463604</v>
+        <v>816682390812</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>251855243676</v>
+        <v>755565731028</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>335506143474</v>
+        <v>1006518430422</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>314107140168</v>
+        <v>942321420504</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>334731302496</v>
+        <v>1004193907488</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>377376254100</v>
+        <v>1132128762300</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>251852015664</v>
+        <v>755556046992</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>251852015664</v>
+        <v>755556046992</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10616,7 +10616,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11379,7 +11379,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11534,7 +11534,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12005,7 +12005,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12162,7 +12162,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>316135119024</v>
+        <v>948405357072</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12779,7 +12779,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>251852015664</v>
+        <v>755556046992</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13580,7 +13580,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13740,7 +13740,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14815,7 +14815,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14976,7 +14976,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15137,7 +15137,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15284,7 +15284,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16154,7 +16154,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16299,7 +16299,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16879,7 +16879,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -17037,7 +17037,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>271997881092</v>
+        <v>815993643276</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17358,7 +17358,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>272055276720</v>
+        <v>816165830160</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17518,7 +17518,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>258050743488</v>
+        <v>774152230464</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17839,7 +17839,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>251316323136</v>
+        <v>753948969408</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -18000,7 +18000,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18160,7 +18160,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>251306757198</v>
+        <v>753920271594</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>251134570314</v>
+        <v>753403710942</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ115"/>
+  <dimension ref="A1:AP115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,30 +616,25 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>previous_candidate</t>
+          <t>candidate_rank</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>candidate_rank</t>
+          <t>shared_contact</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>shared_contact</t>
+          <t>send_eligible</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>send_eligible</t>
+          <t>personalization_safe</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>personalization_safe</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -764,7 +759,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1006518430422</v>
+        <v>3019555291266</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -783,20 +778,19 @@
       <c r="AK2" t="b">
         <v>0</v>
       </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>1</v>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>0</v>
       </c>
       <c r="AN2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="b">
         <v>1</v>
       </c>
-      <c r="AP2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -921,7 +915,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -940,20 +934,19 @@
       <c r="AK3" t="b">
         <v>0</v>
       </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>1</v>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="b">
+        <v>0</v>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="b">
         <v>1</v>
       </c>
-      <c r="AP3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1078,7 +1071,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1097,20 +1090,19 @@
       <c r="AK4" t="b">
         <v>0</v>
       </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>1</v>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="b">
+        <v>0</v>
       </c>
       <c r="AN4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="b">
         <v>1</v>
       </c>
-      <c r="AP4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1235,7 +1227,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1254,20 +1246,19 @@
       <c r="AK5" t="b">
         <v>0</v>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>1</v>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="b">
+        <v>0</v>
       </c>
       <c r="AN5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="b">
         <v>1</v>
       </c>
-      <c r="AP5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1392,7 +1383,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1411,20 +1402,19 @@
       <c r="AK6" t="b">
         <v>0</v>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>1</v>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
       </c>
       <c r="AN6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="b">
         <v>1</v>
       </c>
-      <c r="AP6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1549,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1568,20 +1558,19 @@
       <c r="AK7" t="b">
         <v>0</v>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>1</v>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="b">
+        <v>0</v>
       </c>
       <c r="AN7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="b">
         <v>1</v>
       </c>
-      <c r="AP7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1709,7 +1698,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1728,20 +1717,19 @@
       <c r="AK8" t="b">
         <v>0</v>
       </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>1</v>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
       </c>
       <c r="AN8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="b">
         <v>1</v>
       </c>
-      <c r="AP8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1867,7 +1855,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1886,20 +1874,19 @@
       <c r="AK9" t="b">
         <v>0</v>
       </c>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>1</v>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="b">
+        <v>0</v>
       </c>
       <c r="AN9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="b">
         <v>1</v>
       </c>
-      <c r="AP9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2024,7 +2011,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1004193907488</v>
+        <v>3012581722464</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2043,20 +2030,19 @@
       <c r="AK10" t="b">
         <v>0</v>
       </c>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="n">
-        <v>1</v>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="b">
         <v>1</v>
       </c>
-      <c r="AP10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2181,7 +2167,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1004193907488</v>
+        <v>3012581722464</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2200,20 +2186,19 @@
       <c r="AK11" t="b">
         <v>0</v>
       </c>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="n">
-        <v>1</v>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="b">
+        <v>0</v>
       </c>
       <c r="AN11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="b">
         <v>1</v>
       </c>
-      <c r="AP11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2338,7 +2323,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1004193907488</v>
+        <v>3012581722464</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2357,20 +2342,19 @@
       <c r="AK12" t="b">
         <v>0</v>
       </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="n">
-        <v>1</v>
+      <c r="AL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="b">
+        <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="b">
         <v>1</v>
       </c>
-      <c r="AP12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2495,7 +2479,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>942206629248</v>
+        <v>2826619887744</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2514,20 +2498,19 @@
       <c r="AK13" t="b">
         <v>0</v>
       </c>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="n">
-        <v>1</v>
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="b">
+        <v>0</v>
       </c>
       <c r="AN13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13" t="b">
         <v>1</v>
       </c>
-      <c r="AP13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2652,7 +2635,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1004193907488</v>
+        <v>3012581722464</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2671,20 +2654,19 @@
       <c r="AK14" t="b">
         <v>0</v>
       </c>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="n">
-        <v>1</v>
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="b">
+        <v>0</v>
       </c>
       <c r="AN14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="b">
         <v>1</v>
       </c>
-      <c r="AP14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2809,7 +2791,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1004193907488</v>
+        <v>3012581722464</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2828,20 +2810,19 @@
       <c r="AK15" t="b">
         <v>0</v>
       </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="n">
+      <c r="AL15" t="n">
         <v>2</v>
       </c>
+      <c r="AM15" t="b">
+        <v>0</v>
+      </c>
       <c r="AN15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15" t="b">
         <v>1</v>
       </c>
-      <c r="AP15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="AP15" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2966,7 +2947,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1006776710748</v>
+        <v>3020330132244</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2985,20 +2966,19 @@
       <c r="AK16" t="b">
         <v>0</v>
       </c>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="n">
-        <v>1</v>
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="b">
+        <v>0</v>
       </c>
       <c r="AN16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="b">
         <v>1</v>
       </c>
-      <c r="AP16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="AP16" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3123,7 +3103,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>816682390812</v>
+        <v>2450047172436</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3142,20 +3122,19 @@
       <c r="AK17" t="b">
         <v>0</v>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="n">
-        <v>1</v>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="b">
+        <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="b">
         <v>1</v>
       </c>
-      <c r="AP17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="AP17" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3280,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1006862804190</v>
+        <v>3020588412570</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3299,20 +3278,19 @@
       <c r="AK18" t="b">
         <v>0</v>
       </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="n">
-        <v>1</v>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="b">
+        <v>0</v>
       </c>
       <c r="AN18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="b">
         <v>1</v>
       </c>
-      <c r="AP18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3437,7 +3415,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>816682390812</v>
+        <v>2450047172436</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3456,20 +3434,19 @@
       <c r="AK19" t="b">
         <v>0</v>
       </c>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="n">
-        <v>1</v>
+      <c r="AL19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM19" t="b">
+        <v>0</v>
       </c>
       <c r="AN19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO19" t="b">
         <v>1</v>
       </c>
-      <c r="AP19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ19" t="inlineStr">
+      <c r="AP19" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3594,7 +3571,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1004193907488</v>
+        <v>3012581722464</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3613,20 +3590,19 @@
       <c r="AK20" t="b">
         <v>0</v>
       </c>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="n">
-        <v>1</v>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="b">
+        <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="b">
         <v>1</v>
       </c>
-      <c r="AP20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ20" t="inlineStr">
+      <c r="AP20" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3751,7 +3727,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3770,20 +3746,19 @@
       <c r="AK21" t="b">
         <v>0</v>
       </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="n">
-        <v>1</v>
+      <c r="AL21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM21" t="b">
+        <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="b">
         <v>1</v>
       </c>
-      <c r="AP21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ21" t="inlineStr">
+      <c r="AP21" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3908,7 +3883,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3927,20 +3902,19 @@
       <c r="AK22" t="b">
         <v>0</v>
       </c>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="n">
-        <v>1</v>
+      <c r="AL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM22" t="b">
+        <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="b">
         <v>1</v>
       </c>
-      <c r="AP22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ22" t="inlineStr">
+      <c r="AP22" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4065,7 +4039,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4084,20 +4058,19 @@
       <c r="AK23" t="b">
         <v>0</v>
       </c>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="n">
+      <c r="AL23" t="n">
         <v>2</v>
       </c>
+      <c r="AM23" t="b">
+        <v>0</v>
+      </c>
       <c r="AN23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO23" t="b">
         <v>1</v>
       </c>
-      <c r="AP23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AP23" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4222,7 +4195,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>816682390812</v>
+        <v>2450047172436</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4241,20 +4214,19 @@
       <c r="AK24" t="b">
         <v>0</v>
       </c>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="n">
-        <v>1</v>
+      <c r="AL24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM24" t="b">
+        <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="b">
         <v>1</v>
       </c>
-      <c r="AP24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4379,7 +4351,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4398,20 +4370,19 @@
       <c r="AK25" t="b">
         <v>0</v>
       </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="n">
-        <v>1</v>
+      <c r="AL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" t="b">
+        <v>0</v>
       </c>
       <c r="AN25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO25" t="b">
         <v>1</v>
       </c>
-      <c r="AP25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4536,7 +4507,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4555,20 +4526,19 @@
       <c r="AK26" t="b">
         <v>0</v>
       </c>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="n">
-        <v>1</v>
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="b">
+        <v>0</v>
       </c>
       <c r="AN26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="b">
         <v>1</v>
       </c>
-      <c r="AP26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ26" t="inlineStr">
+      <c r="AP26" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4683,7 +4653,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4700,20 +4670,19 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="n">
-        <v>1</v>
+      <c r="AL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM27" t="b">
+        <v>0</v>
       </c>
       <c r="AN27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="b">
         <v>1</v>
       </c>
-      <c r="AP27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ27" t="inlineStr">
+      <c r="AP27" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4838,7 +4807,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4857,20 +4826,19 @@
       <c r="AK28" t="b">
         <v>0</v>
       </c>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="n">
-        <v>1</v>
+      <c r="AL28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM28" t="b">
+        <v>0</v>
       </c>
       <c r="AN28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="b">
         <v>1</v>
       </c>
-      <c r="AP28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ28" t="inlineStr">
+      <c r="AP28" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4995,7 +4963,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5014,20 +4982,19 @@
       <c r="AK29" t="b">
         <v>0</v>
       </c>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="n">
-        <v>1</v>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="b">
+        <v>0</v>
       </c>
       <c r="AN29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO29" t="b">
         <v>1</v>
       </c>
-      <c r="AP29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ29" t="inlineStr">
+      <c r="AP29" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5152,7 +5119,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5171,20 +5138,19 @@
       <c r="AK30" t="b">
         <v>0</v>
       </c>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="n">
-        <v>1</v>
+      <c r="AL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM30" t="b">
+        <v>0</v>
       </c>
       <c r="AN30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO30" t="b">
         <v>1</v>
       </c>
-      <c r="AP30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ30" t="inlineStr">
+      <c r="AP30" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5299,7 +5265,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5316,20 +5282,19 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="n">
-        <v>1</v>
+      <c r="AL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM31" t="b">
+        <v>0</v>
       </c>
       <c r="AN31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="b">
         <v>1</v>
       </c>
-      <c r="AP31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ31" t="inlineStr">
+      <c r="AP31" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5454,7 +5419,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5473,20 +5438,19 @@
       <c r="AK32" t="b">
         <v>0</v>
       </c>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="n">
-        <v>1</v>
+      <c r="AL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" t="b">
+        <v>0</v>
       </c>
       <c r="AN32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO32" t="b">
         <v>1</v>
       </c>
-      <c r="AP32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ32" t="inlineStr">
+      <c r="AP32" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5611,7 +5575,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>774324417348</v>
+        <v>2322973252044</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5630,20 +5594,19 @@
       <c r="AK33" t="b">
         <v>0</v>
       </c>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="n">
-        <v>1</v>
+      <c r="AL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" t="b">
+        <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" t="b">
         <v>1</v>
       </c>
-      <c r="AP33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ33" t="inlineStr">
+      <c r="AP33" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5766,7 +5729,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5783,20 +5746,19 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="n">
-        <v>1</v>
+      <c r="AL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="b">
+        <v>0</v>
       </c>
       <c r="AN34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO34" t="b">
         <v>1</v>
       </c>
-      <c r="AP34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ34" t="inlineStr">
+      <c r="AP34" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5911,7 +5873,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5928,20 +5890,19 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="n">
-        <v>1</v>
+      <c r="AL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" t="b">
+        <v>0</v>
       </c>
       <c r="AN35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="b">
         <v>1</v>
       </c>
-      <c r="AP35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ35" t="inlineStr">
+      <c r="AP35" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6066,7 +6027,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6085,20 +6046,19 @@
       <c r="AK36" t="b">
         <v>0</v>
       </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="n">
-        <v>1</v>
+      <c r="AL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM36" t="b">
+        <v>0</v>
       </c>
       <c r="AN36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO36" t="b">
         <v>1</v>
       </c>
-      <c r="AP36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ36" t="inlineStr">
+      <c r="AP36" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6221,7 +6181,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6238,20 +6198,19 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="n">
-        <v>1</v>
+      <c r="AL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM37" t="b">
+        <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO37" t="b">
         <v>1</v>
       </c>
-      <c r="AP37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="inlineStr">
+      <c r="AP37" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6376,7 +6335,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>755565731028</v>
+        <v>2266697193084</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6395,20 +6354,19 @@
       <c r="AK38" t="b">
         <v>0</v>
       </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="n">
-        <v>1</v>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="b">
+        <v>0</v>
       </c>
       <c r="AN38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38" t="b">
         <v>1</v>
       </c>
-      <c r="AP38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ38" t="inlineStr">
+      <c r="AP38" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6533,7 +6491,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6552,20 +6510,19 @@
       <c r="AK39" t="b">
         <v>0</v>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="n">
-        <v>1</v>
+      <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="b">
+        <v>0</v>
       </c>
       <c r="AN39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO39" t="b">
         <v>1</v>
       </c>
-      <c r="AP39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ39" t="inlineStr">
+      <c r="AP39" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6690,7 +6647,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6709,20 +6666,19 @@
       <c r="AK40" t="b">
         <v>0</v>
       </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="n">
-        <v>1</v>
+      <c r="AL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="b">
+        <v>0</v>
       </c>
       <c r="AN40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO40" t="b">
         <v>1</v>
       </c>
-      <c r="AP40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ40" t="inlineStr">
+      <c r="AP40" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6852,7 +6808,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6871,20 +6827,19 @@
       <c r="AK41" t="b">
         <v>0</v>
       </c>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="n">
-        <v>1</v>
+      <c r="AL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM41" t="b">
+        <v>0</v>
       </c>
       <c r="AN41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO41" t="b">
         <v>1</v>
       </c>
-      <c r="AP41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ41" t="inlineStr">
+      <c r="AP41" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7009,7 +6964,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7028,20 +6983,19 @@
       <c r="AK42" t="b">
         <v>0</v>
       </c>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="n">
+      <c r="AL42" t="n">
         <v>2</v>
       </c>
+      <c r="AM42" t="b">
+        <v>0</v>
+      </c>
       <c r="AN42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO42" t="b">
         <v>1</v>
       </c>
-      <c r="AP42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ42" t="inlineStr">
+      <c r="AP42" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7171,7 +7125,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7190,20 +7144,19 @@
       <c r="AK43" t="b">
         <v>0</v>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="n">
-        <v>1</v>
+      <c r="AL43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM43" t="b">
+        <v>0</v>
       </c>
       <c r="AN43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO43" t="b">
         <v>1</v>
       </c>
-      <c r="AP43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ43" t="inlineStr">
+      <c r="AP43" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7328,7 +7281,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1006518430422</v>
+        <v>3019555291266</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7347,20 +7300,19 @@
       <c r="AK44" t="b">
         <v>0</v>
       </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="n">
-        <v>1</v>
+      <c r="AL44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM44" t="b">
+        <v>0</v>
       </c>
       <c r="AN44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO44" t="b">
         <v>1</v>
       </c>
-      <c r="AP44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ44" t="inlineStr">
+      <c r="AP44" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7485,7 +7437,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7504,20 +7456,19 @@
       <c r="AK45" t="b">
         <v>0</v>
       </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="n">
-        <v>1</v>
+      <c r="AL45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM45" t="b">
+        <v>0</v>
       </c>
       <c r="AN45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO45" t="b">
         <v>1</v>
       </c>
-      <c r="AP45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ45" t="inlineStr">
+      <c r="AP45" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7642,7 +7593,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7661,20 +7612,19 @@
       <c r="AK46" t="b">
         <v>0</v>
       </c>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="n">
-        <v>1</v>
+      <c r="AL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM46" t="b">
+        <v>0</v>
       </c>
       <c r="AN46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO46" t="b">
         <v>1</v>
       </c>
-      <c r="AP46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ46" t="inlineStr">
+      <c r="AP46" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7789,7 +7739,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7806,20 +7756,19 @@
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="n">
-        <v>1</v>
+      <c r="AL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="b">
+        <v>0</v>
       </c>
       <c r="AN47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO47" t="b">
         <v>1</v>
       </c>
-      <c r="AP47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ47" t="inlineStr">
+      <c r="AP47" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7944,7 +7893,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7963,20 +7912,19 @@
       <c r="AK48" t="b">
         <v>0</v>
       </c>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="n">
-        <v>1</v>
+      <c r="AL48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM48" t="b">
+        <v>0</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO48" t="b">
         <v>1</v>
       </c>
-      <c r="AP48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ48" t="inlineStr">
+      <c r="AP48" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8101,7 +8049,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8120,20 +8068,19 @@
       <c r="AK49" t="b">
         <v>0</v>
       </c>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="n">
-        <v>1</v>
+      <c r="AL49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM49" t="b">
+        <v>0</v>
       </c>
       <c r="AN49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO49" t="b">
         <v>1</v>
       </c>
-      <c r="AP49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ49" t="inlineStr">
+      <c r="AP49" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8258,7 +8205,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8277,20 +8224,19 @@
       <c r="AK50" t="b">
         <v>0</v>
       </c>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="n">
-        <v>1</v>
+      <c r="AL50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM50" t="b">
+        <v>0</v>
       </c>
       <c r="AN50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO50" t="b">
         <v>1</v>
       </c>
-      <c r="AP50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ50" t="inlineStr">
+      <c r="AP50" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8415,7 +8361,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8434,20 +8380,19 @@
       <c r="AK51" t="b">
         <v>0</v>
       </c>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="n">
-        <v>1</v>
+      <c r="AL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM51" t="b">
+        <v>0</v>
       </c>
       <c r="AN51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO51" t="b">
         <v>1</v>
       </c>
-      <c r="AP51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ51" t="inlineStr">
+      <c r="AP51" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8572,7 +8517,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8591,20 +8536,19 @@
       <c r="AK52" t="b">
         <v>0</v>
       </c>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="n">
-        <v>1</v>
+      <c r="AL52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM52" t="b">
+        <v>0</v>
       </c>
       <c r="AN52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO52" t="b">
         <v>1</v>
       </c>
-      <c r="AP52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ52" t="inlineStr">
+      <c r="AP52" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8729,7 +8673,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>942321420504</v>
+        <v>2826964261512</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8748,20 +8692,19 @@
       <c r="AK53" t="b">
         <v>0</v>
       </c>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="n">
-        <v>1</v>
+      <c r="AL53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM53" t="b">
+        <v>0</v>
       </c>
       <c r="AN53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO53" t="b">
         <v>1</v>
       </c>
-      <c r="AP53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ53" t="inlineStr">
+      <c r="AP53" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8886,7 +8829,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1004193907488</v>
+        <v>3012581722464</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8905,20 +8848,19 @@
       <c r="AK54" t="b">
         <v>0</v>
       </c>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="n">
-        <v>1</v>
+      <c r="AL54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM54" t="b">
+        <v>0</v>
       </c>
       <c r="AN54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO54" t="b">
         <v>1</v>
       </c>
-      <c r="AP54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ54" t="inlineStr">
+      <c r="AP54" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9043,7 +8985,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9062,20 +9004,19 @@
       <c r="AK55" t="b">
         <v>0</v>
       </c>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="n">
-        <v>1</v>
+      <c r="AL55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM55" t="b">
+        <v>0</v>
       </c>
       <c r="AN55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO55" t="b">
         <v>1</v>
       </c>
-      <c r="AP55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ55" t="inlineStr">
+      <c r="AP55" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9200,7 +9141,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1132128762300</v>
+        <v>3396386286900</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9219,20 +9160,19 @@
       <c r="AK56" t="b">
         <v>0</v>
       </c>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="n">
-        <v>1</v>
+      <c r="AL56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM56" t="b">
+        <v>0</v>
       </c>
       <c r="AN56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO56" t="b">
         <v>1</v>
       </c>
-      <c r="AP56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ56" t="inlineStr">
+      <c r="AP56" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9357,7 +9297,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>774324417348</v>
+        <v>2322973252044</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9376,20 +9316,19 @@
       <c r="AK57" t="b">
         <v>0</v>
       </c>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="n">
-        <v>1</v>
+      <c r="AL57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM57" t="b">
+        <v>0</v>
       </c>
       <c r="AN57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO57" t="b">
         <v>1</v>
       </c>
-      <c r="AP57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ57" t="inlineStr">
+      <c r="AP57" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9514,7 +9453,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>774324417348</v>
+        <v>2322973252044</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9533,20 +9472,19 @@
       <c r="AK58" t="b">
         <v>0</v>
       </c>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="n">
-        <v>1</v>
+      <c r="AL58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM58" t="b">
+        <v>0</v>
       </c>
       <c r="AN58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO58" t="b">
         <v>1</v>
       </c>
-      <c r="AP58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ58" t="inlineStr">
+      <c r="AP58" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9674,7 +9612,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>774324417348</v>
+        <v>2322973252044</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9693,20 +9631,19 @@
       <c r="AK59" t="b">
         <v>0</v>
       </c>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="n">
-        <v>1</v>
+      <c r="AL59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM59" t="b">
+        <v>0</v>
       </c>
       <c r="AN59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO59" t="b">
         <v>1</v>
       </c>
-      <c r="AP59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ59" t="inlineStr">
+      <c r="AP59" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9831,7 +9768,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>774324417348</v>
+        <v>2322973252044</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9850,20 +9787,19 @@
       <c r="AK60" t="b">
         <v>0</v>
       </c>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="n">
-        <v>1</v>
+      <c r="AL60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM60" t="b">
+        <v>0</v>
       </c>
       <c r="AN60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO60" t="b">
         <v>1</v>
       </c>
-      <c r="AP60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ60" t="inlineStr">
+      <c r="AP60" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9988,7 +9924,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>755556046992</v>
+        <v>2266668140976</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10007,20 +9943,19 @@
       <c r="AK61" t="b">
         <v>0</v>
       </c>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="n">
-        <v>1</v>
+      <c r="AL61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM61" t="b">
+        <v>0</v>
       </c>
       <c r="AN61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO61" t="b">
         <v>1</v>
       </c>
-      <c r="AP61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ61" t="inlineStr">
+      <c r="AP61" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10145,7 +10080,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>755556046992</v>
+        <v>2266668140976</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10164,20 +10099,19 @@
       <c r="AK62" t="b">
         <v>0</v>
       </c>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="n">
-        <v>1</v>
+      <c r="AL62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM62" t="b">
+        <v>0</v>
       </c>
       <c r="AN62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO62" t="b">
         <v>1</v>
       </c>
-      <c r="AP62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ62" t="inlineStr">
+      <c r="AP62" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10302,7 +10236,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10321,20 +10255,19 @@
       <c r="AK63" t="b">
         <v>0</v>
       </c>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="n">
-        <v>1</v>
+      <c r="AL63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM63" t="b">
+        <v>0</v>
       </c>
       <c r="AN63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO63" t="b">
         <v>1</v>
       </c>
-      <c r="AP63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ63" t="inlineStr">
+      <c r="AP63" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10459,7 +10392,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10478,20 +10411,19 @@
       <c r="AK64" t="b">
         <v>0</v>
       </c>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="n">
-        <v>1</v>
+      <c r="AL64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM64" t="b">
+        <v>0</v>
       </c>
       <c r="AN64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO64" t="b">
         <v>1</v>
       </c>
-      <c r="AP64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ64" t="inlineStr">
+      <c r="AP64" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10616,7 +10548,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10635,20 +10567,19 @@
       <c r="AK65" t="b">
         <v>0</v>
       </c>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="n">
-        <v>1</v>
+      <c r="AL65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM65" t="b">
+        <v>0</v>
       </c>
       <c r="AN65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO65" t="b">
         <v>1</v>
       </c>
-      <c r="AP65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ65" t="inlineStr">
+      <c r="AP65" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10773,7 +10704,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>753920271594</v>
+        <v>2261760814782</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10792,20 +10723,19 @@
       <c r="AK66" t="b">
         <v>0</v>
       </c>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="n">
-        <v>1</v>
+      <c r="AL66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM66" t="b">
+        <v>0</v>
       </c>
       <c r="AN66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO66" t="b">
         <v>1</v>
       </c>
-      <c r="AP66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ66" t="inlineStr">
+      <c r="AP66" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10930,7 +10860,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>753920271594</v>
+        <v>2261760814782</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10949,20 +10879,19 @@
       <c r="AK67" t="b">
         <v>0</v>
       </c>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="n">
-        <v>1</v>
+      <c r="AL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM67" t="b">
+        <v>0</v>
       </c>
       <c r="AN67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO67" t="b">
         <v>1</v>
       </c>
-      <c r="AP67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ67" t="inlineStr">
+      <c r="AP67" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11087,7 +11016,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>753948969408</v>
+        <v>2261846908224</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11106,20 +11035,19 @@
       <c r="AK68" t="b">
         <v>0</v>
       </c>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="n">
-        <v>1</v>
+      <c r="AL68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM68" t="b">
+        <v>0</v>
       </c>
       <c r="AN68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO68" t="b">
         <v>1</v>
       </c>
-      <c r="AP68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ68" t="inlineStr">
+      <c r="AP68" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11234,7 +11162,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11251,20 +11179,19 @@
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="n">
-        <v>1</v>
+      <c r="AL69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM69" t="b">
+        <v>0</v>
       </c>
       <c r="AN69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO69" t="b">
         <v>1</v>
       </c>
-      <c r="AP69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ69" t="inlineStr">
+      <c r="AP69" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11379,7 +11306,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11396,20 +11323,19 @@
       <c r="AI70" t="inlineStr"/>
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="n">
-        <v>1</v>
+      <c r="AL70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM70" t="b">
+        <v>0</v>
       </c>
       <c r="AN70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO70" t="b">
         <v>1</v>
       </c>
-      <c r="AP70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ70" t="inlineStr">
+      <c r="AP70" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11534,7 +11460,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>815993643276</v>
+        <v>2447980929828</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11553,20 +11479,19 @@
       <c r="AK71" t="b">
         <v>0</v>
       </c>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="n">
-        <v>1</v>
+      <c r="AL71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM71" t="b">
+        <v>0</v>
       </c>
       <c r="AN71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO71" t="b">
         <v>1</v>
       </c>
-      <c r="AP71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ71" t="inlineStr">
+      <c r="AP71" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11691,7 +11616,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>815993643276</v>
+        <v>2447980929828</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11710,20 +11635,19 @@
       <c r="AK72" t="b">
         <v>0</v>
       </c>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="n">
-        <v>1</v>
+      <c r="AL72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM72" t="b">
+        <v>0</v>
       </c>
       <c r="AN72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO72" t="b">
         <v>1</v>
       </c>
-      <c r="AP72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ72" t="inlineStr">
+      <c r="AP72" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11848,7 +11772,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11867,20 +11791,19 @@
       <c r="AK73" t="b">
         <v>0</v>
       </c>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="n">
-        <v>1</v>
+      <c r="AL73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM73" t="b">
+        <v>0</v>
       </c>
       <c r="AN73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO73" t="b">
         <v>1</v>
       </c>
-      <c r="AP73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ73" t="inlineStr">
+      <c r="AP73" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12005,7 +11928,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12024,20 +11947,19 @@
       <c r="AK74" t="b">
         <v>0</v>
       </c>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="n">
-        <v>1</v>
+      <c r="AL74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM74" t="b">
+        <v>0</v>
       </c>
       <c r="AN74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO74" t="b">
         <v>1</v>
       </c>
-      <c r="AP74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ74" t="inlineStr">
+      <c r="AP74" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12162,7 +12084,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>815993643276</v>
+        <v>2447980929828</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12181,20 +12103,19 @@
       <c r="AK75" t="b">
         <v>0</v>
       </c>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="n">
-        <v>1</v>
+      <c r="AL75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM75" t="b">
+        <v>0</v>
       </c>
       <c r="AN75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO75" t="b">
         <v>1</v>
       </c>
-      <c r="AP75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ75" t="inlineStr">
+      <c r="AP75" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12309,7 +12230,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12326,20 +12247,19 @@
       <c r="AI76" t="inlineStr"/>
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="n">
-        <v>1</v>
+      <c r="AL76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM76" t="b">
+        <v>0</v>
       </c>
       <c r="AN76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO76" t="b">
         <v>1</v>
       </c>
-      <c r="AP76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ76" t="inlineStr">
+      <c r="AP76" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12464,7 +12384,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12483,20 +12403,19 @@
       <c r="AK77" t="b">
         <v>0</v>
       </c>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="n">
-        <v>1</v>
+      <c r="AL77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM77" t="b">
+        <v>0</v>
       </c>
       <c r="AN77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO77" t="b">
         <v>1</v>
       </c>
-      <c r="AP77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ77" t="inlineStr">
+      <c r="AP77" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12621,7 +12540,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>948405357072</v>
+        <v>2845216071216</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12638,20 +12557,19 @@
       <c r="AI78" t="inlineStr"/>
       <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="n">
-        <v>1</v>
+      <c r="AL78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM78" t="b">
+        <v>0</v>
       </c>
       <c r="AN78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO78" t="b">
         <v>1</v>
       </c>
-      <c r="AP78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ78" t="inlineStr">
+      <c r="AP78" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12779,7 +12697,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>755556046992</v>
+        <v>2266668140976</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12798,20 +12716,19 @@
       <c r="AK79" t="b">
         <v>0</v>
       </c>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="n">
-        <v>1</v>
+      <c r="AL79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM79" t="b">
+        <v>0</v>
       </c>
       <c r="AN79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO79" t="b">
         <v>1</v>
       </c>
-      <c r="AP79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ79" t="inlineStr">
+      <c r="AP79" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12938,7 +12855,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12957,20 +12874,19 @@
       <c r="AK80" t="b">
         <v>0</v>
       </c>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="n">
-        <v>1</v>
+      <c r="AL80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM80" t="b">
+        <v>0</v>
       </c>
       <c r="AN80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO80" t="b">
         <v>1</v>
       </c>
-      <c r="AP80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ80" t="inlineStr">
+      <c r="AP80" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13099,7 +13015,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13118,20 +13034,19 @@
       <c r="AK81" t="b">
         <v>0</v>
       </c>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="n">
-        <v>1</v>
+      <c r="AL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM81" t="b">
+        <v>0</v>
       </c>
       <c r="AN81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO81" t="b">
         <v>1</v>
       </c>
-      <c r="AP81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ81" t="inlineStr">
+      <c r="AP81" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13259,7 +13174,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>753948969408</v>
+        <v>2261846908224</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13278,20 +13193,19 @@
       <c r="AK82" t="b">
         <v>0</v>
       </c>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="n">
-        <v>1</v>
+      <c r="AL82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM82" t="b">
+        <v>0</v>
       </c>
       <c r="AN82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO82" t="b">
         <v>1</v>
       </c>
-      <c r="AP82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ82" t="inlineStr">
+      <c r="AP82" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13419,7 +13333,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>753920271594</v>
+        <v>2261760814782</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13438,20 +13352,19 @@
       <c r="AK83" t="b">
         <v>0</v>
       </c>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="n">
-        <v>1</v>
+      <c r="AL83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM83" t="b">
+        <v>0</v>
       </c>
       <c r="AN83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO83" t="b">
         <v>1</v>
       </c>
-      <c r="AP83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ83" t="inlineStr">
+      <c r="AP83" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13580,7 +13493,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>753403710942</v>
+        <v>2260211132826</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13599,20 +13512,19 @@
       <c r="AK84" t="b">
         <v>0</v>
       </c>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="n">
-        <v>1</v>
+      <c r="AL84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM84" t="b">
+        <v>0</v>
       </c>
       <c r="AN84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO84" t="b">
         <v>1</v>
       </c>
-      <c r="AP84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ84" t="inlineStr">
+      <c r="AP84" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13740,7 +13652,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>753403710942</v>
+        <v>2260211132826</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13759,20 +13671,19 @@
       <c r="AK85" t="b">
         <v>0</v>
       </c>
-      <c r="AL85" t="inlineStr"/>
-      <c r="AM85" t="n">
-        <v>1</v>
+      <c r="AL85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM85" t="b">
+        <v>0</v>
       </c>
       <c r="AN85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO85" t="b">
         <v>1</v>
       </c>
-      <c r="AP85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ85" t="inlineStr">
+      <c r="AP85" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -13897,7 +13808,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>753403710942</v>
+        <v>2260211132826</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13916,20 +13827,19 @@
       <c r="AK86" t="b">
         <v>0</v>
       </c>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86" t="n">
-        <v>1</v>
+      <c r="AL86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM86" t="b">
+        <v>0</v>
       </c>
       <c r="AN86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO86" t="b">
         <v>1</v>
       </c>
-      <c r="AP86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ86" t="inlineStr">
+      <c r="AP86" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14054,7 +13964,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14071,20 +13981,19 @@
       <c r="AI87" t="inlineStr"/>
       <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="inlineStr"/>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="n">
-        <v>1</v>
+      <c r="AL87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM87" t="b">
+        <v>0</v>
       </c>
       <c r="AN87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO87" t="b">
         <v>1</v>
       </c>
-      <c r="AP87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ87" t="inlineStr">
+      <c r="AP87" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14209,7 +14118,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>753403710942</v>
+        <v>2260211132826</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14228,20 +14137,19 @@
       <c r="AK88" t="b">
         <v>0</v>
       </c>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88" t="n">
-        <v>1</v>
+      <c r="AL88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM88" t="b">
+        <v>0</v>
       </c>
       <c r="AN88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO88" t="b">
         <v>1</v>
       </c>
-      <c r="AP88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ88" t="inlineStr">
+      <c r="AP88" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14366,7 +14274,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>753403710942</v>
+        <v>2260211132826</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14385,20 +14293,19 @@
       <c r="AK89" t="b">
         <v>0</v>
       </c>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="n">
-        <v>1</v>
+      <c r="AL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM89" t="b">
+        <v>0</v>
       </c>
       <c r="AN89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO89" t="b">
         <v>1</v>
       </c>
-      <c r="AP89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ89" t="inlineStr">
+      <c r="AP89" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14513,7 +14420,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14530,20 +14437,19 @@
       <c r="AI90" t="inlineStr"/>
       <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="inlineStr"/>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90" t="n">
-        <v>1</v>
+      <c r="AL90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM90" t="b">
+        <v>0</v>
       </c>
       <c r="AN90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO90" t="b">
         <v>1</v>
       </c>
-      <c r="AP90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ90" t="inlineStr">
+      <c r="AP90" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14658,7 +14564,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14675,20 +14581,19 @@
       <c r="AI91" t="inlineStr"/>
       <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="inlineStr"/>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91" t="n">
-        <v>1</v>
+      <c r="AL91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM91" t="b">
+        <v>0</v>
       </c>
       <c r="AN91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO91" t="b">
         <v>1</v>
       </c>
-      <c r="AP91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ91" t="inlineStr">
+      <c r="AP91" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14815,7 +14720,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14834,20 +14739,19 @@
       <c r="AK92" t="b">
         <v>0</v>
       </c>
-      <c r="AL92" t="inlineStr"/>
-      <c r="AM92" t="n">
+      <c r="AL92" t="n">
         <v>2</v>
       </c>
+      <c r="AM92" t="b">
+        <v>0</v>
+      </c>
       <c r="AN92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO92" t="b">
         <v>1</v>
       </c>
-      <c r="AP92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ92" t="inlineStr">
+      <c r="AP92" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -14976,7 +14880,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>753920271594</v>
+        <v>2261760814782</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14995,20 +14899,19 @@
       <c r="AK93" t="b">
         <v>0</v>
       </c>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="n">
+      <c r="AL93" t="n">
         <v>2</v>
       </c>
+      <c r="AM93" t="b">
+        <v>0</v>
+      </c>
       <c r="AN93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO93" t="b">
         <v>1</v>
       </c>
-      <c r="AP93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ93" t="inlineStr">
+      <c r="AP93" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15137,7 +15040,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>753403710942</v>
+        <v>2260211132826</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15156,20 +15059,19 @@
       <c r="AK94" t="b">
         <v>0</v>
       </c>
-      <c r="AL94" t="inlineStr"/>
-      <c r="AM94" t="n">
+      <c r="AL94" t="n">
         <v>2</v>
       </c>
+      <c r="AM94" t="b">
+        <v>0</v>
+      </c>
       <c r="AN94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO94" t="b">
         <v>1</v>
       </c>
-      <c r="AP94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ94" t="inlineStr">
+      <c r="AP94" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15284,7 +15186,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15301,20 +15203,19 @@
       <c r="AI95" t="inlineStr"/>
       <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="inlineStr"/>
-      <c r="AL95" t="inlineStr"/>
-      <c r="AM95" t="n">
-        <v>1</v>
+      <c r="AL95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM95" t="b">
+        <v>0</v>
       </c>
       <c r="AN95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO95" t="b">
         <v>1</v>
       </c>
-      <c r="AP95" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ95" t="inlineStr">
+      <c r="AP95" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15429,7 +15330,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15446,20 +15347,19 @@
       <c r="AI96" t="inlineStr"/>
       <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="inlineStr"/>
-      <c r="AL96" t="inlineStr"/>
-      <c r="AM96" t="n">
-        <v>1</v>
+      <c r="AL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM96" t="b">
+        <v>0</v>
       </c>
       <c r="AN96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO96" t="b">
         <v>1</v>
       </c>
-      <c r="AP96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ96" t="inlineStr">
+      <c r="AP96" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15574,7 +15474,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15591,20 +15491,19 @@
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="inlineStr"/>
-      <c r="AL97" t="inlineStr"/>
-      <c r="AM97" t="n">
-        <v>1</v>
+      <c r="AL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM97" t="b">
+        <v>0</v>
       </c>
       <c r="AN97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO97" t="b">
         <v>1</v>
       </c>
-      <c r="AP97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ97" t="inlineStr">
+      <c r="AP97" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15719,7 +15618,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15736,20 +15635,19 @@
       <c r="AI98" t="inlineStr"/>
       <c r="AJ98" t="inlineStr"/>
       <c r="AK98" t="inlineStr"/>
-      <c r="AL98" t="inlineStr"/>
-      <c r="AM98" t="n">
-        <v>1</v>
+      <c r="AL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM98" t="b">
+        <v>0</v>
       </c>
       <c r="AN98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO98" t="b">
         <v>1</v>
       </c>
-      <c r="AP98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ98" t="inlineStr">
+      <c r="AP98" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -15864,7 +15762,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15881,20 +15779,19 @@
       <c r="AI99" t="inlineStr"/>
       <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="inlineStr"/>
-      <c r="AL99" t="inlineStr"/>
-      <c r="AM99" t="n">
-        <v>1</v>
+      <c r="AL99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM99" t="b">
+        <v>0</v>
       </c>
       <c r="AN99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO99" t="b">
         <v>1</v>
       </c>
-      <c r="AP99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ99" t="inlineStr">
+      <c r="AP99" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16009,7 +15906,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16026,20 +15923,19 @@
       <c r="AI100" t="inlineStr"/>
       <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="inlineStr"/>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100" t="n">
-        <v>1</v>
+      <c r="AL100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM100" t="b">
+        <v>0</v>
       </c>
       <c r="AN100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO100" t="b">
         <v>1</v>
       </c>
-      <c r="AP100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ100" t="inlineStr">
+      <c r="AP100" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16154,7 +16050,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16171,20 +16067,19 @@
       <c r="AI101" t="inlineStr"/>
       <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="inlineStr"/>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101" t="n">
-        <v>1</v>
+      <c r="AL101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM101" t="b">
+        <v>0</v>
       </c>
       <c r="AN101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO101" t="b">
         <v>1</v>
       </c>
-      <c r="AP101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ101" t="inlineStr">
+      <c r="AP101" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16299,7 +16194,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16316,20 +16211,19 @@
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="inlineStr"/>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102" t="n">
-        <v>1</v>
+      <c r="AL102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM102" t="b">
+        <v>0</v>
       </c>
       <c r="AN102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO102" t="b">
         <v>1</v>
       </c>
-      <c r="AP102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ102" t="inlineStr">
+      <c r="AP102" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16444,7 +16338,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16461,20 +16355,19 @@
       <c r="AI103" t="inlineStr"/>
       <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="inlineStr"/>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="n">
-        <v>1</v>
+      <c r="AL103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM103" t="b">
+        <v>0</v>
       </c>
       <c r="AN103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO103" t="b">
         <v>1</v>
       </c>
-      <c r="AP103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ103" t="inlineStr">
+      <c r="AP103" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16589,7 +16482,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16606,20 +16499,19 @@
       <c r="AI104" t="inlineStr"/>
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr"/>
-      <c r="AL104" t="inlineStr"/>
-      <c r="AM104" t="n">
-        <v>1</v>
+      <c r="AL104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM104" t="b">
+        <v>0</v>
       </c>
       <c r="AN104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO104" t="b">
         <v>1</v>
       </c>
-      <c r="AP104" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ104" t="inlineStr">
+      <c r="AP104" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16734,7 +16626,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16751,20 +16643,19 @@
       <c r="AI105" t="inlineStr"/>
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="inlineStr"/>
-      <c r="AL105" t="inlineStr"/>
-      <c r="AM105" t="n">
-        <v>1</v>
+      <c r="AL105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM105" t="b">
+        <v>0</v>
       </c>
       <c r="AN105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO105" t="b">
         <v>1</v>
       </c>
-      <c r="AP105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ105" t="inlineStr">
+      <c r="AP105" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -16879,7 +16770,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16896,20 +16787,19 @@
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="inlineStr"/>
-      <c r="AL106" t="inlineStr"/>
-      <c r="AM106" t="n">
-        <v>1</v>
+      <c r="AL106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM106" t="b">
+        <v>0</v>
       </c>
       <c r="AN106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO106" t="b">
         <v>1</v>
       </c>
-      <c r="AP106" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ106" t="inlineStr">
+      <c r="AP106" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17037,7 +16927,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>815993643276</v>
+        <v>2447980929828</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17056,20 +16946,19 @@
       <c r="AK107" t="b">
         <v>0</v>
       </c>
-      <c r="AL107" t="inlineStr"/>
-      <c r="AM107" t="n">
-        <v>1</v>
+      <c r="AL107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM107" t="b">
+        <v>0</v>
       </c>
       <c r="AN107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO107" t="b">
         <v>1</v>
       </c>
-      <c r="AP107" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ107" t="inlineStr">
+      <c r="AP107" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17197,7 +17086,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17216,20 +17105,19 @@
       <c r="AK108" t="b">
         <v>0</v>
       </c>
-      <c r="AL108" t="inlineStr"/>
-      <c r="AM108" t="n">
-        <v>1</v>
+      <c r="AL108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM108" t="b">
+        <v>0</v>
       </c>
       <c r="AN108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO108" t="b">
         <v>1</v>
       </c>
-      <c r="AP108" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ108" t="inlineStr">
+      <c r="AP108" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17358,7 +17246,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>816165830160</v>
+        <v>2448497490480</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17377,20 +17265,19 @@
       <c r="AK109" t="b">
         <v>0</v>
       </c>
-      <c r="AL109" t="inlineStr"/>
-      <c r="AM109" t="n">
-        <v>1</v>
+      <c r="AL109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM109" t="b">
+        <v>0</v>
       </c>
       <c r="AN109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO109" t="b">
         <v>1</v>
       </c>
-      <c r="AP109" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ109" t="inlineStr">
+      <c r="AP109" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17518,7 +17405,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>774152230464</v>
+        <v>2322456691392</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17537,20 +17424,19 @@
       <c r="AK110" t="b">
         <v>0</v>
       </c>
-      <c r="AL110" t="inlineStr"/>
-      <c r="AM110" t="n">
-        <v>1</v>
+      <c r="AL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM110" t="b">
+        <v>0</v>
       </c>
       <c r="AN110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO110" t="b">
         <v>1</v>
       </c>
-      <c r="AP110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ110" t="inlineStr">
+      <c r="AP110" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17678,7 +17564,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>753920271594</v>
+        <v>2261760814782</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17697,20 +17583,19 @@
       <c r="AK111" t="b">
         <v>0</v>
       </c>
-      <c r="AL111" t="inlineStr"/>
-      <c r="AM111" t="n">
-        <v>1</v>
+      <c r="AL111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM111" t="b">
+        <v>0</v>
       </c>
       <c r="AN111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO111" t="b">
         <v>1</v>
       </c>
-      <c r="AP111" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ111" t="inlineStr">
+      <c r="AP111" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -17839,7 +17724,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>753948969408</v>
+        <v>2261846908224</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17858,20 +17743,19 @@
       <c r="AK112" t="b">
         <v>0</v>
       </c>
-      <c r="AL112" t="inlineStr"/>
-      <c r="AM112" t="n">
-        <v>1</v>
+      <c r="AL112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM112" t="b">
+        <v>0</v>
       </c>
       <c r="AN112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO112" t="b">
         <v>1</v>
       </c>
-      <c r="AP112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ112" t="inlineStr">
+      <c r="AP112" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -18000,7 +17884,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>753920271594</v>
+        <v>2261760814782</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18019,20 +17903,19 @@
       <c r="AK113" t="b">
         <v>0</v>
       </c>
-      <c r="AL113" t="inlineStr"/>
-      <c r="AM113" t="n">
-        <v>1</v>
+      <c r="AL113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM113" t="b">
+        <v>0</v>
       </c>
       <c r="AN113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO113" t="b">
         <v>1</v>
       </c>
-      <c r="AP113" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ113" t="inlineStr">
+      <c r="AP113" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -18160,7 +18043,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>753920271594</v>
+        <v>2261760814782</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18179,20 +18062,19 @@
       <c r="AK114" t="b">
         <v>0</v>
       </c>
-      <c r="AL114" t="inlineStr"/>
-      <c r="AM114" t="n">
-        <v>1</v>
+      <c r="AL114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM114" t="b">
+        <v>0</v>
       </c>
       <c r="AN114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO114" t="b">
         <v>1</v>
       </c>
-      <c r="AP114" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ114" t="inlineStr">
+      <c r="AP114" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -18320,7 +18202,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>753403710942</v>
+        <v>2260211132826</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18339,20 +18221,19 @@
       <c r="AK115" t="b">
         <v>0</v>
       </c>
-      <c r="AL115" t="inlineStr"/>
-      <c r="AM115" t="n">
-        <v>1</v>
+      <c r="AL115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM115" t="b">
+        <v>0</v>
       </c>
       <c r="AN115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO115" t="b">
         <v>1</v>
       </c>
-      <c r="AP115" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ115" t="inlineStr">
+      <c r="AP115" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -645,7 +645,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>9058665873798</v>
+        <v>27175997621394</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -957,7 +957,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1269,7 +1269,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1425,7 +1425,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1581,7 +1581,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1897,7 +1897,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>9037745167392</v>
+        <v>27113235502176</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2053,7 +2053,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>9037745167392</v>
+        <v>27113235502176</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2209,7 +2209,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>9037745167392</v>
+        <v>27113235502176</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2365,7 +2365,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>8479859663232</v>
+        <v>25439578989696</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2521,7 +2521,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>7350228678252</v>
+        <v>22050686034756</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2651,7 +2651,9 @@
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
+      <c r="AK14" t="b">
+        <v>0</v>
+      </c>
       <c r="AL14" t="n">
         <v>1</v>
       </c>
@@ -2675,7 +2677,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2789,7 +2791,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>9037745167392</v>
+        <v>27113235502176</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2831,7 +2833,7 @@
         <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2945,7 +2947,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>9037745167392</v>
+        <v>27113235502176</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2987,7 +2989,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3101,7 +3103,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>9060990396732</v>
+        <v>27182971190196</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3143,7 +3145,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3257,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>7350141517308</v>
+        <v>22050424551924</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3299,7 +3301,7 @@
         <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3413,7 +3415,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>9061765237710</v>
+        <v>27185295713130</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3455,7 +3457,7 @@
         <v>12</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3569,7 +3571,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>7350141517308</v>
+        <v>22050424551924</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3611,7 +3613,7 @@
         <v>12</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3725,7 +3727,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>9037745167392</v>
+        <v>27113235502176</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3767,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3881,7 +3883,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3923,7 +3925,7 @@
         <v>12</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -4037,7 +4039,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4079,7 +4081,7 @@
         <v>12</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4193,7 +4195,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4235,7 +4237,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4349,7 +4351,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>7350141517308</v>
+        <v>22050424551924</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4391,7 +4393,7 @@
         <v>12</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4505,7 +4507,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4547,7 +4549,7 @@
         <v>12</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4661,7 +4663,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4807,7 +4809,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4847,7 +4849,7 @@
         <v>12</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4961,7 +4963,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5003,7 +5005,7 @@
         <v>12</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5117,7 +5119,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5159,7 +5161,7 @@
         <v>12</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5273,7 +5275,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5419,7 +5421,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5459,7 +5461,7 @@
         <v>12</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5573,7 +5575,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5615,7 +5617,7 @@
         <v>12</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5729,7 +5731,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>6968919756132</v>
+        <v>20906759268396</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5883,7 +5885,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6027,7 +6029,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6067,7 +6069,7 @@
         <v>12</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6181,7 +6183,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6335,7 +6337,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6375,7 +6377,7 @@
         <v>12</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6489,7 +6491,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>6800091579252</v>
+        <v>20400274737756</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6531,7 +6533,7 @@
         <v>12</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6645,7 +6647,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6687,7 +6689,7 @@
         <v>12</v>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6801,7 +6803,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6843,7 +6845,7 @@
         <v>12</v>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6962,7 +6964,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7004,7 +7006,7 @@
         <v>12</v>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7118,7 +7120,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7160,7 +7162,7 @@
         <v>12</v>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -7279,7 +7281,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7321,7 +7323,7 @@
         <v>12</v>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -7435,7 +7437,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>9058665873798</v>
+        <v>27175997621394</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7477,7 +7479,7 @@
         <v>12</v>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7591,7 +7593,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7633,7 +7635,7 @@
         <v>12</v>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7747,7 +7749,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7893,7 +7895,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7933,7 +7935,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -8047,7 +8049,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8089,7 +8091,7 @@
         <v>12</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -8203,7 +8205,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8245,7 +8247,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -8359,7 +8361,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8401,7 +8403,7 @@
         <v>12</v>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -8515,7 +8517,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8557,7 +8559,7 @@
         <v>12</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -8671,7 +8673,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8713,7 +8715,7 @@
         <v>12</v>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8827,7 +8829,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>8480892784536</v>
+        <v>25442678353608</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8869,7 +8871,7 @@
         <v>12</v>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8983,7 +8985,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>9037745167392</v>
+        <v>27113235502176</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9025,7 +9027,7 @@
         <v>12</v>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -9139,7 +9141,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9181,7 +9183,7 @@
         <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -9295,7 +9297,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>10189158860700</v>
+        <v>30567476582100</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9337,7 +9339,7 @@
         <v>12</v>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -9451,7 +9453,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>6968919756132</v>
+        <v>20906759268396</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9493,7 +9495,7 @@
         <v>12</v>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -9607,7 +9609,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>6968919756132</v>
+        <v>20906759268396</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9649,7 +9651,7 @@
         <v>12</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -9766,7 +9768,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>6968919756132</v>
+        <v>20906759268396</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9808,7 +9810,7 @@
         <v>12</v>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9922,7 +9924,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>6968919756132</v>
+        <v>20906759268396</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -9964,7 +9966,7 @@
         <v>12</v>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -10078,7 +10080,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>6800004422928</v>
+        <v>20400013268784</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10120,7 +10122,7 @@
         <v>12</v>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -10234,7 +10236,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>6800004422928</v>
+        <v>20400013268784</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10276,7 +10278,7 @@
         <v>12</v>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -10390,7 +10392,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10432,7 +10434,7 @@
         <v>12</v>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -10546,7 +10548,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10588,7 +10590,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -10702,7 +10704,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10744,7 +10746,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -10858,7 +10860,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>6785282444346</v>
+        <v>20355847333038</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10900,7 +10902,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -11014,7 +11016,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>6785282444346</v>
+        <v>20355847333038</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11056,7 +11058,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -11170,7 +11172,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>6785540724672</v>
+        <v>20356622174016</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11316,7 +11318,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11460,7 +11462,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11500,7 +11502,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -11614,7 +11616,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>7343942789484</v>
+        <v>22031828368452</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11656,7 +11658,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -11770,7 +11772,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>7343942789484</v>
+        <v>22031828368452</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11812,7 +11814,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -11926,7 +11928,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11968,7 +11970,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -12082,7 +12084,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12124,7 +12126,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -12238,7 +12240,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>7343942789484</v>
+        <v>22031828368452</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12384,7 +12386,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12424,7 +12426,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -12538,7 +12540,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12694,7 +12696,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>8535648213648</v>
+        <v>25606944640944</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12734,7 +12736,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -12851,7 +12853,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>6800004422928</v>
+        <v>20400013268784</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -12893,7 +12895,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -13009,7 +13011,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13051,7 +13053,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -13169,7 +13171,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13211,7 +13213,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -13328,7 +13330,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>6785540724672</v>
+        <v>20356622174016</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13370,7 +13372,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -13487,7 +13489,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>6785282444346</v>
+        <v>20355847333038</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13529,7 +13531,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -13647,7 +13649,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>6780633398478</v>
+        <v>20341900195434</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13689,7 +13691,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -13806,7 +13808,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>6780633398478</v>
+        <v>20341900195434</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13848,7 +13850,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -13962,7 +13964,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>6780633398478</v>
+        <v>20341900195434</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14118,7 +14120,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14158,7 +14160,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -14272,7 +14274,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>6780633398478</v>
+        <v>20341900195434</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14314,7 +14316,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -14428,7 +14430,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>6780633398478</v>
+        <v>20341900195434</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14574,7 +14576,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14718,7 +14720,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14758,7 +14760,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -14874,7 +14876,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -14916,7 +14918,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -15034,7 +15036,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>6785282444346</v>
+        <v>20355847333038</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15076,7 +15078,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -15194,7 +15196,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>6780633398478</v>
+        <v>20341900195434</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15340,7 +15342,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15484,7 +15486,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15628,7 +15630,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15772,7 +15774,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15916,7 +15918,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16060,7 +16062,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16204,7 +16206,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16348,7 +16350,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16492,7 +16494,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16636,7 +16638,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16780,7 +16782,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16924,7 +16926,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -16964,7 +16966,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -17081,7 +17083,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>7343942789484</v>
+        <v>22031828368452</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17123,7 +17125,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -17240,7 +17242,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17282,7 +17284,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -17400,7 +17402,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>7345492471440</v>
+        <v>22036477414320</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17442,7 +17444,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -17559,7 +17561,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>6967370074176</v>
+        <v>20902110222528</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17601,7 +17603,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -17718,7 +17720,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>6785282444346</v>
+        <v>20355847333038</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17760,7 +17762,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -17878,7 +17880,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>6785540724672</v>
+        <v>20356622174016</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -17920,7 +17922,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -18038,7 +18040,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>6785282444346</v>
+        <v>20355847333038</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18080,7 +18082,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -18197,7 +18199,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>6785282444346</v>
+        <v>20355847333038</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18239,7 +18241,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -18356,7 +18358,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>6780633398478</v>
+        <v>20341900195434</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>27175997621394</v>
+        <v>81527992864182</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>22050686034756</v>
+        <v>66152058104268</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>27182971190196</v>
+        <v>81548913570588</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>22050424551924</v>
+        <v>66151273655772</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>27185295713130</v>
+        <v>81555887139390</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>22050424551924</v>
+        <v>66151273655772</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>22050424551924</v>
+        <v>66151273655772</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>20400274737756</v>
+        <v>61200824213268</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>27175997621394</v>
+        <v>81527992864182</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>25442678353608</v>
+        <v>76328035060824</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>27113235502176</v>
+        <v>81339706506528</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>30567476582100</v>
+        <v>91702429746300</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>20400013268784</v>
+        <v>61200039806352</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>20400013268784</v>
+        <v>61200039806352</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10392,7 +10392,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11016,7 +11016,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>20356622174016</v>
+        <v>61069866522048</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11616,7 +11616,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12084,7 +12084,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12386,7 +12386,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>25606944640944</v>
+        <v>76820833922832</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>20400013268784</v>
+        <v>61200039806352</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13171,7 +13171,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>20356622174016</v>
+        <v>61069866522048</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13489,7 +13489,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13808,7 +13808,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14120,7 +14120,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14720,7 +14720,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14876,7 +14876,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15036,7 +15036,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15196,7 +15196,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15342,7 +15342,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15486,7 +15486,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15630,7 +15630,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15918,7 +15918,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16062,7 +16062,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16638,7 +16638,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16782,7 +16782,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>22031828368452</v>
+        <v>66095485105356</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17242,7 +17242,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17402,7 +17402,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>22036477414320</v>
+        <v>66109432242960</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>20902110222528</v>
+        <v>62706330667584</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>20356622174016</v>
+        <v>61069866522048</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18199,7 +18199,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>20355847333038</v>
+        <v>61067541999114</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18358,7 +18358,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>20341900195434</v>
+        <v>61025700586302</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>244583978592546</v>
+        <v>733751935777638</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>198456174312804</v>
+        <v>595368522938412</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>244646740711764</v>
+        <v>733940222135292</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>198453820967316</v>
+        <v>595361462901948</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>244667661418170</v>
+        <v>734002984254510</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>198453820967316</v>
+        <v>595361462901948</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>198453820967316</v>
+        <v>595361462901948</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>183602472639804</v>
+        <v>550807417919412</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>244583978592546</v>
+        <v>733751935777638</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>228984105182472</v>
+        <v>686952315547416</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>244019119519584</v>
+        <v>732057358558752</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9603,7 +9603,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>275107289238900</v>
+        <v>825321867716700</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>183602472764466</v>
+        <v>550807418293398</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>183602472764464</v>
+        <v>550807418293392</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>183600119419056</v>
+        <v>550800358257168</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>183600119419056</v>
+        <v>550800358257168</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>183209599566144</v>
+        <v>549628798698432</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12386,7 +12386,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12852,7 +12852,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13164,7 +13164,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13464,7 +13464,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13620,7 +13620,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>230462501768496</v>
+        <v>691387505305488</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13777,7 +13777,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>183600119419056</v>
+        <v>550800358257168</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>183209599566144</v>
+        <v>549628798698432</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14413,7 +14413,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14732,7 +14732,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14888,7 +14888,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15198,7 +15198,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15354,7 +15354,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15500,7 +15500,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15800,7 +15800,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15960,7 +15960,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16410,7 +16410,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16554,7 +16554,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16698,7 +16698,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17130,7 +17130,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17274,7 +17274,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17418,7 +17418,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17562,7 +17562,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17706,7 +17706,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>198286455316068</v>
+        <v>594859365948204</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18166,7 +18166,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18326,7 +18326,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>198328296728880</v>
+        <v>594984890186640</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18485,7 +18485,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>188118992002752</v>
+        <v>564356976008256</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -18644,7 +18644,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>183209599566144</v>
+        <v>549628798698432</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19123,7 +19123,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>183202625997342</v>
+        <v>549607877992026</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19282,7 +19282,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>183077101758906</v>
+        <v>549231305276718</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2201255807332914</v>
+        <v>6603767421998742</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1786105568815236</v>
+        <v>5358316706445708</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2201820666405876</v>
+        <v>6605461999217628</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1786084388705844</v>
+        <v>5358253166117532</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2202008952763530</v>
+        <v>6606026858290590</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1786084388705844</v>
+        <v>5358253166117532</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1786105568815239</v>
+        <v>5358316706445717</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1786105568815239</v>
+        <v>5358316706445717</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1786105568815239</v>
+        <v>5358316706445717</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1786084388705844</v>
+        <v>5358253166117532</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1652422253758236</v>
+        <v>4957266761274708</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2201255807332914</v>
+        <v>6603767421998742</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8819,7 +8819,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2060856946642248</v>
+        <v>6182570839926744</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2196172075676256</v>
+        <v>6588516227028768</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2475965603150100</v>
+        <v>7427896809450300</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1652422254880194</v>
+        <v>4957266764640582</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1652422254880176</v>
+        <v>4957266764640528</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1652401074771504</v>
+        <v>4957203224314512</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1652401074771504</v>
+        <v>4957203224314512</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12402,7 +12402,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12558,7 +12558,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1648886396095296</v>
+        <v>4946659188285888</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12704,7 +12704,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -12848,7 +12848,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -13002,7 +13002,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1784578097844612</v>
+        <v>5353734293533836</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -13158,7 +13158,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1784578097844612</v>
+        <v>5353734293533836</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -13626,7 +13626,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1784578097844612</v>
+        <v>5353734293533836</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -13926,7 +13926,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -14082,7 +14082,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2074162515916464</v>
+        <v>6222487547749392</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1652401074771504</v>
+        <v>4957203224314512</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -14716,7 +14716,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1648886396095296</v>
+        <v>4946659188285888</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -15194,7 +15194,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -15506,7 +15506,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -15660,7 +15660,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -15816,7 +15816,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -16262,7 +16262,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -16422,7 +16422,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -17016,7 +17016,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -17160,7 +17160,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -17304,7 +17304,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -17448,7 +17448,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -17736,7 +17736,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -17880,7 +17880,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -18024,7 +18024,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -18312,7 +18312,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1784578097844612</v>
+        <v>5353734293533836</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -18788,7 +18788,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1784954670559920</v>
+        <v>5354864011679760</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -18947,7 +18947,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1693070928024768</v>
+        <v>5079212784074304</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -19106,7 +19106,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1648886396095296</v>
+        <v>4946659188285888</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -19585,7 +19585,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1648823633976078</v>
+        <v>4946470901928234</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -19744,7 +19744,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1647693915830154</v>
+        <v>4943081747490462</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR77"/>
+  <dimension ref="A1:AV78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,19 +601,19 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>role_evidence</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>resolution_reason</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>search_fingerprint</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>role_evidence</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
@@ -626,25 +626,45 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>verification_schema_version</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>identity_name_verified</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>identity_specialty_verified</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>identity_evidence</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>candidate_rank</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>shared_contact</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>send_eligible</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>personalization_safe</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -769,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.981130226599622e+16</v>
+        <v>5.943390679798868e+16</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -790,19 +810,23 @@
         <v>0</v>
       </c>
       <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -927,7 +951,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -948,19 +972,23 @@
         <v>0</v>
       </c>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1085,7 +1113,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1106,19 +1134,23 @@
         <v>0</v>
       </c>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1246,7 +1278,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1267,19 +1299,23 @@
         <v>0</v>
       </c>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1405,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1426,19 +1462,23 @@
         <v>0</v>
       </c>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1563,7 +1603,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1584,19 +1624,23 @@
         <v>0</v>
       </c>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1721,7 +1765,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1742,19 +1786,23 @@
         <v>0</v>
       </c>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -1879,7 +1927,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.854545308348838e+16</v>
+        <v>5.563635925046515e+16</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1900,19 +1948,23 @@
         <v>0</v>
       </c>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2037,7 +2089,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.607495011933712e+16</v>
+        <v>4.822485035801138e+16</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2058,19 +2110,23 @@
         <v>0</v>
       </c>
       <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2195,7 +2251,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.60747594983526e+16</v>
+        <v>4.822427849505779e+16</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2216,19 +2272,23 @@
         <v>0</v>
       </c>
       <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2353,7 +2413,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.981808057487177e+16</v>
+        <v>5.945424172461531e+16</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2374,19 +2434,23 @@
         <v>0</v>
       </c>
       <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2511,7 +2575,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.607495011933715e+16</v>
+        <v>4.822485035801146e+16</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2532,19 +2596,23 @@
         <v>0</v>
       </c>
       <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2669,7 +2737,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2690,19 +2758,23 @@
         <v>0</v>
       </c>
       <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2827,7 +2899,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2848,19 +2920,23 @@
         <v>0</v>
       </c>
       <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -2985,7 +3061,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3006,19 +3082,23 @@
         <v>0</v>
       </c>
       <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR16" t="inlineStr">
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3143,7 +3223,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3164,19 +3244,23 @@
         <v>0</v>
       </c>
       <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="n">
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
         <v>2</v>
       </c>
-      <c r="AO17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR17" t="inlineStr">
+      <c r="AS17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3301,7 +3385,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.607495011933715e+16</v>
+        <v>4.822485035801146e+16</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3322,19 +3406,23 @@
         <v>0</v>
       </c>
       <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR18" t="inlineStr">
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3459,7 +3547,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.606478265601749e+16</v>
+        <v>4.819434796805247e+16</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3480,19 +3568,23 @@
         <v>0</v>
       </c>
       <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR19" t="inlineStr">
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3617,7 +3709,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3638,19 +3730,23 @@
         <v>0</v>
       </c>
       <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3775,7 +3871,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2.228199585113202e+16</v>
+        <v>6.684598755339604e+16</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3796,19 +3892,23 @@
         <v>0</v>
       </c>
       <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR21" t="inlineStr">
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -3933,7 +4033,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3954,19 +4054,23 @@
         <v>0</v>
       </c>
       <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR22" t="inlineStr">
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4081,7 +4185,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4100,19 +4204,23 @@
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4227,7 +4335,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4246,19 +4354,23 @@
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR24" t="inlineStr">
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4383,7 +4495,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4404,19 +4516,23 @@
         <v>0</v>
       </c>
       <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR25" t="inlineStr">
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4539,7 +4655,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.853020188851841e+16</v>
+        <v>5.559060566555523e+16</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4558,19 +4674,23 @@
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4685,7 +4805,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4704,19 +4824,23 @@
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR27" t="inlineStr">
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4841,7 +4965,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4862,19 +4986,23 @@
         <v>0</v>
       </c>
       <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR28" t="inlineStr">
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -4997,7 +5125,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.853020188851841e+16</v>
+        <v>5.559060566555523e+16</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5016,19 +5144,23 @@
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR29" t="inlineStr">
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5153,7 +5285,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5174,19 +5306,23 @@
         <v>0</v>
       </c>
       <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR30" t="inlineStr">
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5311,7 +5447,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5332,19 +5468,23 @@
         <v>0</v>
       </c>
       <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR31" t="inlineStr">
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5469,7 +5609,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.981130226599622e+16</v>
+        <v>5.943390679798868e+16</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5490,19 +5630,23 @@
         <v>0</v>
       </c>
       <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR32" t="inlineStr">
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5617,7 +5761,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5636,19 +5780,23 @@
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR33" t="inlineStr">
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5663,7 +5811,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5694,7 +5842,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5707,7 +5855,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5717,17 +5865,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -5744,36 +5892,36 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W34" t="n">
+        <v>8</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2</v>
       </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1</v>
-      </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.606459203503928e+16</v>
+        <v>4.81943479680715e+16</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5784,29 +5932,41 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="b">
         <v>1</v>
       </c>
-      <c r="AQ34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR34" t="inlineStr">
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5821,7 +5981,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5852,7 +6012,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5865,7 +6025,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5875,12 +6035,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5902,36 +6062,36 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W35" t="n">
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.606459203503928e+16</v>
+        <v>4.819377610511784e+16</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5942,7 +6102,7 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
@@ -5952,19 +6112,23 @@
         <v>0</v>
       </c>
       <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR35" t="inlineStr">
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -5979,7 +6143,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6010,7 +6174,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6023,7 +6187,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6033,12 +6197,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6060,36 +6224,36 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.606459203503928e+16</v>
+        <v>4.819377610511784e+16</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6100,7 +6264,7 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
@@ -6110,19 +6274,23 @@
         <v>0</v>
       </c>
       <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR36" t="inlineStr">
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV36" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6137,7 +6305,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6168,7 +6336,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6181,7 +6349,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6191,12 +6359,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6218,36 +6386,36 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>6</v>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.819377610511784e+16</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6258,7 +6426,7 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
@@ -6268,19 +6436,23 @@
         <v>0</v>
       </c>
       <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR37" t="inlineStr">
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6295,7 +6467,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6315,18 +6487,18 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6339,7 +6511,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6349,12 +6521,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6371,25 +6543,25 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
@@ -6401,11 +6573,11 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.854771251978023e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6416,7 +6588,7 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
@@ -6426,19 +6598,23 @@
         <v>0</v>
       </c>
       <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR38" t="inlineStr">
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6453,7 +6629,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6473,7 +6649,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6484,7 +6660,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6497,7 +6673,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6507,12 +6683,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6529,25 +6705,25 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
@@ -6559,11 +6735,11 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.97655486810863e+16</v>
+        <v>5.56431375593407e+16</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6574,7 +6750,7 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -6584,19 +6760,23 @@
         <v>0</v>
       </c>
       <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR39" t="inlineStr">
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6611,7 +6791,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6631,7 +6811,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6642,7 +6822,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6655,7 +6835,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6665,12 +6845,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6692,14 +6872,14 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
         <v>4</v>
@@ -6717,11 +6897,11 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>5.929664604325891e+16</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6732,7 +6912,7 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
@@ -6742,19 +6922,23 @@
         <v>0</v>
       </c>
       <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR40" t="inlineStr">
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6769,7 +6953,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6789,18 +6973,18 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6813,7 +6997,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6823,17 +7007,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -6850,36 +7034,36 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
+        <v>2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
         <v>4</v>
       </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
         <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.606478265601749e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6890,7 +7074,7 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
@@ -6900,19 +7084,23 @@
         <v>0</v>
       </c>
       <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR41" t="inlineStr">
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV41" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -6927,12 +7115,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>היחידה לפוריות והפריה חוץ גופית</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>fertility_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6947,18 +7135,18 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>idoba@szmc.org.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6971,7 +7159,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6981,17 +7169,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -7003,41 +7191,41 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-04T18:29:47.683340+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2.22836904283509e+16</v>
+        <v>4.819434796805247e+16</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7048,7 +7236,7 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
@@ -7058,19 +7246,23 @@
         <v>0</v>
       </c>
       <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR42" t="inlineStr">
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV42" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7085,12 +7277,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>היחידה לפוריות והפריה חוץ גופית</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>fertility_doctor</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7105,18 +7297,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>idoba@szmc.org.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7129,7 +7321,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7139,12 +7331,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7161,28 +7353,28 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-04T18:29:47.683340+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
         <v>2</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -7191,11 +7383,11 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>6.68510712850527e+16</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7206,7 +7398,7 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
@@ -7216,19 +7408,23 @@
         <v>0</v>
       </c>
       <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR43" t="inlineStr">
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7243,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7274,7 +7470,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7287,7 +7483,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7297,12 +7493,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7324,7 +7520,7 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -7334,10 +7530,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7349,11 +7545,11 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7364,7 +7560,7 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
@@ -7374,19 +7570,23 @@
         <v>0</v>
       </c>
       <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR44" t="inlineStr">
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV44" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7401,7 +7601,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7432,7 +7632,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7445,7 +7645,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7455,12 +7655,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7482,7 +7682,7 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -7507,11 +7707,11 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.524102750666068e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7522,7 +7722,7 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
@@ -7532,19 +7732,23 @@
         <v>0</v>
       </c>
       <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR45" t="inlineStr">
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV45" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7559,7 +7763,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7590,7 +7794,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7603,7 +7807,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7613,12 +7817,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7640,14 +7844,14 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>2</v>
@@ -7665,11 +7869,11 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.487180029392158e+16</v>
+        <v>4.572308251998205e+16</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7680,7 +7884,7 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
@@ -7690,19 +7894,23 @@
         <v>0</v>
       </c>
       <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR46" t="inlineStr">
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV46" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7717,7 +7925,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7748,7 +7956,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7761,7 +7969,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -7771,12 +7979,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -7793,41 +8001,41 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
+        <v>4</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
         <v>2</v>
       </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>5</v>
-      </c>
       <c r="Z47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.487160967294354e+16</v>
+        <v>4.461540088176475e+16</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7838,7 +8046,7 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
@@ -7848,19 +8056,23 @@
         <v>0</v>
       </c>
       <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR47" t="inlineStr">
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV47" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -7875,7 +8087,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7906,7 +8118,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -7919,7 +8131,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7929,12 +8141,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -7956,7 +8168,7 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -7966,26 +8178,26 @@
         <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.487160967294354e+16</v>
+        <v>4.461482901883061e+16</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7996,7 +8208,7 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
@@ -8006,19 +8218,23 @@
         <v>0</v>
       </c>
       <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR48" t="inlineStr">
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8033,7 +8249,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8064,7 +8280,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8077,7 +8293,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8087,12 +8303,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8109,41 +8325,41 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
         <v>2</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.461482901883061e+16</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8154,7 +8370,7 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -8164,19 +8380,23 @@
         <v>0</v>
       </c>
       <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR49" t="inlineStr">
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV49" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8191,7 +8411,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8222,7 +8442,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8235,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8245,12 +8465,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8272,7 +8492,7 @@
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
@@ -8282,26 +8502,26 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.486991509572465e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8312,7 +8532,7 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
@@ -8322,19 +8542,23 @@
         <v>0</v>
       </c>
       <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR50" t="inlineStr">
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV50" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8349,7 +8573,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8380,7 +8604,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8393,7 +8617,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8403,12 +8627,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8430,7 +8654,7 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
@@ -8440,13 +8664,13 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -8455,11 +8679,11 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.48394127057847e+16</v>
+        <v>4.460974528717395e+16</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8470,7 +8694,7 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
@@ -8480,19 +8704,23 @@
         <v>0</v>
       </c>
       <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR51" t="inlineStr">
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV51" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8507,7 +8735,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8538,7 +8766,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8551,7 +8779,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8561,12 +8789,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8583,12 +8811,12 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
@@ -8601,10 +8829,10 @@
         <v>6</v>
       </c>
       <c r="Z52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -8613,11 +8841,11 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.483997756485766e+16</v>
+        <v>4.45182381173541e+16</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8628,7 +8856,7 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
@@ -8638,19 +8866,23 @@
         <v>0</v>
       </c>
       <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR52" t="inlineStr">
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV52" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8660,20 +8892,22 @@
       <c r="A53" t="n">
         <v>13</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>6</v>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hadas Dar</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>lactation</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -8683,18 +8917,18 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%94%d7%93%d7%a1-%d7%93%d7%a8/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ialp</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>hadasdar127@gmail.com</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8703,11 +8937,11 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -8717,12 +8951,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>הבית אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי הדס דר – Hadas Dar טלפון: 052-8902748 אימייל: hadasdar127@gmail.com הסמכה: מדריכת הנקה אזורי קבלה: גוש דן, מרכז, שומרון, שרון ערים/ישובים: אורנית, שערי תקוה, אלקנה, עץ אפריים, ראש העין, הוד השרון, פתח-תקוה, כפר-סבא שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: מדריכ</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -8739,33 +8973,41 @@
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
+        </is>
+      </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/", "https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/#contact"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.451993269457299e+16</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -8776,27 +9018,33 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
+      <c r="AL53" t="b">
+        <v>0</v>
+      </c>
       <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV53" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8809,7 +9057,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Liel Boker</t>
+          <t>Hadas Dar</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8829,7 +9077,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%9c%d7%99%d7%90%d7%9c-%d7%91%d7%95%d7%a7%d7%a8/</t>
+          <t>https://ialp.org.il/counselors/%d7%94%d7%93%d7%a1-%d7%93%d7%a8/</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -8840,7 +9088,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>lielhadid@gmail.com</t>
+          <t>hadasdar127@gmail.com</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -8853,7 +9101,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -8863,7 +9111,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>ת אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יאל בוקר – Liel Boker טלפון: 054-3515013 אימייל: Lielhadid@gmail.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שפלה ערים/ישובים: קוה, פתח תקווה, גבעת שמואל, קרית אונו, אור יהודה, רמת גן,בני ברק, גבעתיים, יהוד, מגשימים, אזור, חולון, נחלים, בארות יצחק</t>
+          <t>הבית אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי הדס דר – Hadas Dar טלפון: 052-8902748 אימייל: hadasdar127@gmail.com הסמכה: מדריכת הנקה אזורי קבלה: גוש דן, מרכז, שומרון, שרון ערים/ישובים: אורנית, שערי תקוה, אלקנה, עץ אפריים, ראש העין, הוד השרון, פתח-תקוה, כפר-סבא שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: מדריכ</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -8907,11 +9155,11 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/", "https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/", "https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -8922,7 +9170,7 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
@@ -8930,19 +9178,23 @@
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV54" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -8952,17 +9204,15 @@
       <c r="A55" t="n">
         <v>13</v>
       </c>
-      <c r="B55" t="n">
-        <v>6</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>Liel Boker</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>lactation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -8977,18 +9227,18 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://ialp.org.il/counselors/%d7%9c%d7%99%d7%90%d7%9c-%d7%91%d7%95%d7%a7%d7%a8/</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ialp</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>lielhadid@gmail.com</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -9001,7 +9251,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9011,12 +9261,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t>ת אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יאל בוקר – Liel Boker טלפון: 054-3515013 אימייל: Lielhadid@gmail.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שפלה ערים/ישובים: קוה, פתח תקווה, גבעת שמואל, קרית אונו, אור יהודה, רמת גן,בני ברק, גבעתיים, יהוד, מגשימים, אזור, חולון, נחלים, בארות יצחק</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9026,48 +9276,40 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/", "https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.606120288060151e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9078,29 +9320,31 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR55" t="inlineStr">
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV55" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9115,7 +9359,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9146,7 +9390,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -9159,7 +9403,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9169,12 +9413,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9184,11 +9428,11 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -9196,23 +9440,23 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W56" t="n">
         <v>2</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -9221,11 +9465,11 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.606120288060151e+16</v>
+        <v>4.818360864180453e+16</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9236,7 +9480,7 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
@@ -9246,19 +9490,23 @@
         <v>0</v>
       </c>
       <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV56" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9273,7 +9521,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9304,7 +9552,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -9317,7 +9565,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9327,12 +9575,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9354,7 +9602,7 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
@@ -9364,10 +9612,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9379,11 +9627,11 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.818360864180453e+16</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9394,7 +9642,7 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
@@ -9404,19 +9652,23 @@
         <v>0</v>
       </c>
       <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV57" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9431,7 +9683,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9462,7 +9714,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9475,7 +9727,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9485,12 +9737,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -9512,7 +9764,7 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
@@ -9537,11 +9789,11 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.605950830338262e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9552,7 +9804,7 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
@@ -9562,19 +9814,23 @@
         <v>0</v>
       </c>
       <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV58" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9584,15 +9840,17 @@
       <c r="A59" t="n">
         <v>13</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>דפי רהב הס פסיכולוגית</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>perinatal_mental_health</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9607,18 +9865,18 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>dafyrahav@gmail.com</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9631,7 +9889,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9641,12 +9899,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>עמים ההיריון יופסק מבחירה ולפעמים לא ניתן לבחור. אנשי מקצוע רבים יגדירו את הפסקת ההריון כאירוע טראומתי עבור גוף האישה... &lt; המשך קריאה כתבות ומאמרים צרי קשר איך אוכל לעזור? דפי רהב הס 052-3302900 כרכור / טיפולים און ליין dafyrahav@gmail.com שלח נשלח! תודה שיצרת קשר צור קשר © כל הזכויות שמורות לדפי רהב הס bottom of page</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -9666,15 +9924,19 @@
         <v>0</v>
       </c>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
+        </is>
+      </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z59" t="n">
         <v>1</v>
@@ -9682,14 +9944,18 @@
       <c r="AA59" t="n">
         <v>0</v>
       </c>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://www.dafyrahavhass.com/", "https://www.dafyrahavhass.com/copy-of", "https://www.dafyrahavhass.com/aboutme"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.817852491014786e+16</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9700,27 +9966,33 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
+      <c r="AL59" t="b">
+        <v>0</v>
+      </c>
       <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV59" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9730,17 +10002,15 @@
       <c r="A60" t="n">
         <v>13</v>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>טלי גליקסמן</t>
+          <t>דפי רהב הס פסיכולוגית</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>sleep_consultant</t>
+          <t>perinatal_mental_health</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -9755,7 +10025,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://sleepingbaby.hashevet.co.il/sleep-pro/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -9766,7 +10036,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>tali4baby@gmail.com</t>
+          <t>dafyrahav@gmail.com</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -9779,7 +10049,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -9789,12 +10059,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>ות, מענה לשאלות וסיכום. בין המפגשים יתקיים ליווי ההורים בעבודה לפי התוכנית הספציפית אשר גובשה באמצעות שיחות טלפוניות ומיילים. אתם מוזמנים לפנות אל טלי גליקסמן לשיחת הסבר והרחבה ומענה לשאלותיכם. טלפון: 050-848-6651 מייל: tali4baby@gmail.com Post navigation → גדילת תינוקות הדרכה והכוונה להורים החדשים למניעת עיכוב התפתחותי שמונת היסודות להתפתחות מיטבית ← קישורים מרכזיים בריאות ילדים בראייה הוליסטית טלי גליקסמן מומחית להתפתחות תינוקות אודות</t>
+          <t>עמים ההיריון יופסק מבחירה ולפעמים לא ניתן לבחור. אנשי מקצוע רבים יגדירו את הפסקת ההריון כאירוע טראומתי עבור גוף האישה... &lt; המשך קריאה כתבות ומאמרים צרי קשר איך אוכל לעזור? דפי רהב הס 052-3302900 כרכור / טיפולים און ליין dafyrahav@gmail.com שלח נשלח! תודה שיצרת קשר צור קשר © כל הזכויות שמורות לדפי רהב הס bottom of page</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"טלי גליקסמן" יועצת שינה</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -9804,48 +10074,40 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>[{"email": "info@yaeltzur.co.il", "confidence": 80, "source_url": "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "identity_url": "https://www.yaeltzur.co.il/talie-gliksman/", "evidence": "[email protected]", "matched_query": "\"טלי גליקסמן\" יועצת שינה", "extraction_method": "linked_cloudflare"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>2026-09-04T04:15:05.038841+00:00</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://sleepingbaby.hashevet.co.il/sleep-pro/", "https://sleepingbaby.hashevet.co.il/sleep-pro/#about", "https://www.huggies.co.il/professionals/tali-gliksman", "https://www.huggies.co.il/contact-us", "https://www.facebook.com/hashevet/", "https://www.yaeltzur.co.il/talie-gliksman/", "https://www.allinternet.co.il/", "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "https://www.yaeltzur.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.yaeltzur.co.il/cdn-cgi/l/email-protection#96fff8f0f9d6eff7f3fae2ece3e4b8f5f9b8fffa", "https://linktr.ee/tali4baby", "https://www.hashevet.co.il/", "https://linktr.ee/s/about/trust-center/report?field86145911=https%3A%2F%2Flinktr.ee%2Ftali4baby", "https://linktr.ee/blog/daisy-chain-fields-sticker-pack", "https://linktr.ee/features/contact-forms", "https://linktr.ee/features/audience-management", "https://linktr.ee/features/email-integrations", "https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/", "https://www.hashevet.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.hashevet.co.il/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/%D7%94%D7%93%D7%A8%D7%9B%D7%94%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/", "https://www.hashevet.co.il/category/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.dafyrahavhass.com/", "https://www.dafyrahavhass.com/copy-of", "https://www.dafyrahavhass.com/aboutme"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.866746264324818e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -9856,7 +10118,7 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
@@ -9864,19 +10126,23 @@
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV60" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -9891,12 +10157,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>שיקום רצפת האגן</t>
+          <t>טלי גליקסמן</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>pelvic_floor</t>
+          <t>sleep_consultant</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -9911,7 +10177,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/</t>
+          <t>https://sleepingbaby.hashevet.co.il/sleep-pro/</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -9922,7 +10188,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>michalgilad@gmail.com</t>
+          <t>tali4baby@gmail.com</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -9935,7 +10201,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.michalgilad.com/</t>
+          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -9945,12 +10211,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>לכאבים אורטופדים בהריון טיפולים לימפטיים שיקום רצפת האגן הכנה ללידה Contact Describe your image Describe your image 1/7 התקשרו אלי ליצירת קשר וקביעת טיפול מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com I agree to the terms &amp; conditions שלח הפרטים ישמשו רק ליצירת קשר ולא יעברו לצד שלישי. תודה על הפניה. Back to to</t>
+          <t>ות, מענה לשאלות וסיכום. בין המפגשים יתקיים ליווי ההורים בעבודה לפי התוכנית הספציפית אשר גובשה באמצעות שיחות טלפוניות ומיילים. אתם מוזמנים לפנות אל טלי גליקסמן לשיחת הסבר והרחבה ומענה לשאלותיכם. טלפון: 050-848-6651 מייל: tali4baby@gmail.com Post navigation → גדילת תינוקות הדרכה והכוונה להורים החדשים למניעת עיכוב התפתחותי שמונת היסודות להתפתחות מיטבית ← קישורים מרכזיים בריאות ילדים בראייה הוליסטית טלי גליקסמן מומחית להתפתחות תינוקות אודות</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"שיקום רצפת האגן" רצפת אגן</t>
+          <t>"טלי גליקסמן" יועצת שינה</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -9960,11 +10226,11 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@yaeltzur.co.il", "confidence": 80, "source_url": "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "identity_url": "https://www.yaeltzur.co.il/talie-gliksman/", "evidence": "[email protected]", "matched_query": "\"טלי גליקסמן\" יועצת שינה", "extraction_method": "linked_cloudflare"}]</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
@@ -9972,23 +10238,23 @@
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-09-03T19:11:34.001809+00:00</t>
+          <t>2026-09-04T04:15:05.038841+00:00</t>
         </is>
       </c>
       <c r="W61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
         <v>6</v>
       </c>
       <c r="Z61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -9997,11 +10263,11 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/", "https://www.gov.il/he/departments/ministry_of_health/govil-landing-page", "https://www.szmc.org.il/departments/clinics-and-institutes/machleket-physiotherapia/shikum-ritzpat-agan/", "https://www.shamir.org/clinics/physiotherapy/pelvis/", "https://asafpt.com/pelvic-floor/", "https://asafpt.com/about/", "https://asafpt.com/contact/", "https://he.hadassah.org.il/physiotherapy/pelvic-floor-physiotherapy/", "https://www.michalgilad.com/", "https://www.wix.com/lpviral/enviral?utm_campaign=vir_wixad_live&amp;adsVersion=banner_2024&amp;orig_msid=aa99f552-cce6-4d9b-96f0-a304175f7068&amp;orig_msid=ad07a822-90b8-4e00-adec-53cda74130fe&amp;adsVersion=banner_2024", "https://www.michalgilad.com/#aboutus"]</t>
+          <t>["https://sleepingbaby.hashevet.co.il/sleep-pro/", "https://sleepingbaby.hashevet.co.il/sleep-pro/#about", "https://www.huggies.co.il/professionals/tali-gliksman", "https://www.huggies.co.il/contact-us", "https://www.facebook.com/hashevet/", "https://www.yaeltzur.co.il/talie-gliksman/", "https://www.allinternet.co.il/", "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "https://www.yaeltzur.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.yaeltzur.co.il/cdn-cgi/l/email-protection#96fff8f0f9d6eff7f3fae2ece3e4b8f5f9b8fffa", "https://linktr.ee/tali4baby", "https://www.hashevet.co.il/", "https://linktr.ee/s/about/trust-center/report?field86145911=https%3A%2F%2Flinktr.ee%2Ftali4baby", "https://linktr.ee/blog/daisy-chain-fields-sticker-pack", "https://linktr.ee/features/contact-forms", "https://linktr.ee/features/audience-management", "https://linktr.ee/features/email-integrations", "https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/", "https://www.hashevet.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.hashevet.co.il/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/%D7%94%D7%93%D7%A8%D7%9B%D7%94%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/", "https://www.hashevet.co.il/category/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.853020188851841e+16</v>
+        <v>5.600238792974453e+16</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10012,7 +10278,7 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://www.michalgilad.com/</t>
+          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
@@ -10020,19 +10286,23 @@
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV61" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10043,16 +10313,16 @@
         <v>13</v>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>שיקום רצפת האגן</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>pelvic_floor</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -10067,18 +10337,18 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>michalgilad@gmail.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -10091,7 +10361,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.michalgilad.com/</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10101,12 +10371,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>לכאבים אורטופדים בהריון טיפולים לימפטיים שיקום רצפת האגן הכנה ללידה Contact Describe your image Describe your image 1/7 התקשרו אלי ליצירת קשר וקביעת טיפול מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com I agree to the terms &amp; conditions שלח הפרטים ישמשו רק ליצירת קשר ולא יעברו לצד שלישי. תודה על הפניה. Back to to</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"שיקום רצפת האגן" רצפת אגן</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10116,35 +10386,35 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-03T19:11:34.001809+00:00</t>
         </is>
       </c>
       <c r="W62" t="n">
         <v>2</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -10153,11 +10423,11 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/", "https://www.gov.il/he/departments/ministry_of_health/govil-landing-page", "https://www.szmc.org.il/departments/clinics-and-institutes/machleket-physiotherapia/shikum-ritzpat-agan/", "https://www.shamir.org/clinics/physiotherapy/pelvis/", "https://asafpt.com/pelvic-floor/", "https://asafpt.com/about/", "https://asafpt.com/contact/", "https://he.hadassah.org.il/physiotherapy/pelvic-floor-physiotherapy/", "https://www.michalgilad.com/", "https://www.wix.com/lpviral/enviral?utm_campaign=vir_wixad_live&amp;adsVersion=banner_2024&amp;orig_msid=aa99f552-cce6-4d9b-96f0-a304175f7068&amp;orig_msid=ad07a822-90b8-4e00-adec-53cda74130fe&amp;adsVersion=banner_2024", "https://www.michalgilad.com/#aboutus"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.482924524247139e+16</v>
+        <v>5.559060566555523e+16</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10168,29 +10438,31 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.michalgilad.com/</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR62" t="inlineStr">
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU62" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV62" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10205,7 +10477,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>שלומית שדמון</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10236,7 +10508,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>shlomitshadmon@gmail.com</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -10249,7 +10521,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -10259,12 +10531,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"שלומית שדמון"</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10274,11 +10546,11 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
@@ -10286,7 +10558,7 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -10299,10 +10571,10 @@
         <v>4</v>
       </c>
       <c r="Z63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -10311,11 +10583,11 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.482924524247139e+16</v>
+        <v>4.448773572741416e+16</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10326,7 +10598,7 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr"/>
@@ -10336,19 +10608,23 @@
         <v>0</v>
       </c>
       <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR63" t="inlineStr">
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV63" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10358,15 +10634,17 @@
       <c r="A64" t="n">
         <v>13</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>6</v>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>תזונה אחרי לידה- תזונה בהנקה</t>
+          <t>שרון שלמה קלייטמן</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>pregnancy_dietitian</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -10381,18 +10659,18 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/תזונה-אחרי-לידה-תזונה-בהנקה/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>neta.amiri@gmail.com</t>
+          <t>sharon.kleitman@gmail.com</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10405,7 +10683,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -10415,12 +10693,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>י הגישה הטיפולית סיפורי האישי: כך ירדתי במשקל לתמיד שירותים ייעוץ דיאטנית בניית תפריט שבועי לגן ילדים/ צהרונים הרצאות וסדנאות בתזונה שחלות פוליציסטיות/ טיפולי פוריות מאמרים מתכונים סרטונים יצירת קשר צרי קשר: 050-4350466 neta.amiri@gmail.com 1Z0-053 1Z0-517 640-461 640-722 642-832 648-375 74-344 74-409 A00-212 C2010-503 C2010-598 C2010-651 C2010-652 C2020-605 OG0-091 070-413 070-459 070-496 1Z0-052 C_BOSUP_90 ﻿ תזונה אחרי לידה- תזונה בהנ</t>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"שרון שלמה קלייטמן"</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -10440,30 +10718,38 @@
         <v>0</v>
       </c>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
+        </is>
+      </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>["https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/"]</t>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.448773572741416e+16</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10474,27 +10760,33 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
+      <c r="AL64" t="b">
+        <v>0</v>
+      </c>
       <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV64" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10507,7 +10799,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>תזונה ופוריות</t>
+          <t>תזונה אחרי לידה- תזונה בהנקה</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10527,7 +10819,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/תזונה-ופוריות/</t>
+          <t>https://tzunatbar.co.il/תזונה-אחרי-לידה-תזונה-בהנקה/</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -10538,7 +10830,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>benharoush@gmail.com</t>
+          <t>neta.amiri@gmail.com</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -10551,7 +10843,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
+          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -10561,7 +10853,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>ור לך בתקופת טיפולי הפוריות חשיבותה של התזונה הסינית והמאקרוביוטית בכניסה להריון תזונה ופוריות O.M.D – מומחית לרפואה סינית – רפואה סינית וטיפולי פוריות יצירת קשר מרפאה בפתח תקווה: 050-5589013 מרפאה בתל אביב: 053-9956805 benharoush@gmail.com הרצל רוזנבלום 8 (מתחם סי אנד סאן) תל אביב אנצו סירני 7 פתח תקוה מה באתר דף הבית ויקיפוריות ויקיפוריות - גלריית הסרטונים ויקיפוריות -האנציקלופדיה הוירטואלית פורטל החדשנות של עולם הפוריות מרכז מומחים ב</t>
+          <t>י הגישה הטיפולית סיפורי האישי: כך ירדתי במשקל לתמיד שירותים ייעוץ דיאטנית בניית תפריט שבועי לגן ילדים/ צהרונים הרצאות וסדנאות בתזונה שחלות פוליציסטיות/ טיפולי פוריות מאמרים מתכונים סרטונים יצירת קשר צרי קשר: 050-4350466 neta.amiri@gmail.com 1Z0-053 1Z0-517 640-461 640-722 642-832 648-375 74-344 74-409 A00-212 C2010-503 C2010-598 C2010-651 C2010-652 C2020-605 OG0-091 070-413 070-459 070-496 1Z0-052 C_BOSUP_90 ﻿ תזונה אחרי לידה- תזונה בהנ</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -10605,11 +10897,11 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>["https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.yourdiet.co.il/", "https://wikifertility.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/"]</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10620,7 +10912,7 @@
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
+          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr"/>
@@ -10628,19 +10920,23 @@
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR65" t="inlineStr">
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV65" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10653,12 +10949,12 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Adi Kliffer Barmeir</t>
+          <t>תזונה ופוריות</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>lactation</t>
+          <t>pregnancy_dietitian</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -10673,18 +10969,18 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a2%d7%93%d7%99-%d7%a7%d7%9c%d7%99%d7%a4%d7%a8-%d7%91%d7%a8-%d7%9e%d7%90%d7%99%d7%a8/</t>
+          <t>https://wikifertility.com/תזונה-ופוריות/</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ialp</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>adi@kliffer.com</t>
+          <t>benharoush@gmail.com</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -10693,11 +10989,11 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
+          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -10707,7 +11003,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>adi@kliffer.com</t>
+          <t>ור לך בתקופת טיפולי הפוריות חשיבותה של התזונה הסינית והמאקרוביוטית בכניסה להריון תזונה ופוריות O.M.D – מומחית לרפואה סינית – רפואה סינית וטיפולי פוריות יצירת קשר מרפאה בפתח תקווה: 050-5589013 מרפאה בתל אביב: 053-9956805 benharoush@gmail.com הרצל רוזנבלום 8 (מתחם סי אנד סאן) תל אביב אנצו סירני 7 פתח תקוה מה באתר דף הבית ויקיפוריות ויקיפוריות - גלריית הסרטונים ויקיפוריות -האנציקלופדיה הוירטואלית פורטל החדשנות של עולם הפוריות מרכז מומחים ב</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -10717,7 +11013,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -10751,11 +11047,11 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/", "https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/#contact"]</t>
+          <t>["https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.yourdiet.co.il/", "https://wikifertility.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -10766,7 +11062,7 @@
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
+          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr"/>
@@ -10774,19 +11070,23 @@
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV66" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10799,7 +11099,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ariella Dubrowin</t>
+          <t>Adi Kliffer Barmeir</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -10819,7 +11119,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%90%d7%a8%d7%99%d7%90%d7%9c%d7%94-%d7%93%d7%95%d7%91%d7%a8%d7%90%d7%95%d7%99%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%a2%d7%93%d7%99-%d7%a7%d7%9c%d7%99%d7%a4%d7%a8-%d7%91%d7%a8-%d7%9e%d7%90%d7%99%d7%a8/</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -10830,7 +11130,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ariella@hanakatova.com</t>
+          <t>adi@kliffer.com</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -10843,7 +11143,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -10853,7 +11153,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אריאלה דובראוין – Ariella Dubrowin טלפון: 054-6458027 אימייל: ariella@hanakatova.com הסמכה: מדריכת הנקה אזורי קבלה: ירושלים והסביבה, מרכז, שפלה ערים/ישובים: ירושלים, בית שמש, ביתר עילית, אפרת, אלון שבות, כפר עציון, ראש צורים, אלעזר, בת עין, מגדל עוז, תקוע, נוקדים, מעלה עמוס, פני קד</t>
+          <t>adi@kliffer.com</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -10863,7 +11163,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -10897,11 +11197,11 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/", "https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -10912,7 +11212,7 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr"/>
@@ -10920,19 +11220,23 @@
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr"/>
-      <c r="AN67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV67" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -10945,7 +11249,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Aviella Natalie</t>
+          <t>Ariella Dubrowin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -10965,7 +11269,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%90%d7%91%d7%99%d7%90%d7%9c%d7%94/</t>
+          <t>https://ialp.org.il/counselors/%d7%90%d7%a8%d7%99%d7%90%d7%9c%d7%94-%d7%93%d7%95%d7%91%d7%a8%d7%90%d7%95%d7%99%d7%9f/</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -10976,7 +11280,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>natalie.by@mail.huji.ac.il</t>
+          <t>ariella@hanakatova.com</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -10989,7 +11293,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -10999,7 +11303,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אביאלה נטלי – Aviella Natalie טלפון: 050-6523233 אימייל: natalie.by@mail.huji.ac.il הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שרון ערים/ישובים: תל אביב, הרצליה, כפר סבא, רעננה, רמת גן, גבעתיים, בני ברק, פתח תקוה, קריית אונו, ראשון לציון. שפות: אנגלית, עברית</t>
+          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אריאלה דובראוין – Ariella Dubrowin טלפון: 054-6458027 אימייל: ariella@hanakatova.com הסמכה: מדריכת הנקה אזורי קבלה: ירושלים והסביבה, מרכז, שפלה ערים/ישובים: ירושלים, בית שמש, ביתר עילית, אפרת, אלון שבות, כפר עציון, ראש צורים, אלעזר, בת עין, מגדל עוז, תקוע, נוקדים, מעלה עמוס, פני קד</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -11043,11 +11347,11 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11058,7 +11362,7 @@
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr"/>
@@ -11066,19 +11370,23 @@
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr"/>
-      <c r="AN68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV68" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11091,7 +11399,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dalit Elan</t>
+          <t>Aviella Natalie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11111,7 +11419,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%93%d7%9c%d7%99%d7%aa-%d7%90%d7%99%d7%9c%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%90%d7%91%d7%99%d7%90%d7%9c%d7%94/</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -11122,7 +11430,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>delan@017.net.il</t>
+          <t>natalie.by@mail.huji.ac.il</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -11135,7 +11443,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -11145,7 +11453,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דלית אילן – Dalit Elan טלפון: 050-9200925 אימייל: delan@017.net.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: שרון ערים/ישובים: מזרחית לכביש 4 עד יהוד בדרום וכביש 57 בצפון. מגיעה לאריאל שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: דלית, אמא לשלוש בנות, יועצת הנקה בעלת </t>
+          <t>על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אביאלה נטלי – Aviella Natalie טלפון: 050-6523233 אימייל: natalie.by@mail.huji.ac.il הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שרון ערים/ישובים: תל אביב, הרצליה, כפר סבא, רעננה, רמת גן, גבעתיים, בני ברק, פתח תקוה, קריית אונו, ראשון לציון. שפות: אנגלית, עברית</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -11189,11 +11497,11 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/", "https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/#contact"]</t>
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11204,7 +11512,7 @@
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr"/>
@@ -11212,19 +11520,23 @@
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr"/>
-      <c r="AN69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV69" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11237,7 +11549,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Devorah Shaked</t>
+          <t>Dalit Elan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11257,7 +11569,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%93%d7%91%d7%95%d7%a8%d7%94-%d7%a9%d7%a7%d7%93/</t>
+          <t>https://ialp.org.il/counselors/%d7%93%d7%9c%d7%99%d7%aa-%d7%90%d7%99%d7%9c%d7%9f/</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -11268,7 +11580,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>devorah@almondweb.com</t>
+          <t>delan@017.net.il</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -11281,7 +11593,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -11291,7 +11603,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דבורה שקד – Devorah Shaked טלפון: 054-4773421 אימייל: devorah@almondweb.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: ירושלים והסביבה ערים/ישובים: ירושלים והסביבה, גבעת זאב, כוכב יעקב, גוש עציון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: מעל 30 שנות ניסיון כתומכת </t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דלית אילן – Dalit Elan טלפון: 050-9200925 אימייל: delan@017.net.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: שרון ערים/ישובים: מזרחית לכביש 4 עד יהוד בדרום וכביש 57 בצפון. מגיעה לאריאל שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: דלית, אמא לשלוש בנות, יועצת הנקה בעלת </t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -11335,11 +11647,11 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/", "https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/", "https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11350,7 +11662,7 @@
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr"/>
@@ -11358,19 +11670,23 @@
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr"/>
-      <c r="AN70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR70" t="inlineStr">
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV70" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11383,7 +11699,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hagit Naim</t>
+          <t>Devorah Shaked</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11403,7 +11719,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%97%d7%92%d7%99%d7%aa-%d7%a0%d7%a2%d7%99%d7%9d/</t>
+          <t>https://ialp.org.il/counselors/%d7%93%d7%91%d7%95%d7%a8%d7%94-%d7%a9%d7%a7%d7%93/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -11414,7 +11730,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>hagit04@inter.net.il</t>
+          <t>devorah@almondweb.com</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -11427,7 +11743,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -11437,7 +11753,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי חגית נעים – Hagit Naim טלפון: 052-4662443 אימייל: hagit04@inter.net.il הסמכה: מדריכת הנקה אזורי קבלה: מרכז, שפלה ערים/ישובים: ראשון לציון , נס ציונה, רחובות, באר יעקב, בת ים, חולון, גבעתיים, רמת גן , תל אביב, יפו קרית אונו, יהוד שפות: עברית הסדרים עם קופ"ח: קצת עלי: סבל</t>
+          <t xml:space="preserve">ות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דבורה שקד – Devorah Shaked טלפון: 054-4773421 אימייל: devorah@almondweb.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: ירושלים והסביבה ערים/ישובים: ירושלים והסביבה, גבעת זאב, כוכב יעקב, גוש עציון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: מעל 30 שנות ניסיון כתומכת </t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -11481,11 +11797,11 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/", "https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/", "https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/#contact"]</t>
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11496,7 +11812,7 @@
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr"/>
@@ -11504,19 +11820,23 @@
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr"/>
-      <c r="AN71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR71" t="inlineStr">
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV71" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11529,7 +11849,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Maddy Smadar Haran</t>
+          <t>Hagit Naim</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11549,7 +11869,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a1%d7%9e%d7%93%d7%a8-%d7%9e%d7%90%d7%93%d7%99-%d7%94%d7%a8%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%97%d7%92%d7%99%d7%aa-%d7%a0%d7%a2%d7%99%d7%9d/</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -11560,7 +11880,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>maddy@dmclub.co.il</t>
+          <t>hagit04@inter.net.il</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -11573,7 +11893,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -11583,7 +11903,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מאדי סמדר הרן – Maddy Smadar Haran טלפון: 054-3030901 אימייל: Maddy@dmclub.co.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: תל אביב, רמת גן, קרית אונו, גבעת שמואל, הרצליה, רעננה, הוד השרון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: גישה עניינית וידי</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי חגית נעים – Hagit Naim טלפון: 052-4662443 אימייל: hagit04@inter.net.il הסמכה: מדריכת הנקה אזורי קבלה: מרכז, שפלה ערים/ישובים: ראשון לציון , נס ציונה, רחובות, באר יעקב, בת ים, חולון, גבעתיים, רמת גן , תל אביב, יפו קרית אונו, יהוד שפות: עברית הסדרים עם קופ"ח: קצת עלי: סבל</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -11627,11 +11947,11 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/", "https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/", "https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/#contact"]</t>
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11642,7 +11962,7 @@
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr"/>
@@ -11650,19 +11970,23 @@
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr"/>
-      <c r="AN72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR72" t="inlineStr">
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV72" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11675,7 +11999,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Merav Matus</t>
+          <t>Maddy Smadar Haran</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11695,7 +12019,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%9e%d7%a8%d7%91-%d7%9e%d7%98%d7%95%d7%a1/</t>
+          <t>https://ialp.org.il/counselors/%d7%a1%d7%9e%d7%93%d7%a8-%d7%9e%d7%90%d7%93%d7%99-%d7%94%d7%a8%d7%9f/</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -11706,7 +12030,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>meravmatus@walla.com</t>
+          <t>maddy@dmclub.co.il</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -11719,7 +12043,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -11729,7 +12053,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מרב מטוס – Merav Matus טלפון: 050-6619578 אימייל: meravmatus@walla.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: גוש דן, מרכז ערים/ישובים: אלעד, ראש העין, שהם, פתח תקוה, אלקנה, שערי תקוה, אורנית ועץ אפריים שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית מושלם, לאומית, מאוחד</t>
+          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מאדי סמדר הרן – Maddy Smadar Haran טלפון: 054-3030901 אימייל: Maddy@dmclub.co.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: תל אביב, רמת גן, קרית אונו, גבעת שמואל, הרצליה, רעננה, הוד השרון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: גישה עניינית וידי</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -11773,11 +12097,11 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/", "https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/", "https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -11788,7 +12112,7 @@
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr"/>
@@ -11796,19 +12120,23 @@
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr"/>
-      <c r="AN73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR73" t="inlineStr">
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV73" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11821,7 +12149,7 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Natalie Levin</t>
+          <t>Merav Matus</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -11841,7 +12169,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%9c%d7%95%d7%99%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%9e%d7%a8%d7%91-%d7%9e%d7%98%d7%95%d7%a1/</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -11852,7 +12180,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>natalie@bshvil.com</t>
+          <t>meravmatus@walla.com</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -11865,7 +12193,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -11875,7 +12203,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>דות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי נטלי לוין – Natalie Levin טלפון: 052-5787072 אימייל: natalie@bshvil.com הסמכה: מדריכת הנקה אזורי קבלה: דרום ערים/ישובים: אשדוד, אשקלון, קרית גת, קרית מלאכי, שדרות ויישובי הסביבה שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: שמי נטלי, מדריכת הנקה מוסמכת, אמא לשניים. כאמא חו</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מרב מטוס – Merav Matus טלפון: 050-6619578 אימייל: meravmatus@walla.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: גוש דן, מרכז ערים/ישובים: אלעד, ראש העין, שהם, פתח תקוה, אלקנה, שערי תקוה, אורנית ועץ אפריים שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית מושלם, לאומית, מאוחד</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -11919,11 +12247,11 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/", "https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/#contact"]</t>
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -11934,7 +12262,7 @@
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr"/>
@@ -11942,19 +12270,23 @@
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr"/>
-      <c r="AN74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR74" t="inlineStr">
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV74" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -11967,7 +12299,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sarit Perez</t>
+          <t>Natalie Levin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -11987,7 +12319,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a9%d7%a8%d7%99%d7%aa-%d7%a4%d7%a8%d7%a5/</t>
+          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%9c%d7%95%d7%99%d7%9f/</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -11998,7 +12330,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>saritush85@walla.com</t>
+          <t>natalie@bshvil.com</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -12011,7 +12343,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -12021,7 +12353,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי שרית פרץ – Sarit Perez טלפון: 052-5673614 אימייל: saritush85@walla.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: דרום ערים/ישובים: שדרות נתיבות יישובים קיבוצים מושבים בסביבה שפות: עברית הסדרים עם קופ"ח: קצת עלי: אמא לארבע מתוקות , אחות מוסמכת ויועצת הנקה מבחינתי ה</t>
+          <t>דות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי נטלי לוין – Natalie Levin טלפון: 052-5787072 אימייל: natalie@bshvil.com הסמכה: מדריכת הנקה אזורי קבלה: דרום ערים/ישובים: אשדוד, אשקלון, קרית גת, קרית מלאכי, שדרות ויישובי הסביבה שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: שמי נטלי, מדריכת הנקה מוסמכת, אמא לשניים. כאמא חו</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -12065,11 +12397,11 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/", "https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12080,7 +12412,7 @@
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr"/>
@@ -12088,19 +12420,23 @@
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr"/>
-      <c r="AN75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR75" t="inlineStr">
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV75" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12113,7 +12449,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Shirley Amit Shalam</t>
+          <t>Sarit Perez</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12133,7 +12469,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a9%d7%99%d7%a8%d7%9c%d7%99-%d7%a2%d7%9e%d7%99%d7%aa-%d7%a9%d7%9c%d7%9d/</t>
+          <t>https://ialp.org.il/counselors/%d7%a9%d7%a8%d7%99%d7%aa-%d7%a4%d7%a8%d7%a5/</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -12144,7 +12480,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>shirley@shalam.co.il</t>
+          <t>saritush85@walla.com</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -12157,7 +12493,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -12167,7 +12503,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>shirley@shalam.co.il</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי שרית פרץ – Sarit Perez טלפון: 052-5673614 אימייל: saritush85@walla.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: דרום ערים/ישובים: שדרות נתיבות יישובים קיבוצים מושבים בסביבה שפות: עברית הסדרים עם קופ"ח: קצת עלי: אמא לארבע מתוקות , אחות מוסמכת ויועצת הנקה מבחינתי ה</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -12177,7 +12513,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -12211,11 +12547,11 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/", "https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/", "https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/#contact"]</t>
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12226,7 +12562,7 @@
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr"/>
@@ -12234,19 +12570,23 @@
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="inlineStr"/>
-      <c r="AN76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR76" t="inlineStr">
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV76" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>
@@ -12259,7 +12599,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yael Giller</t>
+          <t>Shirley Amit Shalam</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12279,7 +12619,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%99%d7%a2%d7%9c-%d7%92%d7%99%d7%9c%d7%a8/</t>
+          <t>https://ialp.org.il/counselors/%d7%a9%d7%99%d7%a8%d7%9c%d7%99-%d7%a2%d7%9e%d7%99%d7%aa-%d7%a9%d7%9c%d7%9d/</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -12290,7 +12630,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>yael@tly.org.il</t>
+          <t>shirley@shalam.co.il</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -12303,7 +12643,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -12313,7 +12653,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יעל גילר – Yael Giller טלפון: 054-2399534 אימייל: yael@tly.org.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: נתניה, חדרה, כפר סבא, הוד השרון, רעננה, תל אביב והסביבה, אמת השרון, מושבי השרון ועמק חפר. שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: ש</t>
+          <t>shirley@shalam.co.il</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -12323,7 +12663,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -12357,11 +12697,11 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/", "https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/", "https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/#contact"]</t>
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.482416151081473e+16</v>
+        <v>4.447248453244418e+16</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12372,7 +12712,7 @@
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr"/>
@@ -12380,19 +12720,173 @@
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr"/>
-      <c r="AN77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR77" t="inlineStr">
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>13</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Yael Giller</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>lactation</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%d7%99%d7%a2%d7%9c-%d7%92%d7%99%d7%9c%d7%a8/</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>ialp</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>yael@tly.org.il</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>98</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יעל גילר – Yael Giller טלפון: 054-2399534 אימייל: yael@tly.org.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: נתניה, חדרה, כפר סבא, הוד השרון, רעננה, תל אביב והסביבה, אמת השרון, מושבי השרון ועמק חפר. שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: ש</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>seed_source</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>["https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/", "https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/#contact"]</t>
+        </is>
+      </c>
+      <c r="AD78" t="n">
+        <v>4.447248453244418e+16</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV78" t="inlineStr">
         <is>
           <t>PERSON</t>
         </is>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.943390679798868e+16</v>
+        <v>1.78301720393966e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.822485035801138e+16</v>
+        <v>1.446745510740341e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>4.822427849505779e+16</v>
+        <v>1.446728354851734e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>5.945424172461531e+16</v>
+        <v>1.783627251738459e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.822485035801146e+16</v>
+        <v>1.446745510740344e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4.822485035801146e+16</v>
+        <v>1.446745510740344e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>4.819434796805247e+16</v>
+        <v>1.445830439041574e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>6.684598755339604e+16</v>
+        <v>2.005379626601881e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>5.943390679798868e+16</v>
+        <v>1.78301720393966e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>4.81943479680715e+16</v>
+        <v>1.445830439042145e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>4.819377610511784e+16</v>
+        <v>1.445813283153535e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>5.56431375593407e+16</v>
+        <v>1.669294126780221e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>5.929664604325891e+16</v>
+        <v>1.778899381297767e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.819434796805247e+16</v>
+        <v>1.445830439041574e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>6.68510712850527e+16</v>
+        <v>2.005532138551581e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4.572308251998205e+16</v>
+        <v>1.371692475599462e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4.461540088176475e+16</v>
+        <v>1.338462026452943e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8197,7 +8197,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4.461482901883061e+16</v>
+        <v>1.338444870564918e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4.461482901883061e+16</v>
+        <v>1.338444870564918e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4.460974528717395e+16</v>
+        <v>1.338292358615219e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.45182381173541e+16</v>
+        <v>1.335547143520623e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4.451993269457299e+16</v>
+        <v>1.33559798083719e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9309,7 +9309,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4.818360864180453e+16</v>
+        <v>1.445508259254136e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9793,7 +9793,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.817852491014786e+16</v>
+        <v>1.445355747304436e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>5.600238792974453e+16</v>
+        <v>1.680071637892336e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>4.448773572741416e+16</v>
+        <v>1.334632071822425e+17</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4.448773572741416e+16</v>
+        <v>1.334632071822425e+17</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11201,7 +11201,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11351,7 +11351,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11651,7 +11651,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11951,7 +11951,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12251,7 +12251,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12551,7 +12551,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12851,7 +12851,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV78"/>
+  <dimension ref="A1:AV79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.78301720393966e+17</v>
+        <v>5.349051611818981e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.446745510740341e+17</v>
+        <v>4.340236532221023e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.446728354851734e+17</v>
+        <v>4.340185064555201e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.783627251738459e+17</v>
+        <v>5.350881755215378e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.446745510740344e+17</v>
+        <v>4.340236532221031e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.446745510740344e+17</v>
+        <v>4.340236532221031e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.445830439041574e+17</v>
+        <v>4.337491317124723e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2.005379626601881e+17</v>
+        <v>6.016138879805644e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.78301720393966e+17</v>
+        <v>5.349051611818981e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5656,15 +5656,17 @@
       <c r="A33" t="n">
         <v>13</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>6</v>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>שיין ברגנר</t>
+          <t>רחל דהן</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>midwife</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5679,18 +5681,18 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/שיין-ברגנר/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>shaynemidwife@gmail.com</t>
+          <t>racheldahan@hotmail.com</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5703,7 +5705,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5713,12 +5715,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>דת בית לבחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה שיין ברגנר 0523627000 WhatsApp shaynemidwife@gmail.com אשל 15, עומר שיין , אם לחמישה ילדים שנולדו בלידה טבעית ובבית , מיילדת נשים בביתן מזה יותר משלושים שנה. לפי תפיסת עולמה של שיין לאישה וליילוד זכות על גופם והיא מאמינה בכבוד ובקדושת חוויית הלידה . ב</t>
+          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"רחל דהן" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5735,44 +5737,52 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-09-10T13:53:25.006579+00:00</t>
+        </is>
+      </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/"]</t>
+          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.003947683133098e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
@@ -5780,10 +5790,20 @@
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
+      <c r="AN33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
+        </is>
+      </c>
       <c r="AR33" t="n">
         <v>1</v>
       </c>
@@ -5806,17 +5826,15 @@
       <c r="A34" t="n">
         <v>13</v>
       </c>
-      <c r="B34" t="n">
-        <v>6</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>אוהד חורי</t>
+          <t>שיין ברגנר</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>midwife</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5831,18 +5849,18 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.imahi.co.il/שיין-ברגנר/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ohadho@clalit.org.il</t>
+          <t>shaynemidwife@gmail.com</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5851,11 +5869,11 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5865,17 +5883,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>דת בית לבחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה שיין ברגנר 0523627000 WhatsApp shaynemidwife@gmail.com אשל 15, עומר שיין , אם לחמישה ילדים שנולדו בלידה טבעית ובבית , מיילדת נשים בביתן מזה יותר משלושים שנה. לפי תפיסת עולמה של שיין לאישה וליילוד זכות על גופם והיא מאמינה בכבוד ובקדושת חוויית הלידה . ב</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -5890,38 +5908,30 @@
         <v>0</v>
       </c>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>2026-09-09T23:21:42.073181+00:00</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
+          <t>["https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.445830439042145e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5932,7 +5942,7 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
@@ -5940,20 +5950,10 @@
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
-        </is>
-      </c>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="n">
         <v>1</v>
       </c>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6035,17 +6035,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -6062,36 +6062,36 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W35" t="n">
+        <v>8</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2</v>
       </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1</v>
-      </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.445813283153535e+17</v>
+        <v>4.337491317126436e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6102,20 +6102,28 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
+      <c r="AN35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
       <c r="AR35" t="n">
         <v>1</v>
       </c>
@@ -6143,7 +6151,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6174,7 +6182,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6187,7 +6195,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6197,12 +6205,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6224,36 +6232,36 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.445813283153535e+17</v>
+        <v>4.337439849460605e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6264,7 +6272,7 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
@@ -6305,7 +6313,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6336,7 +6344,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6349,7 +6357,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6359,12 +6367,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6386,36 +6394,36 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.445813283153535e+17</v>
+        <v>4.337439849460605e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6426,7 +6434,7 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
@@ -6467,7 +6475,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6498,7 +6506,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6511,7 +6519,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6521,12 +6529,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6548,36 +6556,36 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
         <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.337439849460605e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6588,7 +6596,7 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
@@ -6629,7 +6637,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6649,18 +6657,18 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6673,7 +6681,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6683,12 +6691,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6705,25 +6713,25 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
@@ -6735,11 +6743,11 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.669294126780221e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6750,7 +6758,7 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -6791,7 +6799,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6811,7 +6819,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6822,7 +6830,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6835,7 +6843,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6845,12 +6853,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6867,25 +6875,25 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
@@ -6897,11 +6905,11 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.778899381297767e+17</v>
+        <v>5.007882380340662e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6912,7 +6920,7 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
@@ -6953,7 +6961,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6973,7 +6981,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6984,7 +6992,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6997,7 +7005,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7007,12 +7015,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7034,14 +7042,14 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
         <v>4</v>
@@ -7059,11 +7067,11 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>5.336698143893302e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7074,7 +7082,7 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
@@ -7115,7 +7123,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7135,18 +7143,18 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7159,7 +7167,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7169,17 +7177,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -7196,36 +7204,36 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
+        <v>2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
         <v>4</v>
       </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1</v>
-      </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
         <v>1</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.445830439041574e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7236,7 +7244,7 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
@@ -7277,12 +7285,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>היחידה לפוריות והפריה חוץ גופית</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>fertility_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7297,18 +7305,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>idoba@szmc.org.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7321,7 +7329,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7331,17 +7339,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -7353,41 +7361,41 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-04T18:29:47.683340+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X43" t="n">
         <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2.005532138551581e+17</v>
+        <v>4.337491317124723e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7398,7 +7406,7 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
@@ -7439,12 +7447,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>היחידה לפוריות והפריה חוץ גופית</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>fertility_doctor</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -7459,18 +7467,18 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>idoba@szmc.org.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7483,7 +7491,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7493,12 +7501,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7515,28 +7523,28 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-04T18:29:47.683340+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
         <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -7545,11 +7553,11 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>6.016596415654743e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7560,7 +7568,7 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
@@ -7601,7 +7609,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7632,7 +7640,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7645,7 +7653,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7655,12 +7663,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7682,7 +7690,7 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
@@ -7692,10 +7700,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7707,11 +7715,11 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7722,7 +7730,7 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
@@ -7763,7 +7771,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7794,7 +7802,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7807,7 +7815,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7817,12 +7825,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7844,7 +7852,7 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -7869,11 +7877,11 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.371692475599462e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7884,7 +7892,7 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
@@ -7925,7 +7933,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7956,7 +7964,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7969,7 +7977,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -7979,12 +7987,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8006,14 +8014,14 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
         <v>2</v>
@@ -8031,11 +8039,11 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.338462026452943e+17</v>
+        <v>4.115077426798385e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8046,7 +8054,7 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
@@ -8087,7 +8095,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8118,7 +8126,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -8131,7 +8139,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8141,12 +8149,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8163,41 +8171,41 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
+        <v>4</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
         <v>2</v>
       </c>
-      <c r="X48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>5</v>
-      </c>
       <c r="Z48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.338444870564918e+17</v>
+        <v>4.015386079358828e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8208,7 +8216,7 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
@@ -8249,7 +8257,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8280,7 +8288,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8293,7 +8301,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8303,12 +8311,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8330,7 +8338,7 @@
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
@@ -8340,26 +8348,26 @@
         <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.338444870564918e+17</v>
+        <v>4.015334611694755e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8370,7 +8378,7 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -8411,7 +8419,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8442,7 +8450,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8455,7 +8463,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8465,12 +8473,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8487,41 +8495,41 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
         <v>2</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.015334611694755e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8532,7 +8540,7 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
@@ -8573,7 +8581,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8604,7 +8612,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8617,7 +8625,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8627,12 +8635,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8654,7 +8662,7 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
@@ -8664,26 +8672,26 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.338292358615219e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8694,7 +8702,7 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
@@ -8735,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8766,7 +8774,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8779,7 +8787,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8789,12 +8797,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8816,7 +8824,7 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
@@ -8826,13 +8834,13 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -8841,11 +8849,11 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.335547143520623e+17</v>
+        <v>4.014877075845656e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8856,7 +8864,7 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
@@ -8897,7 +8905,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8928,7 +8936,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8941,7 +8949,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -8951,12 +8959,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -8973,12 +8981,12 @@
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
@@ -8991,10 +8999,10 @@
         <v>6</v>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -9003,11 +9011,11 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.33559798083719e+17</v>
+        <v>4.006641430561869e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9018,7 +9026,7 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
@@ -9054,20 +9062,22 @@
       <c r="A54" t="n">
         <v>13</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>6</v>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hadas Dar</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>lactation</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -9077,18 +9087,18 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%94%d7%93%d7%a1-%d7%93%d7%a8/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ialp</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>hadasdar127@gmail.com</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -9097,11 +9107,11 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9111,12 +9121,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>הבית אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי הדס דר – Hadas Dar טלפון: 052-8902748 אימייל: hadasdar127@gmail.com הסמכה: מדריכת הנקה אזורי קבלה: גוש דן, מרכז, שומרון, שרון ערים/ישובים: אורנית, שערי תקוה, אלקנה, עץ אפריים, ראש העין, הוד השרון, פתח-תקוה, כפר-סבא שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: מדריכ</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -9133,33 +9143,41 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
+        </is>
+      </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/", "https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/#contact"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.006793942511569e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9170,13 +9188,15 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
+      <c r="AL54" t="b">
+        <v>0</v>
+      </c>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="inlineStr"/>
@@ -9207,7 +9227,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Liel Boker</t>
+          <t>Hadas Dar</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9227,7 +9247,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%9c%d7%99%d7%90%d7%9c-%d7%91%d7%95%d7%a7%d7%a8/</t>
+          <t>https://ialp.org.il/counselors/%d7%94%d7%93%d7%a1-%d7%93%d7%a8/</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -9238,7 +9258,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>lielhadid@gmail.com</t>
+          <t>hadasdar127@gmail.com</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -9251,7 +9271,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9261,7 +9281,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>ת אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יאל בוקר – Liel Boker טלפון: 054-3515013 אימייל: Lielhadid@gmail.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שפלה ערים/ישובים: קוה, פתח תקווה, גבעת שמואל, קרית אונו, אור יהודה, רמת גן,בני ברק, גבעתיים, יהוד, מגשימים, אזור, חולון, נחלים, בארות יצחק</t>
+          <t>הבית אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי הדס דר – Hadas Dar טלפון: 052-8902748 אימייל: hadasdar127@gmail.com הסמכה: מדריכת הנקה אזורי קבלה: גוש דן, מרכז, שומרון, שרון ערים/ישובים: אורנית, שערי תקוה, אלקנה, עץ אפריים, ראש העין, הוד השרון, פתח-תקוה, כפר-סבא שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: מדריכ</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -9305,11 +9325,11 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/", "https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/", "https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9320,7 +9340,7 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
@@ -9354,17 +9374,15 @@
       <c r="A56" t="n">
         <v>13</v>
       </c>
-      <c r="B56" t="n">
-        <v>6</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>Liel Boker</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>lactation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9379,18 +9397,18 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://ialp.org.il/counselors/%d7%9c%d7%99%d7%90%d7%9c-%d7%91%d7%95%d7%a7%d7%a8/</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ialp</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>lielhadid@gmail.com</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -9403,7 +9421,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9413,12 +9431,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t>ת אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יאל בוקר – Liel Boker טלפון: 054-3515013 אימייל: Lielhadid@gmail.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שפלה ערים/ישובים: קוה, פתח תקווה, גבעת שמואל, קרית אונו, אור יהודה, רמת גן,בני ברק, גבעתיים, יהוד, מגשימים, אזור, חולון, נחלים, בארות יצחק</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9428,48 +9446,40 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/", "https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.445508259254136e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9480,15 +9490,13 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="inlineStr"/>
@@ -9521,7 +9529,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9552,7 +9560,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -9565,7 +9573,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9575,12 +9583,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9590,11 +9598,11 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -9602,23 +9610,23 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W57" t="n">
         <v>2</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -9627,11 +9635,11 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.445508259254136e+17</v>
+        <v>4.336524777762407e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9642,7 +9650,7 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
@@ -9683,7 +9691,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9714,7 +9722,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9727,7 +9735,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9737,12 +9745,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -9764,7 +9772,7 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
@@ -9774,10 +9782,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9789,11 +9797,11 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336524777762407e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9804,7 +9812,7 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
@@ -9845,7 +9853,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9876,7 +9884,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9889,7 +9897,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9899,12 +9907,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -9926,7 +9934,7 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
@@ -9951,11 +9959,11 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.445355747304436e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9966,7 +9974,7 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
@@ -10002,15 +10010,17 @@
       <c r="A60" t="n">
         <v>13</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>6</v>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>דפי רהב הס פסיכולוגית</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>perinatal_mental_health</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -10025,18 +10035,18 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>dafyrahav@gmail.com</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -10049,7 +10059,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10059,12 +10069,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>עמים ההיריון יופסק מבחירה ולפעמים לא ניתן לבחור. אנשי מקצוע רבים יגדירו את הפסקת ההריון כאירוע טראומתי עבור גוף האישה... &lt; המשך קריאה כתבות ומאמרים צרי קשר איך אוכל לעזור? דפי רהב הס 052-3302900 כרכור / טיפולים און ליין dafyrahav@gmail.com שלח נשלח! תודה שיצרת קשר צור קשר © כל הזכויות שמורות לדפי רהב הס bottom of page</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -10084,15 +10094,19 @@
         <v>0</v>
       </c>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
+        </is>
+      </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="n">
         <v>1</v>
@@ -10100,14 +10114,18 @@
       <c r="AA60" t="n">
         <v>0</v>
       </c>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://www.dafyrahavhass.com/", "https://www.dafyrahavhass.com/copy-of", "https://www.dafyrahavhass.com/aboutme"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.336067241913308e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10118,13 +10136,15 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
+      <c r="AL60" t="b">
+        <v>0</v>
+      </c>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
       <c r="AO60" t="inlineStr"/>
@@ -10152,17 +10172,15 @@
       <c r="A61" t="n">
         <v>13</v>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>טלי גליקסמן</t>
+          <t>דפי רהב הס פסיכולוגית</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>sleep_consultant</t>
+          <t>perinatal_mental_health</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -10177,7 +10195,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://sleepingbaby.hashevet.co.il/sleep-pro/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -10188,7 +10206,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>tali4baby@gmail.com</t>
+          <t>dafyrahav@gmail.com</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -10201,7 +10219,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10211,12 +10229,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>ות, מענה לשאלות וסיכום. בין המפגשים יתקיים ליווי ההורים בעבודה לפי התוכנית הספציפית אשר גובשה באמצעות שיחות טלפוניות ומיילים. אתם מוזמנים לפנות אל טלי גליקסמן לשיחת הסבר והרחבה ומענה לשאלותיכם. טלפון: 050-848-6651 מייל: tali4baby@gmail.com Post navigation → גדילת תינוקות הדרכה והכוונה להורים החדשים למניעת עיכוב התפתחותי שמונת היסודות להתפתחות מיטבית ← קישורים מרכזיים בריאות ילדים בראייה הוליסטית טלי גליקסמן מומחית להתפתחות תינוקות אודות</t>
+          <t>עמים ההיריון יופסק מבחירה ולפעמים לא ניתן לבחור. אנשי מקצוע רבים יגדירו את הפסקת ההריון כאירוע טראומתי עבור גוף האישה... &lt; המשך קריאה כתבות ומאמרים צרי קשר איך אוכל לעזור? דפי רהב הס 052-3302900 כרכור / טיפולים און ליין dafyrahav@gmail.com שלח נשלח! תודה שיצרת קשר צור קשר © כל הזכויות שמורות לדפי רהב הס bottom of page</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>"טלי גליקסמן" יועצת שינה</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10226,48 +10244,40 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>[{"email": "info@yaeltzur.co.il", "confidence": 80, "source_url": "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "identity_url": "https://www.yaeltzur.co.il/talie-gliksman/", "evidence": "[email protected]", "matched_query": "\"טלי גליקסמן\" יועצת שינה", "extraction_method": "linked_cloudflare"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>2026-09-04T04:15:05.038841+00:00</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://sleepingbaby.hashevet.co.il/sleep-pro/", "https://sleepingbaby.hashevet.co.il/sleep-pro/#about", "https://www.huggies.co.il/professionals/tali-gliksman", "https://www.huggies.co.il/contact-us", "https://www.facebook.com/hashevet/", "https://www.yaeltzur.co.il/talie-gliksman/", "https://www.allinternet.co.il/", "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "https://www.yaeltzur.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.yaeltzur.co.il/cdn-cgi/l/email-protection#96fff8f0f9d6eff7f3fae2ece3e4b8f5f9b8fffa", "https://linktr.ee/tali4baby", "https://www.hashevet.co.il/", "https://linktr.ee/s/about/trust-center/report?field86145911=https%3A%2F%2Flinktr.ee%2Ftali4baby", "https://linktr.ee/blog/daisy-chain-fields-sticker-pack", "https://linktr.ee/features/contact-forms", "https://linktr.ee/features/audience-management", "https://linktr.ee/features/email-integrations", "https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/", "https://www.hashevet.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.hashevet.co.il/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/%D7%94%D7%93%D7%A8%D7%9B%D7%94%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/", "https://www.hashevet.co.il/category/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.dafyrahavhass.com/", "https://www.dafyrahavhass.com/copy-of", "https://www.dafyrahavhass.com/aboutme"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.680071637892336e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10278,7 +10288,7 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
@@ -10317,12 +10327,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>שיקום רצפת האגן</t>
+          <t>טלי גליקסמן</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>pelvic_floor</t>
+          <t>sleep_consultant</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -10337,7 +10347,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/</t>
+          <t>https://sleepingbaby.hashevet.co.il/sleep-pro/</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -10348,7 +10358,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>michalgilad@gmail.com</t>
+          <t>tali4baby@gmail.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -10361,7 +10371,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.michalgilad.com/</t>
+          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10371,12 +10381,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>לכאבים אורטופדים בהריון טיפולים לימפטיים שיקום רצפת האגן הכנה ללידה Contact Describe your image Describe your image 1/7 התקשרו אלי ליצירת קשר וקביעת טיפול מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com I agree to the terms &amp; conditions שלח הפרטים ישמשו רק ליצירת קשר ולא יעברו לצד שלישי. תודה על הפניה. Back to to</t>
+          <t>ות, מענה לשאלות וסיכום. בין המפגשים יתקיים ליווי ההורים בעבודה לפי התוכנית הספציפית אשר גובשה באמצעות שיחות טלפוניות ומיילים. אתם מוזמנים לפנות אל טלי גליקסמן לשיחת הסבר והרחבה ומענה לשאלותיכם. טלפון: 050-848-6651 מייל: tali4baby@gmail.com Post navigation → גדילת תינוקות הדרכה והכוונה להורים החדשים למניעת עיכוב התפתחותי שמונת היסודות להתפתחות מיטבית ← קישורים מרכזיים בריאות ילדים בראייה הוליסטית טלי גליקסמן מומחית להתפתחות תינוקות אודות</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"שיקום רצפת האגן" רצפת אגן</t>
+          <t>"טלי גליקסמן" יועצת שינה</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10386,11 +10396,11 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@yaeltzur.co.il", "confidence": 80, "source_url": "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "identity_url": "https://www.yaeltzur.co.il/talie-gliksman/", "evidence": "[email protected]", "matched_query": "\"טלי גליקסמן\" יועצת שינה", "extraction_method": "linked_cloudflare"}]</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
@@ -10398,23 +10408,23 @@
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-09-03T19:11:34.001809+00:00</t>
+          <t>2026-09-04T04:15:05.038841+00:00</t>
         </is>
       </c>
       <c r="W62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
         <v>6</v>
       </c>
       <c r="Z62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -10423,11 +10433,11 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/", "https://www.gov.il/he/departments/ministry_of_health/govil-landing-page", "https://www.szmc.org.il/departments/clinics-and-institutes/machleket-physiotherapia/shikum-ritzpat-agan/", "https://www.shamir.org/clinics/physiotherapy/pelvis/", "https://asafpt.com/pelvic-floor/", "https://asafpt.com/about/", "https://asafpt.com/contact/", "https://he.hadassah.org.il/physiotherapy/pelvic-floor-physiotherapy/", "https://www.michalgilad.com/", "https://www.wix.com/lpviral/enviral?utm_campaign=vir_wixad_live&amp;adsVersion=banner_2024&amp;orig_msid=aa99f552-cce6-4d9b-96f0-a304175f7068&amp;orig_msid=ad07a822-90b8-4e00-adec-53cda74130fe&amp;adsVersion=banner_2024", "https://www.michalgilad.com/#aboutus"]</t>
+          <t>["https://sleepingbaby.hashevet.co.il/sleep-pro/", "https://sleepingbaby.hashevet.co.il/sleep-pro/#about", "https://www.huggies.co.il/professionals/tali-gliksman", "https://www.huggies.co.il/contact-us", "https://www.facebook.com/hashevet/", "https://www.yaeltzur.co.il/talie-gliksman/", "https://www.allinternet.co.il/", "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "https://www.yaeltzur.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.yaeltzur.co.il/cdn-cgi/l/email-protection#96fff8f0f9d6eff7f3fae2ece3e4b8f5f9b8fffa", "https://linktr.ee/tali4baby", "https://www.hashevet.co.il/", "https://linktr.ee/s/about/trust-center/report?field86145911=https%3A%2F%2Flinktr.ee%2Ftali4baby", "https://linktr.ee/blog/daisy-chain-fields-sticker-pack", "https://linktr.ee/features/contact-forms", "https://linktr.ee/features/audience-management", "https://linktr.ee/features/email-integrations", "https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/", "https://www.hashevet.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.hashevet.co.il/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/%D7%94%D7%93%D7%A8%D7%9B%D7%94%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/", "https://www.hashevet.co.il/category/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.040214913677007e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10438,7 +10448,7 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://www.michalgilad.com/</t>
+          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
@@ -10473,16 +10483,16 @@
         <v>13</v>
       </c>
       <c r="B63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>שיקום רצפת האגן</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>pelvic_floor</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -10497,18 +10507,18 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>michalgilad@gmail.com</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -10521,7 +10531,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.michalgilad.com/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -10531,12 +10541,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>לכאבים אורטופדים בהריון טיפולים לימפטיים שיקום רצפת האגן הכנה ללידה Contact Describe your image Describe your image 1/7 התקשרו אלי ליצירת קשר וקביעת טיפול מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com I agree to the terms &amp; conditions שלח הפרטים ישמשו רק ליצירת קשר ולא יעברו לצד שלישי. תודה על הפניה. Back to to</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"שיקום רצפת האגן" רצפת אגן</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10546,35 +10556,35 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-03T19:11:34.001809+00:00</t>
         </is>
       </c>
       <c r="W63" t="n">
         <v>2</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -10583,11 +10593,11 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/", "https://www.gov.il/he/departments/ministry_of_health/govil-landing-page", "https://www.szmc.org.il/departments/clinics-and-institutes/machleket-physiotherapia/shikum-ritzpat-agan/", "https://www.shamir.org/clinics/physiotherapy/pelvis/", "https://asafpt.com/pelvic-floor/", "https://asafpt.com/about/", "https://asafpt.com/contact/", "https://he.hadassah.org.il/physiotherapy/pelvic-floor-physiotherapy/", "https://www.michalgilad.com/", "https://www.wix.com/lpviral/enviral?utm_campaign=vir_wixad_live&amp;adsVersion=banner_2024&amp;orig_msid=aa99f552-cce6-4d9b-96f0-a304175f7068&amp;orig_msid=ad07a822-90b8-4e00-adec-53cda74130fe&amp;adsVersion=banner_2024", "https://www.michalgilad.com/#aboutus"]</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.334632071822425e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10598,15 +10608,13 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.michalgilad.com/</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr"/>
       <c r="AN63" t="inlineStr"/>
       <c r="AO63" t="inlineStr"/>
@@ -10639,7 +10647,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>שלומית שדמון</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10670,7 +10678,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>shlomitshadmon@gmail.com</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10683,7 +10691,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -10693,12 +10701,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"שלומית שדמון"</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -10708,11 +10716,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -10720,7 +10728,7 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
         </is>
       </c>
       <c r="W64" t="n">
@@ -10733,10 +10741,10 @@
         <v>4</v>
       </c>
       <c r="Z64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
@@ -10745,11 +10753,11 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.334632071822425e+17</v>
+        <v>4.003896215467274e+17</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10760,7 +10768,7 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
@@ -10796,15 +10804,17 @@
       <c r="A65" t="n">
         <v>13</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>6</v>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>תזונה אחרי לידה- תזונה בהנקה</t>
+          <t>שרון שלמה קלייטמן</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>pregnancy_dietitian</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -10819,18 +10829,18 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/תזונה-אחרי-לידה-תזונה-בהנקה/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>neta.amiri@gmail.com</t>
+          <t>sharon.kleitman@gmail.com</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -10843,7 +10853,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -10853,12 +10863,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>י הגישה הטיפולית סיפורי האישי: כך ירדתי במשקל לתמיד שירותים ייעוץ דיאטנית בניית תפריט שבועי לגן ילדים/ צהרונים הרצאות וסדנאות בתזונה שחלות פוליציסטיות/ טיפולי פוריות מאמרים מתכונים סרטונים יצירת קשר צרי קשר: 050-4350466 neta.amiri@gmail.com 1Z0-053 1Z0-517 640-461 640-722 642-832 648-375 74-344 74-409 A00-212 C2010-503 C2010-598 C2010-651 C2010-652 C2020-605 OG0-091 070-413 070-459 070-496 1Z0-052 C_BOSUP_90 ﻿ תזונה אחרי לידה- תזונה בהנ</t>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"שרון שלמה קלייטמן"</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -10878,30 +10888,38 @@
         <v>0</v>
       </c>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
+        </is>
+      </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>["https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/"]</t>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.003896215467274e+17</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10912,13 +10930,15 @@
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
+      <c r="AL65" t="b">
+        <v>0</v>
+      </c>
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr"/>
       <c r="AO65" t="inlineStr"/>
@@ -10949,7 +10969,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>תזונה ופוריות</t>
+          <t>תזונה אחרי לידה- תזונה בהנקה</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10969,7 +10989,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/תזונה-ופוריות/</t>
+          <t>https://tzunatbar.co.il/תזונה-אחרי-לידה-תזונה-בהנקה/</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -10980,7 +11000,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>benharoush@gmail.com</t>
+          <t>neta.amiri@gmail.com</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -10993,7 +11013,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
+          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11003,7 +11023,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>ור לך בתקופת טיפולי הפוריות חשיבותה של התזונה הסינית והמאקרוביוטית בכניסה להריון תזונה ופוריות O.M.D – מומחית לרפואה סינית – רפואה סינית וטיפולי פוריות יצירת קשר מרפאה בפתח תקווה: 050-5589013 מרפאה בתל אביב: 053-9956805 benharoush@gmail.com הרצל רוזנבלום 8 (מתחם סי אנד סאן) תל אביב אנצו סירני 7 פתח תקוה מה באתר דף הבית ויקיפוריות ויקיפוריות - גלריית הסרטונים ויקיפוריות -האנציקלופדיה הוירטואלית פורטל החדשנות של עולם הפוריות מרכז מומחים ב</t>
+          <t>י הגישה הטיפולית סיפורי האישי: כך ירדתי במשקל לתמיד שירותים ייעוץ דיאטנית בניית תפריט שבועי לגן ילדים/ צהרונים הרצאות וסדנאות בתזונה שחלות פוליציסטיות/ טיפולי פוריות מאמרים מתכונים סרטונים יצירת קשר צרי קשר: 050-4350466 neta.amiri@gmail.com 1Z0-053 1Z0-517 640-461 640-722 642-832 648-375 74-344 74-409 A00-212 C2010-503 C2010-598 C2010-651 C2010-652 C2020-605 OG0-091 070-413 070-459 070-496 1Z0-052 C_BOSUP_90 ﻿ תזונה אחרי לידה- תזונה בהנ</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -11047,11 +11067,11 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>["https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.yourdiet.co.il/", "https://wikifertility.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/"]</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11062,7 +11082,7 @@
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
+          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr"/>
@@ -11099,12 +11119,12 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Adi Kliffer Barmeir</t>
+          <t>תזונה ופוריות</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>lactation</t>
+          <t>pregnancy_dietitian</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -11119,18 +11139,18 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a2%d7%93%d7%99-%d7%a7%d7%9c%d7%99%d7%a4%d7%a8-%d7%91%d7%a8-%d7%9e%d7%90%d7%99%d7%a8/</t>
+          <t>https://wikifertility.com/תזונה-ופוריות/</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ialp</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>adi@kliffer.com</t>
+          <t>benharoush@gmail.com</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -11139,11 +11159,11 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
+          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11153,7 +11173,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>adi@kliffer.com</t>
+          <t>ור לך בתקופת טיפולי הפוריות חשיבותה של התזונה הסינית והמאקרוביוטית בכניסה להריון תזונה ופוריות O.M.D – מומחית לרפואה סינית – רפואה סינית וטיפולי פוריות יצירת קשר מרפאה בפתח תקווה: 050-5589013 מרפאה בתל אביב: 053-9956805 benharoush@gmail.com הרצל רוזנבלום 8 (מתחם סי אנד סאן) תל אביב אנצו סירני 7 פתח תקוה מה באתר דף הבית ויקיפוריות ויקיפוריות - גלריית הסרטונים ויקיפוריות -האנציקלופדיה הוירטואלית פורטל החדשנות של עולם הפוריות מרכז מומחים ב</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -11163,7 +11183,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -11197,11 +11217,11 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/", "https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/#contact"]</t>
+          <t>["https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.yourdiet.co.il/", "https://wikifertility.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11212,7 +11232,7 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
+          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr"/>
@@ -11249,7 +11269,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ariella Dubrowin</t>
+          <t>Adi Kliffer Barmeir</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11269,7 +11289,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%90%d7%a8%d7%99%d7%90%d7%9c%d7%94-%d7%93%d7%95%d7%91%d7%a8%d7%90%d7%95%d7%99%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%a2%d7%93%d7%99-%d7%a7%d7%9c%d7%99%d7%a4%d7%a8-%d7%91%d7%a8-%d7%9e%d7%90%d7%99%d7%a8/</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -11280,7 +11300,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ariella@hanakatova.com</t>
+          <t>adi@kliffer.com</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -11293,7 +11313,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -11303,7 +11323,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אריאלה דובראוין – Ariella Dubrowin טלפון: 054-6458027 אימייל: ariella@hanakatova.com הסמכה: מדריכת הנקה אזורי קבלה: ירושלים והסביבה, מרכז, שפלה ערים/ישובים: ירושלים, בית שמש, ביתר עילית, אפרת, אלון שבות, כפר עציון, ראש צורים, אלעזר, בת עין, מגדל עוז, תקוע, נוקדים, מעלה עמוס, פני קד</t>
+          <t>adi@kliffer.com</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -11313,7 +11333,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -11347,11 +11367,11 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/", "https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11362,7 +11382,7 @@
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr"/>
@@ -11399,7 +11419,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Aviella Natalie</t>
+          <t>Ariella Dubrowin</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11419,7 +11439,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%90%d7%91%d7%99%d7%90%d7%9c%d7%94/</t>
+          <t>https://ialp.org.il/counselors/%d7%90%d7%a8%d7%99%d7%90%d7%9c%d7%94-%d7%93%d7%95%d7%91%d7%a8%d7%90%d7%95%d7%99%d7%9f/</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -11430,7 +11450,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>natalie.by@mail.huji.ac.il</t>
+          <t>ariella@hanakatova.com</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -11443,7 +11463,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -11453,7 +11473,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אביאלה נטלי – Aviella Natalie טלפון: 050-6523233 אימייל: natalie.by@mail.huji.ac.il הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שרון ערים/ישובים: תל אביב, הרצליה, כפר סבא, רעננה, רמת גן, גבעתיים, בני ברק, פתח תקוה, קריית אונו, ראשון לציון. שפות: אנגלית, עברית</t>
+          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אריאלה דובראוין – Ariella Dubrowin טלפון: 054-6458027 אימייל: ariella@hanakatova.com הסמכה: מדריכת הנקה אזורי קבלה: ירושלים והסביבה, מרכז, שפלה ערים/ישובים: ירושלים, בית שמש, ביתר עילית, אפרת, אלון שבות, כפר עציון, ראש צורים, אלעזר, בת עין, מגדל עוז, תקוע, נוקדים, מעלה עמוס, פני קד</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -11497,11 +11517,11 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11512,7 +11532,7 @@
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr"/>
@@ -11549,7 +11569,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dalit Elan</t>
+          <t>Aviella Natalie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11569,7 +11589,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%93%d7%9c%d7%99%d7%aa-%d7%90%d7%99%d7%9c%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%90%d7%91%d7%99%d7%90%d7%9c%d7%94/</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -11580,7 +11600,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>delan@017.net.il</t>
+          <t>natalie.by@mail.huji.ac.il</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -11593,7 +11613,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -11603,7 +11623,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דלית אילן – Dalit Elan טלפון: 050-9200925 אימייל: delan@017.net.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: שרון ערים/ישובים: מזרחית לכביש 4 עד יהוד בדרום וכביש 57 בצפון. מגיעה לאריאל שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: דלית, אמא לשלוש בנות, יועצת הנקה בעלת </t>
+          <t>על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אביאלה נטלי – Aviella Natalie טלפון: 050-6523233 אימייל: natalie.by@mail.huji.ac.il הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שרון ערים/ישובים: תל אביב, הרצליה, כפר סבא, רעננה, רמת גן, גבעתיים, בני ברק, פתח תקוה, קריית אונו, ראשון לציון. שפות: אנגלית, עברית</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -11647,11 +11667,11 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/", "https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/#contact"]</t>
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11662,7 +11682,7 @@
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr"/>
@@ -11699,7 +11719,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Devorah Shaked</t>
+          <t>Dalit Elan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11719,7 +11739,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%93%d7%91%d7%95%d7%a8%d7%94-%d7%a9%d7%a7%d7%93/</t>
+          <t>https://ialp.org.il/counselors/%d7%93%d7%9c%d7%99%d7%aa-%d7%90%d7%99%d7%9c%d7%9f/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -11730,7 +11750,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>devorah@almondweb.com</t>
+          <t>delan@017.net.il</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -11743,7 +11763,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -11753,7 +11773,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דבורה שקד – Devorah Shaked טלפון: 054-4773421 אימייל: devorah@almondweb.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: ירושלים והסביבה ערים/ישובים: ירושלים והסביבה, גבעת זאב, כוכב יעקב, גוש עציון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: מעל 30 שנות ניסיון כתומכת </t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דלית אילן – Dalit Elan טלפון: 050-9200925 אימייל: delan@017.net.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: שרון ערים/ישובים: מזרחית לכביש 4 עד יהוד בדרום וכביש 57 בצפון. מגיעה לאריאל שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: דלית, אמא לשלוש בנות, יועצת הנקה בעלת </t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -11797,11 +11817,11 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/", "https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/", "https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11812,7 +11832,7 @@
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr"/>
@@ -11849,7 +11869,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hagit Naim</t>
+          <t>Devorah Shaked</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11869,7 +11889,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%97%d7%92%d7%99%d7%aa-%d7%a0%d7%a2%d7%99%d7%9d/</t>
+          <t>https://ialp.org.il/counselors/%d7%93%d7%91%d7%95%d7%a8%d7%94-%d7%a9%d7%a7%d7%93/</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -11880,7 +11900,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>hagit04@inter.net.il</t>
+          <t>devorah@almondweb.com</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -11893,7 +11913,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -11903,7 +11923,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי חגית נעים – Hagit Naim טלפון: 052-4662443 אימייל: hagit04@inter.net.il הסמכה: מדריכת הנקה אזורי קבלה: מרכז, שפלה ערים/ישובים: ראשון לציון , נס ציונה, רחובות, באר יעקב, בת ים, חולון, גבעתיים, רמת גן , תל אביב, יפו קרית אונו, יהוד שפות: עברית הסדרים עם קופ"ח: קצת עלי: סבל</t>
+          <t xml:space="preserve">ות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דבורה שקד – Devorah Shaked טלפון: 054-4773421 אימייל: devorah@almondweb.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: ירושלים והסביבה ערים/ישובים: ירושלים והסביבה, גבעת זאב, כוכב יעקב, גוש עציון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: מעל 30 שנות ניסיון כתומכת </t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -11947,11 +11967,11 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/", "https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/", "https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/#contact"]</t>
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11962,7 +11982,7 @@
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr"/>
@@ -11999,7 +12019,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Maddy Smadar Haran</t>
+          <t>Hagit Naim</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12019,7 +12039,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a1%d7%9e%d7%93%d7%a8-%d7%9e%d7%90%d7%93%d7%99-%d7%94%d7%a8%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%97%d7%92%d7%99%d7%aa-%d7%a0%d7%a2%d7%99%d7%9d/</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -12030,7 +12050,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>maddy@dmclub.co.il</t>
+          <t>hagit04@inter.net.il</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -12043,7 +12063,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -12053,7 +12073,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מאדי סמדר הרן – Maddy Smadar Haran טלפון: 054-3030901 אימייל: Maddy@dmclub.co.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: תל אביב, רמת גן, קרית אונו, גבעת שמואל, הרצליה, רעננה, הוד השרון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: גישה עניינית וידי</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי חגית נעים – Hagit Naim טלפון: 052-4662443 אימייל: hagit04@inter.net.il הסמכה: מדריכת הנקה אזורי קבלה: מרכז, שפלה ערים/ישובים: ראשון לציון , נס ציונה, רחובות, באר יעקב, בת ים, חולון, גבעתיים, רמת גן , תל אביב, יפו קרית אונו, יהוד שפות: עברית הסדרים עם קופ"ח: קצת עלי: סבל</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -12097,11 +12117,11 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/", "https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/", "https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/#contact"]</t>
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12112,7 +12132,7 @@
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr"/>
@@ -12149,7 +12169,7 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Merav Matus</t>
+          <t>Maddy Smadar Haran</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12169,7 +12189,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%9e%d7%a8%d7%91-%d7%9e%d7%98%d7%95%d7%a1/</t>
+          <t>https://ialp.org.il/counselors/%d7%a1%d7%9e%d7%93%d7%a8-%d7%9e%d7%90%d7%93%d7%99-%d7%94%d7%a8%d7%9f/</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -12180,7 +12200,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>meravmatus@walla.com</t>
+          <t>maddy@dmclub.co.il</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -12193,7 +12213,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -12203,7 +12223,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מרב מטוס – Merav Matus טלפון: 050-6619578 אימייל: meravmatus@walla.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: גוש דן, מרכז ערים/ישובים: אלעד, ראש העין, שהם, פתח תקוה, אלקנה, שערי תקוה, אורנית ועץ אפריים שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית מושלם, לאומית, מאוחד</t>
+          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מאדי סמדר הרן – Maddy Smadar Haran טלפון: 054-3030901 אימייל: Maddy@dmclub.co.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: תל אביב, רמת גן, קרית אונו, גבעת שמואל, הרצליה, רעננה, הוד השרון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: גישה עניינית וידי</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -12247,11 +12267,11 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/", "https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/", "https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12262,7 +12282,7 @@
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr"/>
@@ -12299,7 +12319,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Natalie Levin</t>
+          <t>Merav Matus</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12319,7 +12339,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%9c%d7%95%d7%99%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%9e%d7%a8%d7%91-%d7%9e%d7%98%d7%95%d7%a1/</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -12330,7 +12350,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>natalie@bshvil.com</t>
+          <t>meravmatus@walla.com</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -12343,7 +12363,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -12353,7 +12373,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>דות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי נטלי לוין – Natalie Levin טלפון: 052-5787072 אימייל: natalie@bshvil.com הסמכה: מדריכת הנקה אזורי קבלה: דרום ערים/ישובים: אשדוד, אשקלון, קרית גת, קרית מלאכי, שדרות ויישובי הסביבה שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: שמי נטלי, מדריכת הנקה מוסמכת, אמא לשניים. כאמא חו</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מרב מטוס – Merav Matus טלפון: 050-6619578 אימייל: meravmatus@walla.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: גוש דן, מרכז ערים/ישובים: אלעד, ראש העין, שהם, פתח תקוה, אלקנה, שערי תקוה, אורנית ועץ אפריים שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית מושלם, לאומית, מאוחד</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -12397,11 +12417,11 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/", "https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/#contact"]</t>
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12412,7 +12432,7 @@
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr"/>
@@ -12449,7 +12469,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sarit Perez</t>
+          <t>Natalie Levin</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12469,7 +12489,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a9%d7%a8%d7%99%d7%aa-%d7%a4%d7%a8%d7%a5/</t>
+          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%9c%d7%95%d7%99%d7%9f/</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -12480,7 +12500,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>saritush85@walla.com</t>
+          <t>natalie@bshvil.com</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -12493,7 +12513,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -12503,7 +12523,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי שרית פרץ – Sarit Perez טלפון: 052-5673614 אימייל: saritush85@walla.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: דרום ערים/ישובים: שדרות נתיבות יישובים קיבוצים מושבים בסביבה שפות: עברית הסדרים עם קופ"ח: קצת עלי: אמא לארבע מתוקות , אחות מוסמכת ויועצת הנקה מבחינתי ה</t>
+          <t>דות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי נטלי לוין – Natalie Levin טלפון: 052-5787072 אימייל: natalie@bshvil.com הסמכה: מדריכת הנקה אזורי קבלה: דרום ערים/ישובים: אשדוד, אשקלון, קרית גת, קרית מלאכי, שדרות ויישובי הסביבה שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: שמי נטלי, מדריכת הנקה מוסמכת, אמא לשניים. כאמא חו</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -12547,11 +12567,11 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/", "https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12562,7 +12582,7 @@
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr"/>
@@ -12599,7 +12619,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shirley Amit Shalam</t>
+          <t>Sarit Perez</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12619,7 +12639,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a9%d7%99%d7%a8%d7%9c%d7%99-%d7%a2%d7%9e%d7%99%d7%aa-%d7%a9%d7%9c%d7%9d/</t>
+          <t>https://ialp.org.il/counselors/%d7%a9%d7%a8%d7%99%d7%aa-%d7%a4%d7%a8%d7%a5/</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -12630,7 +12650,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>shirley@shalam.co.il</t>
+          <t>saritush85@walla.com</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -12643,7 +12663,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -12653,7 +12673,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>shirley@shalam.co.il</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי שרית פרץ – Sarit Perez טלפון: 052-5673614 אימייל: saritush85@walla.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: דרום ערים/ישובים: שדרות נתיבות יישובים קיבוצים מושבים בסביבה שפות: עברית הסדרים עם קופ"ח: קצת עלי: אמא לארבע מתוקות , אחות מוסמכת ויועצת הנקה מבחינתי ה</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -12663,7 +12683,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -12697,11 +12717,11 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/", "https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/", "https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/#contact"]</t>
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12712,7 +12732,7 @@
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr"/>
@@ -12749,7 +12769,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yael Giller</t>
+          <t>Shirley Amit Shalam</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12769,7 +12789,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%99%d7%a2%d7%9c-%d7%92%d7%99%d7%9c%d7%a8/</t>
+          <t>https://ialp.org.il/counselors/%d7%a9%d7%99%d7%a8%d7%9c%d7%99-%d7%a2%d7%9e%d7%99%d7%aa-%d7%a9%d7%9c%d7%9d/</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -12780,7 +12800,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>yael@tly.org.il</t>
+          <t>shirley@shalam.co.il</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -12793,7 +12813,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -12803,7 +12823,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יעל גילר – Yael Giller טלפון: 054-2399534 אימייל: yael@tly.org.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: נתניה, חדרה, כפר סבא, הוד השרון, רעננה, תל אביב והסביבה, אמת השרון, מושבי השרון ועמק חפר. שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: ש</t>
+          <t>shirley@shalam.co.il</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -12813,7 +12833,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -12847,11 +12867,11 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/", "https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/", "https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/#contact"]</t>
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12862,7 +12882,7 @@
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr"/>
@@ -12892,6 +12912,156 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>13</v>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Yael Giller</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>lactation</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%d7%99%d7%a2%d7%9c-%d7%92%d7%99%d7%9c%d7%a8/</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ialp</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>yael@tly.org.il</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>98</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יעל גילר – Yael Giller טלפון: 054-2399534 אימייל: yael@tly.org.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: נתניה, חדרה, כפר סבא, הוד השרון, רעננה, תל אביב והסביבה, אמת השרון, מושבי השרון ועמק חפר. שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: ש</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>seed_source</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>["https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/", "https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/#contact"]</t>
+        </is>
+      </c>
+      <c r="AD79" t="n">
+        <v>4.002523607919976e+17</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV79"/>
+  <dimension ref="A1:AV80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,32 +616,32 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>verification_schema_version</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>identity_name_verified</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>identity_specialty_verified</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>identity_evidence</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>verification_schema_version</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>identity_name_verified</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>identity_specialty_verified</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>identity_evidence</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>אביטל ורטהיימר</t>
+          <t>אבי גולדברג</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>avital.wer@gmail.com</t>
+          <t>dravigol@gmail.com</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.dravitalwertheimer.com/contact</t>
+          <t>https://biobalance.co.il/about-us-https-biobalance-co-il/</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -733,85 +733,93 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>זרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, Wix bottom of page</t>
+          <t>אודות ד"ר אבי גולדברג - Dr. Avi Goldberg - BioBalance 050-6020061 drAviGol@gmail.com Facebook עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפול מאמרים שאלות ותשובות צרו קשר עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפ</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>"אביטל ורטהיימר"</t>
+          <t>"אבי גולדברג" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{"email": "sec101@bri.co.il", "confidence": 98, "source_url": "https://www.dravitalwertheimer.com/contact", "identity_url": "https://www.dravitalwertheimer.com/", "evidence": "הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, W", "matched_query": "אביטל ורטהיימר יילוד", "extraction_method": "linked_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-04T04:20:36.746946+00:00</t>
+          <t>2026-09-10T18:34:17.572391+00:00</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>["https://www.dravitalwertheimer.com/", "https://www.dravitalwertheimer.com/contact", "https://www.dravitalwertheimer.com/about-3", "https://www.dravitalwertheimer.com/about-2", "https://www.dravitalwertheimer.com/about-5"]</t>
+          <t>["https://biobalance.co.il/about-us-https-biobalance-co-il/", "https://biobalance.co.il/%D7%90%D7%95%D7%A8%D7%99-%D7%9E%D7%A0%D7%94%D7%9C%D7%AA-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://biobalance.co.il/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94/", "https://biobalance.co.il/contact-us/", "https://avigoldberg.co.il/", "https://avigoldberg.co.il/%D7%A1%D7%99%D7%A4%D7%95%D7%A8-%D7%97%D7%99%D7%99%D7%95/", "https://www.srugim.co.il/1053331-%D7%A6%D7%A4%D7%95-%D7%94%D7%A8%D7%91-%D7%90%D7%91%D7%99-%D7%92%D7%95%D7%9C%D7%93%D7%91%D7%A8%D7%92-%D7%94%D7%99%D7%93-%D7%91%D7%AA%D7%A4%D7%99%D7%9C%D7%94-%D7%9C%D7%A4%D7%A0%D7%99-%D7%94%D7%99", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fbygwldbrg.438538%2F", "https://www.c14.co.il/archive/96776", "https://www.izkor.gov.il/%D7%90%D7%91%D7%A8%D7%94%D7%9D+%D7%99%D7%95%D7%A1%D7%A3+%D7%92%D7%95%D7%9C%D7%93%D7%91%D7%A8%D7%92/en_700097013c53fc0bc9f7dc07a2457af7"]</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.349051611818981e+17</v>
+        <v>1.301247395137417e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>https://www.dravitalwertheimer.com/</t>
+          <t>https://biobalance.co.il/about-us-https-biobalance-co-il/</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>אודות ד"ר אבי גולדברג - Dr. Avi Goldberg - BioBalance אודות ד"ר אבי גולדברג - Dr. Avi Goldberg - BioBalance 050-6020061 drAviGol@gmail.com Facebook עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפול מאמרים שאלות ותשובות צרו קשר עמוד הבית צוות המרפאה ד”ר אבי גולדברג אורי מנהלת המרפאה שירותי המרפאה תהליך הטיפול מאמרים שאלות ותשובות צרו קשר אודות ד"ר אבי גולדברג אודות ד"ר אבי גולדברג שמי ד"ר אבי גולדברג, מומחה ברפואת משפחה. את לימודי הרפואה סיימתי בבית הספר לרפואה בהדסה עין כרם. לאחר מסלול מפרך בבית הספר לרפואה, החלטתי שמקומי הוא דווקא בקהילה, ולא בבית החולים, ולכן לאחר שקילת האפשרויות שעומדות בפני, החלטתי להתמחות ברפואת משפחה בקופת חולים מכבי. לאחר סיום ההתמחות בהצלחה עבדתי מספר שנים בקופת חולים כללית, כרופא בית בדיור מוגן ובתור רופא במספר מוקדים רפואיים שונים. במקביל ללימודים, להתמחות ובהמשך לעבודתי, בשל צורך אישי ומשפחתי התחלתי לחקור לעומק מספר תחומים רפואיים אשר בהם ראיתי שיש צורך גדול בטיפול ברמה גבוהה הרבה יותר, גאוט, סוכרת והטיפול ההורמונלי בנשים וגברים. את רזי ואמנות הטיפול ההורמונלי למדתי במספר בתי ספ</t>
+        </is>
+      </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
@@ -841,7 +849,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>אלון קדם</t>
+          <t>אביטל ורטהיימר</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -872,7 +880,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>doctorkedem@gmail.com</t>
+          <t>avital.wer@gmail.com</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -885,7 +893,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.kedemalon.co.il/</t>
+          <t>https://www.dravitalwertheimer.com/contact</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -895,26 +903,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>פרופ' אלון קדם גניקולוגיה | מיילדות | פוריות | IVF 050-7234597 שלם 3, רמת גן (רמת חן) ומדינת היהודים 89, הרצליה פיתוח doctorkedem@gmail.com מדיניות פרטיות | הצהרת נגישות</t>
+          <t>זרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, Wix bottom of page</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>"אלון קדם"</t>
+          <t>"אביטל ורטהיימר"</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[{"email": "faceitsd@gmail.com", "confidence": 92, "source_url": "https://www.kedemalon.co.il/contact", "identity_url": "https://www.kedemalon.co.il/", "evidence": "doctorkedem@gmail.com", "matched_query": "\"אלון קדם\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[{"email": "sec101@bri.co.il", "confidence": 98, "source_url": "https://www.dravitalwertheimer.com/contact", "identity_url": "https://www.dravitalwertheimer.com/", "evidence": "הפריה חוץ גופית הזרעה תוך הרחמית More Use tab to navigate through the menu items. Dr. Avital Wertheimer רופאת נשים מומחית בפריון, מיילדות וגניקולוגיה ד״ר אביטל ורטהיימר כתובת ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב sec101@bri.co.il avital.wer@gmail.com 03 - 7620620 Mail Phone Mail ד״ר אביטל ורטהיימר ​ רופאת נשיםֿֿ, מומחית בגניקולוגיה ומיילדות ​ ​ ​ ​ כתובת המרפאה ברודצקי 43, ת״א המרכז לבריאות האישה רמת אביב ג׳ © By Roni Rapaport, W", "matched_query": "אביטל ורטהיימר יילוד", "extraction_method": "linked_text"}]</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -922,14 +930,14 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-03T22:06:03.406318+00:00</t>
+          <t>2026-09-04T04:20:36.746946+00:00</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
@@ -942,16 +950,16 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>["https://www.kedemalon.co.il/", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact"]</t>
+          <t>["https://www.dravitalwertheimer.com/", "https://www.dravitalwertheimer.com/contact", "https://www.dravitalwertheimer.com/about-3", "https://www.dravitalwertheimer.com/about-2", "https://www.dravitalwertheimer.com/about-5"]</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.604715483545694e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -962,19 +970,19 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>https://www.kedemalon.co.il/</t>
+          <t>https://www.dravitalwertheimer.com/</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+      <c r="AP3" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>1</v>
@@ -1003,7 +1011,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>אנה פטרוסב</t>
+          <t>אלון קדם</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1034,7 +1042,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>annapetruseva@gmail.com</t>
+          <t>doctorkedem@gmail.com</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1047,7 +1055,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
+          <t>https://www.kedemalon.co.il/</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1057,26 +1065,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ייעוץ ונמצא יחד את הפתרון הנכון ביותר עבורך! זה המקום להשאיר פרטים כדי שנוכל לקבוע שיחת ייעוץ בה תוכלו לקבל תשובות לכל השאלות ולבחור את הטיפול המתאים לכן. Name Phone Email ההסתדרות 55, חיפה, מרפאת שר"פ פלוס 073-2139418 annapetruseva@gmail.com אודות ד"ר אנה פטרוסב, מומחית בגינקולוגיה ובהפרעות הורמונליות לאורך שלבי החיים. מטפלת במחלות העריה, הנרתיק וצוואר הרחם. מבצעת ניתוחים פלסטיים באיברי המין החיצוניים. קישורים אודות המלצות יצירת קשר ה</t>
+          <t>פרופ' אלון קדם גניקולוגיה | מיילדות | פוריות | IVF 050-7234597 שלם 3, רמת גן (רמת חן) ומדינת היהודים 89, הרצליה פיתוח doctorkedem@gmail.com מדיניות פרטיות | הצהרת נגישות</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>"אנה פטרוסב"</t>
+          <t>"אלון קדם"</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "faceitsd@gmail.com", "confidence": 92, "source_url": "https://www.kedemalon.co.il/contact", "identity_url": "https://www.kedemalon.co.il/", "evidence": "doctorkedem@gmail.com", "matched_query": "\"אלון קדם\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1084,7 +1092,7 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-03T22:25:40.742527+00:00</t>
+          <t>2026-09-03T22:06:03.406318+00:00</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1109,11 +1117,11 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>["https://dr-annapetruseva.co.il/", "https://dr-annapetruseva.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.kedemalon.co.il/", "https://www.kedemalon.co.il/about", "https://www.kedemalon.co.il/contact"]</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1124,19 +1132,19 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>https://dr-annapetruseva.co.il/</t>
+          <t>https://www.kedemalon.co.il/</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AP4" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
         <v>1</v>
@@ -1165,7 +1173,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ג'וניה עאמר-אלשיק</t>
+          <t>אנה פטרוסב</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1196,7 +1204,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>jonia.alshiek@gmail.com</t>
+          <t>annapetruseva@gmail.com</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1209,15 +1217,177 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ייעוץ ונמצא יחד את הפתרון הנכון ביותר עבורך! זה המקום להשאיר פרטים כדי שנוכל לקבוע שיחת ייעוץ בה תוכלו לקבל תשובות לכל השאלות ולבחור את הטיפול המתאים לכן. Name Phone Email ההסתדרות 55, חיפה, מרפאת שר"פ פלוס 073-2139418 annapetruseva@gmail.com אודות ד"ר אנה פטרוסב, מומחית בגינקולוגיה ובהפרעות הורמונליות לאורך שלבי החיים. מטפלת במחלות העריה, הנרתיק וצוואר הרחם. מבצעת ניתוחים פלסטיים באיברי המין החיצוניים. קישורים אודות המלצות יצירת קשר ה</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>"אנה פטרוסב"</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>linked_text</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:25:40.742527+00:00</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>["https://dr-annapetruseva.co.il/", "https://dr-annapetruseva.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-annapetruseva.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.300820172573992e+18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>https://dr-annapetruseva.co.il/</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ג'וניה עאמר-אלשיק</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>gynecologist</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>moh</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>jonia.alshiek@gmail.com</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve"> מדיניות הבטיחות והבריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה פרופ'
   ג'וניה
@@ -1225,172 +1395,9 @@
 הפקול</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>"וניה עאמר אלשיק"</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>direct_text</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-03T22:56:01.688904+00:00</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>["https://medicine.biu.ac.il/node/7845", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.336067241913308e+17</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>https://medicine.biu.ac.il/node/7845</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>PERSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>גדי בן שטרית</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>gynecologist</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>moh</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dr.benshitrit@gmail.com</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>PERSONAL_PROFESSIONAL</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>100</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://www.drbenshitrit.co.il/</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>י צוות המרפאה לבדיקות וטיפולים. והתנהלות מול חברות הביטוח. מדריכים רפואים בוידאו שעות פתיחה: ביקורים פרטיים: לפי תיאום מראש. דרכי התקשרות: כתובתינו: רח' הכרמל 20, גני תקווה, מרכז הבמה קומה א'. 
-טלפון: 073-3890435 דוא"ל: dr.benshitrit@gmail.com האם משחות להחלקת הצלוליט אכן עובדות? למעבר לכתבה &gt;&gt; ד"ר בן שטרית נבחר ע"י מגזין פורבס היוקרתי לאחד הרופאים הטובים לשנת 2022 בישראל למעבר לכתבה &gt;&gt; משהו מפריע לך? אל תתביישי להתייעץ עם רופא נשים! שם</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>"גדי בן שטרית"</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1412,7 +1419,7 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-03T22:59:50.505947+00:00</t>
+          <t>2026-09-03T22:56:01.688904+00:00</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1437,11 +1444,11 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>["https://www.drbenshitrit.co.il/", "https://www.drbenshitrit.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://medicine.biu.ac.il/node/7845", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1452,19 +1459,19 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>https://www.drbenshitrit.co.il/</t>
+          <t>https://medicine.biu.ac.il/node/7845</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AP6" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
         <v>1</v>
@@ -1493,7 +1500,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ד"ר ארבל אריאל</t>
+          <t>גדי בן שטרית</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1513,18 +1520,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>arbel.ariel.md@gmail.com</t>
+          <t>dr.benshitrit@gmail.com</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1537,7 +1544,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
+          <t>https://www.drbenshitrit.co.il/</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1547,12 +1554,13 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>מידע למטופל שאלות ותשובות הורדת טפסים מדיניות פרטיות סרטונים צור קשר ד"ר אריאל ארבל לזימון תור ד"ר אריאל ארבל לאתר הרופא/ה לעמוד הפייסבוק לערוץ היוטיוב לזימון תור ד"ר אריאל ארבל התקשר עכשיו יום א', בין השעות 15:00-20:00 arbel.ariel.md@gmail.com 055-9922120 התמחות מומחה ברפואת נשים / OBGYN. מומחה במחלות העריה והלדן / VULVO-VAGINAL DISEASE SPECIALIST. תחומי טיפול מומחה ביילוד גינקולוגיה ופריון, מחלות העריה והלדן תחומי טיפול מחלות עריה ולד</t>
+          <t>י צוות המרפאה לבדיקות וטיפולים. והתנהלות מול חברות הביטוח. מדריכים רפואים בוידאו שעות פתיחה: ביקורים פרטיים: לפי תיאום מראש. דרכי התקשרות: כתובתינו: רח' הכרמל 20, גני תקווה, מרכז הבמה קומה א'. 
+טלפון: 073-3890435 דוא"ל: dr.benshitrit@gmail.com האם משחות להחלקת הצלוליט אכן עובדות? למעבר לכתבה &gt;&gt; ד"ר בן שטרית נבחר ע"י מגזין פורבס היוקרתי לאחד הרופאים הטובים לשנת 2022 בישראל למעבר לכתבה &gt;&gt; משהו מפריע לך? אל תתביישי להתייעץ עם רופא נשים! שם</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>"ארבל אריאל"</t>
+          <t>"גדי בן שטרית"</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1562,11 +1570,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1574,23 +1582,23 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-03T20:23:48.175654+00:00</t>
+          <t>2026-09-03T22:59:50.505947+00:00</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1599,11 +1607,11 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
+          <t>["https://www.drbenshitrit.co.il/", "https://www.drbenshitrit.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1614,19 +1622,19 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
+          <t>https://www.drbenshitrit.co.il/</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AP7" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
         <v>1</v>
@@ -1655,7 +1663,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ד"ר בלייכר אינה</t>
+          <t>ד"ר ארבל אריאל</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1675,7 +1683,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1686,7 +1694,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>he.la.medical@gmail.com</t>
+          <t>arbel.ariel.md@gmail.com</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1699,7 +1707,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA</t>
+          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1709,26 +1717,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>א. אנו ממשיכים לשפר את הנגשת האתר על מנת לאפשר בו שימוש רחב לכלל האוכלוסיה לרבות אנשים עם מוגבלויות. במידה וניתקלת באלמנט באתר שאינו נגיש והנך זקוק להתאמתו לנגישות, ניתן לפנות אלינו: בטלפון: 050-2882400 או במייל לכתובת: he.la.medical@gmail.com ​ יצירת קשר צוות המרפאה ד"ר אינה בלייכר מומחית במיילדות וגינקולוגיה ורפואת האם והעובר (הריון בסיכון) ד"ר לילא חדאד מומחית במיילדות וגינקולוגיה ובאולטרסאונד מיילדותי וגינקולוגי, עם ניסיון רב בתחומי</t>
+          <t>מידע למטופל שאלות ותשובות הורדת טפסים מדיניות פרטיות סרטונים צור קשר ד"ר אריאל ארבל לזימון תור ד"ר אריאל ארבל לאתר הרופא/ה לעמוד הפייסבוק לערוץ היוטיוב לזימון תור ד"ר אריאל ארבל התקשר עכשיו יום א', בין השעות 15:00-20:00 arbel.ariel.md@gmail.com 055-9922120 התמחות מומחה ברפואת נשים / OBGYN. מומחה במחלות העריה והלדן / VULVO-VAGINAL DISEASE SPECIALIST. תחומי טיפול מומחה ביילוד גינקולוגיה ופריון, מחלות העריה והלדן תחומי טיפול מחלות עריה ולד</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>"בלייכר אינה"</t>
+          <t>"ארבל אריאל"</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@eryaveladan.com", "confidence": 88, "source_url": "https://www.eryaveladan.com/", "identity_url": "https://www.eryaveladan.com/", "evidence": "החזיר את האיזון. קראי עוד השאירי פרטים ונחזור אלייך בהקדם שם מלא טלפון דוא״ל שליחה רופא נשים מומחה מחלות העריה והלדן ​ ד״ר אריאל ארבל לקביעת תור: 077-2311245 כתובת המרפאה: בית למומחים ברפואה - בורוכוב 54, גבעתיים דוא״ל: info@eryaveladan.com bottom of page", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}, {"email": "office@b54.co.il", "confidence": 88, "source_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "identity_url": "https://www.b54.co.il/doctors/dr-arbel-ariel/", "evidence": "ד\"ר אריאל ארבל - מרפאת מומחים B54, הבית למומחים ברפואה בגבעתיים דילוג לתוכן B54 03-757-8562 office@b54.co.il א׳-ה׳ 8:00-20:00 | ו׳ 08:00-13:00 Facebook-f Youtube Google דף הבית אודות B54 מי אנחנו שכונת בורוכוב מרכז Friendly הנהלת המרפאה שאלות נפוצות הרופאים שלנו קליניקה להשכרה מידע למטופל שאלות ותשובות הורדת טפ", "matched_query": "\"ארבל אריאל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1736,20 +1744,20 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-03T20:24:23.400825+00:00</t>
+          <t>2026-09-03T20:23:48.175654+00:00</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
@@ -1761,11 +1769,11 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F4D046F297BAD3648A25E08D58F6A97C27A9F79486CAA0E21C76A59F89CCEEBF&amp;RequestId=00000000-0000-0000-0001-000000000629", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=303818454&amp;ProviderProfession=1&amp;docClinic=4002031&amp;Service=1&amp;NewObjectId=70056970&amp;NewObjectType=S&amp;NewPerNr=90012266&amp;ol1=70056970&amp;ol2=S&amp;ol3=90012266&amp;isKosher=1&amp;beginDate=2026-09-03T23:24:04&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.facebook.com/ina.blicher/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8-%D7%90%D7%99%D7%A0%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=AB2EF07D4F34EBC58E5E46A0566D6548AE1759D494C6A4CEBACE849A1921D61C&amp;RequestId=00000000-0000-0000-0001-000000000732", "https://www.medreviews.co.il/provider/dr-bleicher-inna", "https://www.helaclinic.com/", "https://www.helaclinic.com/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA", "https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA", "https://www.infomed.co.il/experts/147166/", "https://knowmore.co.il/doctors/אינה-בלייכר/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F2E5439F4D7FC4EB4A3BD70F1E153BCC012FCC2B1F7B620D1119D7AA921F32A0&amp;RequestId=00000000-0000-0000-0001-000000000689", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment/high-risk-pregnancy-consult", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%90%D7%99%D7%A0%D7%94-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e2cfd468-3549-4ce0-87ca-86babc3ba598", "https://www.facebook.com/people/%D7%90%D7%A8%D7%99%D7%90%D7%9C-%D7%90%D7%A8%D7%91%D7%9C/pfbid0NCmi7FZgUyu2EVV5mLJMpBfndXiDQPqseAxUny7KWHsDvucQScUiVnBeMef3ByStl/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%90%D7%A8%D7%91%D7%9C-%D7%90%D7%A8%D7%99%D7%90%D7%9C/", "https://www.eryaveladan.com/", "https://www.eryaveladan.com/%D7%90%D7%95%D7%93%D7%95%D7%AA-1", "https://www.b54.co.il/doctors/dr-arbel-ariel/", "https://www.medreviews.co.il/provider/dr-arbel-ariel", "https://www.b54.co.il/about/", "https://www.b54.co.il/about", "https://www.b54.co.il/about#borohov", "https://www.b54.co.il/about#Friendly", "https://www.b54.co.il/about#management", "https://www.b54.co.il/about#qa", "https://www.medreviews.co.il/provider/dr-arbel-ariel#contact-doctor-section", "https://www.medreviews.co.il/contact-us", "https://www.medreviews.co.il/about", "https://woman.mymc.co.il/doctors/dr-arielarbel/", "https://www.ima.org.il/DoctorsIndex/Default.aspx", "https://www.infomed.co.il/experts/145655/", "https://www.ami.org.il/blog/families/not-the-same-shirley"]</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1776,19 +1784,19 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
+          <t>https://www.b54.co.il/doctors/dr-arbel-ariel/</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AP8" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
         <v>1</v>
@@ -1817,7 +1825,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ד"ר בראל אושרי</t>
+          <t>ד"ר בלייכר אינה</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1837,7 +1845,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1848,7 +1856,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>privatepractice.barel@gmail.com</t>
+          <t>he.la.medical@gmail.com</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1861,7 +1869,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.droshribarel.com/</t>
+          <t>https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1871,17 +1879,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>בחנתית וטיפולית Jul 21, 2018 ניתוחים לפרוסקופים Aug 29, 2016 צרי קשר אסותא רמת החייל - הברזל 20, תל אביב, קומה 2 מתחם גינקולוגיה נס ציונה  - מרפאת לליב, קמפוס יובלים בניין B קומה 3 אסותא כלניות - שד' מנחם בגין 126 אשדוד privatepractice.barel@gmail.com וואטסאפ 054-2592902 Send Your details were sent successfully! ד״ר אושרי בראל רופא מומחה במיילדות, גינקולוגיה וכירורגיה גינקולוגית ליצירת קשר בטלפון או ווטסאפ ליצירת קשר במייל לזימון תור במ</t>
+          <t>א. אנו ממשיכים לשפר את הנגשת האתר על מנת לאפשר בו שימוש רחב לכלל האוכלוסיה לרבות אנשים עם מוגבלויות. במידה וניתקלת באלמנט באתר שאינו נגיש והנך זקוק להתאמתו לנגישות, ניתן לפנות אלינו: בטלפון: 050-2882400 או במייל לכתובת: he.la.medical@gmail.com ​ יצירת קשר צוות המרפאה ד"ר אינה בלייכר מומחית במיילדות וגינקולוגיה ורפואת האם והעובר (הריון בסיכון) ד"ר לילא חדאד מומחית במיילדות וגינקולוגיה ובאולטרסאונד מיילדותי וגינקולוגי, עם ניסיון רב בתחומי</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>"בראל אושרי"</t>
+          <t>"בלייכר אינה"</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1898,20 +1906,20 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-04T11:17:14.785768+00:00</t>
+          <t>2026-09-03T20:24:23.400825+00:00</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
         <v>1</v>
@@ -1923,11 +1931,11 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0", "https://www.droshribarel.com/", "https://www.droshribarel.com/about", "https://doctors.assuta.co.il/doctor/oshri-barel-32645"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3930db83-dd31-4cd4-baa4-ffbee4b85ee6", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F4D046F297BAD3648A25E08D58F6A97C27A9F79486CAA0E21C76A59F89CCEEBF&amp;RequestId=00000000-0000-0000-0001-000000000629", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=303818454&amp;ProviderProfession=1&amp;docClinic=4002031&amp;Service=1&amp;NewObjectId=70056970&amp;NewObjectType=S&amp;NewPerNr=90012266&amp;ol1=70056970&amp;ol2=S&amp;ol3=90012266&amp;isKosher=1&amp;beginDate=2026-09-03T23:24:04&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.facebook.com/ina.blicher/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8-%D7%90%D7%99%D7%A0%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=AB2EF07D4F34EBC58E5E46A0566D6548AE1759D494C6A4CEBACE849A1921D61C&amp;RequestId=00000000-0000-0000-0001-000000000732", "https://www.medreviews.co.il/provider/dr-bleicher-inna", "https://www.helaclinic.com/", "https://www.helaclinic.com/%D7%9E%D7%93%D7%99%D7%A0%D7%99%D7%95%D7%AA-%D7%A4%D7%A8%D7%98%D7%99%D7%95%D7%AA", "https://www.helaclinic.com/%D7%94%D7%A6%D7%94%D7%A8%D7%AA-%D7%A0%D7%92%D7%99%D7%A9%D7%95%D7%AA", "https://www.infomed.co.il/experts/147166/", "https://knowmore.co.il/doctors/אינה-בלייכר/", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=F2E5439F4D7FC4EB4A3BD70F1E153BCC012FCC2B1F7B620D1119D7AA921F32A0&amp;RequestId=00000000-0000-0000-0001-000000000689", "https://www.medreviews.co.il/provider/dr-bleicher-inna/treatment/high-risk-pregnancy-consult", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%90%D7%99%D7%A0%D7%94-%D7%91%D7%9C%D7%99%D7%99%D7%9B%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/"]</t>
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>5.007272332541864e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -1938,19 +1946,19 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>https://www.droshribarel.com/</t>
+          <t>https://www.medreviews.co.il/provider/dr-bleicher-inna</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AP9" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
         <v>1</v>
@@ -1979,7 +1987,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ד"ר גורצק לימור</t>
+          <t>ד"ר בראל אושרי</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1999,7 +2007,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -2010,7 +2018,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>limorgortzak@gmail.com</t>
+          <t>privatepractice.barel@gmail.com</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2023,7 +2031,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
+          <t>https://www.droshribarel.com/</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2033,17 +2041,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ד"ר לימור גורצק אוזן | גינקולוגיה ומיילדות | ניתוחיי ... ניתוחיי גינקולוגיה מרפאות אלי כהן 8, רעננה-דוקטור גורצק אוזן לימור רעננה אלי כהן 8 מייל מרפאה : limorgortzak@gmail.com הסדרים ביטוח הראל כלל חברה לביטוח בעמ</t>
+          <t>בחנתית וטיפולית Jul 21, 2018 ניתוחים לפרוסקופים Aug 29, 2016 צרי קשר אסותא רמת החייל - הברזל 20, תל אביב, קומה 2 מתחם גינקולוגיה נס ציונה  - מרפאת לליב, קמפוס יובלים בניין B קומה 3 אסותא כלניות - שד' מנחם בגין 126 אשדוד privatepractice.barel@gmail.com וואטסאפ 054-2592902 Send Your details were sent successfully! ד״ר אושרי בראל רופא מומחה במיילדות, גינקולוגיה וכירורגיה גינקולוגית ליצירת קשר בטלפון או ווטסאפ ליצירת קשר במייל לזימון תור במ</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>"גורצק לימור" יילוד מרפאה</t>
+          <t>"בראל אושרי"</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2060,17 +2068,17 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-08T07:40:03.644359+00:00</t>
+          <t>2026-09-04T11:17:14.785768+00:00</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
         <v>2</v>
@@ -2080,16 +2088,16 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=3C4EDA09705370ECB68D9C2264B607ED40FF0BE76904B81AEE276453C8369C5C&amp;RequestId=00000000-0000-0000-0001-000000000264", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=24990111&amp;ProviderProfession=2&amp;docClinic=67701&amp;Service=1&amp;NewObjectId=70021435&amp;NewObjectType=S&amp;NewPerNr=90005047&amp;ol1=70021435&amp;ol2=S&amp;ol3=90005047&amp;isKosher=1&amp;beginDate=2026-09-08T10:39:13&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/limor-gortzak-31448"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3d307898-6be3-4d9e-a284-ee467c2622b0", "https://www.droshribarel.com/", "https://www.droshribarel.com/about", "https://doctors.assuta.co.il/doctor/oshri-barel-32645"]</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.340236532221023e+17</v>
+        <v>1.502181699762559e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2100,19 +2108,19 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
+          <t>https://www.droshribarel.com/</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
+      <c r="AP10" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
         <v>1</v>
@@ -2141,7 +2149,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ד"ר הר-טוב יוסף</t>
+          <t>ד"ר גורצק לימור</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2161,7 +2169,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -2172,7 +2180,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dr.hartoov@gmail.com</t>
+          <t>limorgortzak@gmail.com</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2185,7 +2193,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.dr-hartoov.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2195,17 +2203,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>ד"ר יוסי הר-טוב דלג לתוכן כתובת: ויצמן 14, תל אביב, מגדל מרכז ויצמן קומה 19, חדר 1923 אימייל: dr.hartoov@gmail.com שעות פעילות: ​א' - ו' בתיאום מראש 052-8305566 מספר מקשר(?) בית אודות בדיקות גינקולוגיות בדיקת מי שפיר וסיסי שליה סקירת מערכות סקירת מערכות מוקדמת סקירת מערכות מאוחרת סקירת מערכות שלישית מעקבי הריון ש</t>
+          <t>ד"ר לימור גורצק אוזן | גינקולוגיה ומיילדות | ניתוחיי ... ניתוחיי גינקולוגיה מרפאות אלי כהן 8, רעננה-דוקטור גורצק אוזן לימור רעננה אלי כהן 8 מייל מרפאה : limorgortzak@gmail.com הסדרים ביטוח הראל כלל חברה לביטוח בעמ</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>"הר טוב יוסף"</t>
+          <t>"גורצק לימור" יילוד מרפאה</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>official_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2222,36 +2230,36 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-04T11:52:18.314932+00:00</t>
+          <t>2026-09-08T07:40:03.644359+00:00</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
         <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0", "https://www.d.co.il/reviews-80237533-c46500-p1/", "https://www.dr-hartoov.co.il/", "https://www.dr-hartoov.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.dr-hartoov.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=e4863880-ea20-4af5-8f93-9ca81c2181c8", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=3C4EDA09705370ECB68D9C2264B607ED40FF0BE76904B81AEE276453C8369C5C&amp;RequestId=00000000-0000-0000-0001-000000000264", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=8&amp;ProviderID=24990111&amp;ProviderProfession=2&amp;docClinic=67701&amp;Service=1&amp;NewObjectId=70021435&amp;NewObjectType=S&amp;NewPerNr=90005047&amp;ol1=70021435&amp;ol2=S&amp;ol3=90005047&amp;isKosher=1&amp;beginDate=2026-09-08T10:39:13&amp;shaban=false&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/limor-gortzak-31448"]</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>4.340185064555201e+17</v>
+        <v>1.302070959666307e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2262,19 +2270,19 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>https://www.dr-hartoov.co.il/</t>
+          <t>https://doctors.assuta.co.il/doctor/limor-gortzak-31448</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+      <c r="AP11" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
         <v>1</v>
@@ -2303,7 +2311,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ד"ר הראל יעל</t>
+          <t>ד"ר הר-טוב יוסף</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2323,7 +2331,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -2334,7 +2342,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>doc.yaelharel@gmail.com</t>
+          <t>dr.hartoov@gmail.com</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2347,7 +2355,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
+          <t>https://www.dr-hartoov.co.il/</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2357,17 +2365,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>גוד הישראלי הישראלי למיילדות וגינקולוגיה החברה לגינקולוגיה של ילדות ומתבגרות החברה הישראלית לקידום, אבחון, טיפול ומניעה של פגיעה מינית קליניקה : רחוב הברזל 9א, קומה 4, תל אביב טלפון : 051-2613697 פקס: 03-7744069 אימייל: Doc.yaelharel@gmail.com © כל הזכויות שמורות לד"ר יעל הראל 2022 הצהרת נגישות Made with 💙 by box גלילה לראש העמוד דילוג לתוכן פתח סרגל נגישות כלי נגישות הגדל טקסט הקטן טקסט גווני אפור ניגודיות גבוהה ניגודיות הפוכה רקע בהיר</t>
+          <t>ד"ר יוסי הר-טוב דלג לתוכן כתובת: ויצמן 14, תל אביב, מגדל מרכז ויצמן קומה 19, חדר 1923 אימייל: dr.hartoov@gmail.com שעות פעילות: ​א' - ו' בתיאום מראש 052-8305566 מספר מקשר(?) בית אודות בדיקות גינקולוגיות בדיקת מי שפיר וסיסי שליה סקירת מערכות סקירת מערכות מוקדמת סקירת מערכות מאוחרת סקירת מערכות שלישית מעקבי הריון ש</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>"הראל יעל"</t>
+          <t>"הר טוב יוסף"</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>official_text</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2379,25 +2387,25 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-04T19:38:04.257632+00:00</t>
+          <t>2026-09-04T11:52:18.314932+00:00</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2409,11 +2417,11 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/100083269862452/", "https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/", "https://dryaelharel.co.il/", "https://dryaelharel.co.il/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://israel-psychotherapy.org/therapist/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://upr.co.il/listing/%D7%93%D7%A8-%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://www.prtfl.co.il/archives/writer/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=BBC5ED8B-BCA3-44E9-AD8C-5614970C09B0", "https://www.d.co.il/reviews-80237533-c46500-p1/", "https://www.dr-hartoov.co.il/", "https://www.dr-hartoov.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.dr-hartoov.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>5.350881755215378e+17</v>
+        <v>1.30205551936656e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2424,19 +2432,19 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
+          <t>https://www.dr-hartoov.co.il/</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+      <c r="AP12" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="n">
         <v>1</v>
@@ -2465,7 +2473,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ד"ר לוריא מיכל</t>
+          <t>ד"ר הראל יעל</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2485,7 +2493,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -2496,7 +2504,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mijalluria@gmail.com</t>
+          <t>doc.yaelharel@gmail.com</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2509,7 +2517,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
+          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2519,12 +2527,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>יות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 072-211-9500 כתובת "מרכז רותם: המרכז הרב תחומי למיניות"  גבעת בית הכרם 3, ירושלים אימייל mijalluria@gmail.com לוריא מיכל (MD) – ירושלים מקצוע: רופאה, מומחית ברפואת נשים, מטפלת מינית מוסמכת התמחות: גינקולוגית איזור טיפול: ירושלים אודותי התמחות: טיפול מיני זוגי ופרטני, פערים בחשק המיני, חוסר הנאה מחיי המין, כא</t>
+          <t>גוד הישראלי הישראלי למיילדות וגינקולוגיה החברה לגינקולוגיה של ילדות ומתבגרות החברה הישראלית לקידום, אבחון, טיפול ומניעה של פגיעה מינית קליניקה : רחוב הברזל 9א, קומה 4, תל אביב טלפון : 051-2613697 פקס: 03-7744069 אימייל: Doc.yaelharel@gmail.com © כל הזכויות שמורות לד"ר יעל הראל 2022 הצהרת נגישות Made with 💙 by box גלילה לראש העמוד דילוג לתוכן פתח סרגל נגישות כלי נגישות הגדל טקסט הקטן טקסט גווני אפור ניגודיות גבוהה ניגודיות הפוכה רקע בהיר</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>"לוריא מיכל" יילוד מרפאה</t>
+          <t>"הראל יעל"</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2534,71 +2542,71 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "evidence": "ter.rotem.www שעות פעילות: שעות פעילות:\r\nא'-ה' 08.00-22.00 | ו' 8.00-15.00 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"לוריא מיכל\" יילוד מרפאה", "extraction_method": "linked_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-08T23:26:20.598402+00:00</t>
+          <t>2026-09-04T19:38:04.257632+00:00</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>ddgs:yahoo</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4", "https://www.meuhedet.co.il/poi/Doctors/000250300130100613000000000000_0", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C/", "https://www.doctorita.co.il/experts/72051", "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=1f53d60d-6e05-4854-8a46-954ca448b33c", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/100083269862452/", "https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/", "https://dryaelharel.co.il/", "https://dryaelharel.co.il/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://israel-psychotherapy.org/therapist/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://upr.co.il/listing/%D7%93%D7%A8-%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C/", "https://www.prtfl.co.il/archives/writer/%D7%99%D7%A2%D7%9C-%D7%94%D7%A8%D7%90%D7%9C"]</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.340236532221031e+17</v>
+        <v>1.605264526564613e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
+          <t>https://dryaelharel.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
+      <c r="AP13" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="n">
         <v>1</v>
@@ -2627,7 +2635,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ד"ר פז מורן</t>
+          <t>ד"ר לוריא מיכל</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2647,7 +2655,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2658,7 +2666,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>drmoranpaz@gmail.com</t>
+          <t>mijalluria@gmail.com</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2671,7 +2679,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.drmoranpaz.com/</t>
+          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2681,12 +2689,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>אליק, ישראל top of page Moran Paz M.D. Obstetrics &amp; Gynaecology Minimally invasive surgery Tel: 050-6265854 058-6265854 ד"ר מורן פז מומחה ברפואת נשים ומיילדות כירורגיה גינקולוגית זער פולשנית טל': 050-6265854 058-6265854 drmoranpaz@gmail.com צרי קשר מיילדות אנדומטריוזיס אמצעי מניעה אמצעי מניעה התקן תוך רחמי גלולות למניעת הריון גינקולוגיה גניקולוגיה הפרשות נרתיקיות פוליפים שרירנים היסטרוסקופיה לפרוסקופיה אודות אודות מכתבי תודה ד"ר מורן פז</t>
+          <t>יות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 072-211-9500 כתובת "מרכז רותם: המרכז הרב תחומי למיניות"  גבעת בית הכרם 3, ירושלים אימייל mijalluria@gmail.com לוריא מיכל (MD) – ירושלים מקצוע: רופאה, מומחית ברפואת נשים, מטפלת מינית מוסמכת התמחות: גינקולוגית איזור טיפול: ירושלים אודותי התמחות: טיפול מיני זוגי ופרטני, פערים בחשק המיני, חוסר הנאה מחיי המין, כא</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>"פז מורן"</t>
+          <t>"לוריא מיכל" יילוד מרפאה</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2696,11 +2704,11 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "evidence": "ter.rotem.www שעות פעילות: שעות פעילות:\r\nא'-ה' 08.00-22.00 | ו' 8.00-15.00 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"לוריא מיכל\" יילוד מרפאה", "extraction_method": "linked_text"}]</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2708,11 +2716,11 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:18.342248+00:00</t>
+          <t>2026-09-08T23:26:20.598402+00:00</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2721,46 +2729,46 @@
         <v>4</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8", "https://www.drmoranpaz.com/", "https://www.drmoranpaz.com/blank-1", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%96-%D7%9E%D7%95%D7%A8%D7%9F/", "https://docsrated.com/doctors/מורן-פז", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx?edeptcode=999012319&amp;eservicecode=1722022&amp;employeeid=99B380F756CF96813AEADDED4FF08A8C", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%96/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4", "https://www.meuhedet.co.il/poi/Doctors/000250300130100613000000000000_0", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C/", "https://www.doctorita.co.il/experts/72051", "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.302070959666309e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>https://www.drmoranpaz.com/</t>
+          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
+      <c r="AP14" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
         <v>1</v>
@@ -2789,7 +2797,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ד"ר צוקרמן צבי</t>
+          <t>ד"ר פז מורן</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2809,7 +2817,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2820,7 +2828,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>zukerman_z@hotmail.com</t>
+          <t>drmoranpaz@gmail.com</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2833,7 +2841,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2843,12 +2851,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>עילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 52-2444908 0, פקס': 03-9310870 כתובת ברנדה 4 פתח תקווה 49600 אימייל Zukerman_z@hotmail.com צוקרמן צבי (MD) התמחות: גינקולוגיה איזור טיפול: פתח תקווה אודותי צוקרמן צבי (MD) גינקולוגיה פתח תקווה 52-2444908 0, פקס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה</t>
+          <t>אליק, ישראל top of page Moran Paz M.D. Obstetrics &amp; Gynaecology Minimally invasive surgery Tel: 050-6265854 058-6265854 ד"ר מורן פז מומחה ברפואת נשים ומיילדות כירורגיה גינקולוגית זער פולשנית טל': 050-6265854 058-6265854 drmoranpaz@gmail.com צרי קשר מיילדות אנדומטריוזיס אמצעי מניעה אמצעי מניעה התקן תוך רחמי גלולות למניעת הריון גינקולוגיה גניקולוגיה הפרשות נרתיקיות פוליפים שרירנים היסטרוסקופיה לפרוסקופיה אודות אודות מכתבי תודה ד"ר מורן פז</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>"צוקרמן צבי"</t>
+          <t>"פז מורן"</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2858,11 +2866,11 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "evidence": "קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "direct_text"}, {"email": "info@israeli-expert.co.il", "confidence": 80, "source_url": "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "identity_url": "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "evidence": "info@israeli-expert.co.il Moriya Av. 105, Haifa 34616 Phone: 04-8244633, Fax: 04-8113444", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2870,24 +2878,24 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-03T21:00:59.983523+00:00</t>
+          <t>2026-09-03T20:26:18.342248+00:00</t>
         </is>
       </c>
       <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>ddgs:bing</t>
@@ -2895,11 +2903,11 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167", "https://www.facebook.com/people/%D7%A6%D7%91%D7%99-%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F/pfbid02E1Nxj3wfhR6MF8D6JXXRW7A6Jhoq792SjPLH1nRCvRmFTDrKUVsZSCxcg5BXdSXDl/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fzby.zwqrmn%2F", "https://benyehuda.org/read/38950", "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "https://www.interuse.co.il/", "https://www.israeli-expert.co.il/about-en", "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "https://www.israeli-expert.co.il/about", "https://www.israeli-expert.co.il/index2.php?id=3&amp;lang=HEB", "https://www.palmach.org.il/veterans/veteranpage/?itemId=73755", "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=5eee8cff-ee8c-40c5-807b-acf6f5374dd8", "https://www.drmoranpaz.com/", "https://www.drmoranpaz.com/blank-1", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%96-%D7%9E%D7%95%D7%A8%D7%9F/", "https://docsrated.com/doctors/מורן-פז", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx?edeptcode=999012319&amp;eservicecode=1722022&amp;employeeid=99B380F756CF96813AEADDED4FF08A8C", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%96/"]</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2910,19 +2918,19 @@
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://www.drmoranpaz.com/</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
+      <c r="AP15" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="n">
         <v>1</v>
@@ -2951,7 +2959,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ד"ר קאופמן יובל</t>
+          <t>ד"ר צוקרמן צבי</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2971,7 +2979,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2982,7 +2990,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mdykaufman@gmail.com</t>
+          <t>zukerman_z@hotmail.com</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2995,7 +3003,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.gynsurg.co.il/</t>
+          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -3005,12 +3013,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">תמחויות לפרוסקופיה היסטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את </t>
+          <t>עילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 52-2444908 0, פקס': 03-9310870 כתובת ברנדה 4 פתח תקווה 49600 אימייל Zukerman_z@hotmail.com צוקרמן צבי (MD) התמחות: גינקולוגיה איזור טיפול: פתח תקווה אודותי צוקרמן צבי (MD) גינקולוגיה פתח תקווה 52-2444908 0, פקס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>"קאופמן יובל"</t>
+          <t>"צוקרמן צבי"</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -3020,11 +3028,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[{"email": "yochi750@gmail.com", "confidence": 100, "source_url": "https://www.gynsurg.co.il/", "identity_url": "https://www.gynsurg.co.il/", "evidence": "סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל\"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע\"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת", "matched_query": "\"קאופמן יובל\"", "extraction_method": "direct_text"}]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "evidence": "קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "direct_text"}, {"email": "info@israeli-expert.co.il", "confidence": 80, "source_url": "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "identity_url": "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "evidence": "info@israeli-expert.co.il Moriya Av. 105, Haifa 34616 Phone: 04-8244633, Fax: 04-8113444", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -3032,7 +3040,7 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-03T21:01:40.564925+00:00</t>
+          <t>2026-09-03T21:00:59.983523+00:00</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -3042,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3057,11 +3065,11 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0", "https://www.gynsurg.co.il/", "https://www.gynsurg.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.gynsurg.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167", "https://www.facebook.com/people/%D7%A6%D7%91%D7%99-%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F/pfbid02E1Nxj3wfhR6MF8D6JXXRW7A6Jhoq792SjPLH1nRCvRmFTDrKUVsZSCxcg5BXdSXDl/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fzby.zwqrmn%2F", "https://benyehuda.org/read/38950", "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "https://www.interuse.co.il/", "https://www.israeli-expert.co.il/about-en", "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "https://www.israeli-expert.co.il/about", "https://www.israeli-expert.co.il/index2.php?id=3&amp;lang=HEB", "https://www.palmach.org.il/veterans/veteranpage/?itemId=73755", "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3072,19 +3080,19 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>https://www.gynsurg.co.il/</t>
+          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
+      <c r="AP16" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="n">
         <v>1</v>
@@ -3144,7 +3152,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>yochi750@gmail.com</t>
+          <t>mdykaufman@gmail.com</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3167,7 +3175,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת</t>
+          <t xml:space="preserve">תמחויות לפרוסקופיה היסטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את </t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3223,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3240,16 +3248,16 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
+      <c r="AP17" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="b">
         <v>0</v>
@@ -3275,7 +3283,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ד"ר קוגן לירון</t>
+          <t>ד"ר קאופמן יובל</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3295,7 +3303,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3306,7 +3314,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>shelach.medical@gmail.com</t>
+          <t>yochi750@gmail.com</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3319,7 +3327,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
+          <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3329,26 +3337,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>ד"ר לירון קוגן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא Jul 16, 2026 · מרפאות החבצלת 1, פתח תקווה-דוקטור קוגן לירון פתח תקווה החבצלת 1 ימי שני 18:00-19:00 מייל מרפאה: shelach.medical@gmail.com</t>
+          <t>סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>"קוגן לירון" יילוד</t>
+          <t>"קאופמן יובל"</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "yochi750@gmail.com", "confidence": 100, "source_url": "https://www.gynsurg.co.il/", "identity_url": "https://www.gynsurg.co.il/", "evidence": "סטרוסקופיה גישה נרתיקית בעיות גניקולוגיות בעיות פוריות פוליפ רחמי שרירנים ברחם ציסטה בשחלה אנדומטריוזיס פרטי התקשרות בית חולים 'אסותא' חיפה, קניון לב המפרץ (קומה ג') שד' ההסתדרות 55 , צ'ק פוסט, חיפה mdykaufman@gmail.com yochi750@gmail.com 03-7644777 050-9500525 © כל הזכויות שמורות ל\"ר יובל קאופמן- כירורגיה גניקולוגית מתקדמת | נבנה ע\"י ADACTIVE לזימון תורים - לחץ כאן זימון תור טלפון מרפאה סגירת תפריט אנחנו מכבדים את הפרטיות שלך אנחנו משת", "matched_query": "\"קאופמן יובל\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -3356,62 +3364,62 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-08T23:31:56.357314+00:00</t>
+          <t>2026-09-03T21:01:40.564925+00:00</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223", "https://www.meuhedet.co.il/poi/Doctors/7070866300000839730000009928_99", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A7%D7%95%D7%92%D7%9F-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=4D7994DA1EF011E23924766CCB7D4323448E0FB52729DF77F063BC8E422E0345&amp;RequestId=00000000-0000-0000-0001-000000000518", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-09T02:30:57&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true", "https://www.medreviews.co.il/provider/dr-kogan-liron", "https://www.gynonc.co.il/", "https://www.gynonc.co.il/about", "https://doctors.assuta.co.il/doctor/liron-kogan-83973", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.lironkogan%2F", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-04T00:01:58&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.raphaelhospitals.co.il/doctors/liron-kogen/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=87371F6B-AEDA-480B-855B-A665C2A570C0", "https://www.gynsurg.co.il/", "https://www.gynsurg.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.gynsurg.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4.340236532221031e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
+          <t>https://www.gynsurg.co.il/</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
+      <c r="AP18" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS18" t="b">
         <v>0</v>
@@ -3437,12 +3445,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ד"ר שטטר אורנה</t>
+          <t>ד"ר קוגן לירון</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3457,7 +3465,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -3468,7 +3476,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ornastatter@gmail.com</t>
+          <t>shelach.medical@gmail.com</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3481,7 +3489,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.fps.org.il/metapel/drornas/</t>
+          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3491,26 +3499,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>ם והרצאות הרצאות מוקלטות מאמרים חיפוש מטפל/ת אורנה שטטר (ד"ר) דף הבית &gt; מטפלים &gt; אורנה שטטר (ד"ר) פרטי המטפל: אזור טיפול: שפלה ישוב: חולדה (ליד מזכרת בתיה, כ-20 דק מרחובות) נייד: 054-7338883 כתובת המייל של המטפל/מדריך:  ornastatter@gmail.com מידע נוסף: מומחית ברפואת משפחה מטפלת מוסמכת בפסיכותרפיה ממוקדת חברת וועד האגודה הישראלית לפסיכוסומטיקה וועד הסניף הישראלי של acbs אודות האגודה על האגודה חזון ומטרות המייסדים מאפייני טיפול קצר-מועד ה</t>
+          <t>ד"ר לירון קוגן | גינקולוגיה ומיילדות | גינקואונקולוגיה | אסותא Jul 16, 2026 · מרפאות החבצלת 1, פתח תקווה-דוקטור קוגן לירון פתח תקווה החבצלת 1 ימי שני 18:00-19:00 מייל מרפאה: shelach.medical@gmail.com</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>"שטטר אורנה" רפואת משפחה</t>
+          <t>"קוגן לירון" יילוד</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>[{"email": "fps.israel@gmail.com", "confidence": 92, "source_url": "https://www.fps.org.il/contactus/", "identity_url": "https://www.fps.org.il/metapel/drornas/", "evidence": "Envelope", "matched_query": "\"שטטר אורנה\" רפואת משפחה", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -3518,23 +3526,23 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-08T14:11:08.841786+00:00</t>
+          <t>2026-09-08T23:31:56.357314+00:00</t>
         </is>
       </c>
       <c r="W19" t="n">
+        <v>8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" t="n">
         <v>4</v>
       </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6</v>
-      </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -3543,34 +3551,34 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%98%D7%98%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://www.doctorita.co.il/experts/95407", "https://medpage.co.il/doctors/%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%A9%D7%98%D7%98%D7%A8-913/", "https://drtor.co.il/doctor/18797", "https://drtor.co.il/cdn-cgi/l/email-protection#3a5955544e5b594e7a5e484e5548145955145356", "https://www.fps.org.il/metapel/drornas/", "https://www.fps.org.il/contactus/", "https://www.fps.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fps.org.il/about/theassociation/", "https://www.fps.org.il/about/goals/", "https://www.fps.org.il/about/founders/", "https://www.fps.org.il/about/dstterapy/", "https://www.fps.org.il/aguda-members/%D7%90%D7%95%D7%A8%D7%A0%D7%94%D7%A9%D7%98%D7%98%D7%A8/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=874a0be8-2288-4588-8c92-8fd98e173223", "https://www.meuhedet.co.il/poi/Doctors/7070866300000839730000009928_99", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A7%D7%95%D7%92%D7%9F-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=4D7994DA1EF011E23924766CCB7D4323448E0FB52729DF77F063BC8E422E0345&amp;RequestId=00000000-0000-0000-0001-000000000518", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-09T02:30:57&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true", "https://www.medreviews.co.il/provider/dr-kogan-liron", "https://www.gynonc.co.il/", "https://www.gynonc.co.il/about", "https://doctors.assuta.co.il/doctor/liron-kogan-83973", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.lironkogan%2F", "https://mc.maccabi4u.co.il/transfer/?module=NewAppointment&amp;LinkType=3&amp;ProviderID=32912818&amp;ProviderProfession=W&amp;docClinic=4008135&amp;Service=1&amp;NewObjectId=70064900&amp;NewObjectType=S&amp;NewPerNr=90006758&amp;ol1=70064900&amp;ol2=S&amp;ol3=90006758&amp;isKosher=1&amp;beginDate=2026-09-04T00:01:58&amp;shaban=true&amp;appversion=4.1.3&amp;relative=-2&amp;action_type=1&amp;source=1", "https://www.raphaelhospitals.co.il/doctors/liron-kogen/"]</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>4.337491317124723e+17</v>
+        <v>1.302070959666309e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>https://www.fps.org.il/metapel/drornas/</t>
+          <t>https://doctors.assuta.co.il/doctor/liron-kogan-83973?readmore=true</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
+      <c r="AP19" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="n">
         <v>1</v>
@@ -3599,12 +3607,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ד"ר שרים גיא</t>
+          <t>ד"ר שטטר אורנה</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3619,7 +3627,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -3630,7 +3638,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dr.shremguy@gmail.com</t>
+          <t>ornastatter@gmail.com</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3643,7 +3651,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.fps.org.il/metapel/drornas/</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3653,12 +3661,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>אודות - ד"ר גיא שרים חיפוש חיפוש אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות ד"ר גיא שרים יצירת קשר 077-230-3222 dr.shremguy@gmail.com שדרות ההגשמה 18, חריש לתיאום פגישה: שם טלפון אימייל שליחה אודות ד"ר גיא שרים - מומחה בגינקולוגיה ופוריות ד"ר שרים הינו מומחה באנדוקרינולוגיה של הרביה ואי-פוריות – Reproductive Endocrinology and Infe</t>
+          <t>ם והרצאות הרצאות מוקלטות מאמרים חיפוש מטפל/ת אורנה שטטר (ד"ר) דף הבית &gt; מטפלים &gt; אורנה שטטר (ד"ר) פרטי המטפל: אזור טיפול: שפלה ישוב: חולדה (ליד מזכרת בתיה, כ-20 דק מרחובות) נייד: 054-7338883 כתובת המייל של המטפל/מדריך:  ornastatter@gmail.com מידע נוסף: מומחית ברפואת משפחה מטפלת מוסמכת בפסיכותרפיה ממוקדת חברת וועד האגודה הישראלית לפסיכוסומטיקה וועד הסניף הישראלי של acbs אודות האגודה על האגודה חזון ומטרות המייסדים מאפייני טיפול קצר-מועד ה</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>"שרים גיא"</t>
+          <t>"שטטר אורנה" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3668,11 +3676,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "fps.israel@gmail.com", "confidence": 92, "source_url": "https://www.fps.org.il/contactus/", "identity_url": "https://www.fps.org.il/metapel/drornas/", "evidence": "Envelope", "matched_query": "\"שטטר אורנה\" רפואת משפחה", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -3680,36 +3688,36 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-03T21:14:53.999772+00:00</t>
+          <t>2026-09-08T14:11:08.841786+00:00</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00", "https://medicine.biu.ac.il/node/8582", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgy.srym%2F", "https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "http://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3029d9ab-24fa-43c3-93a2-29329c1b952c", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%98%D7%98%D7%A8-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://www.doctorita.co.il/experts/95407", "https://medpage.co.il/doctors/%D7%90%D7%95%D7%A8%D7%A0%D7%94-%D7%A9%D7%98%D7%98%D7%A8-913/", "https://drtor.co.il/doctor/18797", "https://drtor.co.il/cdn-cgi/l/email-protection#3a5955544e5b594e7a5e484e5548145955145356", "https://www.fps.org.il/metapel/drornas/", "https://www.fps.org.il/contactus/", "https://www.fps.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fps.org.il/about/theassociation/", "https://www.fps.org.il/about/goals/", "https://www.fps.org.il/about/founders/", "https://www.fps.org.il/about/dstterapy/", "https://www.fps.org.il/aguda-members/%D7%90%D7%95%D7%A8%D7%A0%D7%94%D7%A9%D7%98%D7%98%D7%A8/", "https://doctorindex.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D-%D7%9E%D7%95%D7%9E%D7%97%D7%99%D7%9D-%D7%A8%D7%A4%D7%95%D7%90%D7%AA-%D7%94%D7%9E%D7%A9%D7%A4%D7%97%D7%94/"]</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.301247395137417e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3720,19 +3728,19 @@
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.fps.org.il/metapel/drornas/</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
+      <c r="AP20" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="n">
         <v>1</v>
@@ -3761,12 +3769,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ד''ר משה רויבורט</t>
+          <t>ד"ר שרים גיא</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fertility_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3781,18 +3789,18 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.fertility-clinic.co.il/</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dr.royburt@gmail.com</t>
+          <t>dr.shremguy@gmail.com</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3805,7 +3813,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.e-piryon.com/</t>
+          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3815,12 +3823,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">עמוד הבית - ד''ר משה רויבורט 0723301439 dr.royburt@gmail.com שפירא 43, פתח תקווה מומחה לפוריות טיפולי פוריות הפרייה מלאכותית תרומת ביציות שימור פוריות פונדקאות ייעוץ ותמיכה צור קשר מומחה לפוריות טיפולי פוריות הפרייה מלאכותית תרומת ביציות שימור פוריות פונדקאות </t>
+          <t>אודות - ד"ר גיא שרים חיפוש חיפוש אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות בירור בעיות פוריות צילום רחם מרכז הידע צרו קשר אודות ד"ר גיא שרים יצירת קשר 077-230-3222 dr.shremguy@gmail.com שדרות ההגשמה 18, חריש לתיאום פגישה: שם טלפון אימייל שליחה אודות ד"ר גיא שרים - מומחה בגינקולוגיה ופוריות ד"ר שרים הינו מומחה באנדוקרינולוגיה של הרביה ואי-פוריות – Reproductive Endocrinology and Infe</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>"משה רויבורט"</t>
+          <t>"שרים גיא"</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3842,23 +3850,23 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-04T04:17:53.335818+00:00</t>
+          <t>2026-09-03T21:14:53.999772+00:00</t>
         </is>
       </c>
       <c r="W21" t="n">
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -3867,11 +3875,11 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>["https://www.fertility-clinic.co.il/", "https://www.fertility-clinic.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fertility-clinic.co.il/%D7%94%D7%9E%D7%9C%D7%A6%D7%95%D7%AA-%D7%93%D7%A8-%D7%9E%D7%A9%D7%94-%D7%A8%D7%95%D7%99%D7%91%D7%95%D7%A8%D7%98/", "https://www.fertility-clinic.co.il/%D7%9E%D7%99%D7%93%D7%A2-%D7%A8%D7%A4%D7%95%D7%90%D7%99/", "https://www.fertility-clinic.co.il/%D7%A4%D7%95%D7%93%D7%A7%D7%A1%D7%98-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.fertility-clinic.co.il/%D7%A1%D7%A8%D7%98%D7%95%D7%A0%D7%99-%D7%94%D7%A8%D7%99%D7%95%D7%9F/", "https://www.e-piryon.com/", "https://www.e-piryon.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.fertility-clinic.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.doctorim.co.il/s/doctor-25517/דר-משה-רויבורט/מומחה-בפריון-וגניקולוגיה", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_m_royburt.aspx", "https://www.infomed.co.il/experts/93638/", "https://www.poriyut-guide.com/doctors/dr-royburt/", "http://www.fertility-docs.com/index.phtml", "https://www.poriyut-guide.com/about/", "https://www.poriyut-guide.com/contact/", "https://www.poriyut-guide.com/about/terms_of_use/", "https://www.medreviews.co.il/provider/dr-royburt-moshe/treatment/pregnancy-followup", "https://www.doctors.co.il/forum-3188/", "https://www.fertility-clinic.co.il/%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-%D7%9C%D7%96%D7%99%D7%9E%D7%95%D7%9F-%D7%AA%D7%95%D7%A8%D7%99%D7%9D/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%9E%D7%A9%D7%94_%D7%A8%D7%95%D7%99%D7%91%D7%95%D7%A8%D7%98", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=F9FC3D7F-C0DD-440E-8AA7-DC41A9FCCC00", "https://medicine.biu.ac.il/node/8582", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgy.srym%2F", "https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "http://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>6.016138879805644e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3882,19 +3890,19 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>https://www.e-piryon.com/</t>
+          <t>https://guyshrem.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
+      <c r="AP21" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="n">
         <v>1</v>
@@ -3923,12 +3931,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>דוד גורדון</t>
+          <t>ד''ר משה רויבורט</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>fertility_doctor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3943,18 +3951,18 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.fertility-clinic.co.il/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>davidgordon14@yahoo.com</t>
+          <t>dr.royburt@gmail.com</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3967,7 +3975,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.davidgordon.co.il/</t>
+          <t>https://www.e-piryon.com/</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3977,12 +3985,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>ניחת רחם טיפול בבריחת שתן הערכה אורו-דינמית מדיניות הפרטיות הצהרת נגישות יצירת קשר ותיאם פגישה צרי איתי קשר צוות המרפאה עומד לשרותכם! כתובתנו: מגדל מרכז ויצמן רחוב ויצמן 14, תל אביב טלפון : 03-544-9339 נייד: 052-2411171 davidgordon14@yahoo.com Facebook Google+ Instagram לשיחת יעוץ ותיאום פגישה אני מסכים/ה ל מדיניות הפרטיות ולעיבוד המידע ליצירת קשר Please leave this field empty. Ⓒ  כל הזכויות שמורות ל פרופ' דוד גורדון אורוגניקולוג | טיפו</t>
+          <t xml:space="preserve">עמוד הבית - ד''ר משה רויבורט 0723301439 dr.royburt@gmail.com שפירא 43, פתח תקווה מומחה לפוריות טיפולי פוריות הפרייה מלאכותית תרומת ביציות שימור פוריות פונדקאות ייעוץ ותמיכה צור קשר מומחה לפוריות טיפולי פוריות הפרייה מלאכותית תרומת ביציות שימור פוריות פונדקאות </t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>"דוד גורדון"</t>
+          <t>"משה רויבורט"</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -4004,23 +4012,23 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-03T23:18:02.537185+00:00</t>
+          <t>2026-09-04T04:17:53.335818+00:00</t>
         </is>
       </c>
       <c r="W22" t="n">
         <v>2</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -4029,11 +4037,11 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>["https://www.davidgordon.co.il/", "https://www.davidgordon.co.il/contact/", "https://www.davidgordon.co.il/our-clinic/", "https://www.davidgordon.co.il/our-clinic/faq/"]</t>
+          <t>["https://www.fertility-clinic.co.il/", "https://www.fertility-clinic.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.fertility-clinic.co.il/%D7%94%D7%9E%D7%9C%D7%A6%D7%95%D7%AA-%D7%93%D7%A8-%D7%9E%D7%A9%D7%94-%D7%A8%D7%95%D7%99%D7%91%D7%95%D7%A8%D7%98/", "https://www.fertility-clinic.co.il/%D7%9E%D7%99%D7%93%D7%A2-%D7%A8%D7%A4%D7%95%D7%90%D7%99/", "https://www.fertility-clinic.co.il/%D7%A4%D7%95%D7%93%D7%A7%D7%A1%D7%98-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.fertility-clinic.co.il/%D7%A1%D7%A8%D7%98%D7%95%D7%A0%D7%99-%D7%94%D7%A8%D7%99%D7%95%D7%9F/", "https://www.e-piryon.com/", "https://www.e-piryon.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.fertility-clinic.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.doctorim.co.il/s/doctor-25517/דר-משה-רויבורט/מומחה-בפריון-וגניקולוגיה", "https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_m_royburt.aspx", "https://www.infomed.co.il/experts/93638/", "https://www.poriyut-guide.com/doctors/dr-royburt/", "http://www.fertility-docs.com/index.phtml", "https://www.poriyut-guide.com/about/", "https://www.poriyut-guide.com/contact/", "https://www.poriyut-guide.com/about/terms_of_use/", "https://www.medreviews.co.il/provider/dr-royburt-moshe/treatment/pregnancy-followup", "https://www.doctors.co.il/forum-3188/", "https://www.fertility-clinic.co.il/%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-%D7%9C%D7%96%D7%99%D7%9E%D7%95%D7%9F-%D7%AA%D7%95%D7%A8%D7%99%D7%9D/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%9E%D7%A9%D7%94_%D7%A8%D7%95%D7%99%D7%91%D7%95%D7%A8%D7%98", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx"]</t>
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.804841663941693e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4044,19 +4052,19 @@
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>https://www.davidgordon.co.il/</t>
+          <t>https://www.e-piryon.com/</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
+      <c r="AP22" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="n">
         <v>1</v>
@@ -4080,15 +4088,17 @@
       <c r="A23" t="n">
         <v>13</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>דולה מומלצת במרכז ובשרון</t>
+          <t>דוד גורדון</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>doula</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4103,18 +4113,18 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.sivandoula.com/דולה-מומלצת-במרכז-ובשרון</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>sivanpotash@gmail.com</t>
+          <t>davidgordon14@yahoo.com</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4127,7 +4137,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.sivandoula.com/contact</t>
+          <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4137,17 +4147,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>ריון המלצות רגעים של אושר צרי קשר בלוג שאלות ותשובות מושגים מעולם הלידה More Use tab to navigate through the menu items. צרי קשר אם יש לך שאלות לגביי או לגבי שירותיי את מוזמנת לפנות אליי בשמחה סיון פוטש טלפון 0549294349 sivanpotash@gmail.com אימייל שלח תודה ! Copyright © 2023 Sivan Potash. All Rights Reserved. Pictures and Vectors Freepik סיון פוטש דולה ומדריכת הכנה ללידה  במרכז ובשרון Tel: 0549294349 bottom of page</t>
+          <t>ניחת רחם טיפול בבריחת שתן הערכה אורו-דינמית מדיניות הפרטיות הצהרת נגישות יצירת קשר ותיאם פגישה צרי איתי קשר צוות המרפאה עומד לשרותכם! כתובתנו: מגדל מרכז ויצמן רחוב ויצמן 14, תל אביב טלפון : 03-544-9339 נייד: 052-2411171 davidgordon14@yahoo.com Facebook Google+ Instagram לשיחת יעוץ ותיאום פגישה אני מסכים/ה ל מדיניות הפרטיות ולעיבוד המידע ליצירת קשר Please leave this field empty. Ⓒ  כל הזכויות שמורות ל פרופ' דוד גורדון אורוגניקולוג | טיפו</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"דוד גורדון"</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -4162,15 +4172,19 @@
         <v>0</v>
       </c>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:18:02.537185+00:00</t>
+        </is>
+      </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
@@ -4178,14 +4192,18 @@
       <c r="AA23" t="n">
         <v>0</v>
       </c>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>["https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F", "https://www.sivandoula.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%99", "https://www.sivandoula.com/contact"]</t>
+          <t>["https://www.davidgordon.co.il/", "https://www.davidgordon.co.il/contact/", "https://www.davidgordon.co.il/our-clinic/", "https://www.davidgordon.co.il/our-clinic/faq/"]</t>
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4196,7 +4214,7 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
+          <t>https://www.davidgordon.co.il/</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr"/>
@@ -4206,7 +4224,9 @@
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
+      <c r="AP23" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="n">
         <v>1</v>
@@ -4233,12 +4253,12 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>חנה בורר</t>
+          <t>דולה מומלצת במרכז ובשרון</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>midwife</t>
+          <t>doula</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4253,18 +4273,18 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/חנה-בורר/</t>
+          <t>https://www.sivandoula.com/דולה-מומלצת-במרכז-ובשרון</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>hannaborer@gmail.com</t>
+          <t>sivanpotash@gmail.com</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4277,7 +4297,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
+          <t>https://www.sivandoula.com/contact</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -4287,7 +4307,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>בחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה חנה בורר 0584190630 089790630 WhatsApp hannaborer@gmail.com אתר אינטרנט שמי חנה בורר, אני אחות ומיילדת מוסמכת, אם לתשעה יהלומים וסבתא מאושרת. התחלתי לעבוד בשדה הלידות בשנת 1997, כדולה ומדריכת הכנה ללידה. לאורך השנים הוכשרתי כאחות מוסמכת ומיילדת, וכמטפלת בנשים</t>
+          <t>ריון המלצות רגעים של אושר צרי קשר בלוג שאלות ותשובות מושגים מעולם הלידה More Use tab to navigate through the menu items. צרי קשר אם יש לך שאלות לגביי או לגבי שירותיי את מוזמנת לפנות אליי בשמחה סיון פוטש טלפון 0549294349 sivanpotash@gmail.com אימייל שלח תודה ! Copyright © 2023 Sivan Potash. All Rights Reserved. Pictures and Vectors Freepik סיון פוטש דולה ומדריכת הכנה ללידה  במרכז ובשרון Tel: 0549294349 bottom of page</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4297,7 +4317,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -4331,11 +4351,11 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>["https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/"]</t>
+          <t>["https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F", "https://www.sivandoula.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%99", "https://www.sivandoula.com/contact"]</t>
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4346,7 +4366,7 @@
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
+          <t>https://www.sivandoula.com/%D7%93%D7%95%D7%9C%D7%94-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%95%D7%91%D7%A9%D7%A8%D7%95%D7%9F</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr"/>
@@ -4380,17 +4400,15 @@
       <c r="A25" t="n">
         <v>13</v>
       </c>
-      <c r="B25" t="n">
-        <v>6</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>יניב צפורי</t>
+          <t>חנה בורר</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>midwife</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4405,18 +4423,18 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.imahi.co.il/חנה-בורר/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>zipori.obgyn@gmail.com</t>
+          <t>hannaborer@gmail.com</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4429,7 +4447,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.zipori-obgyn.com/</t>
+          <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4439,12 +4457,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> דופלר. פרטי, כללית מושלם, הסדר עם כל חברות הביטוח לקרוא עוד להזמין תור כתובת המרפאה: פרופ' דן שכטמן 10, קניון מול החוף וילג', בניין B קומה 2, חדרה ליצירת קשר וקביעת תורים: 072-3937709 מיטל מזכירה ראשית 📞 ד"ר יניב צפורי zipori.obgyn@gmail.com ©2022 by Doctor Yaniv Zipori bottom of page</t>
+          <t>בחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה חנה בורר 0584190630 089790630 WhatsApp hannaborer@gmail.com אתר אינטרנט שמי חנה בורר, אני אחות ומיילדת מוסמכת, אם לתשעה יהלומים וסבתא מאושרת. התחלתי לעבוד בשדה הלידות בשנת 1997, כדולה ומדריכת הכנה ללידה. לאורך השנים הוכשרתי כאחות מוסמכת ומיילדת, וכמטפלת בנשים</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>"יניב צפורי"</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4464,38 +4482,30 @@
         <v>0</v>
       </c>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2026-09-04T16:52:16.086371+00:00</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/65276", "https://www.zipori-obgyn.com/", "https://www.zipori-obgyn.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.zipori-obgyn.com/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94"]</t>
+          <t>["https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4506,15 +4516,13 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>https://www.zipori-obgyn.com/</t>
+          <t>https://www.imahi.co.il/%D7%97%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%A8/</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
@@ -4542,15 +4550,17 @@
       <c r="A26" t="n">
         <v>13</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ליווי הריון ~ הכנה ללידה ~ דולה</t>
+          <t>יניב צפורי</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>doula</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4565,18 +4575,18 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://en.babygaga.co.il/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>emmalihemed@gmail.com</t>
+          <t>zipori.obgyn@gmail.com</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4589,7 +4599,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.babygaga.co.il/contact4</t>
+          <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4599,17 +4609,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> לאתר של FEMMA צרי קשר More Use tab to navigate through the menu items. צרי קשר .הרגישי חופשיה לפנות אלי בכל שאלה או בקשה, אני תמיד זמינה בשבילך, בכל יום ובכל שעה .התקשרי אלי, שלחי לי אימייל או כתבי לי הודעה 052-9596370 emmalihemed@gmail.com ההודעה נשלחה בהצלחה שליחה דולה הכנה ללידה ספינינג בייביס ליווי הריון טיפול איזון אקווילבריו equilibrio Follow הגלישה באתר והשימוש ברשימת התפוצה כפופים לתקנון כללים והבהרות לגבי שימוש במידע ליצירת קש</t>
+          <t xml:space="preserve"> דופלר. פרטי, כללית מושלם, הסדר עם כל חברות הביטוח לקרוא עוד להזמין תור כתובת המרפאה: פרופ' דן שכטמן 10, קניון מול החוף וילג', בניין B קומה 2, חדרה ליצירת קשר וקביעת תורים: 072-3937709 מיטל מזכירה ראשית 📞 ד"ר יניב צפורי zipori.obgyn@gmail.com ©2022 by Doctor Yaniv Zipori bottom of page</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>"ליווי הריון הכנה ללידה דולה" אתר רשמי צור קשר</t>
+          <t>"יניב צפורי"</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -4626,17 +4636,17 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-03T16:27:03.922775+00:00</t>
+          <t>2026-09-04T16:52:16.086371+00:00</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
         <v>2</v>
@@ -4646,16 +4656,16 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>["https://en.babygaga.co.il/", "https://www.babygaga.co.il/", "https://www.femma.co.il/", "https://www.babygaga.co.il/about-me-picture", "https://www.babygaga.co.il/contact4"]</t>
+          <t>["https://www.doctorita.co.il/experts/65276", "https://www.zipori-obgyn.com/", "https://www.zipori-obgyn.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.zipori-obgyn.com/%D7%A9%D7%99%D7%A8%D7%95%D7%AA%D7%99-%D7%94%D7%9E%D7%A8%D7%A4%D7%90%D7%94"]</t>
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4666,7 +4676,7 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>https://www.babygaga.co.il/</t>
+          <t>https://www.zipori-obgyn.com/</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr"/>
@@ -4676,7 +4686,9 @@
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
+      <c r="AP26" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="n">
         <v>1</v>
@@ -4703,12 +4715,12 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>מדריכת הכנה ללידה</t>
+          <t>ליווי הריון ~ הכנה ללידה ~ דולה</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>childbirth_educator</t>
+          <t>doula</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4723,7 +4735,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.einavsitonron.com/birth-guidance</t>
+          <t>https://en.babygaga.co.il/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -4734,7 +4746,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>einav_r@hotmail.com</t>
+          <t>emmalihemed@gmail.com</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4747,7 +4759,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.einavsitonron.com/contact</t>
+          <t>https://www.babygaga.co.il/contact4</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4757,12 +4769,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>קס קרניוסקראל אינטגרטיבי ICS כרטיסיית טיפולים מדריכת הכנה ללידה שובר מתנה על הקליניקה המלצות מאמרים יצירת קשר More Use tab to navigate through the menu items. ליצירת קשר ותיאום טיפולים עינב סיטון-רון קיבוץ החותרים מייל: einav_r@hotmail.com טלפון: 053-9512212 פייסבוק: 'עינב סיטון רון - מגע שבא מהלב' מוזמנים גם להשאיר כאן הודעה אני מאשר/ת את קריאת וקבלת מדיניות הפרטיות שליחה ההודעה נשלחה בהצלחה! עיסוי שבדי | עיסוי רפואי | רפלקסולוגיה | עי</t>
+          <t xml:space="preserve"> לאתר של FEMMA צרי קשר More Use tab to navigate through the menu items. צרי קשר .הרגישי חופשיה לפנות אלי בכל שאלה או בקשה, אני תמיד זמינה בשבילך, בכל יום ובכל שעה .התקשרי אלי, שלחי לי אימייל או כתבי לי הודעה 052-9596370 emmalihemed@gmail.com ההודעה נשלחה בהצלחה שליחה דולה הכנה ללידה ספינינג בייביס ליווי הריון טיפול איזון אקווילבריו equilibrio Follow הגלישה באתר והשימוש ברשימת התפוצה כפופים לתקנון כללים והבהרות לגבי שימוש במידע ליצירת קש</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"ליווי הריון הכנה ללידה דולה" אתר רשמי צור קשר</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4782,30 +4794,38 @@
         <v>0</v>
       </c>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-09-03T16:27:03.922775+00:00</t>
+        </is>
+      </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>ddgs:auto</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>["https://www.einavsitonron.com/birth-guidance", "https://www.einavsitonron.com/about", "https://www.einavsitonron.com/contact"]</t>
+          <t>["https://en.babygaga.co.il/", "https://www.babygaga.co.il/", "https://www.femma.co.il/", "https://www.babygaga.co.il/about-me-picture", "https://www.babygaga.co.il/contact4"]</t>
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4816,7 +4836,7 @@
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>https://www.einavsitonron.com/birth-guidance</t>
+          <t>https://www.babygaga.co.il/</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr"/>
@@ -4850,17 +4870,15 @@
       <c r="A28" t="n">
         <v>13</v>
       </c>
-      <c r="B28" t="n">
-        <v>6</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>נורה גורכד שבסו</t>
+          <t>מדריכת הכנה ללידה</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>childbirth_educator</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4875,18 +4893,18 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>norashapso@gmail.com</t>
+          <t>einav_r@hotmail.com</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4899,7 +4917,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://www.einavsitonron.com/contact</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4909,17 +4927,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
+          <t>קס קרניוסקראל אינטגרטיבי ICS כרטיסיית טיפולים מדריכת הכנה ללידה שובר מתנה על הקליניקה המלצות מאמרים יצירת קשר More Use tab to navigate through the menu items. ליצירת קשר ותיאום טיפולים עינב סיטון-רון קיבוץ החותרים מייל: einav_r@hotmail.com טלפון: 053-9512212 פייסבוק: 'עינב סיטון רון - מגע שבא מהלב' מוזמנים גם להשאיר כאן הודעה אני מאשר/ת את קריאת וקבלת מדיניות הפרטיות שליחה ההודעה נשלחה בהצלחה! עיסוי שבדי | עיסוי רפואי | רפלקסולוגיה | עי</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>"נורה גורכד שבסו"</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -4934,38 +4952,30 @@
         <v>0</v>
       </c>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2026-09-04T04:55:16.280760+00:00</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.einavsitonron.com/birth-guidance", "https://www.einavsitonron.com/about", "https://www.einavsitonron.com/contact"]</t>
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4976,15 +4986,13 @@
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
@@ -5012,15 +5020,17 @@
       <c r="A29" t="n">
         <v>13</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>סדנאות הכנה ללידה</t>
+          <t>נורה גורכד שבסו</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>childbirth_educator</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5035,18 +5045,18 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>hagitswisa10@gmail.com</t>
+          <t>norashapso@gmail.com</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -5059,7 +5069,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -5069,17 +5079,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>הצהרת נגישות חגית לוינגר-סויסה • הדולה של השמחות 🤰💃, ליווי לידה, הכנה ללידה, טיפול איזון גופני-איקווליבריו, מעגלי נשים, סדנאות והרצאות. טלפון: 050-6696937 דוא"ל: hagitswisa10@gmail.com</t>
+          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>"סדנאות הכנה ללידה" הכנה ללידה</t>
+          <t>"נורה גורכד שבסו"</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -5096,7 +5106,7 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-03T16:33:45.692289+00:00</t>
+          <t>2026-09-04T04:55:16.280760+00:00</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -5106,13 +5116,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -5121,11 +5131,11 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>["https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/", "https://birth.org.il/%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94-%D7%9E%D7%93%D7%A8%D7%99%D7%9A-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%9C%D7%A1%D7%93%D7%A0%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%91%D7%98%D7%95/", "https://yardengroup.co.il/", "https://birth.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.maccabi4u.co.il/eligibilites/2625/", "https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94", "https://www.webwecan.co.il/"]</t>
+          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5136,7 +5146,7 @@
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr"/>
@@ -5146,7 +5156,9 @@
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
+      <c r="AP29" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="n">
         <v>1</v>
@@ -5170,17 +5182,15 @@
       <c r="A30" t="n">
         <v>13</v>
       </c>
-      <c r="B30" t="n">
-        <v>6</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>עמיחי רוטנשטרייך</t>
+          <t>סדנאות הכנה ללידה</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>childbirth_educator</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5195,18 +5205,18 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>prof.rottenstreich@gmail.com</t>
+          <t>hagitswisa10@gmail.com</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -5219,7 +5229,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
+          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5229,17 +5239,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
+          <t>הצהרת נגישות חגית לוינגר-סויסה • הדולה של השמחות 🤰💃, ליווי לידה, הכנה ללידה, טיפול איזון גופני-איקווליבריו, מעגלי נשים, סדנאות והרצאות. טלפון: 050-6696937 דוא"ל: hagitswisa10@gmail.com</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>"עמיחי רוטנשטרייך"</t>
+          <t>"סדנאות הכנה ללידה" הכנה ללידה</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -5256,7 +5266,7 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-04T06:21:38.973409+00:00</t>
+          <t>2026-09-03T16:33:45.692289+00:00</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -5266,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -5281,11 +5291,11 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
+          <t>["https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/", "https://birth.org.il/%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94-%D7%9E%D7%93%D7%A8%D7%99%D7%9A-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%9C%D7%A1%D7%93%D7%A0%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%91%D7%98%D7%95/", "https://yardengroup.co.il/", "https://birth.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.maccabi4u.co.il/eligibilites/2625/", "https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94", "https://www.webwecan.co.il/"]</t>
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5296,15 +5306,13 @@
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/</t>
+          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
@@ -5337,7 +5345,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ערן ברזילי</t>
+          <t>עמיחי רוטנשטרייך</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5368,7 +5376,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>prof.eran.barzilay@gmail.com</t>
+          <t>prof.rottenstreich@gmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5381,7 +5389,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5391,17 +5399,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
+          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>"ערן ברזילי"</t>
+          <t>"עמיחי רוטנשטרייך"</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -5418,7 +5426,7 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-04T06:36:53.022308+00:00</t>
+          <t>2026-09-04T06:21:38.973409+00:00</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -5428,13 +5436,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -5443,11 +5451,11 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5458,19 +5466,19 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
+      <c r="AP31" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="n">
         <v>1</v>
@@ -5499,7 +5507,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>פרופ' משען נדב</t>
+          <t>ערן ברזילי</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5519,18 +5527,18 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>drnadavmic@gmail.com</t>
+          <t>prof.eran.barzilay@gmail.com</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5543,7 +5551,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5553,12 +5561,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
+          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>"משען נדב"</t>
+          <t>"ערן ברזילי"</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5580,11 +5588,11 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-04T04:19:53.405262+00:00</t>
+          <t>2026-09-04T06:36:53.022308+00:00</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -5593,7 +5601,7 @@
         <v>4</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
@@ -5605,11 +5613,11 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
+          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>5.349051611818981e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5620,19 +5628,19 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
+      <c r="AP32" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="n">
         <v>1</v>
@@ -5661,12 +5669,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>רחל דהן</t>
+          <t>פרופ' משען נדב</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5681,18 +5689,18 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>racheldahan@hotmail.com</t>
+          <t>drnadavmic@gmail.com</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5705,7 +5713,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5715,12 +5723,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
+          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>"רחל דהן" רפואת משפחה</t>
+          <t>"משען נדב"</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5737,16 +5745,16 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-10T13:53:25.006579+00:00</t>
+          <t>2026-09-04T04:19:53.405262+00:00</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -5755,7 +5763,7 @@
         <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
         <v>1</v>
@@ -5767,22 +5775,22 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.003947683133098e+17</v>
+        <v>1.604715483545694e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
@@ -5790,20 +5798,12 @@
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO33" t="b">
-        <v>1</v>
-      </c>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="n">
         <v>1</v>
       </c>
@@ -5826,15 +5826,17 @@
       <c r="A34" t="n">
         <v>13</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>שיין ברגנר</t>
+          <t>רחל דהן</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>midwife</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5849,18 +5851,18 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/שיין-ברגנר/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>shaynemidwife@gmail.com</t>
+          <t>racheldahan@hotmail.com</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5873,7 +5875,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5883,12 +5885,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>דת בית לבחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה שיין ברגנר 0523627000 WhatsApp shaynemidwife@gmail.com אשל 15, עומר שיין , אם לחמישה ילדים שנולדו בלידה טבעית ובבית , מיילדת נשים בביתן מזה יותר משלושים שנה. לפי תפיסת עולמה של שיין לאישה וליילוד זכות על גופם והיא מאמינה בכבוד ובקדושת חוויית הלידה . ב</t>
+          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"רחל דהן" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5905,53 +5907,71 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-09-10T13:53:25.006579+00:00</t>
+        </is>
+      </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/"]</t>
+          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.201184304939929e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
+      <c r="AL34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
+        </is>
+      </c>
       <c r="AP34" t="inlineStr"/>
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="n">
@@ -5976,17 +5996,15 @@
       <c r="A35" t="n">
         <v>13</v>
       </c>
-      <c r="B35" t="n">
-        <v>6</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>אוהד חורי</t>
+          <t>שיין ברגנר</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>midwife</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6001,18 +6019,18 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.imahi.co.il/שיין-ברגנר/</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ohadho@clalit.org.il</t>
+          <t>shaynemidwife@gmail.com</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6021,11 +6039,11 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6035,17 +6053,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>דת בית לבחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה שיין ברגנר 0523627000 WhatsApp shaynemidwife@gmail.com אשל 15, עומר שיין , אם לחמישה ילדים שנולדו בלידה טבעית ובבית , מיילדת נשים בביתן מזה יותר משלושים שנה. לפי תפיסת עולמה של שיין לאישה וליילוד זכות על גופם והיא מאמינה בכבוד ובקדושת חוויית הלידה . ב</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -6060,38 +6078,30 @@
         <v>0</v>
       </c>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2026-09-09T23:21:42.073181+00:00</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
+          <t>["https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4.337491317126436e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6102,7 +6112,7 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
@@ -6110,20 +6120,10 @@
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
-        </is>
-      </c>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="n">
         <v>1</v>
       </c>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -6232,36 +6232,36 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
+        <v>8</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA36" t="n">
         <v>2</v>
       </c>
-      <c r="X36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4.337439849460605e+17</v>
+        <v>1.301247395137931e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6272,18 +6272,26 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
+      <c r="AL36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
       <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="n">
@@ -6313,7 +6321,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6344,7 +6352,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6357,7 +6365,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6367,12 +6375,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6394,36 +6402,36 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W37" t="n">
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>4.337439849460605e+17</v>
+        <v>1.301231954838182e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6434,19 +6442,19 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
+      <c r="AP37" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="n">
         <v>1</v>
@@ -6475,7 +6483,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6506,7 +6514,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6519,7 +6527,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6529,12 +6537,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6556,36 +6564,36 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4.337439849460605e+17</v>
+        <v>1.301231954838182e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6596,19 +6604,19 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
+      <c r="AP38" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="n">
         <v>1</v>
@@ -6637,7 +6645,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6668,7 +6676,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6681,7 +6689,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6691,12 +6699,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6718,36 +6726,36 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
         <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.301231954838182e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6758,19 +6766,19 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
+      <c r="AP39" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="n">
         <v>1</v>
@@ -6799,7 +6807,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6819,18 +6827,18 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6843,7 +6851,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6853,12 +6861,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6875,25 +6883,25 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
@@ -6905,11 +6913,11 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>5.007882380340662e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6920,19 +6928,19 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
+      <c r="AP40" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="n">
         <v>1</v>
@@ -6961,7 +6969,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6981,7 +6989,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -6992,7 +7000,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -7005,7 +7013,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7015,12 +7023,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7037,25 +7045,25 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
         <v>1</v>
@@ -7067,11 +7075,11 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>5.336698143893302e+17</v>
+        <v>1.502364714102199e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7082,19 +7090,19 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
+      <c r="AP41" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="n">
         <v>1</v>
@@ -7123,7 +7131,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7143,7 +7151,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -7154,7 +7162,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7167,7 +7175,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7177,12 +7185,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7204,14 +7212,14 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
         <v>4</v>
@@ -7229,11 +7237,11 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.601009443167991e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7244,19 +7252,19 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
+      <c r="AP42" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="n">
         <v>1</v>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7305,18 +7313,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7329,7 +7337,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7339,17 +7347,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -7366,36 +7374,36 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
+        <v>2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>4</v>
       </c>
-      <c r="X43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1</v>
-      </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="n">
         <v>1</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4.337491317124723e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7406,19 +7414,19 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
+      <c r="AP43" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ43" t="inlineStr"/>
       <c r="AR43" t="n">
         <v>1</v>
@@ -7447,12 +7455,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>היחידה לפוריות והפריה חוץ גופית</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>fertility_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -7467,18 +7475,18 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>idoba@szmc.org.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7491,7 +7499,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7501,17 +7509,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -7523,41 +7531,41 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-04T18:29:47.683340+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X44" t="n">
         <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>6.016596415654743e+17</v>
+        <v>1.301247395137417e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7568,19 +7576,19 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
+      <c r="AP44" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="n">
         <v>1</v>
@@ -7609,12 +7617,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>היחידה לפוריות והפריה חוץ גופית</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>fertility_doctor</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7629,18 +7637,18 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>idoba@szmc.org.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7653,7 +7661,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7663,12 +7671,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7685,28 +7693,28 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-04T18:29:47.683340+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -7715,11 +7723,11 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.804978924696423e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7730,19 +7738,19 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
+      <c r="AP45" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ45" t="inlineStr"/>
       <c r="AR45" t="n">
         <v>1</v>
@@ -7771,7 +7779,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7802,7 +7810,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7815,7 +7823,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7825,12 +7833,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7852,7 +7860,7 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -7862,10 +7870,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7877,11 +7885,11 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7892,19 +7900,19 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
+      <c r="AP46" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ46" t="inlineStr"/>
       <c r="AR46" t="n">
         <v>1</v>
@@ -7933,7 +7941,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7964,7 +7972,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7977,7 +7985,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -7987,12 +7995,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8014,7 +8022,7 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -8039,11 +8047,11 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4.115077426798385e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8054,19 +8062,19 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
+      <c r="AP47" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="n">
         <v>1</v>
@@ -8095,7 +8103,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8126,7 +8134,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -8139,7 +8147,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8149,12 +8157,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8176,14 +8184,14 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
         <v>2</v>
@@ -8201,11 +8209,11 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4.015386079358828e+17</v>
+        <v>1.234523228039515e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8216,19 +8224,19 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
+      <c r="AP48" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="n">
         <v>1</v>
@@ -8257,7 +8265,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8288,7 +8296,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8301,7 +8309,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8311,12 +8319,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8333,41 +8341,41 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
+        <v>4</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="n">
         <v>2</v>
       </c>
-      <c r="X49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>5</v>
-      </c>
       <c r="Z49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4.015334611694755e+17</v>
+        <v>1.204615823807648e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8378,19 +8386,19 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
+      <c r="AP49" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="n">
         <v>1</v>
@@ -8419,7 +8427,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8450,7 +8458,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8463,7 +8471,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8473,12 +8481,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8500,7 +8508,7 @@
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
@@ -8510,26 +8518,26 @@
         <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4.015334611694755e+17</v>
+        <v>1.204600383508426e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8540,19 +8548,19 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
+      <c r="AP50" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="n">
         <v>1</v>
@@ -8581,7 +8589,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8612,7 +8620,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8625,7 +8633,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8635,12 +8643,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8657,41 +8665,41 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>2</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204600383508426e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8702,19 +8710,19 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
+      <c r="AP51" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="n">
         <v>1</v>
@@ -8743,7 +8751,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8774,7 +8782,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>revital@drlinder.co.il</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8787,7 +8795,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8797,12 +8805,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"רויטל לינדר"</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8824,7 +8832,7 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T07:14:47.643108+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
@@ -8834,26 +8842,26 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.014877075845656e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8864,19 +8872,19 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.drlinder.co.il/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr"/>
       <c r="AN52" t="inlineStr"/>
       <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="inlineStr"/>
+      <c r="AP52" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ52" t="inlineStr"/>
       <c r="AR52" t="n">
         <v>1</v>
@@ -8905,7 +8913,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>רליקה הרשקוביץ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8936,7 +8944,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>ralikah@bgu.ac.il</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8949,7 +8957,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -8959,12 +8967,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"רליקה הרשקוביץ"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -8986,7 +8994,7 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T07:56:40.372731+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
@@ -8996,13 +9004,13 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -9011,11 +9019,11 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4.006641430561869e+17</v>
+        <v>1.204463122753697e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9026,19 +9034,19 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
       <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
+      <c r="AP53" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="n">
         <v>1</v>
@@ -9067,7 +9075,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>שקמה בר און</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9098,7 +9106,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>shikmabo@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -9111,7 +9119,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9121,12 +9129,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
+          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"שרית הלמן"</t>
+          <t>"שקמה בר און"</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -9143,12 +9151,12 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-05T00:06:28.339643+00:00</t>
+          <t>2026-09-04T10:28:27.702590+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
@@ -9161,10 +9169,10 @@
         <v>6</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -9173,11 +9181,11 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4.006793942511569e+17</v>
+        <v>1.201992429168561e+18</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9188,19 +9196,19 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
+      <c r="AP54" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="n">
         <v>1</v>
@@ -9224,20 +9232,22 @@
       <c r="A55" t="n">
         <v>13</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>6</v>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hadas Dar</t>
+          <t>שרית הלמן</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>lactation</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9247,18 +9257,18 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%94%d7%93%d7%a1-%d7%93%d7%a8/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ialp</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>hadasdar127@gmail.com</t>
+          <t>hsarit@szmc.org.il</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -9267,11 +9277,11 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9281,12 +9291,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>הבית אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי הדס דר – Hadas Dar טלפון: 052-8902748 אימייל: hadasdar127@gmail.com הסמכה: מדריכת הנקה אזורי קבלה: גוש דן, מרכז, שומרון, שרון ערים/ישובים: אורנית, שערי תקוה, אלקנה, עץ אפריים, ראש העין, הוד השרון, פתח-תקוה, כפר-סבא שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: מדריכ</t>
+          <t xml:space="preserve"> רופאים בשערי צדק ד"ר שרית  הלמן רופאה בכירה Dr. Sarit  Helman התמחות: גינקולוגיה ויילוד תת התמחות: הריון בסיכון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 026666656 מחלקה: 026666656 hsarit@szmc.org.il hsarit@szmc.org.il נסיון מקצועי Harvard T.H. Chan School of Public Health, Joslin Diabetes Center, Research intern under the supervision of Dr. Florence Brown and Dr. Tamarra James-Todd,     Type 1 Dia</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"שרית הלמן"</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9303,33 +9313,41 @@
         <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:06:28.339643+00:00</t>
+        </is>
+      </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/", "https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/#contact"]</t>
+          <t>["https://www.hamichlol.org.il/שרה_(שרית)_הלמן", "https://behevrat-haadam.org/ram-sara-helman/", "https://behevrat-haadam.org/tag/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/IsrAnthro/posts/%D7%A9%D7%A8%D7%99%D7%AA-%D7%94%D7%9C%D7%9E%D7%9F-%D7%A1%D7%95%D7%A6%D7%99%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%AA%D7%90%D7%A0%D7%97%D7%A0%D7%95-%D7%A9%D7%9E%D7%97%D7%99%D7%9D-%D7%9C%D7%A9%D7%AA%D7%A3-%D7%91%D7%91%D7%97%D7%91%D7%A8%D7%AA-%D7%94%D7%90%D7%93%D7%9D-%D7%90%D7%AA-%D7%93%D7%91%D7%A8%D7%99%D7%95-%D7%A9%D7%9C-%D7%90%D7%95%D7%A8%D7%99-%D7%A8%D7%9D-%D7%A4%D7%A8%D7%95%D7%A4-%D7%90%D7%9E%D7%A8%D7%99%D7%98%D7%95/4246861638775714/", "https://www.doctorita.co.il/experts/137665", "https://www.szmc.org.il/doctors/helman-sarit/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.202038182753471e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9340,7 +9358,7 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
+          <t>https://www.szmc.org.il/doctors/helman-sarit/</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr"/>
@@ -9350,7 +9368,9 @@
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
       <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
+      <c r="AP55" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="n">
         <v>1</v>
@@ -9377,7 +9397,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Liel Boker</t>
+          <t>Hadas Dar</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9397,7 +9417,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%9c%d7%99%d7%90%d7%9c-%d7%91%d7%95%d7%a7%d7%a8/</t>
+          <t>https://ialp.org.il/counselors/%d7%94%d7%93%d7%a1-%d7%93%d7%a8/</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -9408,7 +9428,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>lielhadid@gmail.com</t>
+          <t>hadasdar127@gmail.com</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -9421,7 +9441,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -9431,7 +9451,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>ת אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יאל בוקר – Liel Boker טלפון: 054-3515013 אימייל: Lielhadid@gmail.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שפלה ערים/ישובים: קוה, פתח תקווה, גבעת שמואל, קרית אונו, אור יהודה, רמת גן,בני ברק, גבעתיים, יהוד, מגשימים, אזור, חולון, נחלים, בארות יצחק</t>
+          <t>הבית אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי הדס דר – Hadas Dar טלפון: 052-8902748 אימייל: hadasdar127@gmail.com הסמכה: מדריכת הנקה אזורי קבלה: גוש דן, מרכז, שומרון, שרון ערים/ישובים: אורנית, שערי תקוה, אלקנה, עץ אפריים, ראש העין, הוד השרון, פתח-תקוה, כפר-סבא שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: מדריכ</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -9475,11 +9495,11 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/", "https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/", "https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9490,7 +9510,7 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr"/>
@@ -9524,17 +9544,15 @@
       <c r="A57" t="n">
         <v>13</v>
       </c>
-      <c r="B57" t="n">
-        <v>6</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>אירינה דורפמן אלמוג</t>
+          <t>Liel Boker</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>lactation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -9549,18 +9567,18 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://ialp.org.il/counselors/%d7%9c%d7%99%d7%90%d7%9c-%d7%91%d7%95%d7%a7%d7%a8/</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ialp</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>dr.irenadorfman@gmail.com</t>
+          <t>lielhadid@gmail.com</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -9573,7 +9591,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -9583,12 +9601,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
+          <t>ת אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יאל בוקר – Liel Boker טלפון: 054-3515013 אימייל: Lielhadid@gmail.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שפלה ערים/ישובים: קוה, פתח תקווה, גבעת שמואל, קרית אונו, אור יהודה, רמת גן,בני ברק, גבעתיים, יהוד, מגשימים, אזור, חולון, נחלים, בארות יצחק</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>"אירינה דורפמן אלמוג"</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -9598,48 +9616,40 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>2026-09-04T19:17:26.299485+00:00</t>
-        </is>
-      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/", "https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4.336524777762407e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9650,15 +9660,13 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%9C-%D7%91%D7%95%D7%A7%D7%A8/</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
       <c r="AO57" t="inlineStr"/>
@@ -9691,7 +9699,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>אלון שלב</t>
+          <t>אירינה דורפמן אלמוג</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9722,7 +9730,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>alonshalev31@gmail.com</t>
+          <t>dr.irenadorfman@gmail.com</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9735,7 +9743,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -9745,12 +9753,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
+          <t>מוג אירינה כרטיס עסק: ד"ר דורפמן אלמוג אירינה » תחום פעילות: בריאות וספורט » רופא » תאור העסק: רופאת משפחה עצמאית קופת חולים לאומית. » איש קשר: אירנה דורפמן » טלפונים: טלפון: 077-7997456 נייד: 054-4616457 » אתר: » מייל: dr.irenadorfman@gmail.com » כתובת: בן גוריון 123 יהוד, מיקוד: 56209 כלים מחשבונים לעסקים מדריכי ניהול עסק, הקמת עסק נושאי האתר הנהלת חשבונות הפקת חשבוניות חשבונית אלקטרונית ניהול לקוחות שותפים עסקיים אילת סיטי - מדריך הע</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>"אלון שלב"</t>
+          <t>"אירינה דורפמן אלמוג"</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -9760,11 +9768,11 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@flex.co.il", "confidence": 80, "source_url": "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "identity_url": "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "evidence": "info@flex.co.il", "matched_query": "\"אירינה דורפמן אלמוג\"", "extraction_method": "linked_mailto"}]</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -9772,23 +9780,23 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-09-04T19:37:15.755041+00:00</t>
+          <t>2026-09-04T19:17:26.299485+00:00</t>
         </is>
       </c>
       <c r="W58" t="n">
         <v>2</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
@@ -9797,11 +9805,11 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
+          <t>["https://www.dunsguide.co.il/C7195b21475cb11a3e5b86def04a3e20c_רופאים/דורפמן_אלמוג_אירינה/", "https://medpage.co.il/doctors/%D7%90%D7%99%D7%A8%D7%A0%D7%94-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-20871/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%93%D7%95%D7%A8%D7%A4%D7%9E%D7%9F-%D7%90%D7%9C%D7%9E%D7%95%D7%92-%D7%90%D7%99%D7%A8%D7%99%D7%A0%D7%94/", "https://www.beok.co.il/doctors/Doctors-129241/", "https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373", "https://www.flex.co.il/100_General/005_GeneralPages/006_About.aspx", "https://www.flex.co.il/100_General/005_GeneralPages/005_Contact.aspx", "https://www.flex.co.il/100_General/900_DifferentStuff/900_ForTheCommunity.aspx"]</t>
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.336524777762407e+17</v>
+        <v>1.300957433328722e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9812,19 +9820,19 @@
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>https://pain.coi.co.il/</t>
+          <t>https://www.flex.co.il/Businesses-Index/Business-Card.aspx?CardId=4373</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
       <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
+      <c r="AP58" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ58" t="inlineStr"/>
       <c r="AR58" t="n">
         <v>1</v>
@@ -9853,7 +9861,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>אמיר צבעוני</t>
+          <t>אלון שלב</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9884,7 +9892,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>healtms@gmail.com</t>
+          <t>alonshalev31@gmail.com</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9897,7 +9905,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9907,12 +9915,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
+          <t>הודעה לבעלי האתר תקופת הניסיון הסתיימה, יש ליצור מנוי דרך ממשק ניהול האתר. האתר נכנס לרשימת המחיקה ויימחק בקרוב לחץ כאן אם אינך זוכר את כתובת ממשק ניהול האתר שלך. דר אלון שלב - רופא כאב טלפון: 054-6221105 מייל: alonshalev31@gmail.com כתובת: ילדי טהרן 8, ראשון לציון ד"ר אלון שלב מומחה ברפואת המשפחה רופא כאב דף הבית אודות צור קשר אל תחכו - הזמינו תור לרופא עוד היום.. לייעוץ ראשוני ללא עלות והזמנת תורים מלאו פרטים או התקשרו: 05462</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>"אמיר צבעוני"</t>
+          <t>"אלון שלב"</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -9934,7 +9942,7 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-09-03T23:00:56.706890+00:00</t>
+          <t>2026-09-04T19:37:15.755041+00:00</t>
         </is>
       </c>
       <c r="W59" t="n">
@@ -9944,10 +9952,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9959,11 +9967,11 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fdr.shalev.pain%2F&amp;is_from_rle", "https://www.bgu.ac.il/people/shalevn/", "https://www.bgu.ac.il/en/people/shalevn/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fdr.shalev.pain%2F", "https://www.medreviews.co.il/search/pain-management/center/rishon-lezion", "https://pain.coi.co.il/", "https://pain.coi.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA.htm", "https://pain.coi.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8.htm"]</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300957433328722e+18</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -9974,19 +9982,19 @@
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>https://www.drzivony.co.il/</t>
+          <t>https://pain.coi.co.il/</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr"/>
       <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
+      <c r="AP59" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="n">
         <v>1</v>
@@ -10015,7 +10023,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>בתיה קורנבוים</t>
+          <t>אמיר צבעוני</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10046,7 +10054,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>batyakornboim@gmail.com</t>
+          <t>healtms@gmail.com</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -10059,7 +10067,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10069,12 +10077,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
+          <t>"ר אמיר צבעוני ד"ר אמיר צבעוני רופא משפחה מומחה העוסק בטיפול בכאב כרוני בגישת גוף-נפש ללא שימוש בתרופות או בפרוצדורות רפואיות. הטיפול מבוסס מחקר בתחום מדעי המח והכאב. ניתן לקרוא עליי עוד ב דף האודות . טלפון: 051-2303120 healtms@gmail.com קליניקה בגבעת עדה (סמוך לבנימינה) ניתן ליצור איתי קשר גם ב דף יצירת הקשר פוסטים אחרונים על הענק הירוק והדחקת רגשות לאותת עם המגבים רגישות יתר לאחר פציעה אזהרת טריגר בקשת סליחה מעצמי חפש: חיפוש בית אודות</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>"בתיה קורנבוים"</t>
+          <t>"אמיר צבעוני"</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -10096,7 +10104,7 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-09-03T23:52:50.148875+00:00</t>
+          <t>2026-09-03T23:00:56.706890+00:00</t>
         </is>
       </c>
       <c r="W60" t="n">
@@ -10121,11 +10129,11 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
+          <t>["https://www.drzivony.co.il/", "https://www.drzivony.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.336067241913308e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10136,19 +10144,19 @@
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>https://www.dr-batya-kornboim.com/</t>
+          <t>https://www.drzivony.co.il/</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
       <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="inlineStr"/>
+      <c r="AP60" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="n">
         <v>1</v>
@@ -10172,15 +10180,17 @@
       <c r="A61" t="n">
         <v>13</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>6</v>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>דפי רהב הס פסיכולוגית</t>
+          <t>בתיה קורנבוים</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>perinatal_mental_health</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -10195,18 +10205,18 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>dafyrahav@gmail.com</t>
+          <t>batyakornboim@gmail.com</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -10219,7 +10229,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10229,12 +10239,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>עמים ההיריון יופסק מבחירה ולפעמים לא ניתן לבחור. אנשי מקצוע רבים יגדירו את הפסקת ההריון כאירוע טראומתי עבור גוף האישה... &lt; המשך קריאה כתבות ומאמרים צרי קשר איך אוכל לעזור? דפי רהב הס 052-3302900 כרכור / טיפולים און ליין dafyrahav@gmail.com שלח נשלח! תודה שיצרת קשר צור קשר © כל הזכויות שמורות לדפי רהב הס bottom of page</t>
+          <t>שקל בחיפה אודות חוות דעת יצירת קשר כתבות ופרסומים תפריט ד״ר בתיה קורנבוים - מומחית ברפואת משפחה ורפואת השמנה [תיאור המרפאה יתווסף בהמשך] טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו חיפה 3570901 IL 052-567-1100 batyakornboim@gmail.com התמחויות רפואיות עיקריות: [פירוט תחומי הטיפול יתווסף בהמשך] מידע מעשי: יצירת קשר: טלפון 052-567-1100 או וואטסאפ 052-567-1100 מיקום: טשרניחובסקי 37, קומה 3, מרכז סטלה מאריס, בניין סטארקו , חיפה סוג</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"בתיה קורנבוים"</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10254,15 +10264,19 @@
         <v>0</v>
       </c>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-09-03T23:52:50.148875+00:00</t>
+        </is>
+      </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z61" t="n">
         <v>1</v>
@@ -10270,14 +10284,18 @@
       <c r="AA61" t="n">
         <v>0</v>
       </c>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>["https://www.dafyrahavhass.com/", "https://www.dafyrahavhass.com/copy-of", "https://www.dafyrahavhass.com/aboutme"]</t>
+          <t>["https://www.dr-batya-kornboim.com/", "https://www.dr-batya-kornboim.com/#%D7%90%D7%95%D7%93%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.300820172573992e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10288,7 +10306,7 @@
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>https://www.dafyrahavhass.com/</t>
+          <t>https://www.dr-batya-kornboim.com/</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr"/>
@@ -10298,7 +10316,9 @@
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="inlineStr"/>
+      <c r="AP61" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="n">
         <v>1</v>
@@ -10322,17 +10342,15 @@
       <c r="A62" t="n">
         <v>13</v>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>טלי גליקסמן</t>
+          <t>דפי רהב הס פסיכולוגית</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sleep_consultant</t>
+          <t>perinatal_mental_health</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -10347,7 +10365,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://sleepingbaby.hashevet.co.il/sleep-pro/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -10358,7 +10376,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>tali4baby@gmail.com</t>
+          <t>dafyrahav@gmail.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -10371,7 +10389,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10381,12 +10399,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>ות, מענה לשאלות וסיכום. בין המפגשים יתקיים ליווי ההורים בעבודה לפי התוכנית הספציפית אשר גובשה באמצעות שיחות טלפוניות ומיילים. אתם מוזמנים לפנות אל טלי גליקסמן לשיחת הסבר והרחבה ומענה לשאלותיכם. טלפון: 050-848-6651 מייל: tali4baby@gmail.com Post navigation → גדילת תינוקות הדרכה והכוונה להורים החדשים למניעת עיכוב התפתחותי שמונת היסודות להתפתחות מיטבית ← קישורים מרכזיים בריאות ילדים בראייה הוליסטית טלי גליקסמן מומחית להתפתחות תינוקות אודות</t>
+          <t>עמים ההיריון יופסק מבחירה ולפעמים לא ניתן לבחור. אנשי מקצוע רבים יגדירו את הפסקת ההריון כאירוע טראומתי עבור גוף האישה... &lt; המשך קריאה כתבות ומאמרים צרי קשר איך אוכל לעזור? דפי רהב הס 052-3302900 כרכור / טיפולים און ליין dafyrahav@gmail.com שלח נשלח! תודה שיצרת קשר צור קשר © כל הזכויות שמורות לדפי רהב הס bottom of page</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>"טלי גליקסמן" יועצת שינה</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10396,48 +10414,40 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>[{"email": "info@yaeltzur.co.il", "confidence": 80, "source_url": "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "identity_url": "https://www.yaeltzur.co.il/talie-gliksman/", "evidence": "[email protected]", "matched_query": "\"טלי גליקסמן\" יועצת שינה", "extraction_method": "linked_cloudflare"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>2026-09-04T04:15:05.038841+00:00</t>
-        </is>
-      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>["https://sleepingbaby.hashevet.co.il/sleep-pro/", "https://sleepingbaby.hashevet.co.il/sleep-pro/#about", "https://www.huggies.co.il/professionals/tali-gliksman", "https://www.huggies.co.il/contact-us", "https://www.facebook.com/hashevet/", "https://www.yaeltzur.co.il/talie-gliksman/", "https://www.allinternet.co.il/", "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "https://www.yaeltzur.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.yaeltzur.co.il/cdn-cgi/l/email-protection#96fff8f0f9d6eff7f3fae2ece3e4b8f5f9b8fffa", "https://linktr.ee/tali4baby", "https://www.hashevet.co.il/", "https://linktr.ee/s/about/trust-center/report?field86145911=https%3A%2F%2Flinktr.ee%2Ftali4baby", "https://linktr.ee/blog/daisy-chain-fields-sticker-pack", "https://linktr.ee/features/contact-forms", "https://linktr.ee/features/audience-management", "https://linktr.ee/features/email-integrations", "https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/", "https://www.hashevet.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.hashevet.co.il/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/%D7%94%D7%93%D7%A8%D7%9B%D7%94%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/", "https://www.hashevet.co.il/category/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.dafyrahavhass.com/", "https://www.dafyrahavhass.com/copy-of", "https://www.dafyrahavhass.com/aboutme"]</t>
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>5.040214913677007e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10448,7 +10458,7 @@
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
+          <t>https://www.dafyrahavhass.com/</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr"/>
@@ -10487,12 +10497,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>שיקום רצפת האגן</t>
+          <t>טלי גליקסמן</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>pelvic_floor</t>
+          <t>sleep_consultant</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -10507,7 +10517,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/</t>
+          <t>https://sleepingbaby.hashevet.co.il/sleep-pro/</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -10518,7 +10528,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>michalgilad@gmail.com</t>
+          <t>tali4baby@gmail.com</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -10531,7 +10541,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.michalgilad.com/</t>
+          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -10541,12 +10551,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>לכאבים אורטופדים בהריון טיפולים לימפטיים שיקום רצפת האגן הכנה ללידה Contact Describe your image Describe your image 1/7 התקשרו אלי ליצירת קשר וקביעת טיפול מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com I agree to the terms &amp; conditions שלח הפרטים ישמשו רק ליצירת קשר ולא יעברו לצד שלישי. תודה על הפניה. Back to to</t>
+          <t>ות, מענה לשאלות וסיכום. בין המפגשים יתקיים ליווי ההורים בעבודה לפי התוכנית הספציפית אשר גובשה באמצעות שיחות טלפוניות ומיילים. אתם מוזמנים לפנות אל טלי גליקסמן לשיחת הסבר והרחבה ומענה לשאלותיכם. טלפון: 050-848-6651 מייל: tali4baby@gmail.com Post navigation → גדילת תינוקות הדרכה והכוונה להורים החדשים למניעת עיכוב התפתחותי שמונת היסודות להתפתחות מיטבית ← קישורים מרכזיים בריאות ילדים בראייה הוליסטית טלי גליקסמן מומחית להתפתחות תינוקות אודות</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>"שיקום רצפת האגן" רצפת אגן</t>
+          <t>"טלי גליקסמן" יועצת שינה</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -10556,11 +10566,11 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "info@yaeltzur.co.il", "confidence": 80, "source_url": "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "identity_url": "https://www.yaeltzur.co.il/talie-gliksman/", "evidence": "[email protected]", "matched_query": "\"טלי גליקסמן\" יועצת שינה", "extraction_method": "linked_cloudflare"}]</t>
         </is>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -10568,23 +10578,23 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-09-03T19:11:34.001809+00:00</t>
+          <t>2026-09-04T04:15:05.038841+00:00</t>
         </is>
       </c>
       <c r="W63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
         <v>6</v>
       </c>
       <c r="Z63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -10593,11 +10603,11 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>["https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/", "https://www.gov.il/he/departments/ministry_of_health/govil-landing-page", "https://www.szmc.org.il/departments/clinics-and-institutes/machleket-physiotherapia/shikum-ritzpat-agan/", "https://www.shamir.org/clinics/physiotherapy/pelvis/", "https://asafpt.com/pelvic-floor/", "https://asafpt.com/about/", "https://asafpt.com/contact/", "https://he.hadassah.org.il/physiotherapy/pelvic-floor-physiotherapy/", "https://www.michalgilad.com/", "https://www.wix.com/lpviral/enviral?utm_campaign=vir_wixad_live&amp;adsVersion=banner_2024&amp;orig_msid=aa99f552-cce6-4d9b-96f0-a304175f7068&amp;orig_msid=ad07a822-90b8-4e00-adec-53cda74130fe&amp;adsVersion=banner_2024", "https://www.michalgilad.com/#aboutus"]</t>
+          <t>["https://sleepingbaby.hashevet.co.il/sleep-pro/", "https://sleepingbaby.hashevet.co.il/sleep-pro/#about", "https://www.huggies.co.il/professionals/tali-gliksman", "https://www.huggies.co.il/contact-us", "https://www.facebook.com/hashevet/", "https://www.yaeltzur.co.il/talie-gliksman/", "https://www.allinternet.co.il/", "https://www.yaeltzur.co.il/%d7%94%d7%aa%d7%97%d7%91%d7%a8%d7%95%d7%aa-%d7%95%d7%94%d7%a8%d7%a9%d7%9e%d7%94/", "https://www.yaeltzur.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.yaeltzur.co.il/cdn-cgi/l/email-protection#96fff8f0f9d6eff7f3fae2ece3e4b8f5f9b8fffa", "https://linktr.ee/tali4baby", "https://www.hashevet.co.il/", "https://linktr.ee/s/about/trust-center/report?field86145911=https%3A%2F%2Flinktr.ee%2Ftali4baby", "https://linktr.ee/blog/daisy-chain-fields-sticker-pack", "https://linktr.ee/features/contact-forms", "https://linktr.ee/features/audience-management", "https://linktr.ee/features/email-integrations", "https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/", "https://www.hashevet.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.hashevet.co.il/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/%D7%94%D7%93%D7%A8%D7%9B%D7%94%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/", "https://www.hashevet.co.il/category/%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%9C%D7%A6%D7%95%D7%95%D7%AA%D7%99%D7%9D-%D7%97%D7%99%D7%A0%D7%95%D7%9B%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.512064474103102e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10608,7 +10618,7 @@
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>https://www.michalgilad.com/</t>
+          <t>https://www.hashevet.co.il/%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%A9%D7%AA%D7%9C%D7%9E%D7%95%D7%99%D7%95%D7%AA-%D7%95%D7%94%D7%93%D7%A8%D7%9B%D7%95%D7%AA/%D7%98%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7%D7%A1%D7%9E%D7%9F-%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%94%D7%AA%D7%A4%D7%AA%D7%97%D7%95%D7%AA-%D7%AA%D7%99%D7%A0%D7%95%D7%A7%D7%95%D7%AA-%D7%9E%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr"/>
@@ -10643,16 +10653,16 @@
         <v>13</v>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>שלומית שדמון</t>
+          <t>שיקום רצפת האגן</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>pelvic_floor</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -10667,18 +10677,18 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>shlomitshadmon@gmail.com</t>
+          <t>michalgilad@gmail.com</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -10691,7 +10701,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.michalgilad.com/</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -10701,12 +10711,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
+          <t>לכאבים אורטופדים בהריון טיפולים לימפטיים שיקום רצפת האגן הכנה ללידה Contact Describe your image Describe your image 1/7 התקשרו אלי ליצירת קשר וקביעת טיפול מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com מיכל גלעד שיקום רצפת אגן סנה משה הרצליה טלפון: 0522458554 Email: michalgilad@gmail.com I agree to the terms &amp; conditions שלח הפרטים ישמשו רק ליצירת קשר ולא יעברו לצד שלישי. תודה על הפניה. Back to to</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>"שלומית שדמון"</t>
+          <t>"שיקום רצפת האגן" רצפת אגן</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -10716,35 +10726,35 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-09-04T15:25:57.140597+00:00</t>
+          <t>2026-09-03T19:11:34.001809+00:00</t>
         </is>
       </c>
       <c r="W64" t="n">
         <v>2</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
@@ -10753,11 +10763,11 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://me.health.gov.il/older-adult/keep-me-healthy/rehabilitation/pelvic-floor-therapy/", "https://www.gov.il/he/departments/ministry_of_health/govil-landing-page", "https://www.szmc.org.il/departments/clinics-and-institutes/machleket-physiotherapia/shikum-ritzpat-agan/", "https://www.shamir.org/clinics/physiotherapy/pelvis/", "https://asafpt.com/pelvic-floor/", "https://asafpt.com/about/", "https://asafpt.com/contact/", "https://he.hadassah.org.il/physiotherapy/pelvic-floor-physiotherapy/", "https://www.michalgilad.com/", "https://www.wix.com/lpviral/enviral?utm_campaign=vir_wixad_live&amp;adsVersion=banner_2024&amp;orig_msid=aa99f552-cce6-4d9b-96f0-a304175f7068&amp;orig_msid=ad07a822-90b8-4e00-adec-53cda74130fe&amp;adsVersion=banner_2024", "https://www.michalgilad.com/#aboutus"]</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4.003896215467274e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10768,15 +10778,13 @@
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
+          <t>https://www.michalgilad.com/</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr"/>
       <c r="AN64" t="inlineStr"/>
       <c r="AO64" t="inlineStr"/>
@@ -10809,7 +10817,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>שרון שלמה קלייטמן</t>
+          <t>שלומית שדמון</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10840,7 +10848,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>sharon.kleitman@gmail.com</t>
+          <t>shlomitshadmon@gmail.com</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -10853,7 +10861,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -10863,12 +10871,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
+          <t>ם ופעילויות כנסים והשתלמויות הרצאות מהכנסים מטפלי.ות איט"ם מטפלי.ות איט"ם פיזיותרפיסטים.ית איט"ם מרפאות ציבוריות הצטרפות והתמחות צור קשר פרטי התקשרות טלפון 054-9145177 כתובת אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אימייל shlomitshadmon@gmail.com שדמון שלומית (MD) – תל אביב מקצוע:  רופאת משפחה, מוסמכת ביעוץ וטיפול מיני. התמחות: מטפלת מינית איזור טיפול: תל אביב אודותי אני רופאת משפחה ותיקה, מדריכה קלינית ומרצה בנושאי בריאות האישה, מיניות ה</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>"שרון שלמה קלייטמן"</t>
+          <t>"שלומית שדמון"</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -10878,11 +10886,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "identity_url": "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "evidence": "mail.com אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו אלעזר בן עזריה 10 דירה 8 . תל-אביב-יפו איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"שלומית שדמון\"", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -10890,7 +10898,7 @@
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-09-04T15:41:54.743203+00:00</t>
+          <t>2026-09-04T15:25:57.140597+00:00</t>
         </is>
       </c>
       <c r="W65" t="n">
@@ -10903,10 +10911,10 @@
         <v>4</v>
       </c>
       <c r="Z65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -10915,11 +10923,11 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
+          <t>["https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA/", "https://moonbellboutique.com/index/%D7%93%D7%A8-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%A9%D7%93%D7%9E%D7%95%D7%9F/", "https://moonbellboutique.com/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://www.infomed.co.il/experts/145161/", "https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>4.003896215467274e+17</v>
+        <v>1.201168864640182e+18</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -10930,19 +10938,19 @@
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
+          <t>https://itam.org.il/therapists/%D7%A9%D7%93%D7%9E%D7%95%D7%9F-%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%93%D7%A8-2/</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr"/>
       <c r="AO65" t="inlineStr"/>
-      <c r="AP65" t="inlineStr"/>
+      <c r="AP65" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="n">
         <v>1</v>
@@ -10966,15 +10974,17 @@
       <c r="A66" t="n">
         <v>13</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>6</v>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>תזונה אחרי לידה- תזונה בהנקה</t>
+          <t>שרון שלמה קלייטמן</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>pregnancy_dietitian</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -10989,18 +10999,18 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/תזונה-אחרי-לידה-תזונה-בהנקה/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>neta.amiri@gmail.com</t>
+          <t>sharon.kleitman@gmail.com</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -11013,7 +11023,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11023,12 +11033,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>י הגישה הטיפולית סיפורי האישי: כך ירדתי במשקל לתמיד שירותים ייעוץ דיאטנית בניית תפריט שבועי לגן ילדים/ צהרונים הרצאות וסדנאות בתזונה שחלות פוליציסטיות/ טיפולי פוריות מאמרים מתכונים סרטונים יצירת קשר צרי קשר: 050-4350466 neta.amiri@gmail.com 1Z0-053 1Z0-517 640-461 640-722 642-832 648-375 74-344 74-409 A00-212 C2010-503 C2010-598 C2010-651 C2010-652 C2020-605 OG0-091 070-413 070-459 070-496 1Z0-052 C_BOSUP_90 ﻿ תזונה אחרי לידה- תזונה בהנ</t>
+          <t>ש קשר שיתוף שתפו במייל שתפו בפייסבוק שתפו בטוויטר שתפו בלינקדין ד"ר שרון קלייטמן מומחה ברפואת משפחה, MST - Mind Set Technique, רפואה אינטגרטיבית, IMS - דיקור יבש, תזונה אינטגרטיבית. נייד 052-8325580 פקס 08-6560357 דוא"ל sharon.kleitman@gmail.com אתר www.integrative-med.com שלח/י לי sms פייסבוק אודות ד"ר שרון קלייטמן מומחה ברפואת משפחה, סיים את לימודי הרפואה באוניברסיטת בן גוריון, נשוי ואב לארבעה, מתגורר בקיבוץ שדה בוקר. עוסק בפיתוח והקנ</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"שרון שלמה קלייטמן"</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -11048,30 +11058,38 @@
         <v>0</v>
       </c>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-09-04T15:41:54.743203+00:00</t>
+        </is>
+      </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>["https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/"]</t>
+          <t>["https://docsrated.com/doctors/שרון-קלייטמן", "https://www.dunsguide.co.il/Cb6a87819a48606a97ab6b3a3617e9370_רופאים/קלייטמן_שרון_שלמה/", "https://www.facebook.com/sharon.kleitman.md/directory_category/", "https://dns.dibiz.com/sharon-kleitman-md", "https://longevitepalmbeach.com"]</t>
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.201168864640182e+18</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11082,7 +11100,7 @@
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
+          <t>https://dns.dibiz.com/sharon-kleitman-md</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr"/>
@@ -11092,7 +11110,9 @@
       <c r="AM66" t="inlineStr"/>
       <c r="AN66" t="inlineStr"/>
       <c r="AO66" t="inlineStr"/>
-      <c r="AP66" t="inlineStr"/>
+      <c r="AP66" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ66" t="inlineStr"/>
       <c r="AR66" t="n">
         <v>1</v>
@@ -11119,7 +11139,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>תזונה ופוריות</t>
+          <t>תזונה אחרי לידה- תזונה בהנקה</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11139,7 +11159,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/תזונה-ופוריות/</t>
+          <t>https://tzunatbar.co.il/תזונה-אחרי-לידה-תזונה-בהנקה/</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -11150,7 +11170,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>benharoush@gmail.com</t>
+          <t>neta.amiri@gmail.com</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -11163,7 +11183,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
+          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11173,7 +11193,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>ור לך בתקופת טיפולי הפוריות חשיבותה של התזונה הסינית והמאקרוביוטית בכניסה להריון תזונה ופוריות O.M.D – מומחית לרפואה סינית – רפואה סינית וטיפולי פוריות יצירת קשר מרפאה בפתח תקווה: 050-5589013 מרפאה בתל אביב: 053-9956805 benharoush@gmail.com הרצל רוזנבלום 8 (מתחם סי אנד סאן) תל אביב אנצו סירני 7 פתח תקוה מה באתר דף הבית ויקיפוריות ויקיפוריות - גלריית הסרטונים ויקיפוריות -האנציקלופדיה הוירטואלית פורטל החדשנות של עולם הפוריות מרכז מומחים ב</t>
+          <t>י הגישה הטיפולית סיפורי האישי: כך ירדתי במשקל לתמיד שירותים ייעוץ דיאטנית בניית תפריט שבועי לגן ילדים/ צהרונים הרצאות וסדנאות בתזונה שחלות פוליציסטיות/ טיפולי פוריות מאמרים מתכונים סרטונים יצירת קשר צרי קשר: 050-4350466 neta.amiri@gmail.com 1Z0-053 1Z0-517 640-461 640-722 642-832 648-375 74-344 74-409 A00-212 C2010-503 C2010-598 C2010-651 C2010-652 C2020-605 OG0-091 070-413 070-459 070-496 1Z0-052 C_BOSUP_90 ﻿ תזונה אחרי לידה- תזונה בהנ</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -11217,11 +11237,11 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>["https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.yourdiet.co.il/", "https://wikifertility.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
+          <t>["https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/"]</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11232,7 +11252,7 @@
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
+          <t>https://tzunatbar.co.il/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%90%D7%97%D7%A8%D7%99-%D7%9C%D7%99%D7%93%D7%94-%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%91%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr"/>
@@ -11269,12 +11289,12 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Adi Kliffer Barmeir</t>
+          <t>תזונה ופוריות</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>lactation</t>
+          <t>pregnancy_dietitian</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -11289,18 +11309,18 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a2%d7%93%d7%99-%d7%a7%d7%9c%d7%99%d7%a4%d7%a8-%d7%91%d7%a8-%d7%9e%d7%90%d7%99%d7%a8/</t>
+          <t>https://wikifertility.com/תזונה-ופוריות/</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ialp</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>adi@kliffer.com</t>
+          <t>benharoush@gmail.com</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -11309,11 +11329,11 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
+          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -11323,7 +11343,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>adi@kliffer.com</t>
+          <t>ור לך בתקופת טיפולי הפוריות חשיבותה של התזונה הסינית והמאקרוביוטית בכניסה להריון תזונה ופוריות O.M.D – מומחית לרפואה סינית – רפואה סינית וטיפולי פוריות יצירת קשר מרפאה בפתח תקווה: 050-5589013 מרפאה בתל אביב: 053-9956805 benharoush@gmail.com הרצל רוזנבלום 8 (מתחם סי אנד סאן) תל אביב אנצו סירני 7 פתח תקוה מה באתר דף הבית ויקיפוריות ויקיפוריות - גלריית הסרטונים ויקיפוריות -האנציקלופדיה הוירטואלית פורטל החדשנות של עולם הפוריות מרכז מומחים ב</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -11333,7 +11353,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -11367,11 +11387,11 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/", "https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/#contact"]</t>
+          <t>["https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/", "https://www.yourdiet.co.il/", "https://wikifertility.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11382,7 +11402,7 @@
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
+          <t>https://wikifertility.com/%D7%AA%D7%96%D7%95%D7%A0%D7%94-%D7%95%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr"/>
@@ -11419,7 +11439,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ariella Dubrowin</t>
+          <t>Adi Kliffer Barmeir</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11439,7 +11459,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%90%d7%a8%d7%99%d7%90%d7%9c%d7%94-%d7%93%d7%95%d7%91%d7%a8%d7%90%d7%95%d7%99%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%a2%d7%93%d7%99-%d7%a7%d7%9c%d7%99%d7%a4%d7%a8-%d7%91%d7%a8-%d7%9e%d7%90%d7%99%d7%a8/</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -11450,7 +11470,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ariella@hanakatova.com</t>
+          <t>adi@kliffer.com</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -11463,7 +11483,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -11473,7 +11493,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אריאלה דובראוין – Ariella Dubrowin טלפון: 054-6458027 אימייל: ariella@hanakatova.com הסמכה: מדריכת הנקה אזורי קבלה: ירושלים והסביבה, מרכז, שפלה ערים/ישובים: ירושלים, בית שמש, ביתר עילית, אפרת, אלון שבות, כפר עציון, ראש צורים, אלעזר, בת עין, מגדל עוז, תקוע, נוקדים, מעלה עמוס, פני קד</t>
+          <t>adi@kliffer.com</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -11483,7 +11503,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -11517,11 +11537,11 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/", "https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/#contact"]</t>
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11532,7 +11552,7 @@
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%9C%D7%99%D7%A4%D7%A8-%D7%91%D7%A8-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr"/>
@@ -11569,7 +11589,7 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Aviella Natalie</t>
+          <t>Ariella Dubrowin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11589,7 +11609,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%90%d7%91%d7%99%d7%90%d7%9c%d7%94/</t>
+          <t>https://ialp.org.il/counselors/%d7%90%d7%a8%d7%99%d7%90%d7%9c%d7%94-%d7%93%d7%95%d7%91%d7%a8%d7%90%d7%95%d7%99%d7%9f/</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -11600,7 +11620,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>natalie.by@mail.huji.ac.il</t>
+          <t>ariella@hanakatova.com</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -11613,7 +11633,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -11623,7 +11643,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אביאלה נטלי – Aviella Natalie טלפון: 050-6523233 אימייל: natalie.by@mail.huji.ac.il הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שרון ערים/ישובים: תל אביב, הרצליה, כפר סבא, רעננה, רמת גן, גבעתיים, בני ברק, פתח תקוה, קריית אונו, ראשון לציון. שפות: אנגלית, עברית</t>
+          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אריאלה דובראוין – Ariella Dubrowin טלפון: 054-6458027 אימייל: ariella@hanakatova.com הסמכה: מדריכת הנקה אזורי קבלה: ירושלים והסביבה, מרכז, שפלה ערים/ישובים: ירושלים, בית שמש, ביתר עילית, אפרת, אלון שבות, כפר עציון, ראש צורים, אלעזר, בת עין, מגדל עוז, תקוע, נוקדים, מעלה עמוס, פני קד</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -11667,11 +11687,11 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11682,7 +11702,7 @@
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%93%D7%95%D7%91%D7%A8%D7%90%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr"/>
@@ -11719,7 +11739,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dalit Elan</t>
+          <t>Aviella Natalie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11739,7 +11759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%93%d7%9c%d7%99%d7%aa-%d7%90%d7%99%d7%9c%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%90%d7%91%d7%99%d7%90%d7%9c%d7%94/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -11750,7 +11770,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>delan@017.net.il</t>
+          <t>natalie.by@mail.huji.ac.il</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -11763,7 +11783,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -11773,7 +11793,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דלית אילן – Dalit Elan טלפון: 050-9200925 אימייל: delan@017.net.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: שרון ערים/ישובים: מזרחית לכביש 4 עד יהוד בדרום וכביש 57 בצפון. מגיעה לאריאל שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: דלית, אמא לשלוש בנות, יועצת הנקה בעלת </t>
+          <t>על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי אביאלה נטלי – Aviella Natalie טלפון: 050-6523233 אימייל: natalie.by@mail.huji.ac.il הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: גוש דן, מרכז, שרון ערים/ישובים: תל אביב, הרצליה, כפר סבא, רעננה, רמת גן, גבעתיים, בני ברק, פתח תקוה, קריית אונו, ראשון לציון. שפות: אנגלית, עברית</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -11817,11 +11837,11 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/", "https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/#contact"]</t>
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11832,7 +11852,7 @@
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%90%D7%91%D7%99%D7%90%D7%9C%D7%94/</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr"/>
@@ -11869,7 +11889,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Devorah Shaked</t>
+          <t>Dalit Elan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11889,7 +11909,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%93%d7%91%d7%95%d7%a8%d7%94-%d7%a9%d7%a7%d7%93/</t>
+          <t>https://ialp.org.il/counselors/%d7%93%d7%9c%d7%99%d7%aa-%d7%90%d7%99%d7%9c%d7%9f/</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -11900,7 +11920,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>devorah@almondweb.com</t>
+          <t>delan@017.net.il</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -11913,7 +11933,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -11923,7 +11943,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דבורה שקד – Devorah Shaked טלפון: 054-4773421 אימייל: devorah@almondweb.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: ירושלים והסביבה ערים/ישובים: ירושלים והסביבה, גבעת זאב, כוכב יעקב, גוש עציון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: מעל 30 שנות ניסיון כתומכת </t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דלית אילן – Dalit Elan טלפון: 050-9200925 אימייל: delan@017.net.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: שרון ערים/ישובים: מזרחית לכביש 4 עד יהוד בדרום וכביש 57 בצפון. מגיעה לאריאל שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: דלית, אמא לשלוש בנות, יועצת הנקה בעלת </t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -11967,11 +11987,11 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/", "https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/", "https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -11982,7 +12002,7 @@
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%AA-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr"/>
@@ -12019,7 +12039,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hagit Naim</t>
+          <t>Devorah Shaked</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12039,7 +12059,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%97%d7%92%d7%99%d7%aa-%d7%a0%d7%a2%d7%99%d7%9d/</t>
+          <t>https://ialp.org.il/counselors/%d7%93%d7%91%d7%95%d7%a8%d7%94-%d7%a9%d7%a7%d7%93/</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -12050,7 +12070,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>hagit04@inter.net.il</t>
+          <t>devorah@almondweb.com</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -12063,7 +12083,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -12073,7 +12093,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי חגית נעים – Hagit Naim טלפון: 052-4662443 אימייל: hagit04@inter.net.il הסמכה: מדריכת הנקה אזורי קבלה: מרכז, שפלה ערים/ישובים: ראשון לציון , נס ציונה, רחובות, באר יעקב, בת ים, חולון, גבעתיים, רמת גן , תל אביב, יפו קרית אונו, יהוד שפות: עברית הסדרים עם קופ"ח: קצת עלי: סבל</t>
+          <t xml:space="preserve">ות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי דבורה שקד – Devorah Shaked טלפון: 054-4773421 אימייל: devorah@almondweb.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: ירושלים והסביבה ערים/ישובים: ירושלים והסביבה, גבעת זאב, כוכב יעקב, גוש עציון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: מעל 30 שנות ניסיון כתומכת </t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -12117,11 +12137,11 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/", "https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/", "https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/#contact"]</t>
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12132,7 +12152,7 @@
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%91%D7%95%D7%A8%D7%94-%D7%A9%D7%A7%D7%93/</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr"/>
@@ -12169,7 +12189,7 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Maddy Smadar Haran</t>
+          <t>Hagit Naim</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12189,7 +12209,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a1%d7%9e%d7%93%d7%a8-%d7%9e%d7%90%d7%93%d7%99-%d7%94%d7%a8%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%97%d7%92%d7%99%d7%aa-%d7%a0%d7%a2%d7%99%d7%9d/</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -12200,7 +12220,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>maddy@dmclub.co.il</t>
+          <t>hagit04@inter.net.il</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -12213,7 +12233,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -12223,7 +12243,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מאדי סמדר הרן – Maddy Smadar Haran טלפון: 054-3030901 אימייל: Maddy@dmclub.co.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: תל אביב, רמת גן, קרית אונו, גבעת שמואל, הרצליה, רעננה, הוד השרון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: גישה עניינית וידי</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי חגית נעים – Hagit Naim טלפון: 052-4662443 אימייל: hagit04@inter.net.il הסמכה: מדריכת הנקה אזורי קבלה: מרכז, שפלה ערים/ישובים: ראשון לציון , נס ציונה, רחובות, באר יעקב, בת ים, חולון, גבעתיים, רמת גן , תל אביב, יפו קרית אונו, יהוד שפות: עברית הסדרים עם קופ"ח: קצת עלי: סבל</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -12267,11 +12287,11 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/", "https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/", "https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/#contact"]</t>
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12282,7 +12302,7 @@
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%92%D7%99%D7%AA-%D7%A0%D7%A2%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr"/>
@@ -12319,7 +12339,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Merav Matus</t>
+          <t>Maddy Smadar Haran</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12339,7 +12359,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%9e%d7%a8%d7%91-%d7%9e%d7%98%d7%95%d7%a1/</t>
+          <t>https://ialp.org.il/counselors/%d7%a1%d7%9e%d7%93%d7%a8-%d7%9e%d7%90%d7%93%d7%99-%d7%94%d7%a8%d7%9f/</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -12350,7 +12370,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>meravmatus@walla.com</t>
+          <t>maddy@dmclub.co.il</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -12363,7 +12383,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -12373,7 +12393,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מרב מטוס – Merav Matus טלפון: 050-6619578 אימייל: meravmatus@walla.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: גוש דן, מרכז ערים/ישובים: אלעד, ראש העין, שהם, פתח תקוה, אלקנה, שערי תקוה, אורנית ועץ אפריים שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית מושלם, לאומית, מאוחד</t>
+          <t>יגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מאדי סמדר הרן – Maddy Smadar Haran טלפון: 054-3030901 אימייל: Maddy@dmclub.co.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: תל אביב, רמת גן, קרית אונו, גבעת שמואל, הרצליה, רעננה, הוד השרון שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית קצת עלי: גישה עניינית וידי</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -12417,11 +12437,11 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/", "https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/", "https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12432,7 +12452,7 @@
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%9E%D7%93%D7%A8-%D7%9E%D7%90%D7%93%D7%99-%D7%94%D7%A8%D7%9F/</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr"/>
@@ -12469,7 +12489,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Natalie Levin</t>
+          <t>Merav Matus</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12489,7 +12509,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%9c%d7%95%d7%99%d7%9f/</t>
+          <t>https://ialp.org.il/counselors/%d7%9e%d7%a8%d7%91-%d7%9e%d7%98%d7%95%d7%a1/</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -12500,7 +12520,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>natalie@bshvil.com</t>
+          <t>meravmatus@walla.com</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -12513,7 +12533,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -12523,7 +12543,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>דות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי נטלי לוין – Natalie Levin טלפון: 052-5787072 אימייל: natalie@bshvil.com הסמכה: מדריכת הנקה אזורי קבלה: דרום ערים/ישובים: אשדוד, אשקלון, קרית גת, קרית מלאכי, שדרות ויישובי הסביבה שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: שמי נטלי, מדריכת הנקה מוסמכת, אמא לשניים. כאמא חו</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי מרב מטוס – Merav Matus טלפון: 050-6619578 אימייל: meravmatus@walla.com הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: גוש דן, מרכז ערים/ישובים: אלעד, ראש העין, שהם, פתח תקוה, אלקנה, שערי תקוה, אורנית ועץ אפריים שפות: אנגלית, עברית הסדרים עם קופ"ח: כללית מושלם, לאומית, מאוחד</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -12567,11 +12587,11 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/", "https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/#contact"]</t>
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12582,7 +12602,7 @@
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%91-%D7%9E%D7%98%D7%95%D7%A1/</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr"/>
@@ -12619,7 +12639,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sarit Perez</t>
+          <t>Natalie Levin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12639,7 +12659,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a9%d7%a8%d7%99%d7%aa-%d7%a4%d7%a8%d7%a5/</t>
+          <t>https://ialp.org.il/counselors/%d7%a0%d7%98%d7%9c%d7%99-%d7%9c%d7%95%d7%99%d7%9f/</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -12650,7 +12670,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>saritush85@walla.com</t>
+          <t>natalie@bshvil.com</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -12663,7 +12683,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -12673,7 +12693,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי שרית פרץ – Sarit Perez טלפון: 052-5673614 אימייל: saritush85@walla.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: דרום ערים/ישובים: שדרות נתיבות יישובים קיבוצים מושבים בסביבה שפות: עברית הסדרים עם קופ"ח: קצת עלי: אמא לארבע מתוקות , אחות מוסמכת ויועצת הנקה מבחינתי ה</t>
+          <t>דות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי נטלי לוין – Natalie Levin טלפון: 052-5787072 אימייל: natalie@bshvil.com הסמכה: מדריכת הנקה אזורי קבלה: דרום ערים/ישובים: אשדוד, אשקלון, קרית גת, קרית מלאכי, שדרות ויישובי הסביבה שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: שמי נטלי, מדריכת הנקה מוסמכת, אמא לשניים. כאמא חו</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -12717,11 +12737,11 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/", "https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/", "https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/#contact"]</t>
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12732,7 +12752,7 @@
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr"/>
@@ -12769,7 +12789,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Shirley Amit Shalam</t>
+          <t>Sarit Perez</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12789,7 +12809,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%a9%d7%99%d7%a8%d7%9c%d7%99-%d7%a2%d7%9e%d7%99%d7%aa-%d7%a9%d7%9c%d7%9d/</t>
+          <t>https://ialp.org.il/counselors/%d7%a9%d7%a8%d7%99%d7%aa-%d7%a4%d7%a8%d7%a5/</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -12800,7 +12820,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>shirley@shalam.co.il</t>
+          <t>saritush85@walla.com</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -12813,7 +12833,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -12823,7 +12843,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>shirley@shalam.co.il</t>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי שרית פרץ – Sarit Perez טלפון: 052-5673614 אימייל: saritush85@walla.com הסמכה: אחות יועצת הנקה מורשית משה"ב אזורי קבלה: דרום ערים/ישובים: שדרות נתיבות יישובים קיבוצים מושבים בסביבה שפות: עברית הסדרים עם קופ"ח: קצת עלי: אמא לארבע מתוקות , אחות מוסמכת ויועצת הנקה מבחינתי ה</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -12833,7 +12853,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -12867,11 +12887,11 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/", "https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/", "https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/#contact"]</t>
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -12882,7 +12902,7 @@
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%99%D7%AA-%D7%A4%D7%A8%D7%A5/</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr"/>
@@ -12919,7 +12939,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Yael Giller</t>
+          <t>Shirley Amit Shalam</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12939,7 +12959,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%d7%99%d7%a2%d7%9c-%d7%92%d7%99%d7%9c%d7%a8/</t>
+          <t>https://ialp.org.il/counselors/%d7%a9%d7%99%d7%a8%d7%9c%d7%99-%d7%a2%d7%9e%d7%99%d7%aa-%d7%a9%d7%9c%d7%9d/</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -12950,7 +12970,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>yael@tly.org.il</t>
+          <t>shirley@shalam.co.il</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -12963,7 +12983,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -12973,7 +12993,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יעל גילר – Yael Giller טלפון: 054-2399534 אימייל: yael@tly.org.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: נתניה, חדרה, כפר סבא, הוד השרון, רעננה, תל אביב והסביבה, אמת השרון, מושבי השרון ועמק חפר. שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: ש</t>
+          <t>shirley@shalam.co.il</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -12983,7 +13003,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -13017,11 +13037,11 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>["https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/", "https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/#contact"]</t>
+          <t>["https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/", "https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/#contact"]</t>
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13032,7 +13052,7 @@
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A2%D7%9E%D7%99%D7%AA-%D7%A9%D7%9C%D7%9D/</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr"/>
@@ -13062,6 +13082,156 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>13</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Yael Giller</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>lactation</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%d7%99%d7%a2%d7%9c-%d7%92%d7%99%d7%9c%d7%a8/</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ialp</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>yael@tly.org.il</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>PERSONAL_PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>98</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אודות על האיגוד קוד אתי וועד מנהל בעלי תפקידים חברות באיגוד מקצועות ההנקה חיפוש יועצת הנקה מאמרים תוכן לאמהות תוכן ליועצות אתגרים בהנקה וועדות האיגוד צרי קשר איזור אישי יעל גילר – Yael Giller טלפון: 054-2399534 אימייל: yael@tly.org.il הסמכה: יועצת הנקה מוסמכת IBCLC אזורי קבלה: מרכז, שרון ערים/ישובים: נתניה, חדרה, כפר סבא, הוד השרון, רעננה, תל אביב והסביבה, אמת השרון, מושבי השרון ועמק חפר. שפות: אנגלית, עברית הסדרים עם קופ"ח: קצת עלי: ש</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>seed_source</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>direct_text</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>["https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/", "https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/#contact"]</t>
+        </is>
+      </c>
+      <c r="AD80" t="n">
+        <v>1.200757082375993e+18</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%99%D7%9C%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>PERSON</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.903742185412251e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.604715483545694e+18</v>
+        <v>4.814146450637083e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.302070959666307e+18</v>
+        <v>3.906212878998921e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.30205551936656e+18</v>
+        <v>3.906166558099681e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.605264526564613e+18</v>
+        <v>4.81579357969384e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.302070959666309e+18</v>
+        <v>3.906212878998928e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.302070959666309e+18</v>
+        <v>3.906212878998928e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.90374218541225e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.804841663941693e+18</v>
+        <v>5.414524991825079e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.604715483545694e+18</v>
+        <v>4.814146450637083e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.201184304939929e+18</v>
+        <v>3.603552914819788e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.301247395137931e+18</v>
+        <v>3.903742185413792e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.301231954838182e+18</v>
+        <v>3.903695864514545e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.502364714102199e+18</v>
+        <v>4.507094142306596e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.601009443167991e+18</v>
+        <v>4.803028329503972e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.301247395137417e+18</v>
+        <v>3.90374218541225e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.804978924696423e+18</v>
+        <v>5.414936774089268e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.234523228039515e+18</v>
+        <v>3.703569684118546e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.204615823807648e+18</v>
+        <v>3.613847471422945e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.204600383508426e+18</v>
+        <v>3.613801150525279e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.204600383508426e+18</v>
+        <v>3.613801150525279e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.204463122753697e+18</v>
+        <v>3.61338936826109e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.201992429168561e+18</v>
+        <v>3.605977287505682e+18</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.202038182753471e+18</v>
+        <v>3.606114548260412e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.300957433328722e+18</v>
+        <v>3.902872299986166e+18</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.300820172573992e+18</v>
+        <v>3.902460517721977e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.512064474103102e+18</v>
+        <v>4.536193422309307e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.201168864640182e+18</v>
+        <v>3.603506593920547e+18</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.201168864640182e+18</v>
+        <v>3.603506593920547e+18</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12141,7 +12141,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12291,7 +12291,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12741,7 +12741,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.903742185412251e+18</v>
+        <v>1.171122655623675e+19</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.814146450637083e+18</v>
+        <v>1.444243935191125e+19</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.506545099287677e+18</v>
+        <v>1.351963529786303e+19</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.906212878998921e+18</v>
+        <v>1.171863863699676e+19</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.906166558099681e+18</v>
+        <v>1.171849967429904e+19</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.81579357969384e+18</v>
+        <v>1.444738073908152e+19</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3.906212878998928e+18</v>
+        <v>1.171863863699678e+19</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3.906212878998928e+18</v>
+        <v>1.171863863699678e+19</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.90374218541225e+18</v>
+        <v>1.171122655623675e+19</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>5.414524991825079e+18</v>
+        <v>1.624357497547524e+19</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.814146450637083e+18</v>
+        <v>1.444243935191125e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>3.603552914819788e+18</v>
+        <v>1.081065874445936e+19</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>3.903742185413792e+18</v>
+        <v>1.171122655624138e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>3.903695864514545e+18</v>
+        <v>1.171108759354363e+19</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>3.903695864514545e+18</v>
+        <v>1.171108759354363e+19</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>3.903695864514545e+18</v>
+        <v>1.171108759354363e+19</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.507094142306596e+18</v>
+        <v>1.352128242691979e+19</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.803028329503972e+18</v>
+        <v>1.440908498851192e+19</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.90374218541225e+18</v>
+        <v>1.171122655623675e+19</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>5.414936774089268e+18</v>
+        <v>1.624481032226781e+19</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>3.703569684118546e+18</v>
+        <v>1.111070905235564e+19</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>3.613847471422945e+18</v>
+        <v>1.084154241426883e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>3.613801150525279e+18</v>
+        <v>1.084140345157584e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>3.613801150525279e+18</v>
+        <v>1.084140345157584e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>3.61338936826109e+18</v>
+        <v>1.084016810478327e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.605977287505682e+18</v>
+        <v>1.081793186251705e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>3.606114548260412e+18</v>
+        <v>1.081834364478124e+19</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>3.902872299986166e+18</v>
+        <v>1.17086168999585e+19</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>3.902872299986166e+18</v>
+        <v>1.17086168999585e+19</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>3.902460517721977e+18</v>
+        <v>1.170738155316593e+19</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>4.536193422309307e+18</v>
+        <v>1.360858026692792e+19</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>3.603506593920547e+18</v>
+        <v>1.081051978176164e+19</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>3.603506593920547e+18</v>
+        <v>1.081051978176164e+19</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12141,7 +12141,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12291,7 +12291,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12741,7 +12741,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.171122655623675e+19</v>
+        <v>3.513367966871026e+19</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.444243935191125e+19</v>
+        <v>4.332731805573375e+19</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.351963529786303e+19</v>
+        <v>4.05589058935891e+19</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.171863863699676e+19</v>
+        <v>3.515591591099029e+19</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.171849967429904e+19</v>
+        <v>3.515549902289713e+19</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.444738073908152e+19</v>
+        <v>4.334214221724456e+19</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.171863863699678e+19</v>
+        <v>3.515591591099035e+19</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.171863863699678e+19</v>
+        <v>3.515591591099035e+19</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.171122655623675e+19</v>
+        <v>3.513367966871025e+19</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.624357497547524e+19</v>
+        <v>4.873072492642571e+19</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.444243935191125e+19</v>
+        <v>4.332731805573375e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.081065874445936e+19</v>
+        <v>3.243197623337809e+19</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.171122655624138e+19</v>
+        <v>3.513367966872413e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.171108759354363e+19</v>
+        <v>3.51332627806309e+19</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.171108759354363e+19</v>
+        <v>3.51332627806309e+19</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.171108759354363e+19</v>
+        <v>3.51332627806309e+19</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.352128242691979e+19</v>
+        <v>4.056384728075937e+19</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.440908498851192e+19</v>
+        <v>4.322725496553574e+19</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.171122655623675e+19</v>
+        <v>3.513367966871025e+19</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.624481032226781e+19</v>
+        <v>4.873443096680342e+19</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.111070905235564e+19</v>
+        <v>3.333212715706692e+19</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.084154241426883e+19</v>
+        <v>3.252462724280651e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.084140345157584e+19</v>
+        <v>3.252421035472751e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.084140345157584e+19</v>
+        <v>3.252421035472751e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.084016810478327e+19</v>
+        <v>3.252050431434981e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.081793186251705e+19</v>
+        <v>3.245379558755114e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.081834364478124e+19</v>
+        <v>3.245503093434371e+19</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.17086168999585e+19</v>
+        <v>3.51258506998755e+19</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.17086168999585e+19</v>
+        <v>3.51258506998755e+19</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.170738155316593e+19</v>
+        <v>3.51221446594978e+19</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.360858026692792e+19</v>
+        <v>4.082574080078376e+19</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.081051978176164e+19</v>
+        <v>3.243155934528492e+19</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.081051978176164e+19</v>
+        <v>3.243155934528492e+19</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -12141,7 +12141,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -12291,7 +12291,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -12741,7 +12741,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>

--- a/output/contacts_personal.xlsx
+++ b/output/contacts_personal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV80"/>
+  <dimension ref="A1:AV86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.513367966871026e+19</v>
+        <v>1.054010390061308e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.332731805573375e+19</v>
+        <v>1.299819541672012e+20</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.05589058935891e+19</v>
+        <v>1.216767176807673e+20</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.515591591099029e+19</v>
+        <v>1.054677477329709e+20</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>3.515549902289713e+19</v>
+        <v>1.054664970686914e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.334214221724456e+19</v>
+        <v>1.300264266517337e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3.515591591099035e+19</v>
+        <v>1.05467747732971e+20</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3.515591591099035e+19</v>
+        <v>1.05467747732971e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.513367966871025e+19</v>
+        <v>1.054010390061307e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.873072492642571e+19</v>
+        <v>1.461921747792771e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.242044122415181e+19</v>
+        <v>9.726132367245543e+19</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.242044122415181e+19</v>
+        <v>9.726132367245543e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.052555153018977e+19</v>
+        <v>1.215766545905693e+20</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4870,15 +4870,17 @@
       <c r="A28" t="n">
         <v>13</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>מדריכת הכנה ללידה</t>
+          <t>לילך מלצקי</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>childbirth_educator</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4893,18 +4895,18 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.einavsitonron.com/birth-guidance</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>einav_r@hotmail.com</t>
+          <t>ms.lilach@gmail.com</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4917,7 +4919,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.einavsitonron.com/contact</t>
+          <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4927,75 +4929,95 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>קס קרניוסקראל אינטגרטיבי ICS כרטיסיית טיפולים מדריכת הכנה ללידה שובר מתנה על הקליניקה המלצות מאמרים יצירת קשר More Use tab to navigate through the menu items. ליצירת קשר ותיאום טיפולים עינב סיטון-רון קיבוץ החותרים מייל: einav_r@hotmail.com טלפון: 053-9512212 פייסבוק: 'עינב סיטון רון - מגע שבא מהלב' מוזמנים גם להשאיר כאן הודעה אני מאשר/ת את קריאת וקבלת מדיניות הפרטיות שליחה ההודעה נשלחה בהצלחה! עיסוי שבדי | עיסוי רפואי | רפלקסולוגיה | עי</t>
+          <t>פשי קמפוס בטוח מדיניות הבטיחות והבריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה ד"ר
+  לילך
+  מלצקי מרצה בכירה קליני Clinical Senior Lecturer דוא"ל ms.lilach@gmail.com דוא"ל בר-אילן lilach.malatskey@biu.ac.il תחום הוראה רפואת המשפחה תחומי מחקר Lifestyle Medicine מרכזי מחקר הפקולטה לרפואה ע"ש עזריאלי, אוניברסיטת בר-אילן, צפת מחלקה משפחה מרפאה שירותי בריאות כללית, מחו</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"לילך מלצקי" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "lilach.malatskey@biu.ac.il", "confidence": 90, "source_url": "https://medicine.biu.ac.il/node/2836", "identity_url": "https://medicine.biu.ac.il/node/2836", "evidence": "ריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר English הדפסה ד\"ר\n \n  לילך\n \n  מלצקי מרצה בכירה קליני Clinical Senior Lecturer דוא\"ל ms.lilach@gmail.com דוא\"ל בר-אילן lilach.malatskey@biu.ac.il תחום הוראה רפואת המשפחה תחומי מחקר Lifestyle Medicine מרכזי מחקר הפקולטה לרפואה ע\"ש עזריאלי, אוניברסיטת בר-אילן, צפת מחלקה משפחה מרפאה שירותי בריאות כללית, מחוז שרון\\שומרון תאריך עדכון אחרון : ", "matched_query": "\"לילך מלצקי\" רפואת משפחה", "extraction_method": "direct_text", "verification_schema_version": 3, "identity_name_verified": true, "identity_specialty_verified": true, "identity_evidence": "מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה \"פרחי רפואה\" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת"}]</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-09-11T18:38:12.718732+00:00</t>
+        </is>
+      </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>ddgs:yahoo+ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>["https://www.einavsitonron.com/birth-guidance", "https://www.einavsitonron.com/about", "https://www.einavsitonron.com/contact"]</t>
+          <t>["https://www.ima.org.il/MainSiteNew/StaticPage.aspx?Page=13564", "https://www.ima.org.il/Main/ViewContent.aspx?CategoryId=19239", "https://doctorindex.co.il/דוקטור-מלצקי-לילך/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9E%D7%9C%D7%A6%D7%A7%D7%99-%D7%9C%D7%99%D7%9C%D7%9A/", "https://family.mednet.co.il/writer/דר-לילך-מלצקי/", "https://www.rofim.org.il/minisite/דר_לילך_מלצקי", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%9C%D7%99%D7%9C%D7%9A_%D7%9E%D7%9C%D7%A6%D7%A7%D7%99", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://medpage.co.il/doctors/לילך-מלצקי-978/", "https://medpage.co.il/doctors/%D7%9C%D7%99%D7%9C%D7%9A-%D7%9E%D7%9C%D7%A6%D7%A7%D7%99-978/", "https://medicine.biu.ac.il/node/2836", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>3.242044122415181e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>https://www.einavsitonron.com/birth-guidance</t>
+          <t>https://medicine.biu.ac.il/node/2836</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי מלצקי לילך | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה "פרחי רפואה" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת</t>
+        </is>
+      </c>
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="n">
@@ -5025,12 +5047,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>נורה גורכד שבסו</t>
+          <t>מאמון הייב</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5056,7 +5078,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>norashapso@gmail.com</t>
+          <t>maamon.haib@gmail.com</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -5069,7 +5091,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -5079,12 +5101,16 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
+          <t xml:space="preserve">דע אישי לסטודנט אגודת הסטודנטים סיוע נפשי קמפוס בטוח מדיניות הבטיחות והבריאות התעסוקתית מניעת הטרדה מינית חדשות חדשות המחקר תקשורת מעבר לגליל כפר הסטודנטים בעמיעד יצירת קשר הדפסה ד"ר
+  הייב
+  מאמון מדריך קליני דוא"ל maamon.haib@gmail.com מחלקה רפואת המשפחה מרפאה שירותי בריאות כללית, מחוז צפון תאריך עדכון אחרון : 20/04/2026 כניסה לעורכי האתר כל הזכויות שמורות:
+הפקולטה לרפואה בגליל ע״ש עזריאלי | אוניברסיטת בר-אילן | יצירת קשר לימודי
+</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>"נורה גורכד שבסו"</t>
+          <t>"מאמון הייב" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -5101,64 +5127,72 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-04T04:55:16.280760+00:00</t>
+          <t>2026-09-11T18:38:09.730192+00:00</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
         <v>1</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
+          <t>["https://www.doctorita.co.il/experts/69492", "https://drtor.co.il/doctor/16532", "https://drtor.co.il/cdn-cgi/l/email-protection#fe9d91908a9f9d8abe9a8c8a918cd09d91d09792", "https://docsrated.com/doctors/מאמון-הייב", "https://medicine.biu.ac.il/node/6715", "https://medicine.biu.ac.il/contact", "https://medicine.biu.ac.il/node/26", "https://medicine.biu.ac.il/pre_clinical", "https://medicine.biu.ac.il/clinical_faculty", "https://medicine.biu.ac.il/node/6861", "https://medicine.biu.ac.il/node/6760"]</t>
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>20415</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
+          <t>https://medicine.biu.ac.il/node/6715</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>מאמון הייב | הפקולטה לרפואה בגליל ע״ש עזריאלי מאמון הייב | הפקולטה לרפואה בגליל ע״ש עזריאלי דילוג לתוכן העיקרי דילוג לתפריט ניווט ראשי תפריט משני ניוזלטר אוגוסט 2026 גלריית תמונות דרושים אירועים צור קשר אוניברסיטת בר-אילן English תפריט הפקולטה לרפואה בגליל ע״ש עזריאלי פייסבוק טוויטר tiktok יוטיוב Linkedin Instagram חיפוש חיפוש חיפוש אודות מי אנחנו חזון הפקולטה מרכזי רפואה מסונפים לפקולטה בקהילה "פרחי רפואה" תוכנית עבודות הגמר של גליליום תוכנית כוכבי הצפון הכירו את הבוגרים/ות שלנו לזכרם וזכרן In Memoriam ארכיון ניוזלטר לזכרם של אהרון ורחל דהאן הסגל הנהלת הפקולטה סגל אקדמי מחקרי סגל אקדמי קליני מינויים וקידומים אקדמיים קליניים סגל מינהלי הנהלת החינוך הרפואי והמחקר בעלי תפקידים מחקר ספריה תחום מומחיות מרכזי מחקר בפקולטה מכוני המחקר בבתי החולים טכנולוגיה ומכשור צוות היחידה ציוד היחידה המרכז הגנומי מאמרים Academic Publications לימודי רפואה M.D. לימודים לתואר דוקטור ברפואה (M.D.) - התכנית השש שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית הארבע שנתית לימודים לתואר דוקטור ברפואה (M.D.) - התכנית התלת שנתית תוכנית MD-PhD רום-גליל (רפואת</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="n">
         <v>1</v>
@@ -5185,7 +5219,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>סדנאות הכנה ללידה</t>
+          <t>מדריכת הכנה ללידה</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5205,7 +5239,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/</t>
+          <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -5216,7 +5250,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>hagitswisa10@gmail.com</t>
+          <t>einav_r@hotmail.com</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -5229,7 +5263,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
+          <t>https://www.einavsitonron.com/contact</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -5239,17 +5273,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>הצהרת נגישות חגית לוינגר-סויסה • הדולה של השמחות 🤰💃, ליווי לידה, הכנה ללידה, טיפול איזון גופני-איקווליבריו, מעגלי נשים, סדנאות והרצאות. טלפון: 050-6696937 דוא"ל: hagitswisa10@gmail.com</t>
+          <t>קס קרניוסקראל אינטגרטיבי ICS כרטיסיית טיפולים מדריכת הכנה ללידה שובר מתנה על הקליניקה המלצות מאמרים יצירת קשר More Use tab to navigate through the menu items. ליצירת קשר ותיאום טיפולים עינב סיטון-רון קיבוץ החותרים מייל: einav_r@hotmail.com טלפון: 053-9512212 פייסבוק: 'עינב סיטון רון - מגע שבא מהלב' מוזמנים גם להשאיר כאן הודעה אני מאשר/ת את קריאת וקבלת מדיניות הפרטיות שליחה ההודעה נשלחה בהצלחה! עיסוי שבדי | עיסוי רפואי | רפלקסולוגיה | עי</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>"סדנאות הכנה ללידה" הכנה ללידה</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -5264,38 +5298,30 @@
         <v>0</v>
       </c>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2026-09-03T16:33:45.692289+00:00</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>["https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/", "https://birth.org.il/%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94-%D7%9E%D7%93%D7%A8%D7%99%D7%9A-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%9C%D7%A1%D7%93%D7%A0%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%91%D7%98%D7%95/", "https://yardengroup.co.il/", "https://birth.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.maccabi4u.co.il/eligibilites/2625/", "https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94", "https://www.webwecan.co.il/"]</t>
+          <t>["https://www.einavsitonron.com/birth-guidance", "https://www.einavsitonron.com/about", "https://www.einavsitonron.com/contact"]</t>
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4.052555153018977e+19</v>
+        <v>9.726132367245543e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -5306,7 +5332,7 @@
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
+          <t>https://www.einavsitonron.com/birth-guidance</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr"/>
@@ -5345,7 +5371,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>עמיחי רוטנשטרייך</t>
+          <t>נורה גורכד שבסו</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5376,7 +5402,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>prof.rottenstreich@gmail.com</t>
+          <t>norashapso@gmail.com</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5389,7 +5415,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -5399,17 +5425,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
+          <t>Med Ted לחברים בלבד ארצ״י בשטח ארצ״י בתקשורת ארצ"י בכנסת פודקאסט "סדציה להמונים" נוהל כניסה להסדר הצטרפות צרו קשר טופס דיווח שיימינג טופס בקשת סיוע קהילה לזכרם חזרה &gt; חזרה &gt; ד"ר נורה שבסו גינקולוגיה ומיילדות 052-5363267 norashapso@gmail.com ד"ר נורה גורכד שפסו היא מומחית בגינקולוגיה ומיילדות, ובעלת על־התמחות בפוריות ובהפריה חוץ־גופית (IVF). נורה למדה רפואה בטכניון והתמחתה במרכז הרפואי צפון. כיום היא עובדת כרופאה בכירה ביחידת ה- IVF  וכר</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>"עמיחי רוטנשטרייך"</t>
+          <t>"נורה גורכד שבסו"</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -5426,7 +5452,7 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-04T06:21:38.973409+00:00</t>
+          <t>2026-09-04T04:55:16.280760+00:00</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -5436,13 +5462,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -5451,11 +5477,11 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
+          <t>["https://www.doctorita.co.il/experts/119054", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-%D7%A0%D7%95%D7%A8%D7%94/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=72FD73030256FB59999957F3E61E03EABE6A8F724FC86F83B2380B60589F61A5&amp;RequestId=00000000-0000-0000-0001-000000000612", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=CE57634ABBFA154920019C7FAAD7385EAB0BB0D5FD8189978016A2325E1941AE&amp;RequestId=00000000-0000-0000-0001-000000000428", "https://www.beok.co.il/doctors/Doctors-1114057/", "https://medpage.co.il/doctors/%D7%A0%D7%95%D7%A8%D7%94-%D7%92%D7%95%D7%A8%D7%9B%D7%93-%D7%A9%D7%91%D7%A1%D7%95-20898/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/", "https://www.amutatartzi.org/%D7%A6%D7%95%D7%95%D7%AA-%D7%95%D7%91%D7%A2%D7%9C%D7%99-%D7%AA%D7%A4%D7%A7%D7%99%D7%93%D7%99%D7%9D/", "https://www.amutatartzi.org/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%90%D7%A8%D7%A6%D7%99/%D7%AA%D7%A7%D7%A0%D7%95%D7%9F-%D7%94%D7%A2%D7%9E%D7%95%D7%AA%D7%94/", "https://www.amutatartzi.org/דרושים-שותפויות-השכרת-מרפאה/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%93%D7%B4%D7%A8-%D7%A2%D7%90%D7%99%D7%93%D7%94-%D7%94%D7%99%D7%99%D7%91-%D7%97%D7%9C%D7%99%D7%99%D7%97%D7%9C/", "https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A4%D7%99%D7%9C%D7%99%D7%A4-%D7%A8%D7%95%D7%96%D7%99%D7%A0%D7%A1%D7%A7%D7%99/", "https://www.amutatartzi.org/team/%D7%93%D7%B4%D7%A8-%D7%A9%D7%9E%D7%A2%D7%95%D7%9F-%D7%90%D7%A8%D7%95%D7%A0%D7%94%D7%99%D7%99%D7%9D/"]</t>
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5466,7 +5492,7 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>https://www.prof-rottenstreich.co.il/</t>
+          <t>https://www.amutatartzi.org/team/%D7%93%D7%A8-%D7%A0%D7%95%D7%A8%D7%94-%D7%A9%D7%91%D7%A1%D7%95/</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr"/>
@@ -5502,17 +5528,15 @@
       <c r="A32" t="n">
         <v>13</v>
       </c>
-      <c r="B32" t="n">
-        <v>6</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ערן ברזילי</t>
+          <t>סדנאות הכנה ללידה</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>childbirth_educator</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5527,18 +5551,18 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>prof.eran.barzilay@gmail.com</t>
+          <t>hagitswisa10@gmail.com</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5551,7 +5575,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5561,17 +5585,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
+          <t>הצהרת נגישות חגית לוינגר-סויסה • הדולה של השמחות 🤰💃, ליווי לידה, הכנה ללידה, טיפול איזון גופני-איקווליבריו, מעגלי נשים, סדנאות והרצאות. טלפון: 050-6696937 דוא"ל: hagitswisa10@gmail.com</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>"ערן ברזילי"</t>
+          <t>"סדנאות הכנה ללידה" הכנה ללידה</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -5588,7 +5612,7 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-04T06:36:53.022308+00:00</t>
+          <t>2026-09-03T16:33:45.692289+00:00</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -5601,10 +5625,10 @@
         <v>4</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -5613,11 +5637,11 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.maccabi4u.co.il/maccabi_circles/health-workshop/birth/", "https://birth.org.il/%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94-%D7%9E%D7%93%D7%A8%D7%99%D7%9A-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%9C%D7%A1%D7%93%D7%A0%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%91%D7%98%D7%95/", "https://yardengroup.co.il/", "https://birth.org.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.maccabi4u.co.il/eligibilites/2625/", "https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94", "https://www.webwecan.co.il/"]</t>
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>1.215766545905693e+20</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5628,7 +5652,7 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+          <t>https://www.big-mama.co.il/%D7%94%D7%A8%D7%A6%D7%90%D7%95%D7%AA-%D7%A1%D7%93%D7%A0%D7%90%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr"/>
@@ -5638,9 +5662,7 @@
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="b">
-        <v>0</v>
-      </c>
+      <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="n">
         <v>1</v>
@@ -5669,7 +5691,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>פרופ' משען נדב</t>
+          <t>עמיחי רוטנשטרייך</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5689,18 +5711,18 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>drnadavmic@gmail.com</t>
+          <t>prof.rottenstreich@gmail.com</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5713,7 +5735,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5723,17 +5745,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
+          <t>פואה פרופסור חבר מטעם האוניברסיטה העברית האגף למיילדות וגינקולוגיה, בית החולים וולפסון, חולון רופא בכיר ומנהל שירות ביחידה להיריון בסיכון Chat Phone פרופ׳ עמיחי רוטנשטרייך מומחה למיילדות גי נ קולוגיה והיריון בסיכון גבוה prof.rottenstreich@gmail.com 055-9787751            , 055-4353787 כל הזכויות שמורות עמיחי רוטנשטרייך 2024 © bottom of page</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>"משען נדב"</t>
+          <t>"עמיחי רוטנשטרייך"</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -5750,23 +5772,23 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-04T04:19:53.405262+00:00</t>
+          <t>2026-09-04T06:21:38.973409+00:00</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -5775,11 +5797,11 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
+          <t>["https://www.prof-rottenstreich.co.il/", "https://www.prof-rottenstreich.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.prof-rottenstreich.co.il/%D7%AA%D7%97%D7%95%D7%9E%D7%99-%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA"]</t>
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.332731805573375e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5790,7 +5812,7 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>https://www.dr-mishan.co.il/</t>
+          <t>https://www.prof-rottenstreich.co.il/</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr"/>
@@ -5831,12 +5853,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>רחל דהן</t>
+          <t>ערן ברזילי</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5862,7 +5884,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>racheldahan@hotmail.com</t>
+          <t>prof.eran.barzilay@gmail.com</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5875,7 +5897,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5885,12 +5907,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
+          <t>ת ה- MD-PhD היוקרתית של הפקולטה לרפואה באוניברסיטת תל אביב, בהצטיינות. עמודים דף הבית אודות אולטרסאונד בהריון ממצאים לא תקינים אולטרסאונד גניקולוגי צור קשר צור קשר ברודצקי 43, כניסה ב', רמת אביב, תל אביב יפו 073-7815218 prof.eran.barzilay@gmail.com פרופ' ערן ברזילי באינפומד © כל הזכויות שמורות לאינפומד בע"מ פרטיות המבקרים באתר חשובה לנו כדי לשפר את חוויית הגלישה, אתר זה משתמש בקבצי עוגיות  (Cookies), המשך גלישה באתר מהווה הסכמתך לכך. מד</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"רחל דהן" רפואת משפחה</t>
+          <t>"ערן ברזילי"</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5907,16 +5929,16 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-10T13:53:25.006579+00:00</t>
+          <t>2026-09-04T06:36:53.022308+00:00</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -5925,7 +5947,7 @@
         <v>4</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
         <v>1</v>
@@ -5937,42 +5959,34 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
+          <t>["https://www.instagram.com/proferanbarzilay/", "https://www.bgu.ac.il/people/barzilae/", "https://www.bgu.ac.il/en/people/barzilae/", "https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://dr-barzilay.com/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>3.243197623337809e+19</v>
+        <v>9.756151294304942e+19</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
+          <t>https://dr-barzilay.com/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="n">
         <v>1</v>
@@ -5996,15 +6010,17 @@
       <c r="A35" t="n">
         <v>13</v>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>שיין ברגנר</t>
+          <t>פרופ' משען נדב</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>midwife</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6019,18 +6035,18 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/שיין-ברגנר/</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>shaynemidwife@gmail.com</t>
+          <t>drnadavmic@gmail.com</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6043,7 +6059,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6053,12 +6069,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>דת בית לבחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה שיין ברגנר 0523627000 WhatsApp shaynemidwife@gmail.com אשל 15, עומר שיין , אם לחמישה ילדים שנולדו בלידה טבעית ובבית , מיילדת נשים בביתן מזה יותר משלושים שנה. לפי תפיסת עולמה של שיין לאישה וליילוד זכות על גופם והיא מאמינה בכבוד ובקדושת חוויית הלידה . ב</t>
+          <t>פרופ' נדב משען ✅️ קבעי כעת ביקור בקליניקה הפרטית ✔️ דלג לתוכן 052-4322732 03-5716996 drnadavmic@gmail.com רחוב רמב"ם 26, גבעתיים בית – פרופ' נדב משען אודות שירותי המרפאה סרטן הרחם סרטן צוואר הרחם סרטן שחלות סרטן הערייה (vulva) בדיקת פאפ בדיקת קולפוסקופיה נשאיות של BRCA קוניזציה גניקולוגיה כללית מחקר רפוא</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"משען נדב"</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6078,30 +6094,38 @@
         <v>0</v>
       </c>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:19:53.405262+00:00</t>
+        </is>
+      </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>["https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=26deea29-fa58-44cd-a7ba-96d9df718414", "https://doctors.assuta.co.il/doctor/nadav-michaan-80431?readmore=true", "https://www.dr-mishan.co.il/", "https://md-digital.co.il/", "https://www.dr-mishan.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.infomed.co.il/experts/144408/", "https://medpage.co.il/doctors/%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-20445/", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F/", "https://www.danielly.co.il/doctors/view/%D7%93%D7%A8-%D7%A0%D7%93%D7%91-%D7%9E%D7%A9%D7%A2%D7%9F-%D7%92%D7%99%D7%A0%D7%A7%D7%95%D7%9C%D7%95%D7%92", "https://www.danielly.co.il/contact/index", "https://www.danielly.co.il/contact", "https://www.danielly.co.il/about", "https://www.danielly.co.il/contact?apt=1&amp;doctor_id=668"]</t>
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>3.242044122415181e+19</v>
+        <v>1.299819541672012e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -6112,7 +6136,7 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
+          <t>https://www.dr-mishan.co.il/</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr"/>
@@ -6122,7 +6146,9 @@
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
+      <c r="AP35" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="n">
         <v>1</v>
@@ -6151,12 +6177,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>אוהד חורי</t>
+          <t>רחל דהן</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6182,7 +6208,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ohadho@clalit.org.il</t>
+          <t>racheldahan@hotmail.com</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -6191,11 +6217,11 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -6205,17 +6231,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>שית בהיפנוזה יועצת גמילה מעישון טיפול בהפרעות שינה, ושינוי הרגלי חיים. רכזת מחקר המחלקה לרפואת משפחה -חיפה מנהלת מרפאת לב הקריה, שירותי בריאות כללית, קרית אתא. טל: 0543130956 אתר אינטרנט http://hypnosis.99k.org ;      : racheldahan@hotmail.com "דוא"ל הפרטים המובאים בכרטיס האישי של רחל דהן, ובכללם פרטים בדבר התואר האקדמי וההכשרה המקצועית נוסחו על ידי רחל דהן ובאחריותו/ה. נצפים ביותר יומנו של עורך וידאו - עדויות מהשבעה באוקטובר / רוני אלפ</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
+          <t>"רחל דהן" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -6227,12 +6253,12 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-09T23:21:42.073181+00:00</t>
+          <t>2026-09-10T13:53:25.006579+00:00</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -6242,37 +6268,37 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
+          <t>["https://www.doctorita.co.il/experts/141424", "https://www.colbonews.co.il/health/166678/", "https://www.hebpsy.net/showprofile.asp?id=18767", "https://www.hebpsy.net/me.asp?id=72&amp;page=6", "https://www.hebpsy.net/pl.asp?cat=about", "https://www.hebpsy.net/me.asp?id=72", "https://www.hebpsy.net/sysMsg.asp?id=profile_about#p10", "https://www.hebpsy.net/sysMsg.asp?id=profile_about", "https://www.hebpsy.net/showprofile.asp?id=18767#profile", "https://www.hebpsy.net/me.asp?id=72&amp;page=6#contact", "https://www.hebpsy.net/sysMsg.asp?id=profile_promotPL", "https://www.hebpsy.net/me.asp?id=72#contact", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fraceldahan%2F", "https://www.facebook.com/public/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/", "https://www.myheritage.com/names/%D7%A8%D7%97%D7%9C_%D7%93%D7%94%D7%9F", "https://gen.rlzm.co.il/persons/%D7%A8%D7%97%D7%9C-%D7%93%D7%94%D7%9F/"]</t>
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>3.513367966872413e+19</v>
+        <v>9.729592870013428e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
+          <t>https://www.hebpsy.net/showprofile.asp?id=18767</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr"/>
@@ -6289,7 +6315,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+          <t>רחל דהן - רופאה רחל דהן - רופאה דלג לתוכן ראשי - מקש קיצור 2 (לחץ Enter) דף הבית - מקש קיצור 1 (לחץ Enter) דלג לתפריט ראשי - מקש קיצור 5 (לחץ Enter) דלג לתיבת חיפוש - מקש קיצור 4 (לחץ Enter) צור קשר - מקש קיצור 9 (לחץ Enter) הצהרת נגישות - מקש קיצור 0 (לחץ Enter) סגור עזרה ראשונה נפשית - בהתנדבות אודות והצטרפות טיפול נפשי מוזל טיפול נפשי בתל אביב מטפלים בהסדר קופת חולים פנויים לקבלת מטופלים חדשים טיפול זוגי טיפול התנהגותי קוגניטיבי - CBT הדרכת הורים טיפול נפשי לילדים אבחון פסיכולוגי לילדים פסיכולוגית בתל אביב פסיכולוגים כניסה רישום צרו קשר חיפוש × × אימייל (דוא"ל) סיסמא שכחת את הסיסמה? הקלידו אימייל ולחצו כאן כניסה אני מסכימ.ה להצטרף לרשימת התפוצה לקבלת עדכונים ומידע שיווקי זכור אותי רישום משתמש חדש ביטול פסיכולוגיה עברית ראשי השער שלי תיבת מסרים כרטיס הביקור שלי הגדרות חשבון אודות פסיכולוגיה עברית שאלות נפוצות יציאה מאמרים המאמרים שלי הגשת טקסט לפרסום נבחרי העורכת אספרגר טיפולי המרה סקס טוב דיו רגשות חינוך מיני תסמונת טורט ניכור הורי רשימות קריאה הכותבים קטגוריות מאמרים מאמרים לפי נושאים ניוזלטר בלוג</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr"/>
@@ -6316,17 +6342,15 @@
       <c r="A37" t="n">
         <v>13</v>
       </c>
-      <c r="B37" t="n">
-        <v>6</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>אופיר אלמסי</t>
+          <t>שיין ברגנר</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>midwife</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6341,18 +6365,18 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.imahi.co.il/שיין-ברגנר/</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ofiral@bgu.ac.il</t>
+          <t>shaynemidwife@gmail.com</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -6361,11 +6385,11 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -6375,12 +6399,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
+          <t>דת בית לבחור מיילדת לידת מים מידע ליולדת הריון הלידה משכב לידה הכשרת מיילדות מקורות וידע חוזרים נהלים ופרוטוקולים אתרים וספרים מומלצים אהבה בראי המדע אינה מי גסקין שאלות נפוצות סיפורי לידה שיין ברגנר 0523627000 WhatsApp shaynemidwife@gmail.com אשל 15, עומר שיין , אם לחמישה ילדים שנולדו בלידה טבעית ובבית , מיילדת נשים בביתן מזה יותר משלושים שנה. לפי תפיסת עולמה של שיין לאישה וליילוד זכות על גופם והיא מאמינה בכבוד ובקדושת חוויית הלידה . ב</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>"אופיר אלמסי"</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6400,38 +6424,30 @@
         <v>0</v>
       </c>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2026-09-04T13:52:28.665114+00:00</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>ddgs:auto</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/"]</t>
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>3.51332627806309e+19</v>
+        <v>9.726132367245543e+19</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -6442,7 +6458,7 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
+          <t>https://www.imahi.co.il/%D7%A9%D7%99%D7%99%D7%9F-%D7%91%D7%A8%D7%92%D7%A0%D7%A8/</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
@@ -6452,9 +6468,7 @@
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="b">
-        <v>0</v>
-      </c>
+      <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="n">
         <v>1</v>
@@ -6483,12 +6497,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>אורנה רייכמן</t>
+          <t>שירי רון ברצ'ילון</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6514,7 +6528,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>oreich@szmc.org.il</t>
+          <t>dr.shiribarchilon@gmail.com</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6523,11 +6537,11 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://dr-shiribarchilon.co.il/</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -6537,12 +6551,13 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
+          <t>לינט, חוג באלינט ישראל. ביקורי הבית מאפשרים הערכה גריאטרית מקיפה בסביבתו הטבעית של המטופל,
+                        ובתנאים הנוחים לו. המפגשים נעשים ברגישות, אמפתיה ומקצועיות. אין כמו בבית. איזור השרון והמרכז 050-8334003 dr.shiribarchilon@gmail.com ד"ר שירי רון ברצ'ילון מומחית ברפואה גריאטרית אם חיפשתם את ד״ר ברצ׳ילון, אורתופד מנתח - לחצו כאן עיצוב-יאיר דיגיטל</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>"אורנה רייכמן"</t>
+          <t>"שירי רון ברצ ילון" רפואת משפחה</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6559,64 +6574,73 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-09-04T13:56:16.031154+00:00</t>
+          <t>2026-09-11T18:42:01.466130+00:00</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z38" t="n">
         <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
+          <t>["https://doctorindex.co.il/דוקטור-רון-ברצילון-שירי/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%95%D7%9F-%D7%91%D7%A8%D7%A6%D7%99%D7%9C%D7%95%D7%9F-%D7%A9%D7%99%D7%A8%D7%99/", "https://dr-shiribarchilon.co.il/", "https://dr-shiribarchilon.co.il/#odot", "https://medpage.co.il/doctors/%D7%A9%D7%99%D7%A8%D7%99-%D7%A8%D7%95%D7%9F-%D7%91%D7%A8%D7%A6%D7%99%D7%9C%D7%95%D7%9F-17881/", "https://www.medreviews.co.il/provider/dr-ron-barchilon-shiri/page/2", "https://www.medreviews.co.il/provider/dr-ron-barchilon-shiri/treatment"]</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>3.51332627806309e+19</v>
+        <v>9.729592870009283e+19</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
+          <t>https://dr-shiribarchilon.co.il/</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>ד”ר שירי רון ברצ'ילון ד”ר שירי רון ברצ'ילון ד"ר שירי רון ברצ'ילון רופאה מומחית בגריאטריה אודות אין כמו בבית הערכה גריאטרית בבית המטופל יצירת קשר יצירת קשר הערכה תפקודית הערכה קוגניטיבית איזון נפשי סידור תרופות ירידה בזכרון ודמנציה כשירות לייפוי כח וצוואה ד"ר שירי רון ברצ'ילון מומחית ברפואה גריאטרית מנהלת יחידת הייעוץ הגריאטרי בבית החולים לניאדו. מומחית ברפואת המשפחה ורפואה גריאטרית. תואר MD מבית הספר לרפואה של אוניברסיטת תל-אביב משנת 2000. מנחת קבוצות, בוגרת התכנית להכשרת מנחי קבוצות, אוניברסיטת בר אילן. מרצה בבית הספר לרפואה, אוניברסיטת תל-אביב. מדריכת באלינט, חוג באלינט ישראל. ביקורי הבית מאפשרים הערכה גריאטרית מקיפה בסביבתו הטבעית של המטופל,
+                        ובתנאים הנוחים לו. המפגשים נעשים ברגישות, אמפתיה ומקצועיות. אין כמו בבית. איזור השרון והמרכז 050-8334003 dr.shiribarchilon@gmail.com ד"ר שירי רון ברצ'ילון מומחית ברפואה גריאטרית אם חיפשתם את ד״ר ברצ׳ילון, אורתופד מנתח - לחצו כאן עיצוב-יאיר דיגיטל</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr"/>
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="n">
         <v>1</v>
@@ -6645,7 +6669,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ארנון סמואלוב</t>
+          <t>אוהד חורי</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6676,7 +6700,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>smuelof@szmc.org.il</t>
+          <t>ohadho@clalit.org.il</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6689,7 +6713,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6699,17 +6723,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>"ארנון סמואלוב"</t>
+          <t>"אוהד חורי" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -6726,36 +6750,36 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-09-04T14:35:26.198949+00:00</t>
+          <t>2026-09-09T23:21:42.073181+00:00</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA39" t="n">
         <v>2</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx", "https://www.doctorita.co.il/experts/94233", "https://www.ha-makom.co.il/author/vhdcvry/", "https://foody.co.il/author/ohad/", "https://knowmore.co.il/doctors/אוהד-חורי-2/", "https://stage.ha-makom.co.il/author/vhdcvry/", "https://www.facebook.com/YoldotBeilinson/videos/%D7%9E%D7%94-%D7%96%D7%95-%D7%9C%D7%99%D7%93%D7%AA-vbac-%D7%A9%D7%9B%D7%95%D7%9C%D7%9F-%D7%9E%D7%93%D7%91%D7%A8%D7%95%D7%AA-%D7%A2%D7%9C%D7%99%D7%94-%D7%A2%D7%95%D7%A9%D7%99%D7%9D-%D7%9C%D7%9B%D7%9F-%D7%A1%D7%93%D7%A8-%D7%91%D7%9E%D7%95%D7%A9%D7%92%D7%99%D7%9D-%D7%A2%D7%9D-%D7%93%D7%A8-%D7%90%D7%95%D7%94%D7%93-%D7%97%D7%95%D7%A8%D7%99-%D7%A9%D7%9B%D7%90%D7%9F-%D7%9B%D7%93%D7%99/1754039901764363/"]</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>3.51332627806309e+19</v>
+        <v>1.054010390061724e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6766,19 +6790,27 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/nashimbeilinson/Pages/dr_o_churi.aspx</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>ד"ר אוהד חורי | מרכז רפואי רבין - Clalit ד"ר אוהד חורי | מרכז רפואי רבין - Clalit הרופאים שלנו נשים - מידע נוסף מתחם הריון ולידה ד"ר אוהד חורי מומחה למיילדות וגינקולוגיה, מומחה להריון בסיכון שם: ד"ר אוהד חורי דוא"ל: Ohadho@clalit.org.il יחידה: בי"ח לנשים ויולדות , היחידה לרפואת אם ועובר</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr"/>
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="n">
         <v>1</v>
@@ -6807,7 +6839,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>גלי פריאנטה</t>
+          <t>אופיר אלמסי</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6838,7 +6870,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>galipa@bgu.ac.il</t>
+          <t>ofiral@bgu.ac.il</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6851,7 +6883,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6861,12 +6893,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
+          <t>بحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان אופיר אלמסי ד"ר אופיר אלמסי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ofiral@bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>"גלי פריאנטה"</t>
+          <t>"אופיר אלמסי"</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6888,36 +6920,36 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-09-03T23:09:10.396904+00:00</t>
+          <t>2026-09-04T13:52:28.665114+00:00</t>
         </is>
       </c>
       <c r="W40" t="n">
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/ofiral/", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/almasi-o.aspx", "https://www.bgu.ac.il/ar/people/ofiral/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053997883418927e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6928,7 +6960,7 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
+          <t>https://www.bgu.ac.il/ar/people/ofiral/</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr"/>
@@ -6969,7 +7001,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ד"ר ברוך יואב</t>
+          <t>אורנה רייכמן</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6989,18 +7021,18 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>yoavb@tlvmc.gov.il</t>
+          <t>oreich@szmc.org.il</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -7013,7 +7045,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7023,12 +7055,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
+          <t xml:space="preserve">אזור אישי רופאים בשערי צדק ד"ר אורנה  רייכמן מנהלת יולדות א' Dr. Orna  Reichman התמחות: גינקולוגיה ויילוד תת התמחות: מחלות שפירות של העריה והלדן הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית משרד 02-6666708 משרד: 02-6666708 oreich@szmc.org.il oreich@szmc.org.il לימודים והכשרה תואר ראשון במדעי החיים באוניברסיטה העברית בירושלים בהצטיינות - 1993 לימודי הרפואה בבית ספר לרפואה של האוניברסיטה העברית הדסה - 1999 ההתמחות במיילדות וגניקולוגיה במרכז </t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"ברוך יואב"</t>
+          <t>"אורנה רייכמן"</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7045,28 +7077,28 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-09-05T00:14:33.719515+00:00</t>
+          <t>2026-09-04T13:56:16.031154+00:00</t>
         </is>
       </c>
       <c r="W41" t="n">
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -7075,11 +7107,11 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
+          <t>["https://www.infomed.co.il/experts/149541/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A8%D7%99%D7%99%D7%9B%D7%9E%D7%9F-%D7%90%D7%95%D7%A8%D7%A0%D7%94/", "https://docsrated.com/doctors/אורנה-רייכמן", "https://www.doctorita.co.il/experts/95406", "https://drtor.co.il/doctor/23937", "https://drtor.co.il/cdn-cgi/l/email-protection#8cefe3e2f8edeff8cce8fef8e3fea2efe3a2e5e0", "https://www.beok.co.il/doctors/Doctors-1340/", "https://www.szmc.org.il/doctors/reichman-orna/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://drtor.co.il/cdn-cgi/l/email-protection#3b5854554f5a584f7b5f494f5449155854155257"]</t>
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.056384728075937e+19</v>
+        <v>1.053997883418927e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -7090,7 +7122,7 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
+          <t>https://www.szmc.org.il/doctors/reichman-orna/</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr"/>
@@ -7131,7 +7163,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ד"ר צוקר נפתלי</t>
+          <t>ארנון סמואלוב</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7151,18 +7183,18 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>drnzuker@arad-medical.co.il</t>
+          <t>smuelof@szmc.org.il</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -7175,7 +7207,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -7185,12 +7217,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
+          <t>ופ' ארנון  סמואלוב רופא בכיר Prof. Arnon  Samueloff התמחות: גינקולוגיה ויילוד תת התמחות: מיילדות וסיבוכי הריון תחומים נוספים: סוכרת בהריון עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית מחלקה 02-6666656 מחלקה: 02-6666656 smuelof@szmc.org.il smuelof@szmc.org.il נסיון מקצועי התמחות ברפואת האם והעובר, סן אנטוניו, ארה"ב רופא בכיר, מחלקת נשים ויולדות, המרכז הרפואי הדסה מנהל, מרפאת היריון בסיכון, קופת חולים לאומית מנהל, מרפאת סוכרת, קופת חולים</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>"צוקר נפתלי"</t>
+          <t>"ארנון סמואלוב"</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7212,36 +7244,36 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-09-03T20:26:24.789692+00:00</t>
+          <t>2026-09-04T14:35:26.198949+00:00</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
         <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
+          <t>["https://docsrated.com/doctors/ארנון-סמואלוב", "https://www.infomed.co.il/experts/93587/", "https://www.doctorita.co.il/experts/47319", "https://www.beok.co.il/doctors/Doctors-116451/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A1%D7%9E%D7%95%D7%90%D7%9C%D7%95%D7%91-%D7%90%D7%A8%D7%A0%D7%95%D7%9F/", "https://www.szmc.org.il/doctors/samueloff-arnon/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/"]</t>
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.322725496553574e+19</v>
+        <v>1.053997883418927e+20</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -7252,7 +7284,7 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>https://www.arad-medical.co.il/</t>
+          <t>https://www.szmc.org.il/doctors/samueloff-arnon/</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr"/>
@@ -7293,7 +7325,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ד"ר רטן גלעד</t>
+          <t>גלי פריאנטה</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7313,18 +7345,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ima</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>giladr@tlvmc.gov.il</t>
+          <t>galipa@bgu.ac.il</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -7337,7 +7369,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -7347,12 +7379,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
+          <t>ث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان גלי פריאנטה פרופ' גלי פריאנטה Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section galipa@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0001-6484-3769 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>"רטן גלעד"</t>
+          <t>"גלי פריאנטה"</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7374,7 +7406,7 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-09-03T21:08:14.761438+00:00</t>
+          <t>2026-09-03T23:09:10.396904+00:00</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -7384,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA43" t="n">
         <v>1</v>
@@ -7399,11 +7431,11 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/people/galipa/", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-%D7%92%D7%9C%D7%99/", "https://medpage.co.il/doctors/%D7%92%D7%9C%D7%99-%D7%A4%D7%A8%D7%99%D7%90%D7%A0%D7%98%D7%94-25448/", "https://www.doctorita.co.il/experts/131973", "https://hospitals.clalit.co.il/soroka/he/our-specialists/Pages/pariente-g.aspx", "https://www.bgu.ac.il/ar/people/galipa/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.51221446594978e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -7414,7 +7446,7 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
+          <t>https://www.bgu.ac.il/ar/people/galipa/</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr"/>
@@ -7455,7 +7487,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>דנה ברבינג-גולדשטיין</t>
+          <t>ד"ר ברוך יואב</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7475,18 +7507,18 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>danabr2@clalit.org.il</t>
+          <t>yoavb@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -7499,7 +7531,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -7509,17 +7541,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
+          <t>י לאורוגינקולוגיה ורצפת אגן שטחי התעניינות ועיסוק מיוחדים ניתוחים וגינאליים וזעיר פולשניים לצניחת אברי האגן טיפול תרופתי וכירורגי לדליפת שתן מרפאת ערייה וצוואר הרחם אבחון וטיפול בקונדילומות ונגעים טרום ממאירים יצירת קשר yoavb@tlvmc.gov.il יחידות רפואיות אורוגינקולוגיה ורצפת האגן רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות נעים להכיר, ​ד"ר יואב ברוך איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציונ</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
+          <t>"ברוך יואב"</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>search_snippet</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -7531,41 +7563,41 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-09-08T13:48:01.035843+00:00</t>
+          <t>2026-09-05T00:14:33.719515+00:00</t>
         </is>
       </c>
       <c r="W44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA44" t="n">
         <v>1</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>ddgs:yahoo+ddgs:bing</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=2a3866cf-0c4f-4b77-90d9-4d3983c6e345", "https://soundcloud.com/wx8fnfybplpt", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A-%D7%91%D7%A8%D7%95%D7%9A/pfbid02DHSfATmK3MDpizZrgGTLc9ZAvZHXUsR9pSCjhd6pmWqSMFvq1BwehNeHCARNitMol/", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/pfbid02BMPnQXQYXt6vzctmybagMUp3nWACPxhE1LqhYeJYs1fVgXWA6B1cK2Z9VpRJ8cJRl/", "https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/", "https://pubmed.ncbi.nlm.nih.gov/?term=yoav+baruch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000546", "https://www.facebook.com/people/%D7%99%D7%95%D7%90%D7%91-%D7%91%D7%A8%D7%95%D7%9A/61559143005435/", "https://www.infomed.co.il/experts/151203/", "https://www.yoavbaruch.com/", "https://www.yoavbaruch.com/about-6", "https://theindex.co.il/phone/ברוך-יואב-0777573393/", "https://go.serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKeyIndex=EF07D8F49D3442F3EBC164C356A1A04AA3430A30E2F7F8333940EE0F822D1ABD&amp;RequestId=00000000-0000-0000-0001-000000000504"]</t>
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.513367966871025e+19</v>
+        <v>1.216915418422781e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -7576,7 +7608,7 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yoav-baruch/</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr"/>
@@ -7617,12 +7649,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>היחידה לפוריות והפריה חוץ גופית</t>
+          <t>ד"ר צוקר נפתלי</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>fertility_doctor</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7637,18 +7669,18 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>idoba@szmc.org.il</t>
+          <t>drnzuker@arad-medical.co.il</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7661,7 +7693,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -7671,12 +7703,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
+          <t xml:space="preserve"> בי"ח אסף הרופא, עבר השתלמות מעמיקה בכירורגיה גניקולוגית ואנדסקופית. כמוכן, גניקולוג בכיר בקופות החולים מכבי ולאומית. קרא עוד עלינו « לפרטים נוספים ולקביעת תור השאר פרטים ונחזור אליך בהקדם! ☎ 077-8037837 | 077-9966036 ✉ drnzuker@arad-medical.co.il שם מלא: מייל: טלפון: שלח © ד"ר נפתלי צוקר — כל הזכויות שמורות אתר זה נבנה ועוצב ע"י קידום פלוס - בניית אתרים</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
+          <t>"צוקר נפתלי"</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7693,28 +7725,28 @@
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-09-04T18:29:47.683340+00:00</t>
+          <t>2026-09-03T20:26:24.789692+00:00</t>
         </is>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z45" t="n">
         <v>4</v>
       </c>
       <c r="AA45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -7723,11 +7755,11 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=d07861e5-173e-4fa6-97ee-40c4b372d28a", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=JM/xPUEkhEzRgBuX3T9AYqhAJkFmVBaeb30sdIDAjgJqc6t/hlXwF9+305eagC9MR2dwestiB5JmwYwMLOCteQ==", "https://doctors.assuta.co.il/doctor/naftaly-zuker-15805", "https://serguide.maccabi4u.co.il/heb/doctors/doctorssearchresults/doctorsinfopage/?ItemKey=AsbND281GonWNafC65Z5in+5Uof0vMwxuFwCtAAhKp6HNUz+Imt4aFWEpjB1dVuW0TI9YD98xqlKyretPdEuvw==", "https://www.arad-medical.co.il/", "http://www.kidumplus.co.il/", "https://www.arad-medical.co.il/contact", "https://www.arad-medical.co.il/about-us", "https://www.doctorim.co.il/s/doctor-21560/דר-נפתלי-צוקר/מומחה-יילוד-וגניקולוגיה", "https://www.infomed.co.il/experts/83793/"]</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.873443096680342e+19</v>
+        <v>1.296817648966072e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7738,7 +7770,7 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
+          <t>https://www.arad-medical.co.il/</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr"/>
@@ -7779,7 +7811,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>יעל שולמן</t>
+          <t>ד"ר רטן גלעד</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7799,18 +7831,18 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>ima</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>yaelshu@tlvmc.gov.il</t>
+          <t>giladr@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7823,7 +7855,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7833,12 +7865,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
+          <t xml:space="preserve">ח "ליס" ליולדות ונשים איכילוב צוות איכילוב גלעד רטן בדיקת היסטרוסקופיה - ד"ר גלעד רטן | ליס, איכילוב ד"ר גלעד רטן על תסמונת אשרמן, סטטוסקופ ערוץ 13 פרק 18 | פרופ' יריב יוגב ופרופ' גלעד רטן | בדיקת היסטרוסקופיה יצירת קשר giladr@tlvmc.gov.il יחידות רפואיות היסטרוסקופיה אבחנתית / טיפולית רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א </t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"יעל שולמן"</t>
+          <t>"רטן גלעד"</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7860,7 +7892,7 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-09-04T17:01:07.432235+00:00</t>
+          <t>2026-09-03T21:08:14.761438+00:00</t>
         </is>
       </c>
       <c r="W46" t="n">
@@ -7870,13 +7902,13 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
@@ -7885,11 +7917,11 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=3bfdc0ce-e104-4df0-8a7e-c550db6827c3", "https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F/", "https://dr-gilad.infomed.co.il/", "https://www.facebook.com/TLVMDC/posts/%D7%95%D7%95%D7%90%D7%95-%D7%9E%D7%AA%D7%A8%D7%92%D7%A9%D7%99%D7%9D-%D7%9C%D7%94%D7%9B%D7%99%D7%A8-%D7%9C%D7%9B%D7%9D-%D7%90%D7%AA-%D7%93%D7%A8-%D7%92%D7%9C%D7%A2%D7%93-%D7%A8%D7%98%D7%9F-%D7%9E%D7%95%D7%9E%D7%97%D7%94-%D7%91%D7%9B%D7%99%D7%A8-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%A8%D7%A4%D7%95%D7%90%D7%99-tlv_medical_center/1344912312574270/", "https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>1.053664339784934e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -7900,7 +7932,7 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/ratan-gilad/</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr"/>
@@ -7941,7 +7973,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ישי לוין</t>
+          <t>דנה ברבינג-גולדשטיין</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7972,7 +8004,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ishail@tlvmc.gov.il</t>
+          <t>danabr2@clalit.org.il</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7985,7 +8017,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -7995,17 +8027,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
+          <t>ד"ר דנה ברבינג גולדשטיין | מרכז רפואי רבין ד"ר דנה ברבינג גולדשטיין מיילדות וגינקולוגיה, גנטיקה רפואית שם: ד"ר דנה ברבינג גולדשטיין דוא"ל: danabr2@clalit.org.il יחידה: מכון רפאל רקנאטי לגנטיקה</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>"ישי לוין"</t>
+          <t>"דנה ברבינג גולדשטיין" יילוד site:clalit.co.il</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>search_snippet</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -8022,36 +8054,36 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-09-04T17:20:48.855691+00:00</t>
+          <t>2026-09-08T13:48:01.035843+00:00</t>
         </is>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo+ddgs:bing</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx"]</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>1.054010390061307e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -8062,7 +8094,7 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
+          <t>https://hospitals.clalit.co.il/rabin/he/departments-and-clinics/genetics/Pages/dr_d_barbing.aspx</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr"/>
@@ -8103,12 +8135,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>לירן הירש</t>
+          <t>היחידה לפוריות והפריה חוץ גופית</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>fertility_doctor</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -8123,18 +8155,18 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>liranh@tlvmc.gov.il</t>
+          <t>idoba@szmc.org.il</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -8147,7 +8179,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8157,12 +8189,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
+          <t>מנהל היחידה לפוריות והפריה חוץ גופית Prof. Ido Ben-Ami התמחות: גינקולוגיה ויילוד תת התמחות: הפריה חוץ גופית תחומים נוספים: פוריות הגבר שימור פוריות תרומת ביצית טיפולי פוריות עוד הסדר ביטוחי הזמנת תור לשירותי רפואה פרטית idoba@szmc.org.il idoba@szmc.org.il נסיון מקצועי התמחות ברפואת נשים ויילוד במרכז הרפואי שמיר (אסף הרופא) מנהל המכון לפוריות הגבר ובנק הזרע במרכז הרפואי שמיר (אסף הרופא) תפקידים ציבוריים חבר ועדת ניירות עמדה, האיגוד הישרא</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>"לירן הירש"</t>
+          <t>"היחידה לפוריות והפריה חוץ גופית"</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8179,28 +8211,28 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-09-04T17:39:56.947224+00:00</t>
+          <t>2026-09-04T18:29:47.683340+00:00</t>
         </is>
       </c>
       <c r="W48" t="n">
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -8209,11 +8241,11 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://hospitals.clalit.co.il/meir/he/med/gyne/ivf/Pages/about.aspx", "https://www.nashim.net/?CategoryID=1146", "https://www.nashim.net/?CategoryID=1054", "https://www.nashim.net/?CategoryID=1048", "https://www.nashim.net/?CategoryID=1143", "https://www.nashim.net/?CategoryID=1163&amp;ArticleID=2361", "https://www.nashim.net/?CategoryID=1215", "https://www.nashim.net/?CategoryID=1054#skip4", "https://www.nashim.net/?CategoryID=1146&amp;SearchParam=", "https://www.nashim.net/?CategoryID=1044&amp;ArticleID=2664", "https://hospitals.clalit.co.il/soroka/he/med-units/ob-gyn-division/pages/ivf.aspx", "https://www.barzilaimc.org.il/?CategoryID=887&amp;ArticleID=4107", "https://hospitals.clalit.co.il/kaplan/he/med_units/ivf/Pages/ivf.aspx", "https://www.laniado.org.il/ivf/", "https://www.szmc.org.il/departments/obstetrics-and-gynecology/ivf/", "https://www.szmc.org.il/doctors/ben-ami-ido/", "https://www.szmc.org.il/about/", "https://www.szmc.org.il/about/about-us/", "https://www.szmc.org.il/about/units/", "https://www.szmc.org.il/about/besharaenu/", "https://www.szmc.org.il/about/regular-updates-during-an-emergency/", "https://www.szmc.org.il/about/privacy-policy/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fcarmel2023%2Fposts%2F%25D7%2594%25D7%2599%25D7%2597%25D7%2599%25D7%2593%25D7%2594-%25D7%259C%25D7%25A4%25D7%2595%25D7%25A8%25D7%2599%25D7%2595%25D7%25AA-%25D7%2595%25D7%2594%25D7%25A4%25D7%25A8%25D7%2599%25D7%2594-%25D7%2597%25D7%2595%25D7%25A5-%25D7%2592%25D7%2595%25D7%25A4%25D7%2599%25D7%25AA-%25D7%259B%25D7%25A8%25D7%259E%25D7%259C-%25D7%259C%25D7%2598%25D7%2595%25D7%2591%25D7%25AA-%25D7%25AA%25D7%2595%25D7%25A9%25D7%2591%25D7%2599-%25D7%2594%25D7%25A2%25D7%2595%25D7%2598%25D7%25A3-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2591%25D7%259E%25D7%25A6%25D7%2595%25D7%25A7%25D7%2594%25D7%2590%25D7%259D-%25D7%2590%25D7%25AA-%25D7%25A0%25D7%259E%25D7%25A6%25D7%2590%2F717139347109836%2F", "https://www.sorokafoundation.com/article/%D7%93%D7%A8-%D7%A2%D7%90%D7%98%D7%A3-%D7%96%D7%99%D7%90%D7%93%D7%A0%D7%94-%D7%9E%D7%95%D7%A0%D7%94-%D7%9C%D7%9E%D7%A0%D7%94%D7%9C-%D7%94%D7%99%D7%97%D7%99%D7%93%D7%94-%D7%9C%D7%A4%D7%95%D7%A8%D7%99/"]</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>3.333212715706692e+19</v>
+        <v>1.462032929004103e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -8224,7 +8256,7 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
+          <t>https://www.szmc.org.il/doctors/ben-ami-ido/</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr"/>
@@ -8265,7 +8297,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>נועה גוהר פורטנוי</t>
+          <t>יעל שולמן</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8296,7 +8328,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>noago@post.bgu.ac.il</t>
+          <t>yaelshu@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -8309,7 +8341,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -8319,12 +8351,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
+          <t>3zgt8o8y2e /search-result/ /api/as/v1/engines/ פתח חיפוש עוד ... זימון תורים אזור אישי כניסה לאיזור האישי AI צ'אט ד"ר יעל שולמן רופאה בכירה במחלקת נשים, ביה"ח 'ליס' ליולדות ונשים איכילוב צוות איכילוב יעל שולמן יצירת קשר yaelshu@tlvmc.gov.il יחידות רפואיות אשפוז נשים - מחלקה רופאים בכירים בליס-יולדות ונשים רפואת  נשים - גינקולוגיה יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך ב</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>"נועה גוהר פורטנוי" יילוד</t>
+          <t>"יעל שולמן"</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8346,20 +8378,20 @@
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-09-08T14:13:12.580343+00:00</t>
+          <t>2026-09-04T17:01:07.432235+00:00</t>
         </is>
       </c>
       <c r="W49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8371,11 +8403,11 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.agmon-law.co.il/team-member/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/", "https://www.facebook.com/people/%D7%99%D7%A2%D7%9C-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F/pfbid02D3uDhLBFvfdSCJScu9afsXcVu6ZWEqNA4AsJgJH4om5Y5hNBNGbDUq3Xyg3nad9hl/", "https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>3.252462724280651e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -8386,7 +8418,7 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/noago/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/yael-shulman/</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -8427,7 +8459,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>עדי יהודה ווינטראוב</t>
+          <t>ישי לוין</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8458,7 +8490,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>adiyehud@bgu.ac.il</t>
+          <t>ishail@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -8471,7 +8503,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -8481,12 +8513,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
+          <t>ריוזיס כנס אונליין אנדומטריאוזיס 2025 | פרופ' יריב יוגב ופרופ' ישי לוין מניעה וגילוי מוקדם של מחלות נשים | ערוץ 10 המכון לפריון - כירורגיה של הפריון | ליס פרופ' ישי לוין על כאבי מחזור חזקים , ערוץ 13, סטטוסקופ יצירת קשר ishail@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה אשפוז נשים - מחלקה אנדומטריוזיס - מרכז רב תחומי המרכז לבריאות האשה-מרפאות מומחים הפלות חוזרות - טיפול בכשל הריוני רופאים בכירים בליס-יולדות ונשים יצירת קשר יחיד</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>"עדי יהודה ווינטראוב"</t>
+          <t>"ישי לוין"</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8503,41 +8535,41 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-09-04T19:20:10.182518+00:00</t>
+          <t>2026-09-04T17:20:48.855691+00:00</t>
         </is>
       </c>
       <c r="W50" t="n">
         <v>2</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.ishai-levin.com/", "https://www.ishai-levin.com/about", "https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/", "https://pubmed.ncbi.nlm.nih.gov/?term=Levin%2c%20Ishai%5bFull%20Author%20Name%5d%20OR%20Ishai%2c%20Levin%5bFull%20Author%20Name%5d&amp;cmd=DetailsSearch", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>3.252421035472751e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -8548,7 +8580,7 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/levin-ishai/</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr"/>
@@ -8589,7 +8621,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>עמרי זמשטין</t>
+          <t>לירן הירש</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8620,7 +8652,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>omrizam@post.bgu.ac.il</t>
+          <t>liranh@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -8633,7 +8665,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -8643,12 +8675,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
+          <t>צועיים החברה הישראלית לרפואת האם והעובר החוג הישראלי למיילדות וגינקולוגיה לידה נדירה - תאומים ברחם נפרד פרק 19 | פרופ' יריב יוגב ופרופ' לירן הירש | תאומים פרק 9 | פרופ' יריב יוגב ופרופ' לירן הירש| הריון בסיכון יצירת קשר liranh@tlvmc.gov.il יחידות רפואיות המחלקה לרפואת האם והעובר מניעת לידה מוקדמת - מרפאה מעקב הריונות תאומים רופאים בכירים בליס-יולדות ונשים היריון ולידה יצירת קשר יחידות רפואיות היריון של 1 למיליון עם פרופ' לירן הירש איכיל</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>"עמרי זמשטין"</t>
+          <t>"לירן הירש"</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8665,25 +8697,25 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-09-04T19:35:09.971397+00:00</t>
+          <t>2026-09-04T17:39:56.947224+00:00</t>
         </is>
       </c>
       <c r="W51" t="n">
         <v>2</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -8695,11 +8727,11 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.profhiersch.com/", "https://www.profhiersch.com/%D7%90%D7%95%D7%93%D7%95%D7%AA", "https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/", "https://pubmed.ncbi.nlm.nih.gov/?term=HIERSCH+L&amp;sort=date", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>3.252421035472751e+19</v>
+        <v>9.999638147120076e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -8710,7 +8742,7 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
+          <t>https://www.tasmc.org.il/doctorssearch/dr/liran-hiersch/</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr"/>
@@ -8751,7 +8783,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>רויטל לינדר</t>
+          <t>נועה גוהר פורטנוי</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8782,7 +8814,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>revital@drlinder.co.il</t>
+          <t>noago@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8795,7 +8827,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -8805,12 +8837,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>בכירה ביחידה הגניקואונקולוגית , בית חולים רמב״ם, חיפה. 4/2014-4/2019 התמחות במיילדות וגניקולוגיה בית חולים רמב״ם,חיפה. לפרטים מלאים חוות דעת יש לך שאלה ? צרי קשר ד״ר רויטל לינדר צפצפה 2 (ישי סנטר) , רמת ישי 058-6918927​ revital@drlinder.co.il הצהרת נגישות © DR. Revital Linder. All rights Reserved , 2023</t>
+          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان נועה גוהר פורטנוי נועה גוהר פורטנוי Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section noago@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>"רויטל לינדר"</t>
+          <t>"נועה גוהר פורטנוי" יילוד</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -8832,14 +8864,14 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-09-04T07:14:47.643108+00:00</t>
+          <t>2026-09-08T14:13:12.580343+00:00</t>
         </is>
       </c>
       <c r="W52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
         <v>2</v>
@@ -8852,16 +8884,16 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>ddgs:auto</t>
+          <t>ddgs:bing</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>["https://www.rambam.org.il/?catid=%7B9F8D1CC1-1F5C-46F1-A395-E19ED48FE2EE%7D&amp;itemid=%7B4B21BA59-AF68-46CA-9483-9639E61A75A8%7D", "https://www.rambam.org.il/about-rambam/", "https://www.rambam.org.il/about-rambam/careers/", "https://www.rambam.org.il/departmentsandclinics/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/urology/", "https://www.rambam.org.il/departmentsandclinics/surgicaldivision/orthopedic/", "https://www.drlinder.co.il/"]</t>
+          <t>["https://www.doctorita.co.il/experts/126297", "https://www.bgu.ac.il/ar/people/noago/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.757388172841951e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -8872,7 +8904,7 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>https://www.drlinder.co.il/</t>
+          <t>https://www.bgu.ac.il/ar/people/noago/</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr"/>
@@ -8913,7 +8945,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>רליקה הרשקוביץ</t>
+          <t>עדי יהודה ווינטראוב</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8944,7 +8976,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>ralikah@bgu.ac.il</t>
+          <t>adiyehud@bgu.ac.il</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8957,7 +8989,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -8967,12 +8999,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> الصفحة الرئيسية جامعة أنشي سيجل في جوريان רליקה הרשקוביץ פרופ' רליקה הרשקוביץ Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section ralikah@bgu.ac.il رابط ملف الأبحاث Cookies Settings</t>
+          <t>رئيسية جامعة أنشي سيجل في جوريان עדי יהודה ווינטראוב פרופ' עדי יהודה ווינטראוב Departments חבר/ת סגל קליני הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section adiyehud@bgu.ac.il رابط ملف الأبحاث https://orcid.org/ 0000-0002-4239-8665 Orcid Number Cookies Settings</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>"רליקה הרשקוביץ"</t>
+          <t>"עדי יהודה ווינטראוב"</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -8989,41 +9021,41 @@
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-09-04T07:56:40.372731+00:00</t>
+          <t>2026-09-04T19:20:10.182518+00:00</t>
         </is>
       </c>
       <c r="W53" t="n">
         <v>2</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:auto</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>["https://www.bgu.ac.il/people/ralikah/", "https://www.doctorita.co.il/experts/101245", "https://www.bgu.ac.il/ar/people/ralikah/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
+          <t>["https://www.bgu.ac.il/people/adiyehud/", "https://www.bgu.ac.il/researcher/adi-weintraub/", "https://www.beok.co.il/doctors/Doctors-136810/", "https://cris.bgu.ac.il/en/publications/%D7%94%D7%A1%D7%99%D7%9B%D7%95%D7%9F-%D7%9C%D7%A1%D7%99%D7%91%D7%95%D7%9B%D7%99-%D7%94%D7%99%D7%A8%D7%99%D7%95%D7%9F-%D7%91%D7%A0%D7%A9%D7%99%D7%9D-%D7%A2%D7%9D-%D7%90%D7%A0%D7%93%D7%95%D7%9E%D7%98%D7%A8%D7%99%D7%95%D7%96%D7%99%D7%A1/", "https://www.bgu.ac.il/ar/people/adiyehud/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>3.252050431434981e+19</v>
+        <v>9.757263106418254e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -9034,7 +9066,7 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/ar/people/ralikah/</t>
+          <t>https://www.bgu.ac.il/ar/people/adiyehud/</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr"/>
@@ -9075,7 +9107,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>שקמה בר און</t>
+          <t>עמרי זמשטין</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9106,7 +9138,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>shikmabo@tlvmc.gov.il</t>
+          <t>omrizam@post.bgu.ac.il</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -9119,7 +9151,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9129,12 +9161,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>ת לאנדוסקופיה גינקולוגית שטחי התעניינות ועיסוק מיוחדים היסטרוסקופיה עם וללא הרדמה, היסטרוסקופיה ניתוחית ללא הרדמה בשיטת "see and treat" לפרוסקופיות פרק 14 | פרופ' יריב יוגב וד״ר שקמה בר און | מרכז בריאות האישה יצירת קשר shikmabo@tlvmc.gov.il יחידות רפואיות רפואת  נשים - גינקולוגיה רופאים בכירים בליס-יולדות ונשים יצירת קשר יחידות רפואיות איכילוב אודות אודות המרכז הרפואי הנהלת בית החולים חזון המרכז הרפואי ת"א ציוני דרך בהתפתחות ביה"ח איכו</t>
+          <t>ريد البحث عنه؟ الصفحة الرئيسية جامعة أنشي سيجل في جوريان עמרי זמשטין עמרי זמשטין Departments אקדמי לא פעיל הפקולטה למדעי הבריאות, החטיבה למיילדות וגניקולוגיה- במרכז הרפואי אוניברסיטאי סורוקה Staff member contact section omrizam@post.bgu.ac.il Cookies Settings</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>"שקמה בר און"</t>
+          <t>"עמרי זמשטין"</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -9151,28 +9183,28 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-09-04T10:28:27.702590+00:00</t>
+          <t>2026-09-04T19:35:09.971397+00:00</t>
         </is>
       </c>
       <c r="W54" t="n">
         <v>2</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -9181,11 +9213,11 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>["https://www.medico.co.il/doctors/%D7%93%D7%A8-%D7%A9%D7%A7%D7%9E%D7%94-%D7%91%D7%A8-%D7%90%D7%95%D7%9F/", "https://tlvmedical.com/doctors/דר-שקמה-בר-און/", "https://www.rofim.org.il/minisite/%D7%93%D7%A8_%D7%A9%D7%A7%D7%9E%D7%94_%D7%91%D7%A8_%D7%90%D7%95%D7%9F", "https://www.shidurit-ltd.co.il/", "https://www.rofim.org.il/about", "https://www.rofim.org.il/Contact", "https://www.rofim.org.il/specialityPage/%D7%9E%D7%A8%D7%9B%D7%96_%D7%A8%D7%A4%D7%95%D7%90%D7%99", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%9E%D7%92%D7%90%D7%A8", "https://www.rofim.org.il/minisite/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA_%D7%91%D7%99%D7%AA_%D7%92%D7%93%D7%99", "https://www.rofim.org.il/minisite/%D7%90%D7%99%D7%99_%D7%90%D7%9C_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A7", "https://docsrated.com/doctors/שקמה-בר-און", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FTLVMDC%2Fphotos%2F%25D7%25A2%25D7%2595%25D7%25A7%25D7%2591%25D7%2595%25D7%25AA-%25D7%2595%25D7%259E%25D7%2598%25D7%2595%25D7%25A4%25D7%259C%25D7%2595%25D7%25AA-%25D7%2590%25D7%25A0%25D7%2595-%25D7%25A9%25D7%259E%25D7%2597%25D7%2599%25D7%259D-%25D7%259C%25D7%2594%25D7%259B%25D7%2599%25D7%25A8-%25D7%259C%25D7%259B%25D7%259F-%25D7%2590%25D7%25AA-%25D7%2593%25D7%25A8-%25D7%25A9%25D7%25A7%25D7%259E%25D7%2594-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F%25D7%2593%25D7%25A8-%25D7%2591%25D7%25A8-%25D7%2590%25D7%2595%25D7%259F-%25D7%2594%25D7%2599%25D7%2590-%25D7%259E%25D7%25A0%25D7%2594%25D7%259C%25D7%25AA-%25D7%2594%25D7%259E%25D7%25A8%25D7%259B%25D7%2596-%25D7%259C%2F1525276317871201%2F", "https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/", "https://www.ncbi.nlm.nih.gov/pubmed/?term=shikma+bar+on", "https://www.tasmc.org.il/odotl/about/", "https://www.tasmc.org.il/segel-unit/sgan-dikan/", "https://www.tasmc.org.il/unit-index-page/", "https://www.tasmc.org.il/unit-index-page/surgery/", "https://www.tasmc.org.il/unit-index-page/surgery/stw/", "https://www.tasmc.org.il/unit-index-page/internalmed/"]</t>
+          <t>["https://www.bgu.ac.il/ar/people/omrizam/", "https://www.bgu.ac.il/ar/general/about/", "https://www.bgu.ac.il/ar/general/what-should-you-know-about-ben-gurion-university/", "https://www.bgu.ac.il:443/ar/general/about/", "https://www.bgu.ac.il:443/ar/general/what-should-you-know-about-ben-gurion-university/"]</t>
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.245379558755114e+19</v>
+        <v>9.757263106418254e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -9196,7 +9228,7 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/doctorssearch/dr/bar-on-shikma/</t>
+          <t>https://www.bgu.ac.il/ar/people/omrizam/</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr"/>
@@ -9237,7 +9269,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>שרית הלמן</t>
+          <t>רויטל לינדר</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9268,7 +9300,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>hsarit@szmc.org.il</t>
+          <t>revital@drl